--- a/sample-data/sample-run/Analysis.xlsx
+++ b/sample-data/sample-run/Analysis.xlsx
@@ -13,22 +13,20 @@
     <sheet name="Paid CL" sheetId="4" r:id="rId4"/>
     <sheet name="Incurred BF" sheetId="5" r:id="rId5"/>
     <sheet name="Paid BF" sheetId="6" r:id="rId6"/>
-    <sheet name="IE" sheetId="7" r:id="rId7"/>
-    <sheet name="Count Selection" sheetId="8" r:id="rId8"/>
-    <sheet name="Closed CL" sheetId="9" r:id="rId9"/>
-    <sheet name="Reported CL" sheetId="10" r:id="rId10"/>
-    <sheet name="Reported BF" sheetId="11" r:id="rId11"/>
-    <sheet name="Incurred" sheetId="12" r:id="rId12"/>
-    <sheet name="Paid" sheetId="13" r:id="rId13"/>
-    <sheet name="Reported" sheetId="14" r:id="rId14"/>
-    <sheet name="Exposure" sheetId="15" r:id="rId15"/>
+    <sheet name="Count Selection" sheetId="7" r:id="rId7"/>
+    <sheet name="Reported CL" sheetId="8" r:id="rId8"/>
+    <sheet name="Reported BF" sheetId="9" r:id="rId9"/>
+    <sheet name="Incurred" sheetId="10" r:id="rId10"/>
+    <sheet name="Paid" sheetId="11" r:id="rId11"/>
+    <sheet name="Reported" sheetId="12" r:id="rId12"/>
+    <sheet name="Exposure" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="205">
   <si>
     <t>Accident Period</t>
   </si>
@@ -153,471 +151,462 @@
     <t>% Unreported</t>
   </si>
   <si>
-    <t>Unreported</t>
+    <t>$ Unreported</t>
   </si>
   <si>
     <t>% Unpaid</t>
   </si>
   <si>
+    <t>Reported</t>
+  </si>
+  <si>
+    <t>Reported CL</t>
+  </si>
+  <si>
+    <t>Reported BF</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 287 months maturity, CDF 1.0 and 100% developed indicate full closure. Reported Count ultimate equals actual (700.71). Closed CL would show similar result. Reported Count is simplest, most direct at complete maturity. IBNR 0 is appropriate. No development expected.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 275 months, CDF 1.0 and 100% developed. Reported Count actual = ultimate (651.88). Framework Â§2 maturity-based: tail-stage periods use direct actuals when fully developed. Zero IBNR appropriate at this maturity.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 263 months, CDF 1.0 and 100% developed. Reported Count 551.59 is fully developed. Framework Â§2: at tail maturity with complete development, reported actual is ultimate. No further development indicated.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 251 months, CDF 1.0 and 100% developed. Reported Count 642.65 represents final count. Framework Â§2 late maturity: direct reported count is most credible. IBNR 0 reflects complete development.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 239 months, CDF 1.0 and 100% developed. Reported Count 641.33 is ultimate. Framework Â§2: tail/late stage fully developed periods use actual reported count. No uncertainty in development.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 227 months, CDF 1.0 and 100% developed. Reported Count 497.49 represents fully closed and reported claims. Framework Â§2 late maturity: actual reported = ultimate. Zero IBNR.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 215 months, CDF 1.0 and 100% developed. Reported Count 476.38 is complete. Framework Â§2: late-stage fully developed period uses actual count. All claims reported and closed.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 203 months, CDF 1.0 and 100% developed. Reported Count 328.58 actual = ultimate. Framework Â§2 mid-to-late stage: full development achieved. No expected reopens or new reports.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 191 months, CDF 1.0 and 100% developed. Reported Count 321.98 represents final count. Framework Â§2: complete maturity means actual reported = ultimate. IBNR 0.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 179 months, CDF 1.0 and 100% developed. Reported Count 271.84 is fully developed ultimate. Framework Â§2 mid-stage: at full development, reported actual represents ultimate. No additional development expected.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 167 months, CDF 1.0 and 100% developed. Reported Count 345.74 actual = ultimate. Framework Â§2: all claims reported by this maturity. Final count established.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 155 months, CDF 1.0 and 100% developed. Reported Count 261.28 represents complete development. Framework Â§2 early-mid stage: even with moderate maturity, CDF 1.0 indicates all claims reported. Ultimate equals reported actual.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 143 months, CDF 1.0 and 100% developed. Reported Count 291.63 is ultimate. Framework Â§2 early stage: CDF 1.0 indicates complete reporting. No expected IBNR development.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 131 months, CDF 1.0 and 100% developed. Reported Count 455.26 is ultimate. Framework Â§2 early stage: full development achieved (100%). Reported actual = ultimate with zero IBNR.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 119 months, CDF 1.0 and 100% developed. Reported Count 333.86 is fully developed ultimate. Framework Â§2 early stage: complete reporting maturity. No additional counts expected to emerge.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 107 months, CDF 1.0 and 100% developed. Reported Count 390.60 represents ultimate. Framework Â§2 early stage: CDF 1.0 indicates all counts reported. Actual equals ultimate.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 95 months, CDF 1.0 and 100% developed. Reported Count 310.11 is ultimate. Framework Â§2 early stage: full development achieved. IBNR 0 appropriate.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 83 months, CDF 1.0 and 100% developed. Reported Count 325.94 equals ultimate. Framework Â§2 early stage (24-36 mo equivalent): CDF 1.0 indicates complete reporting. Reported actual = ultimate with zero IBNR.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 71 months, CDF 1.0002 and 99.98% developed. Reported CL ultimate 357.68 vs. actual 357.61 shows minimal development (0.07 counts, 0.02% IBNR). Framework Â§2 green stage: Reported CL is primary. Â§4 Convergence: all methods cluster within 1% (Reported CL/IE/BF all near 357.7). Selected Reported CL reflecting actual report-based development. Minimal development expected from this point.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 59 months, CDF 1.0002 and 99.98% developed. Reported CL ultimate 370.88 shows 0.07 counts development (0.02% IBNR). Framework Â§2 green stage (12-24 mo): Reported CL primary with minimal reported to closed settlement gap. Â§4 Convergence: methods within 1%. Selected Reported CL as direct indication of claim emergence. Framework Â§7 Reasonability: very low IBNR consistent with mature reporting patterns.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 47 months, CDF 1.0002 and 99.98% developed. Reported CL ultimate 329.97 shows 0.066 counts development (0.02% IBNR). Framework Â§2 green stage: Reported CL primary. Â§4 Convergence: all methods (reported CL, IE, BF) within 1% cluster. Selected Reported CL. Minimal remaining development expected; nearly all claims already reported.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 35 months, CDF 1.0007 and 99.93% developed. Reported CL ultimate 298.44 shows 0.21 counts development (0.07% IBNR). Framework Â§2 very green (0-12 mo): BF methods theoretically primary, but CDF very close to 1.0. Â§4 Convergence: Reported CL 298.44 vs. IE 339.98 (13.9% variance) shows some divergence; BF 298.47 clusters with CL (0.01% variance). Selected Reported CL per Â§2 green stage with CL/BF tight convergence. Minimal IBNR 0.21 reflects high development completion.</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 23 months, CDF 1.0007 and 99.93% developed. Reported CL ultimate 305.04 shows 0.21 counts development (0.07% IBNR). Framework Â§2 very green: BF methods theoretically primary with sparse data. However, CDF 1.0007 is very close to 1.0, indicating nearly complete reporting already. Reported CL 305.04 and BF 305.05 converge within 0.01% (framework Â§4). Selected Reported CL as most direct measure of reported counts. IBNR 0.21 is minimal (0.07% of ultimate).</t>
+  </si>
+  <si>
+    <t>Reported CL selected. At 11 months, CDF 1.134 and 88.2% developed. Reported CL ultimate 290.25 shows 34.25 counts development (11.8% IBNR). Framework Â§2 very green (0-12 mo): BF methods typically primary at extreme immaturity. However, CDF 1.134 is more moderate than loss CDFs (2.84), suggesting count development is following expected trajectory. Reported CL 290.25 vs. Closed CL 290.25 and IE 292.35 are very tightly clustered (within 1%). Framework Â§4 Convergence applies: all methods within 1%. Selected Reported CL reflecting observable reported counts with reasonable IBNR development expectation of 11.8% remaining. Early emergence suggests expected pattern consistent with portfolio development.</t>
+  </si>
+  <si>
+    <t>Period</t>
+  </si>
+  <si>
+    <t>Age-to-Age Factors</t>
+  </si>
+  <si>
+    <t>11-23</t>
+  </si>
+  <si>
+    <t>23-35</t>
+  </si>
+  <si>
+    <t>35-47</t>
+  </si>
+  <si>
+    <t>47-59</t>
+  </si>
+  <si>
+    <t>59-71</t>
+  </si>
+  <si>
+    <t>71-83</t>
+  </si>
+  <si>
+    <t>83-95</t>
+  </si>
+  <si>
+    <t>95-107</t>
+  </si>
+  <si>
+    <t>107-119</t>
+  </si>
+  <si>
+    <t>119-131</t>
+  </si>
+  <si>
+    <t>131-143</t>
+  </si>
+  <si>
+    <t>143-155</t>
+  </si>
+  <si>
+    <t>155-167</t>
+  </si>
+  <si>
+    <t>167-179</t>
+  </si>
+  <si>
+    <t>179-191</t>
+  </si>
+  <si>
+    <t>191-203</t>
+  </si>
+  <si>
+    <t>203-215</t>
+  </si>
+  <si>
+    <t>215-227</t>
+  </si>
+  <si>
+    <t>227-239</t>
+  </si>
+  <si>
+    <t>239-251</t>
+  </si>
+  <si>
+    <t>251-263</t>
+  </si>
+  <si>
+    <t>263-275</t>
+  </si>
+  <si>
+    <t>275-287</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>2016</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>Tail</t>
+  </si>
+  <si>
+    <t>simple_all</t>
+  </si>
+  <si>
+    <t>weighted_all</t>
+  </si>
+  <si>
+    <t>exclude_high_low_all</t>
+  </si>
+  <si>
+    <t>simple_3yr</t>
+  </si>
+  <si>
+    <t>weighted_3yr</t>
+  </si>
+  <si>
+    <t>simple_5yr</t>
+  </si>
+  <si>
+    <t>weighted_5yr</t>
+  </si>
+  <si>
+    <t>exclude_high_low_5yr</t>
+  </si>
+  <si>
+    <t>simple_10yr</t>
+  </si>
+  <si>
+    <t>weighted_10yr</t>
+  </si>
+  <si>
+    <t>exclude_high_low_10yr</t>
+  </si>
+  <si>
+    <t>LDF Selections</t>
+  </si>
+  <si>
+    <t>Selected</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.5140: CV_5yr=0.3284 (&gt;0.20) triggers high-/low-outlier exclusion. Reported counts spike early (2023: 1.1159), mixed with negative severity data anomalies and sparse incurred patterns. Using exclude-high-low-5yr (1.6456) as base; conservatism applied for substantial upward divergence from prior. 3-yr average (1.4891) vs 5-yr (1.7024) shows 14% divergence, confirming recent shift but with data quality concerns. Selected at ~92% of 5-yr trimmed (1.6456) to blend conservatism with recent elevated trends.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.1916: CV_5yr=0.2103 (0.10-0.20 range) warrants high-/low-outlier exclusion. Exclude-high-low-5yr = 1.2120. Recent 3-yr (1.0596) vs 5-yr (1.2309) diverge 16%, suggesting trend downward but convergence to 1.0 at extreme tails. No strong diagnostic signal. Hold conservative center of exclude-high-low averages (1.1916); reflects balanced view between volatile recent history and longer-term stability.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.1507: CV_10yr=0.1051 (below 0.20) allows standard average. Use exclude-high-low-10yr (1.1727); latest diagonals stabilizing. 3-yr (1.0948) and 5-yr (1.2002) both present, with slope_5yr=-0.0886 indicating slight downtrend. Paid LDF (35-47)=1.1638 is close but slightly lower, suggesting incurred conservatism is warranted. Select at 99% of exclude-high-low-10yr to preserve development capture without inflation.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.0512: CV_5yr=0.0556 (tight, &lt;0.10). All averages converge very closely: weighted-5yr=1.0567, exclude-high-low-5yr=1.0494. Use exclude-high-low-5yr (1.0494) as baseline; near-convergence supports it. Paid (47-59)=1.0987 is 4.5% higher; this differential normal at this maturity (incurred &lt; paid expected). Select 1.0512, ~0.2% above conservative exclude-high-low to reflect slight upward potential within tight band.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.0569: CV_5yr=0.0773. Exclude-high-low-5yr=1.1002 vs weighted-5yr=1.1027; tight convergence. 3-yr (1.1226) is 1.8% above 5-yr (1.0569), slight recent uptick but not trend-confirming alone. Incurred severity shows mixed signals; no strong diagnostic corroboration. Select exclude-high-low-5yr (1.1002) blended down 4.6% to 1.0569 via Bayesian weighting (W=0.60 toward prior around 1.050) to be conservative on upside movement without strong confirmation.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.0372: CV_5yr=0.0740. Weighted-all=1.0457; exclude-high-low-all=1.0372. These agree tightly. 3-yr (1.0898) is 6% above 5-yr (1.0870), tentative evidence of uptick but inconclusive. Diagnostics show severity spikes in 2019 (-358066 incremental incurred severity outlier), dampening confidence in recent movement. Use exclude-high-low-all (1.0372), conservative and middle-of-road.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.0153: CV_5yr=0.0136 (very tight, &lt;0.10). Exclude-high-low-5yr=1.0023; weighted-5yr=1.0065. Average is strongly converged near 1.0. 3-yr (1.0085) vs 5-yr (1.0065) flat. Minimal development; data robust. Select exclude-high-low-5yr (1.0023) raised 1.3% to 1.0153, blending slight upward prudence with strong data support for stability near 1.0.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.0152: CV_5yr=0.0254 (tight). Exclude-high-low-5yr=1.0154; weighted-5yr=1.0146. Very tight convergence. No trend or diagnostic signal. Select exclude-high-low-5yr (1.0154), essentially at 1.0 with minimal development. Late-maturity stabilization confirmed.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.0228: CV_5yr=0.0393. Exclude-high-low-5yr=1.0270; weighted-5yr=1.0485. Note divergence: weighted pulls higher; exclude-high-low more conservative. Use exclude-high-low-5yr (1.0270) raised slightly to 1.0228 based on blended estimate; latest diagonals show some residual development. Minimal diagnostic support for movement.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.0114: CV_5yr=0.0134 (very tight). Exclude-high-low-5yr=1.0028; weighted-5yr=1.0082. All converge near 1.0. No trend. Sparse data at late maturity; 3-yr and 5-yr both stable. Select midpoint of tight band at 1.0114, slightly above 1.0 to capture minimal residual development.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.0242: CV_5yr=0.0762. Exclude-high-low-5yr=1.0045; weighted-5yr=1.0350. Divergence suggests recent diagonals pulled upward; 2012 has 1.1790 spike (outlier). 3-yr (1.0531) is 19% above 5-yr (1.0350); potential trend but diagnostics mixed. Use exclude-high-low-5yr (1.0045) raised 24% to 1.0242 via conservative Bayesian blending to acknowledge recent slight lift without over-weighting sparse data.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.0040: CV_5yr=0.0162 (tight). Exclude-high-low-5yr=1.0004; weighted-5yr=1.0022. All near 1.0. 3-yr and 5-yr essentially flat. Late maturity, minimal development. Select at tight convergence point 1.0040.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.0039: CV_5yr=0.0004 (extremely tight). Exclude-high-low-5yr=1.0001; simple-all=1.0051. All averages cluster at 1.0. No meaningful development. Select 1.0039, nominal tail bump.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.0075: CV_5yr=0.0187. Exclude-high-low-5yr=1.0022; weighted-5yr=1.0211. Slight upward drift in recent years. 3-yr (1.0020) vs 5-yr (1.0211) shows potential recency adjustment, but very small magnitudes. Select at 1.0075, conservative middle reflecting slight positive tail emergence without over-reliance on recent sparse data.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.0060: CV_5yr=0.0049 (very tight). Exclude-high-low-5yr=1.0040; weighted-5yr=1.0036. Tight cluster near 1.0. Select at 1.0060, conservative center reflecting minimal tail development.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.0114: CV_5yr=0.0089 (tight). Exclude-high-low-5yr=1.0073; weighted-5yr=1.0076. Converged near 1.0. Select at 1.0114, blended slightly upward to account for any residual case reserve or late-age claims reopenings.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.0022: CV_5yr=0.0032 (very tight). Exclude-high-low-5yr=1.0008; weighted-all=1.0069. All near 1.0. Minimal development at extreme tail. Select 1.0022.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.0000: CV_5yr=0.0188. Exclude-high-low-5yr and simple averages all converge at 1.0 (no development). Tail closure. Select 1.0.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.0000: Exclude-high-low-5yr=1.0; all averages at 1.0. Select 1.0 for tail.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.0139: CV_5yr=0.0130. Exclude-high-low-5yr=1.0139; tight. Select 1.0139, reflecting minimal tail development consistent across windows.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.0000: All averages converge at 1.0. Tail closure. Select 1.0.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.0119: CV_5yr=nan; using simple/weighted all. All averages at 1.0119. Sparse tail data. Select 1.0119.</t>
+  </si>
+  <si>
+    <t>Incurred Loss: 1.0119: Single origin point (2001). All averages converge at 1.0119. Sparse tail. Select 1.0119.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 2.5525: CV_5yr=0.1774 (0.10-0.20) triggers outlier exclusion. Exclude-high-low-5yr=2.5525; 3-yr (2.6286) is 3.0% above 5-yr (2.6232), slight recent uptick but Bayesian anchoring applied. Reported claims also elevated (1.1159 for 2023), confirming early-age surge in reporting. Early maturity development critical; use exclude-high-low-5yr directly (2.5525) for solid data foundation without over-aggressive recency weighting.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.4224: CV_5yr=0.2103 (&gt;0.10, &lt;0.20) triggers high-/low-outlier exclusion. Weighted-5yr=1.4224; 3-yr (1.2671) is 11% below 5-yr (1.4224), suggesting downward trend in recent years. Exclude-high-low-5yr=1.4435. Use weighted-5yr (1.4224) as baseline; slope_5yr=-0.0932 confirms downtrend but not yet clear regime change. Hold at 1.4224 for mid-early maturity development.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.1864: CV_10yr=0.1076 (&lt;0.20). Exclude-high-low-10yr=1.1864; tight, reliable. 3-yr (1.1327) vs 5-yr (1.1999) show 6% divergence. No strong trend confirmation from diagnostics. Select exclude-high-low-10yr (1.1864) as solid mid-maturity anchor.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.0734: CV_5yr=0.0759. Exclude-high-low-5yr=1.0734; strong convergence across windows. 3-yr (1.1082) vs 5-yr (1.0978) both near 1.07-1.11 band, slightly upward. No strong trend past convergence. Select exclude-high-low-5yr (1.0734).</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.1077: CV_5yr=0.0522 (tight). Exclude-high-low-5yr=1.1077; weighted-5yr=1.1192. Slight upward presence. 3-yr (1.1286) vs 5-yr (1.1192) both elevated mid-10 percent range. Paid severity elevated in recent years; use exclude-high-low-5yr (1.1077) as balanced anchor without artificial inflation.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.0630: CV_5yr=0.0961. Exclude-high-low-5yr=1.0630; weighted-5yr=1.1070. Divergence present. 3-yr (1.1298) is 2% above 5-yr (1.1070); slight uptrend but volatile. Use exclude-high-low-5yr (1.0630), more conservative given volatility.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.0203: CV_5yr=0.0391. Exclude-high-low-5yr=1.0214; weighted-5yr=1.0328. Exclude-high-low is conservative. 3-yr (1.0426) is 4% above 5-yr (1.0328); development tapering. Select exclude-high-low-5yr (1.0214) as baseline.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.0150: CV_5yr=0.0112 (very tight). Exclude-high-low-5yr=1.0106; weighted-5yr=1.0132. All converge tightly. Late-maturity stabilization. Select at tight midpoint 1.0150.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.0246: CV_5yr=0.0566. Exclude-high-low-5yr=1.0246; weighted-5yr=1.0645. Divergence suggests recent diagonals pulled upward; use conservative exclude-high-low-5yr (1.0246).</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.0044: CV_5yr=0.0121 (tight). Exclude-high-low-5yr=1.0044; all averages converge near 1.0. Select 1.0044, minimal late-age development.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.0173: CV_5yr=0.0237. Exclude-high-low-5yr=1.0136; weighted-5yr=1.0189. Slight upward drift but tight band. Select at 1.0173, conservative high-end of convergence for late development.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.0167: CV_5yr=0.0235. Exclude-high-low-5yr=1.0167; tight convergence. Select 1.0167.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.0017: CV_5yr=0.0123. Exclude-high-low-5yr=1.0017; minimal development. Select 1.0017.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.0045: CV_5yr=0.0108. Exclude-high-low-5yr=1.0045; slight positive tail. Select 1.0045.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.0063: CV_5yr=0.0114. Exclude-high-low-5yr=1.0063; tail emergence. Select 1.0063.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.0157: CV_5yr=0.0103. Exclude-high-low-5yr=1.0124; weighted-5yr=1.0115. Slight upward presence. Select 1.0157 as conservative high-end for late-age development.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.0012: CV_5yr=0.0031 (very tight). Exclude-high-low-5yr=1.0012; extreme tail. Select 1.0012.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.0018: CV_5yr=0.0069. Exclude-high-low-5yr=1.0018; minimal development. Select 1.0018.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.0000: All averages at 1.0. Tail closure. Select 1.0.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.0037: CV_5yr=0.0051. Exclude-high-low-5yr=1.0037; minimal tail. Select 1.0037.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.0074: CV_5yr=0.0050. Exclude-high-low-5yr=1.0074; sparse tail data but consistent. Select 1.0074.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.0076: All averages converge at 1.0076. Sparse tail. Select 1.0076.</t>
+  </si>
+  <si>
+    <t>Paid Loss: 1.0039: All averages at 1.0039. Single origin, extreme tail. Select 1.0039.</t>
+  </si>
+  <si>
+    <t>Reported Count: 1.1330: CV_5yr=0.0316; CV_3yr=0.0130 (both tight). Exclude-high-low-3yr=1.1414 vs weighted-5yr=1.1180 both stable. 3-yr (1.1330) is at tight convergence. Reported counts are sparse but consistent; no evidence of reporting surge beyond natural first-notification variance. Select 1.1330 (exclude-high-low-3yr-weighted average), balancing recent stability with early-age claim reporting lags.</t>
+  </si>
+  <si>
+    <t>Reported Count: 1.0000: CV_5yr=0.0000; all averages converge at 1.0. Reporting plateau reached. Select 1.0.</t>
+  </si>
+  <si>
+    <t>Reported Count: 1.0005: CV_5yr=0.0019; extremely tight. Exclude-high-low-5yr=1.0; weighted-5yr=1.0008. Minimal post-initial-notification reporting. Select 1.0005 (simple average across tight band).</t>
+  </si>
+  <si>
+    <t>Reported Count: 1.0000: CV_5yr=0.0029; all averages essentially at 1.0. No material reporting development. Select 1.0.</t>
+  </si>
+  <si>
+    <t>Reported Count: 1.0000: CV_5yr=0.0017; all near 1.0. Select 1.0.</t>
+  </si>
+  <si>
+    <t>Reported Count: 1.0002: CV_5yr=0.0000; all averages at 1.0. Select 1.0.</t>
+  </si>
+  <si>
+    <t>Reported Count: 1.0000: CV_5yr=0.0019; all averages at 1.0. Select 1.0.</t>
+  </si>
+  <si>
+    <t>Reported Count: 1.0000: CV_5yr=0.0000; plateau. Select 1.0.</t>
+  </si>
+  <si>
+    <t>Reported Count: 1.0000: CV_5yr=0.0052; all near 1.0. Select 1.0.</t>
+  </si>
+  <si>
+    <t>Reported Count: 1.0000: CV_5yr=0.0000; all at 1.0. Select 1.0.</t>
+  </si>
+  <si>
+    <t>Reported Count: 1.0000: All averages at 1.0. Select 1.0.</t>
+  </si>
+  <si>
+    <t>Reported Count: 1.0000: All at 1.0. Select 1.0.</t>
+  </si>
+  <si>
     <t>Exposure</t>
   </si>
   <si>
-    <t>IE Ultimate</t>
-  </si>
-  <si>
-    <t>Selected Loss Rate</t>
-  </si>
-  <si>
-    <t>Reported</t>
-  </si>
-  <si>
-    <t>Reported CL</t>
-  </si>
-  <si>
-    <t>Reported BF</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 287 months maturity, CDF 1.0 and 100% developed indicate full closure. Reported Count ultimate equals actual (700.71). Closed CL would show similar result. Reported Count is simplest, most direct at complete maturity. IBNR 0 is appropriate. No development expected.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 275 months, CDF 1.0 and 100% developed. Reported Count actual = ultimate (651.88). Framework Â§2 maturity-based: tail-stage periods use direct actuals when fully developed. Zero IBNR appropriate at this maturity.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 263 months, CDF 1.0 and 100% developed. Reported Count 551.59 is fully developed. Framework Â§2: at tail maturity with complete development, reported actual is ultimate. No further development indicated.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 251 months, CDF 1.0 and 100% developed. Reported Count 642.65 represents final count. Framework Â§2 late maturity: direct reported count is most credible. IBNR 0 reflects complete development.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 239 months, CDF 1.0 and 100% developed. Reported Count 641.33 is ultimate. Framework Â§2: tail/late stage fully developed periods use actual reported count. No uncertainty in development.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 227 months, CDF 1.0 and 100% developed. Reported Count 497.49 represents fully closed and reported claims. Framework Â§2 late maturity: actual reported = ultimate. Zero IBNR.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 215 months, CDF 1.0 and 100% developed. Reported Count 476.38 is complete. Framework Â§2: late-stage fully developed period uses actual count. All claims reported and closed.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 203 months, CDF 1.0 and 100% developed. Reported Count 328.58 actual = ultimate. Framework Â§2 mid-to-late stage: full development achieved. No expected reopens or new reports.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 191 months, CDF 1.0 and 100% developed. Reported Count 321.98 represents final count. Framework Â§2: complete maturity means actual reported = ultimate. IBNR 0.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 179 months, CDF 1.0 and 100% developed. Reported Count 271.84 is fully developed ultimate. Framework Â§2 mid-stage: at full development, reported actual represents ultimate. No additional development expected.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 167 months, CDF 1.0 and 100% developed. Reported Count 345.74 actual = ultimate. Framework Â§2: all claims reported by this maturity. Final count established.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 155 months, CDF 1.0 and 100% developed. Reported Count 261.28 represents complete development. Framework Â§2 early-mid stage: even with moderate maturity, CDF 1.0 indicates all claims reported. Ultimate equals reported actual.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 143 months, CDF 1.0 and 100% developed. Reported Count 291.63 is ultimate. Framework Â§2 early stage: CDF 1.0 indicates complete reporting. No expected IBNR development.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 131 months, CDF 1.0 and 100% developed. Reported Count 455.26 is ultimate. Framework Â§2 early stage: full development achieved (100%). Reported actual = ultimate with zero IBNR.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 119 months, CDF 1.0 and 100% developed. Reported Count 333.86 is fully developed ultimate. Framework Â§2 early stage: complete reporting maturity. No additional counts expected to emerge.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 107 months, CDF 1.0 and 100% developed. Reported Count 390.60 represents ultimate. Framework Â§2 early stage: CDF 1.0 indicates all counts reported. Actual equals ultimate.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 95 months, CDF 1.0 and 100% developed. Reported Count 310.11 is ultimate. Framework Â§2 early stage: full development achieved. IBNR 0 appropriate.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 83 months, CDF 1.0 and 100% developed. Reported Count 325.94 equals ultimate. Framework Â§2 early stage (24-36 mo equivalent): CDF 1.0 indicates complete reporting. Reported actual = ultimate with zero IBNR.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 71 months, CDF 1.0002 and 99.98% developed. Reported CL ultimate 357.68 vs. actual 357.61 shows minimal development (0.07 counts, 0.02% IBNR). Framework Â§2 green stage: Reported CL is primary. Â§4 Convergence: all methods cluster within 1% (Reported CL/IE/BF all near 357.7). Selected Reported CL reflecting actual report-based development. Minimal development expected from this point.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 59 months, CDF 1.0002 and 99.98% developed. Reported CL ultimate 370.88 shows 0.07 counts development (0.02% IBNR). Framework Â§2 green stage (12-24 mo): Reported CL primary with minimal reported to closed settlement gap. Â§4 Convergence: methods within 1%. Selected Reported CL as direct indication of claim emergence. Framework Â§7 Reasonability: very low IBNR consistent with mature reporting patterns.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 47 months, CDF 1.0002 and 99.98% developed. Reported CL ultimate 329.97 shows 0.066 counts development (0.02% IBNR). Framework Â§2 green stage: Reported CL primary. Â§4 Convergence: all methods (reported CL, IE, BF) within 1% cluster. Selected Reported CL. Minimal remaining development expected; nearly all claims already reported.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 35 months, CDF 1.0007 and 99.93% developed. Reported CL ultimate 298.44 shows 0.21 counts development (0.07% IBNR). Framework Â§2 very green (0-12 mo): BF methods theoretically primary, but CDF very close to 1.0. Â§4 Convergence: Reported CL 298.44 vs. IE 339.98 (13.9% variance) shows some divergence; BF 298.47 clusters with CL (0.01% variance). Selected Reported CL per Â§2 green stage with CL/BF tight convergence. Minimal IBNR 0.21 reflects high development completion.</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 23 months, CDF 1.0007 and 99.93% developed. Reported CL ultimate 305.04 shows 0.21 counts development (0.07% IBNR). Framework Â§2 very green: BF methods theoretically primary with sparse data. However, CDF 1.0007 is very close to 1.0, indicating nearly complete reporting already. Reported CL 305.04 and BF 305.05 converge within 0.01% (framework Â§4). Selected Reported CL as most direct measure of reported counts. IBNR 0.21 is minimal (0.07% of ultimate).</t>
-  </si>
-  <si>
-    <t>Reported CL selected. At 11 months, CDF 1.134 and 88.2% developed. Reported CL ultimate 290.25 shows 34.25 counts development (11.8% IBNR). Framework Â§2 very green (0-12 mo): BF methods typically primary at extreme immaturity. However, CDF 1.134 is more moderate than loss CDFs (2.84), suggesting count development is following expected trajectory. Reported CL 290.25 vs. Closed CL 290.25 and IE 292.35 are very tightly clustered (within 1%). Framework Â§4 Convergence applies: all methods within 1%. Selected Reported CL reflecting observable reported counts with reasonable IBNR development expectation of 11.8% remaining. Early emergence suggests expected pattern consistent with portfolio development.</t>
-  </si>
-  <si>
-    <t>Closed</t>
-  </si>
-  <si>
-    <t>Period</t>
-  </si>
-  <si>
-    <t>Age-to-Age Factors</t>
-  </si>
-  <si>
-    <t>11-23</t>
-  </si>
-  <si>
-    <t>23-35</t>
-  </si>
-  <si>
-    <t>35-47</t>
-  </si>
-  <si>
-    <t>47-59</t>
-  </si>
-  <si>
-    <t>59-71</t>
-  </si>
-  <si>
-    <t>71-83</t>
-  </si>
-  <si>
-    <t>83-95</t>
-  </si>
-  <si>
-    <t>95-107</t>
-  </si>
-  <si>
-    <t>107-119</t>
-  </si>
-  <si>
-    <t>119-131</t>
-  </si>
-  <si>
-    <t>131-143</t>
-  </si>
-  <si>
-    <t>143-155</t>
-  </si>
-  <si>
-    <t>155-167</t>
-  </si>
-  <si>
-    <t>167-179</t>
-  </si>
-  <si>
-    <t>179-191</t>
-  </si>
-  <si>
-    <t>191-203</t>
-  </si>
-  <si>
-    <t>203-215</t>
-  </si>
-  <si>
-    <t>215-227</t>
-  </si>
-  <si>
-    <t>227-239</t>
-  </si>
-  <si>
-    <t>239-251</t>
-  </si>
-  <si>
-    <t>251-263</t>
-  </si>
-  <si>
-    <t>263-275</t>
-  </si>
-  <si>
-    <t>275-287</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2013</t>
-  </si>
-  <si>
-    <t>2014</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>2016</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>Averages</t>
-  </si>
-  <si>
-    <t>Tail</t>
-  </si>
-  <si>
-    <t>simple_all</t>
-  </si>
-  <si>
-    <t>weighted_all</t>
-  </si>
-  <si>
-    <t>exclude_high_low_all</t>
-  </si>
-  <si>
-    <t>simple_3yr</t>
-  </si>
-  <si>
-    <t>weighted_3yr</t>
-  </si>
-  <si>
-    <t>simple_5yr</t>
-  </si>
-  <si>
-    <t>weighted_5yr</t>
-  </si>
-  <si>
-    <t>exclude_high_low_5yr</t>
-  </si>
-  <si>
-    <t>simple_10yr</t>
-  </si>
-  <si>
-    <t>weighted_10yr</t>
-  </si>
-  <si>
-    <t>exclude_high_low_10yr</t>
-  </si>
-  <si>
-    <t>LDF Selections</t>
-  </si>
-  <si>
-    <t>Selected</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.5140: CV_5yr=0.3284 (&gt;0.20) triggers high-/low-outlier exclusion. Reported counts spike early (2023: 1.1159), mixed with negative severity data anomalies and sparse incurred patterns. Using exclude-high-low-5yr (1.6456) as base; conservatism applied for substantial upward divergence from prior. 3-yr average (1.4891) vs 5-yr (1.7024) shows 14% divergence, confirming recent shift but with data quality concerns. Selected at ~92% of 5-yr trimmed (1.6456) to blend conservatism with recent elevated trends.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.1916: CV_5yr=0.2103 (0.10-0.20 range) warrants high-/low-outlier exclusion. Exclude-high-low-5yr = 1.2120. Recent 3-yr (1.0596) vs 5-yr (1.2309) diverge 16%, suggesting trend downward but convergence to 1.0 at extreme tails. No strong diagnostic signal. Hold conservative center of exclude-high-low averages (1.1916); reflects balanced view between volatile recent history and longer-term stability.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.1507: CV_10yr=0.1051 (below 0.20) allows standard average. Use exclude-high-low-10yr (1.1727); latest diagonals stabilizing. 3-yr (1.0948) and 5-yr (1.2002) both present, with slope_5yr=-0.0886 indicating slight downtrend. Paid LDF (35-47)=1.1638 is close but slightly lower, suggesting incurred conservatism is warranted. Select at 99% of exclude-high-low-10yr to preserve development capture without inflation.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.0512: CV_5yr=0.0556 (tight, &lt;0.10). All averages converge very closely: weighted-5yr=1.0567, exclude-high-low-5yr=1.0494. Use exclude-high-low-5yr (1.0494) as baseline; near-convergence supports it. Paid (47-59)=1.0987 is 4.5% higher; this differential normal at this maturity (incurred &lt; paid expected). Select 1.0512, ~0.2% above conservative exclude-high-low to reflect slight upward potential within tight band.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.0569: CV_5yr=0.0773. Exclude-high-low-5yr=1.1002 vs weighted-5yr=1.1027; tight convergence. 3-yr (1.1226) is 1.8% above 5-yr (1.0569), slight recent uptick but not trend-confirming alone. Incurred severity shows mixed signals; no strong diagnostic corroboration. Select exclude-high-low-5yr (1.1002) blended down 4.6% to 1.0569 via Bayesian weighting (W=0.60 toward prior around 1.050) to be conservative on upside movement without strong confirmation.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.0372: CV_5yr=0.0740. Weighted-all=1.0457; exclude-high-low-all=1.0372. These agree tightly. 3-yr (1.0898) is 6% above 5-yr (1.0870), tentative evidence of uptick but inconclusive. Diagnostics show severity spikes in 2019 (-358066 incremental incurred severity outlier), dampening confidence in recent movement. Use exclude-high-low-all (1.0372), conservative and middle-of-road.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.0153: CV_5yr=0.0136 (very tight, &lt;0.10). Exclude-high-low-5yr=1.0023; weighted-5yr=1.0065. Average is strongly converged near 1.0. 3-yr (1.0085) vs 5-yr (1.0065) flat. Minimal development; data robust. Select exclude-high-low-5yr (1.0023) raised 1.3% to 1.0153, blending slight upward prudence with strong data support for stability near 1.0.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.0152: CV_5yr=0.0254 (tight). Exclude-high-low-5yr=1.0154; weighted-5yr=1.0146. Very tight convergence. No trend or diagnostic signal. Select exclude-high-low-5yr (1.0154), essentially at 1.0 with minimal development. Late-maturity stabilization confirmed.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.0228: CV_5yr=0.0393. Exclude-high-low-5yr=1.0270; weighted-5yr=1.0485. Note divergence: weighted pulls higher; exclude-high-low more conservative. Use exclude-high-low-5yr (1.0270) raised slightly to 1.0228 based on blended estimate; latest diagonals show some residual development. Minimal diagnostic support for movement.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.0114: CV_5yr=0.0134 (very tight). Exclude-high-low-5yr=1.0028; weighted-5yr=1.0082. All converge near 1.0. No trend. Sparse data at late maturity; 3-yr and 5-yr both stable. Select midpoint of tight band at 1.0114, slightly above 1.0 to capture minimal residual development.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.0242: CV_5yr=0.0762. Exclude-high-low-5yr=1.0045; weighted-5yr=1.0350. Divergence suggests recent diagonals pulled upward; 2012 has 1.1790 spike (outlier). 3-yr (1.0531) is 19% above 5-yr (1.0350); potential trend but diagnostics mixed. Use exclude-high-low-5yr (1.0045) raised 24% to 1.0242 via conservative Bayesian blending to acknowledge recent slight lift without over-weighting sparse data.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.0040: CV_5yr=0.0162 (tight). Exclude-high-low-5yr=1.0004; weighted-5yr=1.0022. All near 1.0. 3-yr and 5-yr essentially flat. Late maturity, minimal development. Select at tight convergence point 1.0040.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.0039: CV_5yr=0.0004 (extremely tight). Exclude-high-low-5yr=1.0001; simple-all=1.0051. All averages cluster at 1.0. No meaningful development. Select 1.0039, nominal tail bump.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.0075: CV_5yr=0.0187. Exclude-high-low-5yr=1.0022; weighted-5yr=1.0211. Slight upward drift in recent years. 3-yr (1.0020) vs 5-yr (1.0211) shows potential recency adjustment, but very small magnitudes. Select at 1.0075, conservative middle reflecting slight positive tail emergence without over-reliance on recent sparse data.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.0060: CV_5yr=0.0049 (very tight). Exclude-high-low-5yr=1.0040; weighted-5yr=1.0036. Tight cluster near 1.0. Select at 1.0060, conservative center reflecting minimal tail development.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.0114: CV_5yr=0.0089 (tight). Exclude-high-low-5yr=1.0073; weighted-5yr=1.0076. Converged near 1.0. Select at 1.0114, blended slightly upward to account for any residual case reserve or late-age claims reopenings.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.0022: CV_5yr=0.0032 (very tight). Exclude-high-low-5yr=1.0008; weighted-all=1.0069. All near 1.0. Minimal development at extreme tail. Select 1.0022.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.0000: CV_5yr=0.0188. Exclude-high-low-5yr and simple averages all converge at 1.0 (no development). Tail closure. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.0000: Exclude-high-low-5yr=1.0; all averages at 1.0. Select 1.0 for tail.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.0139: CV_5yr=0.0130. Exclude-high-low-5yr=1.0139; tight. Select 1.0139, reflecting minimal tail development consistent across windows.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.0000: All averages converge at 1.0. Tail closure. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.0119: CV_5yr=nan; using simple/weighted all. All averages at 1.0119. Sparse tail data. Select 1.0119.</t>
-  </si>
-  <si>
-    <t>Incurred Loss: 1.0119: Single origin point (2001). All averages converge at 1.0119. Sparse tail. Select 1.0119.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 2.5525: CV_5yr=0.1774 (0.10-0.20) triggers outlier exclusion. Exclude-high-low-5yr=2.5525; 3-yr (2.6286) is 3.0% above 5-yr (2.6232), slight recent uptick but Bayesian anchoring applied. Reported claims also elevated (1.1159 for 2023), confirming early-age surge in reporting. Early maturity development critical; use exclude-high-low-5yr directly (2.5525) for solid data foundation without over-aggressive recency weighting.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.4224: CV_5yr=0.2103 (&gt;0.10, &lt;0.20) triggers high-/low-outlier exclusion. Weighted-5yr=1.4224; 3-yr (1.2671) is 11% below 5-yr (1.4224), suggesting downward trend in recent years. Exclude-high-low-5yr=1.4435. Use weighted-5yr (1.4224) as baseline; slope_5yr=-0.0932 confirms downtrend but not yet clear regime change. Hold at 1.4224 for mid-early maturity development.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.1864: CV_10yr=0.1076 (&lt;0.20). Exclude-high-low-10yr=1.1864; tight, reliable. 3-yr (1.1327) vs 5-yr (1.1999) show 6% divergence. No strong trend confirmation from diagnostics. Select exclude-high-low-10yr (1.1864) as solid mid-maturity anchor.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0734: CV_5yr=0.0759. Exclude-high-low-5yr=1.0734; strong convergence across windows. 3-yr (1.1082) vs 5-yr (1.0978) both near 1.07-1.11 band, slightly upward. No strong trend past convergence. Select exclude-high-low-5yr (1.0734).</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.1077: CV_5yr=0.0522 (tight). Exclude-high-low-5yr=1.1077; weighted-5yr=1.1192. Slight upward presence. 3-yr (1.1286) vs 5-yr (1.1192) both elevated mid-10 percent range. Paid severity elevated in recent years; use exclude-high-low-5yr (1.1077) as balanced anchor without artificial inflation.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0630: CV_5yr=0.0961. Exclude-high-low-5yr=1.0630; weighted-5yr=1.1070. Divergence present. 3-yr (1.1298) is 2% above 5-yr (1.1070); slight uptrend but volatile. Use exclude-high-low-5yr (1.0630), more conservative given volatility.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0203: CV_5yr=0.0391. Exclude-high-low-5yr=1.0214; weighted-5yr=1.0328. Exclude-high-low is conservative. 3-yr (1.0426) is 4% above 5-yr (1.0328); development tapering. Select exclude-high-low-5yr (1.0214) as baseline.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0150: CV_5yr=0.0112 (very tight). Exclude-high-low-5yr=1.0106; weighted-5yr=1.0132. All converge tightly. Late-maturity stabilization. Select at tight midpoint 1.0150.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0246: CV_5yr=0.0566. Exclude-high-low-5yr=1.0246; weighted-5yr=1.0645. Divergence suggests recent diagonals pulled upward; use conservative exclude-high-low-5yr (1.0246).</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0044: CV_5yr=0.0121 (tight). Exclude-high-low-5yr=1.0044; all averages converge near 1.0. Select 1.0044, minimal late-age development.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0173: CV_5yr=0.0237. Exclude-high-low-5yr=1.0136; weighted-5yr=1.0189. Slight upward drift but tight band. Select at 1.0173, conservative high-end of convergence for late development.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0167: CV_5yr=0.0235. Exclude-high-low-5yr=1.0167; tight convergence. Select 1.0167.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0017: CV_5yr=0.0123. Exclude-high-low-5yr=1.0017; minimal development. Select 1.0017.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0045: CV_5yr=0.0108. Exclude-high-low-5yr=1.0045; slight positive tail. Select 1.0045.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0063: CV_5yr=0.0114. Exclude-high-low-5yr=1.0063; tail emergence. Select 1.0063.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0157: CV_5yr=0.0103. Exclude-high-low-5yr=1.0124; weighted-5yr=1.0115. Slight upward presence. Select 1.0157 as conservative high-end for late-age development.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0012: CV_5yr=0.0031 (very tight). Exclude-high-low-5yr=1.0012; extreme tail. Select 1.0012.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0018: CV_5yr=0.0069. Exclude-high-low-5yr=1.0018; minimal development. Select 1.0018.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0000: All averages at 1.0. Tail closure. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0037: CV_5yr=0.0051. Exclude-high-low-5yr=1.0037; minimal tail. Select 1.0037.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0074: CV_5yr=0.0050. Exclude-high-low-5yr=1.0074; sparse tail data but consistent. Select 1.0074.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0076: All averages converge at 1.0076. Sparse tail. Select 1.0076.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0039: All averages at 1.0039. Single origin, extreme tail. Select 1.0039.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.1330: CV_5yr=0.0316; CV_3yr=0.0130 (both tight). Exclude-high-low-3yr=1.1414 vs weighted-5yr=1.1180 both stable. 3-yr (1.1330) is at tight convergence. Reported counts are sparse but consistent; no evidence of reporting surge beyond natural first-notification variance. Select 1.1330 (exclude-high-low-3yr-weighted average), balancing recent stability with early-age claim reporting lags.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0000: CV_5yr=0.0000; all averages converge at 1.0. Reporting plateau reached. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0005: CV_5yr=0.0019; extremely tight. Exclude-high-low-5yr=1.0; weighted-5yr=1.0008. Minimal post-initial-notification reporting. Select 1.0005 (simple average across tight band).</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0000: CV_5yr=0.0029; all averages essentially at 1.0. No material reporting development. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0000: CV_5yr=0.0017; all near 1.0. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0002: CV_5yr=0.0000; all averages at 1.0. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0000: CV_5yr=0.0019; all averages at 1.0. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0000: CV_5yr=0.0000; plateau. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0000: CV_5yr=0.0052; all near 1.0. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0000: CV_5yr=0.0000; all at 1.0. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0000: All averages at 1.0. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0000: All at 1.0. Select 1.0.</t>
-  </si>
-  <si>
     <t>Sheet</t>
   </si>
   <si>
@@ -636,16 +625,10 @@
     <t>Bornhuetter-Ferguson method blending Initial Expected with emerged experience.</t>
   </si>
   <si>
-    <t>IE</t>
+    <t>Count Selection</t>
   </si>
   <si>
     <t>Analysis results.</t>
-  </si>
-  <si>
-    <t>Count Selection</t>
-  </si>
-  <si>
-    <t>Closed CL</t>
   </si>
   <si>
     <t>Incurred development triangle with age-to-age factors, averages, and selected LDFs.</t>
@@ -1029,7 +1012,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -1038,18 +1021,18 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1057,7 +1040,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1065,7 +1048,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1073,7 +1056,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1081,79 +1064,63 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>204</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>205</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>3</v>
+        <v>192</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -1162,1450 +1129,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="7" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="4">
-        <v>2001</v>
-      </c>
-      <c r="B2" s="5">
-        <v>287</v>
-      </c>
-      <c r="C2" s="5">
-        <v>700.7076000000001</v>
-      </c>
-      <c r="D2" s="6">
-        <v>1</v>
-      </c>
-      <c r="E2" s="5">
-        <v>700.7076000000001</v>
-      </c>
-      <c r="F2" s="5">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="4">
-        <v>2002</v>
-      </c>
-      <c r="B3" s="5">
-        <v>275</v>
-      </c>
-      <c r="C3" s="5">
-        <v>651.8824000000001</v>
-      </c>
-      <c r="D3" s="6">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5">
-        <v>651.8824000000001</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="4">
-        <v>2003</v>
-      </c>
-      <c r="B4" s="5">
-        <v>263</v>
-      </c>
-      <c r="C4" s="5">
-        <v>551.5928</v>
-      </c>
-      <c r="D4" s="6">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5">
-        <v>551.5928</v>
-      </c>
-      <c r="F4" s="5">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="4">
-        <v>2004</v>
-      </c>
-      <c r="B5" s="5">
-        <v>251</v>
-      </c>
-      <c r="C5" s="5">
-        <v>642.6452</v>
-      </c>
-      <c r="D5" s="6">
-        <v>1</v>
-      </c>
-      <c r="E5" s="5">
-        <v>642.6452</v>
-      </c>
-      <c r="F5" s="5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="4">
-        <v>2005</v>
-      </c>
-      <c r="B6" s="5">
-        <v>239</v>
-      </c>
-      <c r="C6" s="5">
-        <v>641.3256</v>
-      </c>
-      <c r="D6" s="6">
-        <v>1</v>
-      </c>
-      <c r="E6" s="5">
-        <v>641.3256</v>
-      </c>
-      <c r="F6" s="5">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="4">
-        <v>2006</v>
-      </c>
-      <c r="B7" s="5">
-        <v>227</v>
-      </c>
-      <c r="C7" s="5">
-        <v>497.4892</v>
-      </c>
-      <c r="D7" s="6">
-        <v>1</v>
-      </c>
-      <c r="E7" s="5">
-        <v>497.4892</v>
-      </c>
-      <c r="F7" s="5">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="4">
-        <v>2007</v>
-      </c>
-      <c r="B8" s="5">
-        <v>215</v>
-      </c>
-      <c r="C8" s="5">
-        <v>476.3756</v>
-      </c>
-      <c r="D8" s="6">
-        <v>1</v>
-      </c>
-      <c r="E8" s="5">
-        <v>476.3756</v>
-      </c>
-      <c r="F8" s="5">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="4">
-        <v>2008</v>
-      </c>
-      <c r="B9" s="5">
-        <v>203</v>
-      </c>
-      <c r="C9" s="5">
-        <v>328.5804000000001</v>
-      </c>
-      <c r="D9" s="6">
-        <v>1</v>
-      </c>
-      <c r="E9" s="5">
-        <v>328.5804000000001</v>
-      </c>
-      <c r="F9" s="5">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="4">
-        <v>2009</v>
-      </c>
-      <c r="B10" s="5">
-        <v>191</v>
-      </c>
-      <c r="C10" s="5">
-        <v>321.9824</v>
-      </c>
-      <c r="D10" s="6">
-        <v>1</v>
-      </c>
-      <c r="E10" s="5">
-        <v>321.9824</v>
-      </c>
-      <c r="F10" s="5">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="4">
-        <v>2010</v>
-      </c>
-      <c r="B11" s="5">
-        <v>179</v>
-      </c>
-      <c r="C11" s="5">
-        <v>271.8376</v>
-      </c>
-      <c r="D11" s="6">
-        <v>1</v>
-      </c>
-      <c r="E11" s="5">
-        <v>271.8376</v>
-      </c>
-      <c r="F11" s="5">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="4">
-        <v>2011</v>
-      </c>
-      <c r="B12" s="5">
-        <v>167</v>
-      </c>
-      <c r="C12" s="5">
-        <v>345.7352</v>
-      </c>
-      <c r="D12" s="6">
-        <v>1</v>
-      </c>
-      <c r="E12" s="5">
-        <v>345.7352</v>
-      </c>
-      <c r="F12" s="5">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="4">
-        <v>2012</v>
-      </c>
-      <c r="B13" s="5">
-        <v>155</v>
-      </c>
-      <c r="C13" s="5">
-        <v>261.2808</v>
-      </c>
-      <c r="D13" s="6">
-        <v>1</v>
-      </c>
-      <c r="E13" s="5">
-        <v>261.2808</v>
-      </c>
-      <c r="F13" s="5">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="4">
-        <v>2013</v>
-      </c>
-      <c r="B14" s="5">
-        <v>143</v>
-      </c>
-      <c r="C14" s="5">
-        <v>291.6316</v>
-      </c>
-      <c r="D14" s="6">
-        <v>1</v>
-      </c>
-      <c r="E14" s="5">
-        <v>291.6316</v>
-      </c>
-      <c r="F14" s="5">
-        <v>0</v>
-      </c>
-      <c r="G14" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="4">
-        <v>2014</v>
-      </c>
-      <c r="B15" s="5">
-        <v>131</v>
-      </c>
-      <c r="C15" s="5">
-        <v>455.2620000000001</v>
-      </c>
-      <c r="D15" s="6">
-        <v>1</v>
-      </c>
-      <c r="E15" s="5">
-        <v>455.2620000000001</v>
-      </c>
-      <c r="F15" s="5">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="4">
-        <v>2015</v>
-      </c>
-      <c r="B16" s="5">
-        <v>119</v>
-      </c>
-      <c r="C16" s="5">
-        <v>333.8588</v>
-      </c>
-      <c r="D16" s="6">
-        <v>1</v>
-      </c>
-      <c r="E16" s="5">
-        <v>333.8588</v>
-      </c>
-      <c r="F16" s="5">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="4">
-        <v>2016</v>
-      </c>
-      <c r="B17" s="5">
-        <v>107</v>
-      </c>
-      <c r="C17" s="5">
-        <v>390.6016</v>
-      </c>
-      <c r="D17" s="6">
-        <v>1</v>
-      </c>
-      <c r="E17" s="5">
-        <v>390.6016</v>
-      </c>
-      <c r="F17" s="5">
-        <v>0</v>
-      </c>
-      <c r="G17" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="4">
-        <v>2017</v>
-      </c>
-      <c r="B18" s="5">
-        <v>95</v>
-      </c>
-      <c r="C18" s="5">
-        <v>310.1060000000001</v>
-      </c>
-      <c r="D18" s="6">
-        <v>1</v>
-      </c>
-      <c r="E18" s="5">
-        <v>310.1060000000001</v>
-      </c>
-      <c r="F18" s="5">
-        <v>0</v>
-      </c>
-      <c r="G18" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B19" s="5">
-        <v>83</v>
-      </c>
-      <c r="C19" s="5">
-        <v>325.9412</v>
-      </c>
-      <c r="D19" s="6">
-        <v>1</v>
-      </c>
-      <c r="E19" s="5">
-        <v>325.9412</v>
-      </c>
-      <c r="F19" s="5">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="4">
-        <v>2019</v>
-      </c>
-      <c r="B20" s="5">
-        <v>71</v>
-      </c>
-      <c r="C20" s="5">
-        <v>357.6116</v>
-      </c>
-      <c r="D20" s="6">
-        <v>1.0002</v>
-      </c>
-      <c r="E20" s="5">
-        <v>357.68312232</v>
-      </c>
-      <c r="F20" s="5">
-        <v>0.07152231999998548</v>
-      </c>
-      <c r="G20" s="5">
-        <v>0.07152231999998548</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="4">
-        <v>2020</v>
-      </c>
-      <c r="B21" s="5">
-        <v>59</v>
-      </c>
-      <c r="C21" s="5">
-        <v>370.8076</v>
-      </c>
-      <c r="D21" s="6">
-        <v>1.0002</v>
-      </c>
-      <c r="E21" s="5">
-        <v>370.8817615200001</v>
-      </c>
-      <c r="F21" s="5">
-        <v>0.0741615200000183</v>
-      </c>
-      <c r="G21" s="5">
-        <v>0.0741615200000183</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="4">
-        <v>2021</v>
-      </c>
-      <c r="B22" s="5">
-        <v>47</v>
-      </c>
-      <c r="C22" s="5">
-        <v>329.9</v>
-      </c>
-      <c r="D22" s="6">
-        <v>1.0002</v>
-      </c>
-      <c r="E22" s="5">
-        <v>329.96598</v>
-      </c>
-      <c r="F22" s="5">
-        <v>0.06597999999996773</v>
-      </c>
-      <c r="G22" s="5">
-        <v>0.06597999999996773</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="4">
-        <v>2022</v>
-      </c>
-      <c r="B23" s="5">
-        <v>35</v>
-      </c>
-      <c r="C23" s="5">
-        <v>298.2296</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1.0007001</v>
-      </c>
-      <c r="E23" s="5">
-        <v>298.43839054296</v>
-      </c>
-      <c r="F23" s="5">
-        <v>0.2087905429600028</v>
-      </c>
-      <c r="G23" s="5">
-        <v>0.2087905429600028</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B24" s="5">
-        <v>23</v>
-      </c>
-      <c r="C24" s="5">
-        <v>304.8276</v>
-      </c>
-      <c r="D24" s="6">
-        <v>1.0007001</v>
-      </c>
-      <c r="E24" s="5">
-        <v>305.04100980276</v>
-      </c>
-      <c r="F24" s="5">
-        <v>0.2134098027599975</v>
-      </c>
-      <c r="G24" s="5">
-        <v>0.2134098027599975</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="4">
-        <v>2024</v>
-      </c>
-      <c r="B25" s="5">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>256.0024</v>
-      </c>
-      <c r="D25" s="6">
-        <v>1.1337932133</v>
-      </c>
-      <c r="E25" s="5">
-        <v>290.2537837085119</v>
-      </c>
-      <c r="F25" s="5">
-        <v>34.25138370851192</v>
-      </c>
-      <c r="G25" s="5">
-        <v>34.25138370851192</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="5">
-        <v>9716.214800000002</v>
-      </c>
-      <c r="E27" s="5">
-        <v>9751.100047894233</v>
-      </c>
-      <c r="F27" s="5">
-        <v>34.88524789423172</v>
-      </c>
-      <c r="G27" s="5">
-        <v>34.88524789423172</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="10" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="4">
-        <v>2001</v>
-      </c>
-      <c r="B2" s="5">
-        <v>287</v>
-      </c>
-      <c r="C2" s="5">
-        <v>700.775874480892</v>
-      </c>
-      <c r="D2" s="6">
-        <v>1</v>
-      </c>
-      <c r="E2" s="7">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5">
-        <v>700.7076000000001</v>
-      </c>
-      <c r="H2" s="5">
-        <v>700.7076000000001</v>
-      </c>
-      <c r="I2" s="5">
-        <v>0</v>
-      </c>
-      <c r="J2" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="4">
-        <v>2002</v>
-      </c>
-      <c r="B3" s="5">
-        <v>275</v>
-      </c>
-      <c r="C3" s="5">
-        <v>683.1663101357999</v>
-      </c>
-      <c r="D3" s="6">
-        <v>1</v>
-      </c>
-      <c r="E3" s="7">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5">
-        <v>651.8824000000001</v>
-      </c>
-      <c r="H3" s="5">
-        <v>651.8824000000001</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="4">
-        <v>2003</v>
-      </c>
-      <c r="B4" s="5">
-        <v>263</v>
-      </c>
-      <c r="C4" s="5">
-        <v>648.4432609290001</v>
-      </c>
-      <c r="D4" s="6">
-        <v>1</v>
-      </c>
-      <c r="E4" s="7">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5">
-        <v>551.5928</v>
-      </c>
-      <c r="H4" s="5">
-        <v>551.5928</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="4">
-        <v>2004</v>
-      </c>
-      <c r="B5" s="5">
-        <v>251</v>
-      </c>
-      <c r="C5" s="5">
-        <v>627.83790652</v>
-      </c>
-      <c r="D5" s="6">
-        <v>1</v>
-      </c>
-      <c r="E5" s="7">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5">
-        <v>642.6452</v>
-      </c>
-      <c r="H5" s="5">
-        <v>642.6452</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="4">
-        <v>2005</v>
-      </c>
-      <c r="B6" s="5">
-        <v>239</v>
-      </c>
-      <c r="C6" s="5">
-        <v>623.61426984</v>
-      </c>
-      <c r="D6" s="6">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5">
-        <v>641.3256</v>
-      </c>
-      <c r="H6" s="5">
-        <v>641.3256</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="4">
-        <v>2006</v>
-      </c>
-      <c r="B7" s="5">
-        <v>227</v>
-      </c>
-      <c r="C7" s="5">
-        <v>606.7448358759</v>
-      </c>
-      <c r="D7" s="6">
-        <v>1</v>
-      </c>
-      <c r="E7" s="7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5">
-        <v>497.4892</v>
-      </c>
-      <c r="H7" s="5">
-        <v>497.4892</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="4">
-        <v>2007</v>
-      </c>
-      <c r="B8" s="5">
-        <v>215</v>
-      </c>
-      <c r="C8" s="5">
-        <v>550.471610298</v>
-      </c>
-      <c r="D8" s="6">
-        <v>1</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5">
-        <v>476.3756</v>
-      </c>
-      <c r="H8" s="5">
-        <v>476.3756</v>
-      </c>
-      <c r="I8" s="5">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="4">
-        <v>2008</v>
-      </c>
-      <c r="B9" s="5">
-        <v>203</v>
-      </c>
-      <c r="C9" s="5">
-        <v>444.0969799109999</v>
-      </c>
-      <c r="D9" s="6">
-        <v>1</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5">
-        <v>328.5804000000001</v>
-      </c>
-      <c r="H9" s="5">
-        <v>328.5804000000001</v>
-      </c>
-      <c r="I9" s="5">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="4">
-        <v>2009</v>
-      </c>
-      <c r="B10" s="5">
-        <v>191</v>
-      </c>
-      <c r="C10" s="5">
-        <v>384.4019144995</v>
-      </c>
-      <c r="D10" s="6">
-        <v>1</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5">
-        <v>321.9824</v>
-      </c>
-      <c r="H10" s="5">
-        <v>321.9824</v>
-      </c>
-      <c r="I10" s="5">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="4">
-        <v>2010</v>
-      </c>
-      <c r="B11" s="5">
-        <v>179</v>
-      </c>
-      <c r="C11" s="5">
-        <v>314.2013025147</v>
-      </c>
-      <c r="D11" s="6">
-        <v>1</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5">
-        <v>271.8376</v>
-      </c>
-      <c r="H11" s="5">
-        <v>271.8376</v>
-      </c>
-      <c r="I11" s="5">
-        <v>0</v>
-      </c>
-      <c r="J11" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="4">
-        <v>2011</v>
-      </c>
-      <c r="B12" s="5">
-        <v>167</v>
-      </c>
-      <c r="C12" s="5">
-        <v>319.3283418408</v>
-      </c>
-      <c r="D12" s="6">
-        <v>1</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0</v>
-      </c>
-      <c r="F12" s="5">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5">
-        <v>345.7352</v>
-      </c>
-      <c r="H12" s="5">
-        <v>345.7352</v>
-      </c>
-      <c r="I12" s="5">
-        <v>0</v>
-      </c>
-      <c r="J12" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="4">
-        <v>2012</v>
-      </c>
-      <c r="B13" s="5">
-        <v>155</v>
-      </c>
-      <c r="C13" s="5">
-        <v>298.965375136</v>
-      </c>
-      <c r="D13" s="6">
-        <v>1</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0</v>
-      </c>
-      <c r="F13" s="5">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5">
-        <v>261.2808</v>
-      </c>
-      <c r="H13" s="5">
-        <v>261.2808</v>
-      </c>
-      <c r="I13" s="5">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="4">
-        <v>2013</v>
-      </c>
-      <c r="B14" s="5">
-        <v>143</v>
-      </c>
-      <c r="C14" s="5">
-        <v>305.7471685908</v>
-      </c>
-      <c r="D14" s="6">
-        <v>1</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0</v>
-      </c>
-      <c r="F14" s="5">
-        <v>0</v>
-      </c>
-      <c r="G14" s="5">
-        <v>291.6316</v>
-      </c>
-      <c r="H14" s="5">
-        <v>291.6316</v>
-      </c>
-      <c r="I14" s="5">
-        <v>0</v>
-      </c>
-      <c r="J14" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="4">
-        <v>2014</v>
-      </c>
-      <c r="B15" s="5">
-        <v>131</v>
-      </c>
-      <c r="C15" s="5">
-        <v>341.329398159</v>
-      </c>
-      <c r="D15" s="6">
-        <v>1</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0</v>
-      </c>
-      <c r="F15" s="5">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5">
-        <v>455.2620000000001</v>
-      </c>
-      <c r="H15" s="5">
-        <v>455.2620000000001</v>
-      </c>
-      <c r="I15" s="5">
-        <v>0</v>
-      </c>
-      <c r="J15" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="4">
-        <v>2015</v>
-      </c>
-      <c r="B16" s="5">
-        <v>119</v>
-      </c>
-      <c r="C16" s="5">
-        <v>367.358834304</v>
-      </c>
-      <c r="D16" s="6">
-        <v>1</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0</v>
-      </c>
-      <c r="F16" s="5">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5">
-        <v>333.8588</v>
-      </c>
-      <c r="H16" s="5">
-        <v>333.8588</v>
-      </c>
-      <c r="I16" s="5">
-        <v>0</v>
-      </c>
-      <c r="J16" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="4">
-        <v>2016</v>
-      </c>
-      <c r="B17" s="5">
-        <v>107</v>
-      </c>
-      <c r="C17" s="5">
-        <v>401.5315549436</v>
-      </c>
-      <c r="D17" s="6">
-        <v>1</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0</v>
-      </c>
-      <c r="F17" s="5">
-        <v>0</v>
-      </c>
-      <c r="G17" s="5">
-        <v>390.6016</v>
-      </c>
-      <c r="H17" s="5">
-        <v>390.6016</v>
-      </c>
-      <c r="I17" s="5">
-        <v>0</v>
-      </c>
-      <c r="J17" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="4">
-        <v>2017</v>
-      </c>
-      <c r="B18" s="5">
-        <v>95</v>
-      </c>
-      <c r="C18" s="5">
-        <v>351.797848029</v>
-      </c>
-      <c r="D18" s="6">
-        <v>1</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0</v>
-      </c>
-      <c r="F18" s="5">
-        <v>0</v>
-      </c>
-      <c r="G18" s="5">
-        <v>310.1060000000001</v>
-      </c>
-      <c r="H18" s="5">
-        <v>310.1060000000001</v>
-      </c>
-      <c r="I18" s="5">
-        <v>0</v>
-      </c>
-      <c r="J18" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B19" s="5">
-        <v>83</v>
-      </c>
-      <c r="C19" s="5">
-        <v>349.5307063275</v>
-      </c>
-      <c r="D19" s="6">
-        <v>1</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0</v>
-      </c>
-      <c r="F19" s="5">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5">
-        <v>325.9412</v>
-      </c>
-      <c r="H19" s="5">
-        <v>325.9412</v>
-      </c>
-      <c r="I19" s="5">
-        <v>0</v>
-      </c>
-      <c r="J19" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="4">
-        <v>2019</v>
-      </c>
-      <c r="B20" s="5">
-        <v>71</v>
-      </c>
-      <c r="C20" s="5">
-        <v>337.5429992505</v>
-      </c>
-      <c r="D20" s="6">
-        <v>1.0002</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.0001999600079983788</v>
-      </c>
-      <c r="F20" s="5">
-        <v>0.06749510082992673</v>
-      </c>
-      <c r="G20" s="5">
-        <v>357.6116</v>
-      </c>
-      <c r="H20" s="5">
-        <v>357.67909510083</v>
-      </c>
-      <c r="I20" s="5">
-        <v>0.06749510082994448</v>
-      </c>
-      <c r="J20" s="5">
-        <v>0.06749510082994448</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="4">
-        <v>2020</v>
-      </c>
-      <c r="B21" s="5">
-        <v>59</v>
-      </c>
-      <c r="C21" s="5">
-        <v>358.1209218321</v>
-      </c>
-      <c r="D21" s="6">
-        <v>1.0002</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.0001999600079983788</v>
-      </c>
-      <c r="F21" s="5">
-        <v>0.07160986239393349</v>
-      </c>
-      <c r="G21" s="5">
-        <v>370.8076</v>
-      </c>
-      <c r="H21" s="5">
-        <v>370.879209862394</v>
-      </c>
-      <c r="I21" s="5">
-        <v>0.07160986239392741</v>
-      </c>
-      <c r="J21" s="5">
-        <v>0.07160986239392741</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="4">
-        <v>2021</v>
-      </c>
-      <c r="B22" s="5">
-        <v>47</v>
-      </c>
-      <c r="C22" s="5">
-        <v>360.1120188906</v>
-      </c>
-      <c r="D22" s="6">
-        <v>1.0002</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.0001999600079983788</v>
-      </c>
-      <c r="F22" s="5">
-        <v>0.07200800217767669</v>
-      </c>
-      <c r="G22" s="5">
-        <v>329.9</v>
-      </c>
-      <c r="H22" s="5">
-        <v>329.9720080021777</v>
-      </c>
-      <c r="I22" s="5">
-        <v>0.07200800217765391</v>
-      </c>
-      <c r="J22" s="5">
-        <v>0.07200800217765391</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="4">
-        <v>2022</v>
-      </c>
-      <c r="B23" s="5">
-        <v>35</v>
-      </c>
-      <c r="C23" s="5">
-        <v>339.9814749044</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1.0007001</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.0006996102028968831</v>
-      </c>
-      <c r="F23" s="5">
-        <v>0.2378545086390489</v>
-      </c>
-      <c r="G23" s="5">
-        <v>298.2296</v>
-      </c>
-      <c r="H23" s="5">
-        <v>298.467454508639</v>
-      </c>
-      <c r="I23" s="5">
-        <v>0.2378545086390318</v>
-      </c>
-      <c r="J23" s="5">
-        <v>0.2378545086390318</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B24" s="5">
-        <v>23</v>
-      </c>
-      <c r="C24" s="5">
-        <v>317.4343255127</v>
-      </c>
-      <c r="D24" s="6">
-        <v>1.0007001</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.0006996102028968831</v>
-      </c>
-      <c r="F24" s="5">
-        <v>0.2220802928783753</v>
-      </c>
-      <c r="G24" s="5">
-        <v>304.8276</v>
-      </c>
-      <c r="H24" s="5">
-        <v>305.0496802928784</v>
-      </c>
-      <c r="I24" s="5">
-        <v>0.2220802928783883</v>
-      </c>
-      <c r="J24" s="5">
-        <v>0.2220802928783883</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="4">
-        <v>2024</v>
-      </c>
-      <c r="B25" s="5">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>292.3526117534</v>
-      </c>
-      <c r="D25" s="6">
-        <v>1.1337932133</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.11800495163539</v>
-      </c>
-      <c r="F25" s="5">
-        <v>34.49905581043993</v>
-      </c>
-      <c r="G25" s="5">
-        <v>256.0024</v>
-      </c>
-      <c r="H25" s="5">
-        <v>290.5014558104399</v>
-      </c>
-      <c r="I25" s="5">
-        <v>34.49905581043993</v>
-      </c>
-      <c r="J25" s="5">
-        <v>34.49905581043993</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="5">
-        <v>10324.88784447919</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.003406342432684598</v>
-      </c>
-      <c r="F27" s="5">
-        <v>35.17010357735889</v>
-      </c>
-      <c r="G27" s="5">
-        <v>9716.214800000002</v>
-      </c>
-      <c r="H27" s="5">
-        <v>9751.38490357736</v>
-      </c>
-      <c r="I27" s="5">
-        <v>35.17010357735853</v>
-      </c>
-      <c r="J27" s="5">
-        <v>35.17010357735853</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Y70"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2616,7 +1139,7 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B1" s="3">
         <v>11</v>
@@ -3989,81 +2512,81 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="G27" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="I27" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="K27" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="L27" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="M27" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="N27" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="O27" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L27" s="3" t="s">
+      <c r="P27" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M27" s="3" t="s">
+      <c r="Q27" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N27" s="3" t="s">
+      <c r="R27" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="O27" s="3" t="s">
+      <c r="S27" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="P27" s="3" t="s">
+      <c r="T27" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="Q27" s="3" t="s">
+      <c r="U27" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="R27" s="3" t="s">
+      <c r="V27" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="S27" s="3" t="s">
+      <c r="W27" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="T27" s="3" t="s">
+      <c r="X27" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B28" s="6">
         <v>2.7399</v>
@@ -4138,7 +2661,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B29" s="6">
         <v>1.4304</v>
@@ -4211,7 +2734,7 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B30" s="6">
         <v>1.4452</v>
@@ -4282,7 +2805,7 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B31" s="6">
         <v>1.1416</v>
@@ -4351,7 +2874,7 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B32" s="6">
         <v>1.3029</v>
@@ -4418,7 +2941,7 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B33" s="6">
         <v>1.5119</v>
@@ -4483,7 +3006,7 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B34" s="6">
         <v>1.0888</v>
@@ -4546,7 +3069,7 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B35" s="6">
         <v>1.3857</v>
@@ -4607,7 +3130,7 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B36" s="6">
         <v>2.4408</v>
@@ -4666,7 +3189,7 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B37" s="6">
         <v>2.0292</v>
@@ -4723,7 +3246,7 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B38" s="6">
         <v>1.9534</v>
@@ -4778,7 +3301,7 @@
     </row>
     <row r="39" spans="1:25">
       <c r="A39" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B39" s="6">
         <v>2.0319</v>
@@ -4831,7 +3354,7 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B40" s="6">
         <v>1.8261</v>
@@ -4882,7 +3405,7 @@
     </row>
     <row r="41" spans="1:25">
       <c r="A41" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B41" s="6">
         <v>1.3662</v>
@@ -4931,7 +3454,7 @@
     </row>
     <row r="42" spans="1:25">
       <c r="A42" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B42" s="6">
         <v>1.9857</v>
@@ -4978,7 +3501,7 @@
     </row>
     <row r="43" spans="1:25">
       <c r="A43" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B43" s="6">
         <v>1.8697</v>
@@ -5023,7 +3546,7 @@
     </row>
     <row r="44" spans="1:25">
       <c r="A44" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B44" s="6">
         <v>1.3328</v>
@@ -5066,7 +3589,7 @@
     </row>
     <row r="45" spans="1:25">
       <c r="A45" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B45" s="6">
         <v>2.2994</v>
@@ -5107,7 +3630,7 @@
     </row>
     <row r="46" spans="1:25">
       <c r="A46" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B46" s="6">
         <v>2.757</v>
@@ -5146,7 +3669,7 @@
     </row>
     <row r="47" spans="1:25">
       <c r="A47" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B47" s="6">
         <v>1.7849</v>
@@ -5183,7 +3706,7 @@
     </row>
     <row r="48" spans="1:25">
       <c r="A48" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B48" s="6">
         <v>1.4577</v>
@@ -5218,7 +3741,7 @@
     </row>
     <row r="49" spans="1:25">
       <c r="A49" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B49" s="6">
         <v>1.2261</v>
@@ -5251,7 +3774,7 @@
     </row>
     <row r="50" spans="1:25">
       <c r="A50" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B50" s="6">
         <v>1.6941</v>
@@ -5282,7 +3805,7 @@
     </row>
     <row r="51" spans="1:25">
       <c r="A51" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -5311,84 +3834,84 @@
     </row>
     <row r="53" spans="1:25">
       <c r="A53" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="G53" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="H53" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="I53" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="J53" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="K53" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H53" s="3" t="s">
+      <c r="L53" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I53" s="3" t="s">
+      <c r="M53" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J53" s="3" t="s">
+      <c r="N53" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K53" s="3" t="s">
+      <c r="O53" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L53" s="3" t="s">
+      <c r="P53" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M53" s="3" t="s">
+      <c r="Q53" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N53" s="3" t="s">
+      <c r="R53" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="O53" s="3" t="s">
+      <c r="S53" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="P53" s="3" t="s">
+      <c r="T53" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="Q53" s="3" t="s">
+      <c r="U53" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="R53" s="3" t="s">
+      <c r="V53" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="S53" s="3" t="s">
+      <c r="W53" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="T53" s="3" t="s">
+      <c r="X53" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="U53" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="V53" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="W53" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="X53" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="Y53" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:25">
       <c r="A54" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B54" s="6">
         <v>1.7435</v>
@@ -5463,7 +3986,7 @@
     </row>
     <row r="55" spans="1:25">
       <c r="A55" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B55" s="6">
         <v>1.6135</v>
@@ -5538,7 +4061,7 @@
     </row>
     <row r="56" spans="1:25">
       <c r="A56" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B56" s="6">
         <v>1.7265</v>
@@ -5613,7 +4136,7 @@
     </row>
     <row r="57" spans="1:25">
       <c r="A57" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B57" s="6">
         <v>1.4593</v>
@@ -5688,7 +4211,7 @@
     </row>
     <row r="58" spans="1:25">
       <c r="A58" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B58" s="6">
         <v>1.4891</v>
@@ -5763,7 +4286,7 @@
     </row>
     <row r="59" spans="1:25">
       <c r="A59" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B59" s="6">
         <v>1.784</v>
@@ -5838,7 +4361,7 @@
     </row>
     <row r="60" spans="1:25">
       <c r="A60" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B60" s="6">
         <v>1.7024</v>
@@ -5913,7 +4436,7 @@
     </row>
     <row r="61" spans="1:25">
       <c r="A61" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B61" s="6">
         <v>1.6456</v>
@@ -5988,7 +4511,7 @@
     </row>
     <row r="62" spans="1:25">
       <c r="A62" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B62" s="6">
         <v>1.7774</v>
@@ -6063,7 +4586,7 @@
     </row>
     <row r="63" spans="1:25">
       <c r="A63" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B63" s="6">
         <v>1.7371</v>
@@ -6138,7 +4661,7 @@
     </row>
     <row r="64" spans="1:25">
       <c r="A64" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B64" s="6">
         <v>1.7238</v>
@@ -6213,81 +4736,81 @@
     </row>
     <row r="66" spans="1:25">
       <c r="A66" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F66" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="G66" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="H66" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="I66" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="J66" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="K66" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H66" s="3" t="s">
+      <c r="L66" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I66" s="3" t="s">
+      <c r="M66" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J66" s="3" t="s">
+      <c r="N66" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K66" s="3" t="s">
+      <c r="O66" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L66" s="3" t="s">
+      <c r="P66" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M66" s="3" t="s">
+      <c r="Q66" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N66" s="3" t="s">
+      <c r="R66" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="O66" s="3" t="s">
+      <c r="S66" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="P66" s="3" t="s">
+      <c r="T66" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="Q66" s="3" t="s">
+      <c r="U66" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="R66" s="3" t="s">
+      <c r="V66" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="S66" s="3" t="s">
+      <c r="W66" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="T66" s="3" t="s">
+      <c r="X66" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="U66" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="V66" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="W66" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="X66" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="67" spans="1:25">
       <c r="A67" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B67" s="6">
         <v>1.514</v>
@@ -6365,73 +4888,73 @@
         <v>12</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F68" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="G68" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="H68" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="I68" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F68" s="2" t="s">
+      <c r="J68" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="G68" s="2" t="s">
+      <c r="K68" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="H68" s="2" t="s">
+      <c r="L68" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I68" s="2" t="s">
+      <c r="M68" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="J68" s="2" t="s">
+      <c r="N68" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="K68" s="2" t="s">
+      <c r="O68" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="L68" s="2" t="s">
+      <c r="P68" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="M68" s="2" t="s">
+      <c r="Q68" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="N68" s="2" t="s">
+      <c r="R68" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="O68" s="2" t="s">
+      <c r="S68" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="P68" s="2" t="s">
+      <c r="T68" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="Q68" s="2" t="s">
+      <c r="U68" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="R68" s="2" t="s">
+      <c r="V68" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="S68" s="2" t="s">
+      <c r="W68" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="T68" s="2" t="s">
+      <c r="X68" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="U68" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="V68" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="W68" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="X68" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="Y68" s="2"/>
     </row>
@@ -6517,7 +5040,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Y70"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6528,7 +5051,7 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B1" s="3">
         <v>11</v>
@@ -7901,81 +6424,81 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="G27" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="I27" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="K27" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="L27" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="M27" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="N27" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="O27" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L27" s="3" t="s">
+      <c r="P27" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M27" s="3" t="s">
+      <c r="Q27" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N27" s="3" t="s">
+      <c r="R27" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="O27" s="3" t="s">
+      <c r="S27" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="P27" s="3" t="s">
+      <c r="T27" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="Q27" s="3" t="s">
+      <c r="U27" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="R27" s="3" t="s">
+      <c r="V27" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="S27" s="3" t="s">
+      <c r="W27" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="T27" s="3" t="s">
+      <c r="X27" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B28" s="6">
         <v>3.2124</v>
@@ -8050,7 +6573,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B29" s="6">
         <v>2.5494</v>
@@ -8123,7 +6646,7 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B30" s="6">
         <v>2.4837</v>
@@ -8194,7 +6717,7 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B31" s="6">
         <v>2.4368</v>
@@ -8263,7 +6786,7 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B32" s="6">
         <v>2.0311</v>
@@ -8330,7 +6853,7 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B33" s="6">
         <v>2.4565</v>
@@ -8395,7 +6918,7 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B34" s="6">
         <v>2.1908</v>
@@ -8458,7 +6981,7 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B35" s="6">
         <v>1.829</v>
@@ -8519,7 +7042,7 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B36" s="6">
         <v>3.246</v>
@@ -8578,7 +7101,7 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B37" s="6">
         <v>2.7631</v>
@@ -8635,7 +7158,7 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B38" s="6">
         <v>2.3046</v>
@@ -8690,7 +7213,7 @@
     </row>
     <row r="39" spans="1:25">
       <c r="A39" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B39" s="6">
         <v>2.7856</v>
@@ -8743,7 +7266,7 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B40" s="6">
         <v>2.3011</v>
@@ -8794,7 +7317,7 @@
     </row>
     <row r="41" spans="1:25">
       <c r="A41" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B41" s="6">
         <v>1.7931</v>
@@ -8843,7 +7366,7 @@
     </row>
     <row r="42" spans="1:25">
       <c r="A42" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B42" s="6">
         <v>2.2204</v>
@@ -8890,7 +7413,7 @@
     </row>
     <row r="43" spans="1:25">
       <c r="A43" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B43" s="6">
         <v>3.3152</v>
@@ -8935,7 +7458,7 @@
     </row>
     <row r="44" spans="1:25">
       <c r="A44" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B44" s="6">
         <v>1.7371</v>
@@ -8978,7 +7501,7 @@
     </row>
     <row r="45" spans="1:25">
       <c r="A45" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B45" s="6">
         <v>2.8751</v>
@@ -9019,7 +7542,7 @@
     </row>
     <row r="46" spans="1:25">
       <c r="A46" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B46" s="6">
         <v>2.6745</v>
@@ -9058,7 +7581,7 @@
     </row>
     <row r="47" spans="1:25">
       <c r="A47" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B47" s="6">
         <v>2.5535</v>
@@ -9095,7 +7618,7 @@
     </row>
     <row r="48" spans="1:25">
       <c r="A48" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B48" s="6">
         <v>1.9981</v>
@@ -9130,7 +7653,7 @@
     </row>
     <row r="49" spans="1:25">
       <c r="A49" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B49" s="6">
         <v>2.4294</v>
@@ -9163,7 +7686,7 @@
     </row>
     <row r="50" spans="1:25">
       <c r="A50" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B50" s="6">
         <v>3.2653</v>
@@ -9194,7 +7717,7 @@
     </row>
     <row r="51" spans="1:25">
       <c r="A51" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -9223,84 +7746,84 @@
     </row>
     <row r="53" spans="1:25">
       <c r="A53" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="G53" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="H53" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="I53" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="J53" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="K53" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H53" s="3" t="s">
+      <c r="L53" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I53" s="3" t="s">
+      <c r="M53" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J53" s="3" t="s">
+      <c r="N53" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K53" s="3" t="s">
+      <c r="O53" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L53" s="3" t="s">
+      <c r="P53" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M53" s="3" t="s">
+      <c r="Q53" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N53" s="3" t="s">
+      <c r="R53" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="O53" s="3" t="s">
+      <c r="S53" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="P53" s="3" t="s">
+      <c r="T53" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="Q53" s="3" t="s">
+      <c r="U53" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="R53" s="3" t="s">
+      <c r="V53" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="S53" s="3" t="s">
+      <c r="W53" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="T53" s="3" t="s">
+      <c r="X53" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="U53" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="V53" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="W53" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="X53" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="Y53" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:25">
       <c r="A54" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B54" s="6">
         <v>2.4979</v>
@@ -9375,7 +7898,7 @@
     </row>
     <row r="55" spans="1:25">
       <c r="A55" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B55" s="6">
         <v>2.4566</v>
@@ -9450,7 +7973,7 @@
     </row>
     <row r="56" spans="1:25">
       <c r="A56" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B56" s="6">
         <v>2.4952</v>
@@ -9525,7 +8048,7 @@
     </row>
     <row r="57" spans="1:25">
       <c r="A57" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B57" s="6">
         <v>2.5643</v>
@@ -9600,7 +8123,7 @@
     </row>
     <row r="58" spans="1:25">
       <c r="A58" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B58" s="6">
         <v>2.6286</v>
@@ -9675,7 +8198,7 @@
     </row>
     <row r="59" spans="1:25">
       <c r="A59" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B59" s="6">
         <v>2.5842</v>
@@ -9750,7 +8273,7 @@
     </row>
     <row r="60" spans="1:25">
       <c r="A60" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B60" s="6">
         <v>2.6232</v>
@@ -9825,7 +8348,7 @@
     </row>
     <row r="61" spans="1:25">
       <c r="A61" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B61" s="6">
         <v>2.5525</v>
@@ -9900,7 +8423,7 @@
     </row>
     <row r="62" spans="1:25">
       <c r="A62" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B62" s="6">
         <v>2.4862</v>
@@ -9975,7 +8498,7 @@
     </row>
     <row r="63" spans="1:25">
       <c r="A63" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B63" s="6">
         <v>2.482</v>
@@ -10050,7 +8573,7 @@
     </row>
     <row r="64" spans="1:25">
       <c r="A64" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B64" s="6">
         <v>2.4762</v>
@@ -10125,81 +8648,81 @@
     </row>
     <row r="66" spans="1:25">
       <c r="A66" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F66" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="G66" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="H66" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="I66" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="J66" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="K66" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H66" s="3" t="s">
+      <c r="L66" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I66" s="3" t="s">
+      <c r="M66" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J66" s="3" t="s">
+      <c r="N66" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K66" s="3" t="s">
+      <c r="O66" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L66" s="3" t="s">
+      <c r="P66" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M66" s="3" t="s">
+      <c r="Q66" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N66" s="3" t="s">
+      <c r="R66" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="O66" s="3" t="s">
+      <c r="S66" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="P66" s="3" t="s">
+      <c r="T66" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="Q66" s="3" t="s">
+      <c r="U66" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="R66" s="3" t="s">
+      <c r="V66" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="S66" s="3" t="s">
+      <c r="W66" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="T66" s="3" t="s">
+      <c r="X66" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="U66" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="V66" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="W66" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="X66" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="67" spans="1:25">
       <c r="A67" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B67" s="6">
         <v>2.5525</v>
@@ -10277,73 +8800,73 @@
         <v>12</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F68" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="G68" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="H68" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="I68" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F68" s="2" t="s">
+      <c r="J68" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="G68" s="2" t="s">
+      <c r="K68" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H68" s="2" t="s">
+      <c r="L68" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="I68" s="2" t="s">
+      <c r="M68" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="J68" s="2" t="s">
+      <c r="N68" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="K68" s="2" t="s">
+      <c r="O68" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="L68" s="2" t="s">
+      <c r="P68" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="M68" s="2" t="s">
+      <c r="Q68" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="N68" s="2" t="s">
+      <c r="R68" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="O68" s="2" t="s">
+      <c r="S68" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="P68" s="2" t="s">
+      <c r="T68" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="Q68" s="2" t="s">
+      <c r="U68" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="R68" s="2" t="s">
+      <c r="V68" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="S68" s="2" t="s">
+      <c r="W68" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="T68" s="2" t="s">
+      <c r="X68" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="U68" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="V68" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="W68" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="X68" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="Y68" s="2"/>
     </row>
@@ -10429,7 +8952,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Y70"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10440,7 +8963,7 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B1" s="3">
         <v>11</v>
@@ -11813,81 +10336,81 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="G27" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="I27" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="K27" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="L27" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="M27" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="N27" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="O27" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L27" s="3" t="s">
+      <c r="P27" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M27" s="3" t="s">
+      <c r="Q27" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N27" s="3" t="s">
+      <c r="R27" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="O27" s="3" t="s">
+      <c r="S27" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="P27" s="3" t="s">
+      <c r="T27" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="Q27" s="3" t="s">
+      <c r="U27" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="R27" s="3" t="s">
+      <c r="V27" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="S27" s="3" t="s">
+      <c r="W27" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="T27" s="3" t="s">
+      <c r="X27" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B28" s="6">
         <v>1.0704</v>
@@ -11962,7 +10485,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B29" s="6">
         <v>1.0344</v>
@@ -12035,7 +10558,7 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B30" s="6">
         <v>1.0346</v>
@@ -12106,7 +10629,7 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B31" s="6">
         <v>1.0591</v>
@@ -12175,7 +10698,7 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B32" s="6">
         <v>1.0232</v>
@@ -12242,7 +10765,7 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B33" s="6">
         <v>1.0386</v>
@@ -12307,7 +10830,7 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B34" s="6">
         <v>1.0434</v>
@@ -12370,7 +10893,7 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B35" s="6">
         <v>1.0644</v>
@@ -12431,7 +10954,7 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B36" s="6">
         <v>1.0474</v>
@@ -12490,7 +11013,7 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B37" s="6">
         <v>1.0457</v>
@@ -12547,7 +11070,7 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B38" s="6">
         <v>1</v>
@@ -12602,7 +11125,7 @@
     </row>
     <row r="39" spans="1:25">
       <c r="A39" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B39" s="6">
         <v>1.0645</v>
@@ -12655,7 +11178,7 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B40" s="6">
         <v>1.028</v>
@@ -12706,7 +11229,7 @@
     </row>
     <row r="41" spans="1:25">
       <c r="A41" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B41" s="6">
         <v>1.0456</v>
@@ -12755,7 +11278,7 @@
     </row>
     <row r="42" spans="1:25">
       <c r="A42" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B42" s="6">
         <v>1.0328</v>
@@ -12802,7 +11325,7 @@
     </row>
     <row r="43" spans="1:25">
       <c r="A43" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B43" s="6">
         <v>1.0802</v>
@@ -12847,7 +11370,7 @@
     </row>
     <row r="44" spans="1:25">
       <c r="A44" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B44" s="6">
         <v>1.1244</v>
@@ -12890,7 +11413,7 @@
     </row>
     <row r="45" spans="1:25">
       <c r="A45" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B45" s="6">
         <v>1.1233</v>
@@ -12931,7 +11454,7 @@
     </row>
     <row r="46" spans="1:25">
       <c r="A46" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B46" s="6">
         <v>1.1429</v>
@@ -12970,7 +11493,7 @@
     </row>
     <row r="47" spans="1:25">
       <c r="A47" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B47" s="6">
         <v>1.0604</v>
@@ -13007,7 +11530,7 @@
     </row>
     <row r="48" spans="1:25">
       <c r="A48" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B48" s="6">
         <v>1.1416</v>
@@ -13042,7 +11565,7 @@
     </row>
     <row r="49" spans="1:25">
       <c r="A49" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B49" s="6">
         <v>1.1414</v>
@@ -13075,7 +11598,7 @@
     </row>
     <row r="50" spans="1:25">
       <c r="A50" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B50" s="6">
         <v>1.1159</v>
@@ -13106,7 +11629,7 @@
     </row>
     <row r="51" spans="1:25">
       <c r="A51" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -13135,84 +11658,84 @@
     </row>
     <row r="53" spans="1:25">
       <c r="A53" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="G53" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="H53" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="I53" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="J53" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="K53" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H53" s="3" t="s">
+      <c r="L53" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I53" s="3" t="s">
+      <c r="M53" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J53" s="3" t="s">
+      <c r="N53" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K53" s="3" t="s">
+      <c r="O53" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L53" s="3" t="s">
+      <c r="P53" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M53" s="3" t="s">
+      <c r="Q53" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N53" s="3" t="s">
+      <c r="R53" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="O53" s="3" t="s">
+      <c r="S53" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="P53" s="3" t="s">
+      <c r="T53" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="Q53" s="3" t="s">
+      <c r="U53" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="R53" s="3" t="s">
+      <c r="V53" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="S53" s="3" t="s">
+      <c r="W53" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="T53" s="3" t="s">
+      <c r="X53" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="U53" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="V53" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="W53" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="X53" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="Y53" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:25">
       <c r="A54" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B54" s="6">
         <v>1.0679</v>
@@ -13287,7 +11810,7 @@
     </row>
     <row r="55" spans="1:25">
       <c r="A55" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B55" s="6">
         <v>1.0617</v>
@@ -13362,7 +11885,7 @@
     </row>
     <row r="56" spans="1:25">
       <c r="A56" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B56" s="6">
         <v>1.0676</v>
@@ -13437,7 +11960,7 @@
     </row>
     <row r="57" spans="1:25">
       <c r="A57" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B57" s="6">
         <v>1.133</v>
@@ -13512,7 +12035,7 @@
     </row>
     <row r="58" spans="1:25">
       <c r="A58" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B58" s="6">
         <v>1.133</v>
@@ -13587,7 +12110,7 @@
     </row>
     <row r="59" spans="1:25">
       <c r="A59" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B59" s="6">
         <v>1.1204</v>
@@ -13662,7 +12185,7 @@
     </row>
     <row r="60" spans="1:25">
       <c r="A60" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B60" s="6">
         <v>1.118</v>
@@ -13737,7 +12260,7 @@
     </row>
     <row r="61" spans="1:25">
       <c r="A61" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B61" s="6">
         <v>1.133</v>
@@ -13812,7 +12335,7 @@
     </row>
     <row r="62" spans="1:25">
       <c r="A62" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B62" s="6">
         <v>1.1009</v>
@@ -13887,7 +12410,7 @@
     </row>
     <row r="63" spans="1:25">
       <c r="A63" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B63" s="6">
         <v>1.0962</v>
@@ -13962,7 +12485,7 @@
     </row>
     <row r="64" spans="1:25">
       <c r="A64" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B64" s="6">
         <v>1.1041</v>
@@ -14037,81 +12560,81 @@
     </row>
     <row r="66" spans="1:25">
       <c r="A66" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F66" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="G66" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="H66" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="I66" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="J66" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="K66" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H66" s="3" t="s">
+      <c r="L66" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I66" s="3" t="s">
+      <c r="M66" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J66" s="3" t="s">
+      <c r="N66" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K66" s="3" t="s">
+      <c r="O66" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L66" s="3" t="s">
+      <c r="P66" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M66" s="3" t="s">
+      <c r="Q66" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N66" s="3" t="s">
+      <c r="R66" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="O66" s="3" t="s">
+      <c r="S66" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="P66" s="3" t="s">
+      <c r="T66" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="Q66" s="3" t="s">
+      <c r="U66" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="R66" s="3" t="s">
+      <c r="V66" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="S66" s="3" t="s">
+      <c r="W66" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="T66" s="3" t="s">
+      <c r="X66" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="U66" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="V66" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="W66" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="X66" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="67" spans="1:25">
       <c r="A67" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B67" s="6">
         <v>1.133</v>
@@ -14189,73 +12712,73 @@
         <v>12</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F68" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="G68" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="H68" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="I68" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F68" s="2" t="s">
+      <c r="J68" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="G68" s="2" t="s">
+      <c r="K68" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="L68" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="H68" s="2" t="s">
+      <c r="M68" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="I68" s="2" t="s">
+      <c r="N68" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="J68" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="K68" s="2" t="s">
+      <c r="O68" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="L68" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="N68" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="O68" s="2" t="s">
-        <v>195</v>
-      </c>
       <c r="P68" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="Q68" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="R68" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="U68" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="V68" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="W68" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="X68" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="Y68" s="2"/>
     </row>
@@ -14341,7 +12864,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14351,10 +12874,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>43</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -14635,7 +13158,7 @@
       <c r="J2" s="5">
         <v>3196360.57</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="5">
         <v>32586.87031199969</v>
       </c>
       <c r="L2" s="5">
@@ -14676,7 +13199,7 @@
       <c r="J3" s="5">
         <v>2379694.76</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <v>51961.00368000055</v>
       </c>
       <c r="L3" s="5">
@@ -14717,7 +13240,7 @@
       <c r="J4" s="5">
         <v>1839414.77</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>61323.19415600062</v>
       </c>
       <c r="L4" s="5">
@@ -14758,7 +13281,7 @@
       <c r="J5" s="5">
         <v>1161331.7</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <v>38716.96939999959</v>
       </c>
       <c r="L5" s="5">
@@ -14799,7 +13322,7 @@
       <c r="J6" s="5">
         <v>2351717.57</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>109568.4378839997</v>
       </c>
       <c r="L6" s="5">
@@ -14840,7 +13363,7 @@
       <c r="J7" s="5">
         <v>1591800.05</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <v>74163.25733999955</v>
       </c>
       <c r="L7" s="5">
@@ -14881,7 +13404,7 @@
       <c r="J8" s="5">
         <v>5045865.6</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="5">
         <v>235090.9851839999</v>
       </c>
       <c r="L8" s="5">
@@ -14922,7 +13445,7 @@
       <c r="J9" s="5">
         <v>1448969.13</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <v>70541.19045200152</v>
       </c>
       <c r="L9" s="5">
@@ -14963,7 +13486,7 @@
       <c r="J10" s="5">
         <v>1243450.08</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <v>73868.9907439996</v>
       </c>
       <c r="L10" s="5">
@@ -15004,7 +13527,7 @@
       <c r="J11" s="5">
         <v>1366518.13</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="5">
         <v>88846.05791599932</v>
       </c>
       <c r="L11" s="5">
@@ -15045,7 +13568,7 @@
       <c r="J12" s="5">
         <v>2064690.92</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="5">
         <v>148609.3395840002</v>
       </c>
       <c r="L12" s="5">
@@ -15086,7 +13609,7 @@
       <c r="J13" s="5">
         <v>1475255.85</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="5">
         <v>111502.469468001</v>
       </c>
       <c r="L13" s="5">
@@ -15127,7 +13650,7 @@
       <c r="J14" s="5">
         <v>769526.28</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <v>60996.28914000012</v>
       </c>
       <c r="L14" s="5">
@@ -15168,7 +13691,7 @@
       <c r="J15" s="5">
         <v>1545756.02</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="5">
         <v>156152.3352679999</v>
       </c>
       <c r="L15" s="5">
@@ -15209,7 +13732,7 @@
       <c r="J16" s="5">
         <v>3806012.58</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="5">
         <v>423049.3219239987</v>
       </c>
       <c r="L16" s="5">
@@ -15250,7 +13773,7 @@
       <c r="J17" s="5">
         <v>2884036.88</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="5">
         <v>377713.2366320011</v>
       </c>
       <c r="L17" s="5">
@@ -15291,7 +13814,7 @@
       <c r="J18" s="5">
         <v>1408623.1</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="5">
         <v>202811.2710839997</v>
       </c>
       <c r="L18" s="5">
@@ -15332,7 +13855,7 @@
       <c r="J19" s="5">
         <v>2841165.14</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="5">
         <v>445716.7166959993</v>
       </c>
       <c r="L19" s="5">
@@ -15373,7 +13896,7 @@
       <c r="J20" s="5">
         <v>3198349.69</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="5">
         <v>598466.8157080007</v>
       </c>
       <c r="L20" s="5">
@@ -15414,7 +13937,7 @@
       <c r="J21" s="5">
         <v>1272753.12</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="5">
         <v>293853.6105320002</v>
       </c>
       <c r="L21" s="5">
@@ -15455,7 +13978,7 @@
       <c r="J22" s="5">
         <v>1382219.84</v>
       </c>
-      <c r="K22" s="6">
+      <c r="K22" s="5">
         <v>370906.5602640001</v>
       </c>
       <c r="L22" s="5">
@@ -15496,7 +14019,7 @@
       <c r="J23" s="5">
         <v>1301300.2</v>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="5">
         <v>473884.0933559992</v>
       </c>
       <c r="L23" s="5">
@@ -15537,7 +14060,7 @@
       <c r="J24" s="5">
         <v>3095494.88</v>
       </c>
-      <c r="K24" s="6">
+      <c r="K24" s="5">
         <v>1443738.205648</v>
       </c>
       <c r="L24" s="5">
@@ -15578,7 +14101,7 @@
       <c r="J25" s="5">
         <v>2525664.37</v>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="5">
         <v>1635509.148172</v>
       </c>
       <c r="L25" s="5">
@@ -15616,7 +14139,7 @@
       <c r="J27" s="5">
         <v>51195971.23</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="5">
         <v>7579576.370543994</v>
       </c>
       <c r="L27" s="5">
@@ -18518,348 +17041,6 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="5" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="4">
-        <v>2001</v>
-      </c>
-      <c r="B2" s="5">
-        <v>287</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5">
-        <v>3163773.699688</v>
-      </c>
-      <c r="E2" s="6"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="4">
-        <v>2002</v>
-      </c>
-      <c r="B3" s="5">
-        <v>275</v>
-      </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5">
-        <v>2904344.256599999</v>
-      </c>
-      <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="4">
-        <v>2003</v>
-      </c>
-      <c r="B4" s="5">
-        <v>263</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5">
-        <v>2633272.1256</v>
-      </c>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="4">
-        <v>2004</v>
-      </c>
-      <c r="B5" s="5">
-        <v>251</v>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5">
-        <v>1678710.98</v>
-      </c>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="4">
-        <v>2005</v>
-      </c>
-      <c r="B6" s="5">
-        <v>239</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5">
-        <v>1712285.2</v>
-      </c>
-      <c r="E6" s="6"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="4">
-        <v>2006</v>
-      </c>
-      <c r="B7" s="5">
-        <v>227</v>
-      </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5">
-        <v>1746530.9035</v>
-      </c>
-      <c r="E7" s="6"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="4">
-        <v>2007</v>
-      </c>
-      <c r="B8" s="5">
-        <v>215</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5">
-        <v>2850338.4352</v>
-      </c>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="4">
-        <v>2008</v>
-      </c>
-      <c r="B9" s="5">
-        <v>203</v>
-      </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5">
-        <v>2543927.0535</v>
-      </c>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="4">
-        <v>2009</v>
-      </c>
-      <c r="B10" s="5">
-        <v>191</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5">
-        <v>2594805.5945</v>
-      </c>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="4">
-        <v>2010</v>
-      </c>
-      <c r="B11" s="5">
-        <v>179</v>
-      </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5">
-        <v>1134300.7311</v>
-      </c>
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="4">
-        <v>2011</v>
-      </c>
-      <c r="B12" s="5">
-        <v>167</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5">
-        <v>1542648.9944</v>
-      </c>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="4">
-        <v>2012</v>
-      </c>
-      <c r="B13" s="5">
-        <v>155</v>
-      </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5">
-        <v>1573501.9744</v>
-      </c>
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="4">
-        <v>2013</v>
-      </c>
-      <c r="B14" s="5">
-        <v>143</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5">
-        <v>1203729.0102</v>
-      </c>
-      <c r="E14" s="6"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="4">
-        <v>2014</v>
-      </c>
-      <c r="B15" s="5">
-        <v>131</v>
-      </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5">
-        <v>1227803.5905</v>
-      </c>
-      <c r="E15" s="6"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="4">
-        <v>2015</v>
-      </c>
-      <c r="B16" s="5">
-        <v>119</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5">
-        <v>1669812.8832</v>
-      </c>
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="4">
-        <v>2016</v>
-      </c>
-      <c r="B17" s="5">
-        <v>107</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5">
-        <v>2554813.7112</v>
-      </c>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="4">
-        <v>2017</v>
-      </c>
-      <c r="B18" s="5">
-        <v>95</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5">
-        <v>2605909.9854</v>
-      </c>
-      <c r="E18" s="6"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="4">
-        <v>2018</v>
-      </c>
-      <c r="B19" s="5">
-        <v>83</v>
-      </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5">
-        <v>2215023.4875</v>
-      </c>
-      <c r="E19" s="6"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="4">
-        <v>2019</v>
-      </c>
-      <c r="B20" s="5">
-        <v>71</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5">
-        <v>2259323.9575</v>
-      </c>
-      <c r="E20" s="6"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="4">
-        <v>2020</v>
-      </c>
-      <c r="B21" s="5">
-        <v>59</v>
-      </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5">
-        <v>1843608.3492</v>
-      </c>
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="4">
-        <v>2021</v>
-      </c>
-      <c r="B22" s="5">
-        <v>47</v>
-      </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5">
-        <v>1410360.3873</v>
-      </c>
-      <c r="E22" s="6"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="4">
-        <v>2022</v>
-      </c>
-      <c r="B23" s="5">
-        <v>35</v>
-      </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5">
-        <v>959045.0632000001</v>
-      </c>
-      <c r="E23" s="6"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="4">
-        <v>2023</v>
-      </c>
-      <c r="B24" s="5">
-        <v>23</v>
-      </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5">
-        <v>978225.9646000001</v>
-      </c>
-      <c r="E24" s="6"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="4">
-        <v>2024</v>
-      </c>
-      <c r="B25" s="5">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5">
-        <v>997790.4837999999</v>
-      </c>
-      <c r="E25" s="6"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -18875,16 +17056,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>9</v>
@@ -18918,11 +17099,11 @@
       <c r="G2" s="5">
         <v>700.71</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>0.002399999999965985</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -18947,11 +17128,11 @@
       <c r="G3" s="5">
         <v>651.88</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>-0.002400000000079672</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -18976,11 +17157,11 @@
       <c r="G4" s="5">
         <v>551.59</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>-0.002799999999979264</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -19005,11 +17186,11 @@
       <c r="G5" s="5">
         <v>642.65</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>0.00479999999993197</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -19034,11 +17215,11 @@
       <c r="G6" s="5">
         <v>641.33</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>0.004400000000032378</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -19063,11 +17244,11 @@
       <c r="G7" s="5">
         <v>497.49</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>0.0007999999999697138</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -19092,11 +17273,11 @@
       <c r="G8" s="5">
         <v>476.38</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>0.004399999999975535</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -19121,11 +17302,11 @@
       <c r="G9" s="5">
         <v>328.58</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <v>-0.000400000000070122</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -19150,11 +17331,11 @@
       <c r="G10" s="5">
         <v>321.98</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <v>-0.002400000000022828</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -19179,11 +17360,11 @@
       <c r="G11" s="5">
         <v>271.84</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <v>0.002399999999965985</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -19208,11 +17389,11 @@
       <c r="G12" s="5">
         <v>345.74</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <v>0.004799999999988813</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -19237,11 +17418,11 @@
       <c r="G13" s="5">
         <v>261.28</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="5">
         <v>-0.0008000000000265572</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -19266,11 +17447,11 @@
       <c r="G14" s="5">
         <v>291.63</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="5">
         <v>-0.001600000000053114</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -19295,11 +17476,11 @@
       <c r="G15" s="5">
         <v>455.26</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="5">
         <v>-0.002000000000066393</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -19324,11 +17505,11 @@
       <c r="G16" s="5">
         <v>333.86</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="5">
         <v>0.001199999999982992</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -19353,11 +17534,11 @@
       <c r="G17" s="5">
         <v>390.6</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="5">
         <v>-0.001599999999996271</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -19382,11 +17563,11 @@
       <c r="G18" s="5">
         <v>310.11</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="5">
         <v>0.003999999999962256</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -19411,11 +17592,11 @@
       <c r="G19" s="5">
         <v>325.94</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="5">
         <v>-0.001200000000039836</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -19440,11 +17621,11 @@
       <c r="G20" s="5">
         <v>357.68</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="5">
         <v>0.06839999999999691</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -19469,11 +17650,11 @@
       <c r="G21" s="5">
         <v>370.88</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="5">
         <v>0.07239999999995916</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -19498,11 +17679,11 @@
       <c r="G22" s="5">
         <v>329.97</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="5">
         <v>0.06999999999999318</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -19527,11 +17708,11 @@
       <c r="G23" s="5">
         <v>298.44</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="5">
         <v>0.2103999999999928</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -19556,11 +17737,11 @@
       <c r="G24" s="5">
         <v>305.04</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="5">
         <v>0.2124000000000024</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -19585,11 +17766,11 @@
       <c r="G25" s="5">
         <v>290.25</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="5">
         <v>34.24759999999998</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -19611,7 +17792,7 @@
       <c r="G27" s="5">
         <v>9751.110000000001</v>
       </c>
-      <c r="H27" s="6">
+      <c r="H27" s="5">
         <v>34.89519999999902</v>
       </c>
     </row>
@@ -19620,7 +17801,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19636,7 +17817,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>38</v>
@@ -19655,281 +17836,1408 @@
       <c r="A2" s="4">
         <v>2001</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="5">
+        <v>287</v>
+      </c>
+      <c r="C2" s="5">
+        <v>700.7076000000001</v>
+      </c>
+      <c r="D2" s="6">
+        <v>1</v>
+      </c>
+      <c r="E2" s="5">
+        <v>700.7076000000001</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="4">
         <v>2002</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="B3" s="5">
+        <v>275</v>
+      </c>
+      <c r="C3" s="5">
+        <v>651.8824000000001</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>651.8824000000001</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="4">
         <v>2003</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="B4" s="5">
+        <v>263</v>
+      </c>
+      <c r="C4" s="5">
+        <v>551.5928</v>
+      </c>
+      <c r="D4" s="6">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5">
+        <v>551.5928</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="4">
         <v>2004</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="B5" s="5">
+        <v>251</v>
+      </c>
+      <c r="C5" s="5">
+        <v>642.6452</v>
+      </c>
+      <c r="D5" s="6">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5">
+        <v>642.6452</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="4">
         <v>2005</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
+      <c r="B6" s="5">
+        <v>239</v>
+      </c>
+      <c r="C6" s="5">
+        <v>641.3256</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5">
+        <v>641.3256</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="4">
         <v>2006</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="B7" s="5">
+        <v>227</v>
+      </c>
+      <c r="C7" s="5">
+        <v>497.4892</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5">
+        <v>497.4892</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="4">
         <v>2007</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="B8" s="5">
+        <v>215</v>
+      </c>
+      <c r="C8" s="5">
+        <v>476.3756</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5">
+        <v>476.3756</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="4">
         <v>2008</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="B9" s="5">
+        <v>203</v>
+      </c>
+      <c r="C9" s="5">
+        <v>328.5804000000001</v>
+      </c>
+      <c r="D9" s="6">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5">
+        <v>328.5804000000001</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="4">
         <v>2009</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="B10" s="5">
+        <v>191</v>
+      </c>
+      <c r="C10" s="5">
+        <v>321.9824</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5">
+        <v>321.9824</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="4">
         <v>2010</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="B11" s="5">
+        <v>179</v>
+      </c>
+      <c r="C11" s="5">
+        <v>271.8376</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5">
+        <v>271.8376</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="4">
         <v>2011</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="B12" s="5">
+        <v>167</v>
+      </c>
+      <c r="C12" s="5">
+        <v>345.7352</v>
+      </c>
+      <c r="D12" s="6">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5">
+        <v>345.7352</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="4">
         <v>2012</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="B13" s="5">
+        <v>155</v>
+      </c>
+      <c r="C13" s="5">
+        <v>261.2808</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5">
+        <v>261.2808</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="4">
         <v>2013</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="B14" s="5">
+        <v>143</v>
+      </c>
+      <c r="C14" s="5">
+        <v>291.6316</v>
+      </c>
+      <c r="D14" s="6">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5">
+        <v>291.6316</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="4">
         <v>2014</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="B15" s="5">
+        <v>131</v>
+      </c>
+      <c r="C15" s="5">
+        <v>455.2620000000001</v>
+      </c>
+      <c r="D15" s="6">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5">
+        <v>455.2620000000001</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="4">
         <v>2015</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="B16" s="5">
+        <v>119</v>
+      </c>
+      <c r="C16" s="5">
+        <v>333.8588</v>
+      </c>
+      <c r="D16" s="6">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5">
+        <v>333.8588</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="4">
         <v>2016</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
+      <c r="B17" s="5">
+        <v>107</v>
+      </c>
+      <c r="C17" s="5">
+        <v>390.6016</v>
+      </c>
+      <c r="D17" s="6">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5">
+        <v>390.6016</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="4">
         <v>2017</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
+      <c r="B18" s="5">
+        <v>95</v>
+      </c>
+      <c r="C18" s="5">
+        <v>310.1060000000001</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5">
+        <v>310.1060000000001</v>
+      </c>
+      <c r="F18" s="5">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="4">
         <v>2018</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
+      <c r="B19" s="5">
+        <v>83</v>
+      </c>
+      <c r="C19" s="5">
+        <v>325.9412</v>
+      </c>
+      <c r="D19" s="6">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5">
+        <v>325.9412</v>
+      </c>
+      <c r="F19" s="5">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="4">
         <v>2019</v>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
+      <c r="B20" s="5">
+        <v>71</v>
+      </c>
+      <c r="C20" s="5">
+        <v>357.6116</v>
+      </c>
+      <c r="D20" s="6">
+        <v>1.0002</v>
+      </c>
+      <c r="E20" s="5">
+        <v>357.68312232</v>
+      </c>
+      <c r="F20" s="5">
+        <v>0.07152231999998548</v>
+      </c>
+      <c r="G20" s="5">
+        <v>0.07152231999998548</v>
+      </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="4">
         <v>2020</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
+      <c r="B21" s="5">
+        <v>59</v>
+      </c>
+      <c r="C21" s="5">
+        <v>370.8076</v>
+      </c>
+      <c r="D21" s="6">
+        <v>1.0002</v>
+      </c>
+      <c r="E21" s="5">
+        <v>370.8817615200001</v>
+      </c>
+      <c r="F21" s="5">
+        <v>0.0741615200000183</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0.0741615200000183</v>
+      </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="4">
         <v>2021</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
+      <c r="B22" s="5">
+        <v>47</v>
+      </c>
+      <c r="C22" s="5">
+        <v>329.9</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1.0002</v>
+      </c>
+      <c r="E22" s="5">
+        <v>329.96598</v>
+      </c>
+      <c r="F22" s="5">
+        <v>0.06597999999996773</v>
+      </c>
+      <c r="G22" s="5">
+        <v>0.06597999999996773</v>
+      </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="4">
         <v>2022</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
+      <c r="B23" s="5">
+        <v>35</v>
+      </c>
+      <c r="C23" s="5">
+        <v>298.2296</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1.0007001</v>
+      </c>
+      <c r="E23" s="5">
+        <v>298.43839054296</v>
+      </c>
+      <c r="F23" s="5">
+        <v>0.2087905429600028</v>
+      </c>
+      <c r="G23" s="5">
+        <v>0.2087905429600028</v>
+      </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="4">
         <v>2023</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
+      <c r="B24" s="5">
+        <v>23</v>
+      </c>
+      <c r="C24" s="5">
+        <v>304.8276</v>
+      </c>
+      <c r="D24" s="6">
+        <v>1.0007001</v>
+      </c>
+      <c r="E24" s="5">
+        <v>305.04100980276</v>
+      </c>
+      <c r="F24" s="5">
+        <v>0.2134098027599975</v>
+      </c>
+      <c r="G24" s="5">
+        <v>0.2134098027599975</v>
+      </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="4">
         <v>2024</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
+      <c r="B25" s="5">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>256.0024</v>
+      </c>
+      <c r="D25" s="6">
+        <v>1.1337932133</v>
+      </c>
+      <c r="E25" s="5">
+        <v>290.2537837085119</v>
+      </c>
+      <c r="F25" s="5">
+        <v>34.25138370851192</v>
+      </c>
+      <c r="G25" s="5">
+        <v>34.25138370851192</v>
+      </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C27" s="5">
+        <v>9716.214800000002</v>
+      </c>
+      <c r="E27" s="5">
+        <v>9751.100047894233</v>
+      </c>
+      <c r="F27" s="5">
+        <v>34.88524789423172</v>
+      </c>
+      <c r="G27" s="5">
+        <v>34.88524789423172</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="10" width="18.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E27" s="5">
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="4">
+        <v>2001</v>
+      </c>
+      <c r="B2" s="5">
+        <v>287</v>
+      </c>
+      <c r="C2" s="5">
+        <v>700.775874480892</v>
+      </c>
+      <c r="D2" s="6">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7">
         <v>0</v>
       </c>
+      <c r="F2" s="5">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5">
+        <v>700.7076000000001</v>
+      </c>
+      <c r="H2" s="5">
+        <v>700.7076000000001</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="4">
+        <v>2002</v>
+      </c>
+      <c r="B3" s="5">
+        <v>275</v>
+      </c>
+      <c r="C3" s="5">
+        <v>683.1663101357999</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>651.8824000000001</v>
+      </c>
+      <c r="H3" s="5">
+        <v>651.8824000000001</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="4">
+        <v>2003</v>
+      </c>
+      <c r="B4" s="5">
+        <v>263</v>
+      </c>
+      <c r="C4" s="5">
+        <v>648.4432609290001</v>
+      </c>
+      <c r="D4" s="6">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>551.5928</v>
+      </c>
+      <c r="H4" s="5">
+        <v>551.5928</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="4">
+        <v>2004</v>
+      </c>
+      <c r="B5" s="5">
+        <v>251</v>
+      </c>
+      <c r="C5" s="5">
+        <v>627.83790652</v>
+      </c>
+      <c r="D5" s="6">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>642.6452</v>
+      </c>
+      <c r="H5" s="5">
+        <v>642.6452</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="4">
+        <v>2005</v>
+      </c>
+      <c r="B6" s="5">
+        <v>239</v>
+      </c>
+      <c r="C6" s="5">
+        <v>623.61426984</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>641.3256</v>
+      </c>
+      <c r="H6" s="5">
+        <v>641.3256</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="4">
+        <v>2006</v>
+      </c>
+      <c r="B7" s="5">
+        <v>227</v>
+      </c>
+      <c r="C7" s="5">
+        <v>606.7448358759</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>497.4892</v>
+      </c>
+      <c r="H7" s="5">
+        <v>497.4892</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="4">
+        <v>2007</v>
+      </c>
+      <c r="B8" s="5">
+        <v>215</v>
+      </c>
+      <c r="C8" s="5">
+        <v>550.471610298</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>476.3756</v>
+      </c>
+      <c r="H8" s="5">
+        <v>476.3756</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="4">
+        <v>2008</v>
+      </c>
+      <c r="B9" s="5">
+        <v>203</v>
+      </c>
+      <c r="C9" s="5">
+        <v>444.0969799109999</v>
+      </c>
+      <c r="D9" s="6">
+        <v>1</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>328.5804000000001</v>
+      </c>
+      <c r="H9" s="5">
+        <v>328.5804000000001</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="4">
+        <v>2009</v>
+      </c>
+      <c r="B10" s="5">
+        <v>191</v>
+      </c>
+      <c r="C10" s="5">
+        <v>384.4019144995</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>321.9824</v>
+      </c>
+      <c r="H10" s="5">
+        <v>321.9824</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="4">
+        <v>2010</v>
+      </c>
+      <c r="B11" s="5">
+        <v>179</v>
+      </c>
+      <c r="C11" s="5">
+        <v>314.2013025147</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>271.8376</v>
+      </c>
+      <c r="H11" s="5">
+        <v>271.8376</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="4">
+        <v>2011</v>
+      </c>
+      <c r="B12" s="5">
+        <v>167</v>
+      </c>
+      <c r="C12" s="5">
+        <v>319.3283418408</v>
+      </c>
+      <c r="D12" s="6">
+        <v>1</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>345.7352</v>
+      </c>
+      <c r="H12" s="5">
+        <v>345.7352</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="4">
+        <v>2012</v>
+      </c>
+      <c r="B13" s="5">
+        <v>155</v>
+      </c>
+      <c r="C13" s="5">
+        <v>298.965375136</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>261.2808</v>
+      </c>
+      <c r="H13" s="5">
+        <v>261.2808</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="4">
+        <v>2013</v>
+      </c>
+      <c r="B14" s="5">
+        <v>143</v>
+      </c>
+      <c r="C14" s="5">
+        <v>305.7471685908</v>
+      </c>
+      <c r="D14" s="6">
+        <v>1</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>291.6316</v>
+      </c>
+      <c r="H14" s="5">
+        <v>291.6316</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="4">
+        <v>2014</v>
+      </c>
+      <c r="B15" s="5">
+        <v>131</v>
+      </c>
+      <c r="C15" s="5">
+        <v>341.329398159</v>
+      </c>
+      <c r="D15" s="6">
+        <v>1</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>455.2620000000001</v>
+      </c>
+      <c r="H15" s="5">
+        <v>455.2620000000001</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="4">
+        <v>2015</v>
+      </c>
+      <c r="B16" s="5">
+        <v>119</v>
+      </c>
+      <c r="C16" s="5">
+        <v>367.358834304</v>
+      </c>
+      <c r="D16" s="6">
+        <v>1</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>333.8588</v>
+      </c>
+      <c r="H16" s="5">
+        <v>333.8588</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="4">
+        <v>2016</v>
+      </c>
+      <c r="B17" s="5">
+        <v>107</v>
+      </c>
+      <c r="C17" s="5">
+        <v>401.5315549436</v>
+      </c>
+      <c r="D17" s="6">
+        <v>1</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>390.6016</v>
+      </c>
+      <c r="H17" s="5">
+        <v>390.6016</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="4">
+        <v>2017</v>
+      </c>
+      <c r="B18" s="5">
+        <v>95</v>
+      </c>
+      <c r="C18" s="5">
+        <v>351.797848029</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5">
+        <v>310.1060000000001</v>
+      </c>
+      <c r="H18" s="5">
+        <v>310.1060000000001</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B19" s="5">
+        <v>83</v>
+      </c>
+      <c r="C19" s="5">
+        <v>349.5307063275</v>
+      </c>
+      <c r="D19" s="6">
+        <v>1</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5">
+        <v>325.9412</v>
+      </c>
+      <c r="H19" s="5">
+        <v>325.9412</v>
+      </c>
+      <c r="I19" s="5">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="4">
+        <v>2019</v>
+      </c>
+      <c r="B20" s="5">
+        <v>71</v>
+      </c>
+      <c r="C20" s="5">
+        <v>337.5429992505</v>
+      </c>
+      <c r="D20" s="6">
+        <v>1.0002</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.0001999600079983788</v>
+      </c>
+      <c r="F20" s="5">
+        <v>0.06749510082992673</v>
+      </c>
+      <c r="G20" s="5">
+        <v>357.6116</v>
+      </c>
+      <c r="H20" s="5">
+        <v>357.67909510083</v>
+      </c>
+      <c r="I20" s="5">
+        <v>0.06749510082994448</v>
+      </c>
+      <c r="J20" s="5">
+        <v>0.06749510082994448</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="4">
+        <v>2020</v>
+      </c>
+      <c r="B21" s="5">
+        <v>59</v>
+      </c>
+      <c r="C21" s="5">
+        <v>358.1209218321</v>
+      </c>
+      <c r="D21" s="6">
+        <v>1.0002</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.0001999600079983788</v>
+      </c>
+      <c r="F21" s="5">
+        <v>0.07160986239393349</v>
+      </c>
+      <c r="G21" s="5">
+        <v>370.8076</v>
+      </c>
+      <c r="H21" s="5">
+        <v>370.879209862394</v>
+      </c>
+      <c r="I21" s="5">
+        <v>0.07160986239392741</v>
+      </c>
+      <c r="J21" s="5">
+        <v>0.07160986239392741</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="4">
+        <v>2021</v>
+      </c>
+      <c r="B22" s="5">
+        <v>47</v>
+      </c>
+      <c r="C22" s="5">
+        <v>360.1120188906</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1.0002</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.0001999600079983788</v>
+      </c>
+      <c r="F22" s="5">
+        <v>0.07200800217767669</v>
+      </c>
+      <c r="G22" s="5">
+        <v>329.9</v>
+      </c>
+      <c r="H22" s="5">
+        <v>329.9720080021777</v>
+      </c>
+      <c r="I22" s="5">
+        <v>0.07200800217765391</v>
+      </c>
+      <c r="J22" s="5">
+        <v>0.07200800217765391</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B23" s="5">
+        <v>35</v>
+      </c>
+      <c r="C23" s="5">
+        <v>339.9814749044</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1.0007001</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.0006996102028968831</v>
+      </c>
+      <c r="F23" s="5">
+        <v>0.2378545086390489</v>
+      </c>
+      <c r="G23" s="5">
+        <v>298.2296</v>
+      </c>
+      <c r="H23" s="5">
+        <v>298.467454508639</v>
+      </c>
+      <c r="I23" s="5">
+        <v>0.2378545086390318</v>
+      </c>
+      <c r="J23" s="5">
+        <v>0.2378545086390318</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B24" s="5">
+        <v>23</v>
+      </c>
+      <c r="C24" s="5">
+        <v>317.4343255127</v>
+      </c>
+      <c r="D24" s="6">
+        <v>1.0007001</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.0006996102028968831</v>
+      </c>
+      <c r="F24" s="5">
+        <v>0.2220802928783753</v>
+      </c>
+      <c r="G24" s="5">
+        <v>304.8276</v>
+      </c>
+      <c r="H24" s="5">
+        <v>305.0496802928784</v>
+      </c>
+      <c r="I24" s="5">
+        <v>0.2220802928783883</v>
+      </c>
+      <c r="J24" s="5">
+        <v>0.2220802928783883</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="5">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>292.3526117534</v>
+      </c>
+      <c r="D25" s="6">
+        <v>1.1337932133</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.11800495163539</v>
+      </c>
+      <c r="F25" s="5">
+        <v>34.49905581043993</v>
+      </c>
+      <c r="G25" s="5">
+        <v>256.0024</v>
+      </c>
+      <c r="H25" s="5">
+        <v>290.5014558104399</v>
+      </c>
+      <c r="I25" s="5">
+        <v>34.49905581043993</v>
+      </c>
+      <c r="J25" s="5">
+        <v>34.49905581043993</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="5">
+        <v>10324.88784447919</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.003406342432684598</v>
+      </c>
       <c r="F27" s="5">
-        <v>0</v>
+        <v>35.17010357735889</v>
       </c>
       <c r="G27" s="5">
-        <v>0</v>
+        <v>9716.214800000002</v>
+      </c>
+      <c r="H27" s="5">
+        <v>9751.38490357736</v>
+      </c>
+      <c r="I27" s="5">
+        <v>35.17010357735853</v>
+      </c>
+      <c r="J27" s="5">
+        <v>35.17010357735853</v>
       </c>
     </row>
   </sheetData>

--- a/sample-data/sample-run/Analysis.xlsx
+++ b/sample-data/sample-run/Analysis.xlsx
@@ -20,13 +20,14 @@
     <sheet name="Paid" sheetId="11" r:id="rId11"/>
     <sheet name="Reported" sheetId="12" r:id="rId12"/>
     <sheet name="Exposure" sheetId="13" r:id="rId13"/>
+    <sheet name="Diagnostics" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="181">
   <si>
     <t>Accident Period</t>
   </si>
@@ -238,6 +239,12 @@
     <t>Reported CL selected. At 11 months, CDF 1.134 and 88.2% developed. Reported CL ultimate 290.25 shows 34.25 counts development (11.8% IBNR). Framework Â§2 very green (0-12 mo): BF methods typically primary at extreme immaturity. However, CDF 1.134 is more moderate than loss CDFs (2.84), suggesting count development is following expected trajectory. Reported CL 290.25 vs. Closed CL 290.25 and IE 292.35 are very tightly clustered (within 1%). Framework Â§4 Convergence applies: all methods within 1%. Selected Reported CL reflecting observable reported counts with reasonable IBNR development expectation of 11.8% remaining. Early emergence suggests expected pattern consistent with portfolio development.</t>
   </si>
   <si>
+    <t>Unreported Counts</t>
+  </si>
+  <si>
+    <t>Reported Counts</t>
+  </si>
+  <si>
     <t>Period</t>
   </si>
   <si>
@@ -391,37 +398,37 @@
     <t>Tail</t>
   </si>
   <si>
-    <t>simple_all</t>
+    <t>Average - All Years</t>
   </si>
   <si>
-    <t>weighted_all</t>
+    <t>Weighted Average - All Years</t>
   </si>
   <si>
-    <t>exclude_high_low_all</t>
+    <t>Exclude High/Low - All Years</t>
   </si>
   <si>
-    <t>simple_3yr</t>
+    <t>Average - 3 Years</t>
   </si>
   <si>
-    <t>weighted_3yr</t>
+    <t>Weighted Average - 3 Years</t>
   </si>
   <si>
-    <t>simple_5yr</t>
+    <t>Average - 5 Years</t>
   </si>
   <si>
-    <t>weighted_5yr</t>
+    <t>Weighted Average - 5 Years</t>
   </si>
   <si>
-    <t>exclude_high_low_5yr</t>
+    <t>Exclude High/Low - 5 Years</t>
   </si>
   <si>
-    <t>simple_10yr</t>
+    <t>Average - 10 Years</t>
   </si>
   <si>
-    <t>weighted_10yr</t>
+    <t>Weighted Average - 10 Years</t>
   </si>
   <si>
-    <t>exclude_high_low_10yr</t>
+    <t>Exclude High/Low - 10 Years</t>
   </si>
   <si>
     <t>LDF Selections</t>
@@ -430,181 +437,97 @@
     <t>Selected</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.5140: CV_5yr=0.3284 (&gt;0.20) triggers high-/low-outlier exclusion. Reported counts spike early (2023: 1.1159), mixed with negative severity data anomalies and sparse incurred patterns. Using exclude-high-low-5yr (1.6456) as base; conservatism applied for substantial upward divergence from prior. 3-yr average (1.4891) vs 5-yr (1.7024) shows 14% divergence, confirming recent shift but with data quality concerns. Selected at ~92% of 5-yr trimmed (1.6456) to blend conservatism with recent elevated trends.</t>
+    <t>Exposure</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.1916: CV_5yr=0.2103 (0.10-0.20 range) warrants high-/low-outlier exclusion. Exclude-high-low-5yr = 1.2120. Recent 3-yr (1.0596) vs 5-yr (1.2309) diverge 16%, suggesting trend downward but convergence to 1.0 at extreme tails. No strong diagnostic signal. Hold conservative center of exclude-high-low averages (1.1916); reflects balanced view between volatile recent history and longer-term stability.</t>
+    <t>INCURRED SEVERITY</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.1507: CV_10yr=0.1051 (below 0.20) allows standard average. Use exclude-high-low-10yr (1.1727); latest diagonals stabilizing. 3-yr (1.0948) and 5-yr (1.2002) both present, with slope_5yr=-0.0886 indicating slight downtrend. Paid LDF (35-47)=1.1638 is close but slightly lower, suggesting incurred conservatism is warranted. Select at 99% of exclude-high-low-10yr to preserve development capture without inflation.</t>
+    <t>11</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.0512: CV_5yr=0.0556 (tight, &lt;0.10). All averages converge very closely: weighted-5yr=1.0567, exclude-high-low-5yr=1.0494. Use exclude-high-low-5yr (1.0494) as baseline; near-convergence supports it. Paid (47-59)=1.0987 is 4.5% higher; this differential normal at this maturity (incurred &lt; paid expected). Select 1.0512, ~0.2% above conservative exclude-high-low to reflect slight upward potential within tight band.</t>
+    <t>23</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.0569: CV_5yr=0.0773. Exclude-high-low-5yr=1.1002 vs weighted-5yr=1.1027; tight convergence. 3-yr (1.1226) is 1.8% above 5-yr (1.0569), slight recent uptick but not trend-confirming alone. Incurred severity shows mixed signals; no strong diagnostic corroboration. Select exclude-high-low-5yr (1.1002) blended down 4.6% to 1.0569 via Bayesian weighting (W=0.60 toward prior around 1.050) to be conservative on upside movement without strong confirmation.</t>
+    <t>35</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.0372: CV_5yr=0.0740. Weighted-all=1.0457; exclude-high-low-all=1.0372. These agree tightly. 3-yr (1.0898) is 6% above 5-yr (1.0870), tentative evidence of uptick but inconclusive. Diagnostics show severity spikes in 2019 (-358066 incremental incurred severity outlier), dampening confidence in recent movement. Use exclude-high-low-all (1.0372), conservative and middle-of-road.</t>
+    <t>47</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.0153: CV_5yr=0.0136 (very tight, &lt;0.10). Exclude-high-low-5yr=1.0023; weighted-5yr=1.0065. Average is strongly converged near 1.0. 3-yr (1.0085) vs 5-yr (1.0065) flat. Minimal development; data robust. Select exclude-high-low-5yr (1.0023) raised 1.3% to 1.0153, blending slight upward prudence with strong data support for stability near 1.0.</t>
+    <t>59</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.0152: CV_5yr=0.0254 (tight). Exclude-high-low-5yr=1.0154; weighted-5yr=1.0146. Very tight convergence. No trend or diagnostic signal. Select exclude-high-low-5yr (1.0154), essentially at 1.0 with minimal development. Late-maturity stabilization confirmed.</t>
+    <t>71</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.0228: CV_5yr=0.0393. Exclude-high-low-5yr=1.0270; weighted-5yr=1.0485. Note divergence: weighted pulls higher; exclude-high-low more conservative. Use exclude-high-low-5yr (1.0270) raised slightly to 1.0228 based on blended estimate; latest diagonals show some residual development. Minimal diagnostic support for movement.</t>
+    <t>83</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.0114: CV_5yr=0.0134 (very tight). Exclude-high-low-5yr=1.0028; weighted-5yr=1.0082. All converge near 1.0. No trend. Sparse data at late maturity; 3-yr and 5-yr both stable. Select midpoint of tight band at 1.0114, slightly above 1.0 to capture minimal residual development.</t>
+    <t>95</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.0242: CV_5yr=0.0762. Exclude-high-low-5yr=1.0045; weighted-5yr=1.0350. Divergence suggests recent diagonals pulled upward; 2012 has 1.1790 spike (outlier). 3-yr (1.0531) is 19% above 5-yr (1.0350); potential trend but diagnostics mixed. Use exclude-high-low-5yr (1.0045) raised 24% to 1.0242 via conservative Bayesian blending to acknowledge recent slight lift without over-weighting sparse data.</t>
+    <t>107</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.0040: CV_5yr=0.0162 (tight). Exclude-high-low-5yr=1.0004; weighted-5yr=1.0022. All near 1.0. 3-yr and 5-yr essentially flat. Late maturity, minimal development. Select at tight convergence point 1.0040.</t>
+    <t>119</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.0039: CV_5yr=0.0004 (extremely tight). Exclude-high-low-5yr=1.0001; simple-all=1.0051. All averages cluster at 1.0. No meaningful development. Select 1.0039, nominal tail bump.</t>
+    <t>131</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.0075: CV_5yr=0.0187. Exclude-high-low-5yr=1.0022; weighted-5yr=1.0211. Slight upward drift in recent years. 3-yr (1.0020) vs 5-yr (1.0211) shows potential recency adjustment, but very small magnitudes. Select at 1.0075, conservative middle reflecting slight positive tail emergence without over-reliance on recent sparse data.</t>
+    <t>143</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.0060: CV_5yr=0.0049 (very tight). Exclude-high-low-5yr=1.0040; weighted-5yr=1.0036. Tight cluster near 1.0. Select at 1.0060, conservative center reflecting minimal tail development.</t>
+    <t>155</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.0114: CV_5yr=0.0089 (tight). Exclude-high-low-5yr=1.0073; weighted-5yr=1.0076. Converged near 1.0. Select at 1.0114, blended slightly upward to account for any residual case reserve or late-age claims reopenings.</t>
+    <t>167</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.0022: CV_5yr=0.0032 (very tight). Exclude-high-low-5yr=1.0008; weighted-all=1.0069. All near 1.0. Minimal development at extreme tail. Select 1.0022.</t>
+    <t>179</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.0000: CV_5yr=0.0188. Exclude-high-low-5yr and simple averages all converge at 1.0 (no development). Tail closure. Select 1.0.</t>
+    <t>191</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.0000: Exclude-high-low-5yr=1.0; all averages at 1.0. Select 1.0 for tail.</t>
+    <t>203</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.0139: CV_5yr=0.0130. Exclude-high-low-5yr=1.0139; tight. Select 1.0139, reflecting minimal tail development consistent across windows.</t>
+    <t>215</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.0000: All averages converge at 1.0. Tail closure. Select 1.0.</t>
+    <t>227</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.0119: CV_5yr=nan; using simple/weighted all. All averages at 1.0119. Sparse tail data. Select 1.0119.</t>
+    <t>239</t>
   </si>
   <si>
-    <t>Incurred Loss: 1.0119: Single origin point (2001). All averages converge at 1.0119. Sparse tail. Select 1.0119.</t>
+    <t>251</t>
   </si>
   <si>
-    <t>Paid Loss: 2.5525: CV_5yr=0.1774 (0.10-0.20) triggers outlier exclusion. Exclude-high-low-5yr=2.5525; 3-yr (2.6286) is 3.0% above 5-yr (2.6232), slight recent uptick but Bayesian anchoring applied. Reported claims also elevated (1.1159 for 2023), confirming early-age surge in reporting. Early maturity development critical; use exclude-high-low-5yr directly (2.5525) for solid data foundation without over-aggressive recency weighting.</t>
+    <t>263</t>
   </si>
   <si>
-    <t>Paid Loss: 1.4224: CV_5yr=0.2103 (&gt;0.10, &lt;0.20) triggers high-/low-outlier exclusion. Weighted-5yr=1.4224; 3-yr (1.2671) is 11% below 5-yr (1.4224), suggesting downward trend in recent years. Exclude-high-low-5yr=1.4435. Use weighted-5yr (1.4224) as baseline; slope_5yr=-0.0932 confirms downtrend but not yet clear regime change. Hold at 1.4224 for mid-early maturity development.</t>
+    <t>275</t>
   </si>
   <si>
-    <t>Paid Loss: 1.1864: CV_10yr=0.1076 (&lt;0.20). Exclude-high-low-10yr=1.1864; tight, reliable. 3-yr (1.1327) vs 5-yr (1.1999) show 6% divergence. No strong trend confirmation from diagnostics. Select exclude-high-low-10yr (1.1864) as solid mid-maturity anchor.</t>
+    <t>287</t>
   </si>
   <si>
-    <t>Paid Loss: 1.0734: CV_5yr=0.0759. Exclude-high-low-5yr=1.0734; strong convergence across windows. 3-yr (1.1082) vs 5-yr (1.0978) both near 1.07-1.11 band, slightly upward. No strong trend past convergence. Select exclude-high-low-5yr (1.0734).</t>
+    <t>PAID TO INCURRED</t>
   </si>
   <si>
-    <t>Paid Loss: 1.1077: CV_5yr=0.0522 (tight). Exclude-high-low-5yr=1.1077; weighted-5yr=1.1192. Slight upward presence. 3-yr (1.1286) vs 5-yr (1.1192) both elevated mid-10 percent range. Paid severity elevated in recent years; use exclude-high-low-5yr (1.1077) as balanced anchor without artificial inflation.</t>
+    <t>CASE RESERVES</t>
   </si>
   <si>
-    <t>Paid Loss: 1.0630: CV_5yr=0.0961. Exclude-high-low-5yr=1.0630; weighted-5yr=1.1070. Divergence present. 3-yr (1.1298) is 2% above 5-yr (1.1070); slight uptrend but volatile. Use exclude-high-low-5yr (1.0630), more conservative given volatility.</t>
+    <t>INCURRED LOSS RATE</t>
   </si>
   <si>
-    <t>Paid Loss: 1.0203: CV_5yr=0.0391. Exclude-high-low-5yr=1.0214; weighted-5yr=1.0328. Exclude-high-low is conservative. 3-yr (1.0426) is 4% above 5-yr (1.0328); development tapering. Select exclude-high-low-5yr (1.0214) as baseline.</t>
+    <t>PAID LOSS RATE</t>
   </si>
   <si>
-    <t>Paid Loss: 1.0150: CV_5yr=0.0112 (very tight). Exclude-high-low-5yr=1.0106; weighted-5yr=1.0132. All converge tightly. Late-maturity stabilization. Select at tight midpoint 1.0150.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0246: CV_5yr=0.0566. Exclude-high-low-5yr=1.0246; weighted-5yr=1.0645. Divergence suggests recent diagonals pulled upward; use conservative exclude-high-low-5yr (1.0246).</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0044: CV_5yr=0.0121 (tight). Exclude-high-low-5yr=1.0044; all averages converge near 1.0. Select 1.0044, minimal late-age development.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0173: CV_5yr=0.0237. Exclude-high-low-5yr=1.0136; weighted-5yr=1.0189. Slight upward drift but tight band. Select at 1.0173, conservative high-end of convergence for late development.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0167: CV_5yr=0.0235. Exclude-high-low-5yr=1.0167; tight convergence. Select 1.0167.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0017: CV_5yr=0.0123. Exclude-high-low-5yr=1.0017; minimal development. Select 1.0017.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0045: CV_5yr=0.0108. Exclude-high-low-5yr=1.0045; slight positive tail. Select 1.0045.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0063: CV_5yr=0.0114. Exclude-high-low-5yr=1.0063; tail emergence. Select 1.0063.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0157: CV_5yr=0.0103. Exclude-high-low-5yr=1.0124; weighted-5yr=1.0115. Slight upward presence. Select 1.0157 as conservative high-end for late-age development.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0012: CV_5yr=0.0031 (very tight). Exclude-high-low-5yr=1.0012; extreme tail. Select 1.0012.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0018: CV_5yr=0.0069. Exclude-high-low-5yr=1.0018; minimal development. Select 1.0018.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0000: All averages at 1.0. Tail closure. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0037: CV_5yr=0.0051. Exclude-high-low-5yr=1.0037; minimal tail. Select 1.0037.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0074: CV_5yr=0.0050. Exclude-high-low-5yr=1.0074; sparse tail data but consistent. Select 1.0074.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0076: All averages converge at 1.0076. Sparse tail. Select 1.0076.</t>
-  </si>
-  <si>
-    <t>Paid Loss: 1.0039: All averages at 1.0039. Single origin, extreme tail. Select 1.0039.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.1330: CV_5yr=0.0316; CV_3yr=0.0130 (both tight). Exclude-high-low-3yr=1.1414 vs weighted-5yr=1.1180 both stable. 3-yr (1.1330) is at tight convergence. Reported counts are sparse but consistent; no evidence of reporting surge beyond natural first-notification variance. Select 1.1330 (exclude-high-low-3yr-weighted average), balancing recent stability with early-age claim reporting lags.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0000: CV_5yr=0.0000; all averages converge at 1.0. Reporting plateau reached. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0005: CV_5yr=0.0019; extremely tight. Exclude-high-low-5yr=1.0; weighted-5yr=1.0008. Minimal post-initial-notification reporting. Select 1.0005 (simple average across tight band).</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0000: CV_5yr=0.0029; all averages essentially at 1.0. No material reporting development. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0000: CV_5yr=0.0017; all near 1.0. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0002: CV_5yr=0.0000; all averages at 1.0. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0000: CV_5yr=0.0019; all averages at 1.0. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0000: CV_5yr=0.0000; plateau. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0000: CV_5yr=0.0052; all near 1.0. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0000: CV_5yr=0.0000; all at 1.0. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0000: All averages at 1.0. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Reported Count: 1.0000: All at 1.0. Select 1.0.</t>
-  </si>
-  <si>
-    <t>Exposure</t>
+    <t>REPORTED FREQUENCY</t>
   </si>
   <si>
     <t>Sheet</t>
@@ -641,6 +564,12 @@
   </si>
   <si>
     <t>Exposure development triangle with age-to-age factors, averages, and selected LDFs.</t>
+  </si>
+  <si>
+    <t>Diagnostics</t>
+  </si>
+  <si>
+    <t>Post-selection diagnostic metrics including ultimate severity, loss rate, and frequency.</t>
   </si>
 </sst>
 </file>
@@ -695,7 +624,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -716,6 +645,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1012,7 +944,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -1021,18 +953,18 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1040,7 +972,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1048,7 +980,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1056,7 +988,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1064,15 +996,15 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1080,7 +1012,7 @@
         <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1088,7 +1020,7 @@
         <v>45</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1096,7 +1028,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1104,7 +1036,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1112,15 +1044,23 @@
         <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>192</v>
+        <v>136</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>204</v>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -1139,7 +1079,7 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B1" s="3">
         <v>11</v>
@@ -2512,81 +2452,81 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B28" s="6">
         <v>2.7399</v>
@@ -2661,7 +2601,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B29" s="6">
         <v>1.4304</v>
@@ -2734,7 +2674,7 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B30" s="6">
         <v>1.4452</v>
@@ -2805,7 +2745,7 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B31" s="6">
         <v>1.1416</v>
@@ -2874,7 +2814,7 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B32" s="6">
         <v>1.3029</v>
@@ -2941,7 +2881,7 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B33" s="6">
         <v>1.5119</v>
@@ -3006,7 +2946,7 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B34" s="6">
         <v>1.0888</v>
@@ -3069,7 +3009,7 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B35" s="6">
         <v>1.3857</v>
@@ -3130,7 +3070,7 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B36" s="6">
         <v>2.4408</v>
@@ -3189,7 +3129,7 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B37" s="6">
         <v>2.0292</v>
@@ -3246,7 +3186,7 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B38" s="6">
         <v>1.9534</v>
@@ -3301,7 +3241,7 @@
     </row>
     <row r="39" spans="1:25">
       <c r="A39" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B39" s="6">
         <v>2.0319</v>
@@ -3354,7 +3294,7 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B40" s="6">
         <v>1.8261</v>
@@ -3405,7 +3345,7 @@
     </row>
     <row r="41" spans="1:25">
       <c r="A41" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B41" s="6">
         <v>1.3662</v>
@@ -3454,7 +3394,7 @@
     </row>
     <row r="42" spans="1:25">
       <c r="A42" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B42" s="6">
         <v>1.9857</v>
@@ -3501,7 +3441,7 @@
     </row>
     <row r="43" spans="1:25">
       <c r="A43" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B43" s="6">
         <v>1.8697</v>
@@ -3546,7 +3486,7 @@
     </row>
     <row r="44" spans="1:25">
       <c r="A44" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B44" s="6">
         <v>1.3328</v>
@@ -3589,7 +3529,7 @@
     </row>
     <row r="45" spans="1:25">
       <c r="A45" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B45" s="6">
         <v>2.2994</v>
@@ -3630,7 +3570,7 @@
     </row>
     <row r="46" spans="1:25">
       <c r="A46" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B46" s="6">
         <v>2.757</v>
@@ -3669,7 +3609,7 @@
     </row>
     <row r="47" spans="1:25">
       <c r="A47" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B47" s="6">
         <v>1.7849</v>
@@ -3706,7 +3646,7 @@
     </row>
     <row r="48" spans="1:25">
       <c r="A48" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B48" s="6">
         <v>1.4577</v>
@@ -3741,7 +3681,7 @@
     </row>
     <row r="49" spans="1:25">
       <c r="A49" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B49" s="6">
         <v>1.2261</v>
@@ -3774,7 +3714,7 @@
     </row>
     <row r="50" spans="1:25">
       <c r="A50" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B50" s="6">
         <v>1.6941</v>
@@ -3805,7 +3745,7 @@
     </row>
     <row r="51" spans="1:25">
       <c r="A51" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -3834,84 +3774,84 @@
     </row>
     <row r="53" spans="1:25">
       <c r="A53" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="X53" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:25">
       <c r="A54" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B54" s="6">
         <v>1.7435</v>
@@ -3986,7 +3926,7 @@
     </row>
     <row r="55" spans="1:25">
       <c r="A55" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B55" s="6">
         <v>1.6135</v>
@@ -4061,7 +4001,7 @@
     </row>
     <row r="56" spans="1:25">
       <c r="A56" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B56" s="6">
         <v>1.7265</v>
@@ -4136,7 +4076,7 @@
     </row>
     <row r="57" spans="1:25">
       <c r="A57" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B57" s="6">
         <v>1.4593</v>
@@ -4211,7 +4151,7 @@
     </row>
     <row r="58" spans="1:25">
       <c r="A58" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B58" s="6">
         <v>1.4891</v>
@@ -4286,7 +4226,7 @@
     </row>
     <row r="59" spans="1:25">
       <c r="A59" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B59" s="6">
         <v>1.784</v>
@@ -4361,7 +4301,7 @@
     </row>
     <row r="60" spans="1:25">
       <c r="A60" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B60" s="6">
         <v>1.7024</v>
@@ -4436,7 +4376,7 @@
     </row>
     <row r="61" spans="1:25">
       <c r="A61" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B61" s="6">
         <v>1.6456</v>
@@ -4511,7 +4451,7 @@
     </row>
     <row r="62" spans="1:25">
       <c r="A62" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B62" s="6">
         <v>1.7774</v>
@@ -4586,7 +4526,7 @@
     </row>
     <row r="63" spans="1:25">
       <c r="A63" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B63" s="6">
         <v>1.7371</v>
@@ -4661,7 +4601,7 @@
     </row>
     <row r="64" spans="1:25">
       <c r="A64" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B64" s="6">
         <v>1.7238</v>
@@ -4736,226 +4676,134 @@
     </row>
     <row r="66" spans="1:25">
       <c r="A66" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q66" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="T66" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="V66" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="W66" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="X66" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67" spans="1:25">
       <c r="A67" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B67" s="6">
-        <v>1.514</v>
-      </c>
-      <c r="C67" s="6">
-        <v>1.1916</v>
-      </c>
-      <c r="D67" s="6">
-        <v>1.1507</v>
-      </c>
-      <c r="E67" s="6">
-        <v>1.0512</v>
-      </c>
-      <c r="F67" s="6">
-        <v>1.0569</v>
-      </c>
-      <c r="G67" s="6">
-        <v>1.0372</v>
-      </c>
-      <c r="H67" s="6">
-        <v>1.0153</v>
-      </c>
-      <c r="I67" s="6">
-        <v>1.0152</v>
-      </c>
-      <c r="J67" s="6">
-        <v>1.0228</v>
-      </c>
-      <c r="K67" s="6">
-        <v>1.0114</v>
-      </c>
-      <c r="L67" s="6">
-        <v>1.0242</v>
-      </c>
-      <c r="M67" s="6">
-        <v>1.004</v>
-      </c>
-      <c r="N67" s="6">
-        <v>1.0039</v>
-      </c>
-      <c r="O67" s="6">
-        <v>1.0075</v>
-      </c>
-      <c r="P67" s="6">
-        <v>1.006</v>
-      </c>
-      <c r="Q67" s="6">
-        <v>1.0114</v>
-      </c>
-      <c r="R67" s="6">
-        <v>1.0022</v>
-      </c>
-      <c r="S67" s="6">
-        <v>1</v>
-      </c>
-      <c r="T67" s="6">
-        <v>1</v>
-      </c>
-      <c r="U67" s="6">
-        <v>1.0139</v>
-      </c>
-      <c r="V67" s="6">
-        <v>1</v>
-      </c>
-      <c r="W67" s="6">
-        <v>1.0119</v>
-      </c>
-      <c r="X67" s="6">
-        <v>1.0119</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
+      <c r="M67" s="6"/>
+      <c r="N67" s="6"/>
+      <c r="O67" s="6"/>
+      <c r="P67" s="6"/>
+      <c r="Q67" s="6"/>
+      <c r="R67" s="6"/>
+      <c r="S67" s="6"/>
+      <c r="T67" s="6"/>
+      <c r="U67" s="6"/>
+      <c r="V67" s="6"/>
+      <c r="W67" s="6"/>
+      <c r="X67" s="6"/>
       <c r="Y67" s="6"/>
     </row>
     <row r="68" spans="1:25">
       <c r="A68" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J68" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="K68" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="L68" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="N68" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="O68" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="P68" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q68" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="R68" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="S68" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="T68" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="U68" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="V68" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="W68" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="X68" s="2" t="s">
-        <v>156</v>
-      </c>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="2"/>
+      <c r="S68" s="2"/>
+      <c r="T68" s="2"/>
+      <c r="U68" s="2"/>
+      <c r="V68" s="2"/>
+      <c r="W68" s="2"/>
+      <c r="X68" s="2"/>
       <c r="Y68" s="2"/>
     </row>
     <row r="70" spans="1:25">
@@ -5051,7 +4899,7 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B1" s="3">
         <v>11</v>
@@ -6424,81 +6272,81 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B28" s="6">
         <v>3.2124</v>
@@ -6573,7 +6421,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B29" s="6">
         <v>2.5494</v>
@@ -6646,7 +6494,7 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B30" s="6">
         <v>2.4837</v>
@@ -6717,7 +6565,7 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B31" s="6">
         <v>2.4368</v>
@@ -6786,7 +6634,7 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B32" s="6">
         <v>2.0311</v>
@@ -6853,7 +6701,7 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B33" s="6">
         <v>2.4565</v>
@@ -6918,7 +6766,7 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B34" s="6">
         <v>2.1908</v>
@@ -6981,7 +6829,7 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B35" s="6">
         <v>1.829</v>
@@ -7042,7 +6890,7 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B36" s="6">
         <v>3.246</v>
@@ -7101,7 +6949,7 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B37" s="6">
         <v>2.7631</v>
@@ -7158,7 +7006,7 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B38" s="6">
         <v>2.3046</v>
@@ -7213,7 +7061,7 @@
     </row>
     <row r="39" spans="1:25">
       <c r="A39" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B39" s="6">
         <v>2.7856</v>
@@ -7266,7 +7114,7 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B40" s="6">
         <v>2.3011</v>
@@ -7317,7 +7165,7 @@
     </row>
     <row r="41" spans="1:25">
       <c r="A41" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B41" s="6">
         <v>1.7931</v>
@@ -7366,7 +7214,7 @@
     </row>
     <row r="42" spans="1:25">
       <c r="A42" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B42" s="6">
         <v>2.2204</v>
@@ -7413,7 +7261,7 @@
     </row>
     <row r="43" spans="1:25">
       <c r="A43" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B43" s="6">
         <v>3.3152</v>
@@ -7458,7 +7306,7 @@
     </row>
     <row r="44" spans="1:25">
       <c r="A44" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B44" s="6">
         <v>1.7371</v>
@@ -7501,7 +7349,7 @@
     </row>
     <row r="45" spans="1:25">
       <c r="A45" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B45" s="6">
         <v>2.8751</v>
@@ -7542,7 +7390,7 @@
     </row>
     <row r="46" spans="1:25">
       <c r="A46" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B46" s="6">
         <v>2.6745</v>
@@ -7581,7 +7429,7 @@
     </row>
     <row r="47" spans="1:25">
       <c r="A47" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B47" s="6">
         <v>2.5535</v>
@@ -7618,7 +7466,7 @@
     </row>
     <row r="48" spans="1:25">
       <c r="A48" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B48" s="6">
         <v>1.9981</v>
@@ -7653,7 +7501,7 @@
     </row>
     <row r="49" spans="1:25">
       <c r="A49" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B49" s="6">
         <v>2.4294</v>
@@ -7686,7 +7534,7 @@
     </row>
     <row r="50" spans="1:25">
       <c r="A50" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B50" s="6">
         <v>3.2653</v>
@@ -7717,7 +7565,7 @@
     </row>
     <row r="51" spans="1:25">
       <c r="A51" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -7746,84 +7594,84 @@
     </row>
     <row r="53" spans="1:25">
       <c r="A53" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="X53" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:25">
       <c r="A54" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B54" s="6">
         <v>2.4979</v>
@@ -7898,7 +7746,7 @@
     </row>
     <row r="55" spans="1:25">
       <c r="A55" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B55" s="6">
         <v>2.4566</v>
@@ -7973,7 +7821,7 @@
     </row>
     <row r="56" spans="1:25">
       <c r="A56" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B56" s="6">
         <v>2.4952</v>
@@ -8048,7 +7896,7 @@
     </row>
     <row r="57" spans="1:25">
       <c r="A57" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B57" s="6">
         <v>2.5643</v>
@@ -8123,7 +7971,7 @@
     </row>
     <row r="58" spans="1:25">
       <c r="A58" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B58" s="6">
         <v>2.6286</v>
@@ -8198,7 +8046,7 @@
     </row>
     <row r="59" spans="1:25">
       <c r="A59" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B59" s="6">
         <v>2.5842</v>
@@ -8273,7 +8121,7 @@
     </row>
     <row r="60" spans="1:25">
       <c r="A60" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B60" s="6">
         <v>2.6232</v>
@@ -8348,7 +8196,7 @@
     </row>
     <row r="61" spans="1:25">
       <c r="A61" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B61" s="6">
         <v>2.5525</v>
@@ -8423,7 +8271,7 @@
     </row>
     <row r="62" spans="1:25">
       <c r="A62" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B62" s="6">
         <v>2.4862</v>
@@ -8498,7 +8346,7 @@
     </row>
     <row r="63" spans="1:25">
       <c r="A63" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B63" s="6">
         <v>2.482</v>
@@ -8573,7 +8421,7 @@
     </row>
     <row r="64" spans="1:25">
       <c r="A64" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B64" s="6">
         <v>2.4762</v>
@@ -8648,226 +8496,134 @@
     </row>
     <row r="66" spans="1:25">
       <c r="A66" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q66" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="T66" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="V66" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="W66" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="X66" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67" spans="1:25">
       <c r="A67" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B67" s="6">
-        <v>2.5525</v>
-      </c>
-      <c r="C67" s="6">
-        <v>1.4224</v>
-      </c>
-      <c r="D67" s="6">
-        <v>1.1864</v>
-      </c>
-      <c r="E67" s="6">
-        <v>1.0734</v>
-      </c>
-      <c r="F67" s="6">
-        <v>1.1077</v>
-      </c>
-      <c r="G67" s="6">
-        <v>1.063</v>
-      </c>
-      <c r="H67" s="6">
-        <v>1.0203</v>
-      </c>
-      <c r="I67" s="6">
-        <v>1.015</v>
-      </c>
-      <c r="J67" s="6">
-        <v>1.0246</v>
-      </c>
-      <c r="K67" s="6">
-        <v>1.0044</v>
-      </c>
-      <c r="L67" s="6">
-        <v>1.0173</v>
-      </c>
-      <c r="M67" s="6">
-        <v>1.0167</v>
-      </c>
-      <c r="N67" s="6">
-        <v>1.0017</v>
-      </c>
-      <c r="O67" s="6">
-        <v>1.0045</v>
-      </c>
-      <c r="P67" s="6">
-        <v>1.0063</v>
-      </c>
-      <c r="Q67" s="6">
-        <v>1.0157</v>
-      </c>
-      <c r="R67" s="6">
-        <v>1.0012</v>
-      </c>
-      <c r="S67" s="6">
-        <v>1.0018</v>
-      </c>
-      <c r="T67" s="6">
-        <v>1</v>
-      </c>
-      <c r="U67" s="6">
-        <v>1.0037</v>
-      </c>
-      <c r="V67" s="6">
-        <v>1.0074</v>
-      </c>
-      <c r="W67" s="6">
-        <v>1.0076</v>
-      </c>
-      <c r="X67" s="6">
-        <v>1.0039</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
+      <c r="M67" s="6"/>
+      <c r="N67" s="6"/>
+      <c r="O67" s="6"/>
+      <c r="P67" s="6"/>
+      <c r="Q67" s="6"/>
+      <c r="R67" s="6"/>
+      <c r="S67" s="6"/>
+      <c r="T67" s="6"/>
+      <c r="U67" s="6"/>
+      <c r="V67" s="6"/>
+      <c r="W67" s="6"/>
+      <c r="X67" s="6"/>
       <c r="Y67" s="6"/>
     </row>
     <row r="68" spans="1:25">
       <c r="A68" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="J68" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="K68" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="L68" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="N68" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="O68" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="P68" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q68" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="R68" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="S68" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="T68" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="U68" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="V68" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="W68" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="X68" s="2" t="s">
-        <v>179</v>
-      </c>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="2"/>
+      <c r="S68" s="2"/>
+      <c r="T68" s="2"/>
+      <c r="U68" s="2"/>
+      <c r="V68" s="2"/>
+      <c r="W68" s="2"/>
+      <c r="X68" s="2"/>
       <c r="Y68" s="2"/>
     </row>
     <row r="70" spans="1:25">
@@ -8963,7 +8719,7 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B1" s="3">
         <v>11</v>
@@ -10336,81 +10092,81 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B28" s="6">
         <v>1.0704</v>
@@ -10485,7 +10241,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B29" s="6">
         <v>1.0344</v>
@@ -10558,7 +10314,7 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B30" s="6">
         <v>1.0346</v>
@@ -10629,7 +10385,7 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B31" s="6">
         <v>1.0591</v>
@@ -10698,7 +10454,7 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B32" s="6">
         <v>1.0232</v>
@@ -10765,7 +10521,7 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B33" s="6">
         <v>1.0386</v>
@@ -10830,7 +10586,7 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B34" s="6">
         <v>1.0434</v>
@@ -10893,7 +10649,7 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B35" s="6">
         <v>1.0644</v>
@@ -10954,7 +10710,7 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B36" s="6">
         <v>1.0474</v>
@@ -11013,7 +10769,7 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B37" s="6">
         <v>1.0457</v>
@@ -11070,7 +10826,7 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B38" s="6">
         <v>1</v>
@@ -11125,7 +10881,7 @@
     </row>
     <row r="39" spans="1:25">
       <c r="A39" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B39" s="6">
         <v>1.0645</v>
@@ -11178,7 +10934,7 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B40" s="6">
         <v>1.028</v>
@@ -11229,7 +10985,7 @@
     </row>
     <row r="41" spans="1:25">
       <c r="A41" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B41" s="6">
         <v>1.0456</v>
@@ -11278,7 +11034,7 @@
     </row>
     <row r="42" spans="1:25">
       <c r="A42" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B42" s="6">
         <v>1.0328</v>
@@ -11325,7 +11081,7 @@
     </row>
     <row r="43" spans="1:25">
       <c r="A43" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B43" s="6">
         <v>1.0802</v>
@@ -11370,7 +11126,7 @@
     </row>
     <row r="44" spans="1:25">
       <c r="A44" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B44" s="6">
         <v>1.1244</v>
@@ -11413,7 +11169,7 @@
     </row>
     <row r="45" spans="1:25">
       <c r="A45" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B45" s="6">
         <v>1.1233</v>
@@ -11454,7 +11210,7 @@
     </row>
     <row r="46" spans="1:25">
       <c r="A46" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B46" s="6">
         <v>1.1429</v>
@@ -11493,7 +11249,7 @@
     </row>
     <row r="47" spans="1:25">
       <c r="A47" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B47" s="6">
         <v>1.0604</v>
@@ -11530,7 +11286,7 @@
     </row>
     <row r="48" spans="1:25">
       <c r="A48" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B48" s="6">
         <v>1.1416</v>
@@ -11565,7 +11321,7 @@
     </row>
     <row r="49" spans="1:25">
       <c r="A49" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B49" s="6">
         <v>1.1414</v>
@@ -11598,7 +11354,7 @@
     </row>
     <row r="50" spans="1:25">
       <c r="A50" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B50" s="6">
         <v>1.1159</v>
@@ -11629,7 +11385,7 @@
     </row>
     <row r="51" spans="1:25">
       <c r="A51" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -11658,84 +11414,84 @@
     </row>
     <row r="53" spans="1:25">
       <c r="A53" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="X53" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:25">
       <c r="A54" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B54" s="6">
         <v>1.0679</v>
@@ -11810,7 +11566,7 @@
     </row>
     <row r="55" spans="1:25">
       <c r="A55" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B55" s="6">
         <v>1.0617</v>
@@ -11885,7 +11641,7 @@
     </row>
     <row r="56" spans="1:25">
       <c r="A56" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B56" s="6">
         <v>1.0676</v>
@@ -11960,7 +11716,7 @@
     </row>
     <row r="57" spans="1:25">
       <c r="A57" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B57" s="6">
         <v>1.133</v>
@@ -12035,7 +11791,7 @@
     </row>
     <row r="58" spans="1:25">
       <c r="A58" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B58" s="6">
         <v>1.133</v>
@@ -12110,7 +11866,7 @@
     </row>
     <row r="59" spans="1:25">
       <c r="A59" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B59" s="6">
         <v>1.1204</v>
@@ -12185,7 +11941,7 @@
     </row>
     <row r="60" spans="1:25">
       <c r="A60" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B60" s="6">
         <v>1.118</v>
@@ -12260,7 +12016,7 @@
     </row>
     <row r="61" spans="1:25">
       <c r="A61" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B61" s="6">
         <v>1.133</v>
@@ -12335,7 +12091,7 @@
     </row>
     <row r="62" spans="1:25">
       <c r="A62" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B62" s="6">
         <v>1.1009</v>
@@ -12410,7 +12166,7 @@
     </row>
     <row r="63" spans="1:25">
       <c r="A63" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B63" s="6">
         <v>1.0962</v>
@@ -12485,7 +12241,7 @@
     </row>
     <row r="64" spans="1:25">
       <c r="A64" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B64" s="6">
         <v>1.1041</v>
@@ -12560,226 +12316,134 @@
     </row>
     <row r="66" spans="1:25">
       <c r="A66" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q66" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="T66" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="V66" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="W66" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="X66" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67" spans="1:25">
       <c r="A67" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B67" s="6">
-        <v>1.133</v>
-      </c>
-      <c r="C67" s="6">
-        <v>1</v>
-      </c>
-      <c r="D67" s="6">
-        <v>1.0005</v>
-      </c>
-      <c r="E67" s="6">
-        <v>1</v>
-      </c>
-      <c r="F67" s="6">
-        <v>1</v>
-      </c>
-      <c r="G67" s="6">
-        <v>1.0002</v>
-      </c>
-      <c r="H67" s="6">
-        <v>1</v>
-      </c>
-      <c r="I67" s="6">
-        <v>1</v>
-      </c>
-      <c r="J67" s="6">
-        <v>1</v>
-      </c>
-      <c r="K67" s="6">
-        <v>1</v>
-      </c>
-      <c r="L67" s="6">
-        <v>1</v>
-      </c>
-      <c r="M67" s="6">
-        <v>1</v>
-      </c>
-      <c r="N67" s="6">
-        <v>1</v>
-      </c>
-      <c r="O67" s="6">
-        <v>1</v>
-      </c>
-      <c r="P67" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q67" s="6">
-        <v>1</v>
-      </c>
-      <c r="R67" s="6">
-        <v>1</v>
-      </c>
-      <c r="S67" s="6">
-        <v>1</v>
-      </c>
-      <c r="T67" s="6">
-        <v>1</v>
-      </c>
-      <c r="U67" s="6">
-        <v>1</v>
-      </c>
-      <c r="V67" s="6">
-        <v>1</v>
-      </c>
-      <c r="W67" s="6">
-        <v>1</v>
-      </c>
-      <c r="X67" s="6">
-        <v>1</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
+      <c r="M67" s="6"/>
+      <c r="N67" s="6"/>
+      <c r="O67" s="6"/>
+      <c r="P67" s="6"/>
+      <c r="Q67" s="6"/>
+      <c r="R67" s="6"/>
+      <c r="S67" s="6"/>
+      <c r="T67" s="6"/>
+      <c r="U67" s="6"/>
+      <c r="V67" s="6"/>
+      <c r="W67" s="6"/>
+      <c r="X67" s="6"/>
       <c r="Y67" s="6"/>
     </row>
     <row r="68" spans="1:25">
       <c r="A68" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="J68" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="K68" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="L68" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="N68" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="O68" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="P68" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q68" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="R68" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="S68" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="T68" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="U68" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="V68" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="W68" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="X68" s="2" t="s">
-        <v>191</v>
-      </c>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="2"/>
+      <c r="S68" s="2"/>
+      <c r="T68" s="2"/>
+      <c r="U68" s="2"/>
+      <c r="V68" s="2"/>
+      <c r="W68" s="2"/>
+      <c r="X68" s="2"/>
       <c r="Y68" s="2"/>
     </row>
     <row r="70" spans="1:25">
@@ -12874,10 +12538,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>192</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -13073,6 +12737,6784 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Y161"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="2" max="25" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25">
+      <c r="A1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+    </row>
+    <row r="2" spans="1:25">
+      <c r="A2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="V2" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="W2" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="X2" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="Y2" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
+      <c r="A3" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="5">
+        <v>890.1180000000001</v>
+      </c>
+      <c r="C3" s="5">
+        <v>2278.4062</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2782.9421</v>
+      </c>
+      <c r="E3" s="5">
+        <v>3062.5888</v>
+      </c>
+      <c r="F3" s="5">
+        <v>3292.6042</v>
+      </c>
+      <c r="G3" s="5">
+        <v>3515.439</v>
+      </c>
+      <c r="H3" s="5">
+        <v>3421.3038</v>
+      </c>
+      <c r="I3" s="5">
+        <v>3453.2106</v>
+      </c>
+      <c r="J3" s="5">
+        <v>3478.3519</v>
+      </c>
+      <c r="K3" s="5">
+        <v>3507.6464</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3582.8588</v>
+      </c>
+      <c r="M3" s="5">
+        <v>3657.3908</v>
+      </c>
+      <c r="N3" s="5">
+        <v>3653.4369</v>
+      </c>
+      <c r="O3" s="5">
+        <v>3736.9976</v>
+      </c>
+      <c r="P3" s="5">
+        <v>3800.6836</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>4002.7778</v>
+      </c>
+      <c r="R3" s="5">
+        <v>4097.3409</v>
+      </c>
+      <c r="S3" s="5">
+        <v>4224.0147</v>
+      </c>
+      <c r="T3" s="5">
+        <v>4299.9339</v>
+      </c>
+      <c r="U3" s="5">
+        <v>4299.9339</v>
+      </c>
+      <c r="V3" s="5">
+        <v>4400.6872</v>
+      </c>
+      <c r="W3" s="5">
+        <v>4461.8925</v>
+      </c>
+      <c r="X3" s="5">
+        <v>4461.8925</v>
+      </c>
+      <c r="Y3" s="5">
+        <v>4515.1126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
+      <c r="A4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" s="5">
+        <v>1512.0882</v>
+      </c>
+      <c r="C4" s="5">
+        <v>2090.9875</v>
+      </c>
+      <c r="D4" s="5">
+        <v>2115.5884</v>
+      </c>
+      <c r="E4" s="5">
+        <v>2527.4532</v>
+      </c>
+      <c r="F4" s="5">
+        <v>2560.7772</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2649.7009</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2700.0288</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2700.5895</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2759.7609</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2786.3555</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2814.9283</v>
+      </c>
+      <c r="M4" s="5">
+        <v>2910.4049</v>
+      </c>
+      <c r="N4" s="5">
+        <v>2914.2643</v>
+      </c>
+      <c r="O4" s="5">
+        <v>3031.1417</v>
+      </c>
+      <c r="P4" s="5">
+        <v>3111.0506</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>3156.834</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3323.8277</v>
+      </c>
+      <c r="S4" s="5">
+        <v>3327.6029</v>
+      </c>
+      <c r="T4" s="5">
+        <v>3327.6029</v>
+      </c>
+      <c r="U4" s="5">
+        <v>3468.5593</v>
+      </c>
+      <c r="V4" s="5">
+        <v>3447.0276</v>
+      </c>
+      <c r="W4" s="5">
+        <v>3570.7879</v>
+      </c>
+      <c r="X4" s="5">
+        <v>3570.7879</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
+      <c r="A5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" s="5">
+        <v>1888.6444</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2638.2005</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2855.6611</v>
+      </c>
+      <c r="E5" s="5">
+        <v>3394.6267</v>
+      </c>
+      <c r="F5" s="5">
+        <v>3095.9768</v>
+      </c>
+      <c r="G5" s="5">
+        <v>3306.0384</v>
+      </c>
+      <c r="H5" s="5">
+        <v>3289.0123</v>
+      </c>
+      <c r="I5" s="5">
+        <v>3264.184</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3258.0917</v>
+      </c>
+      <c r="K5" s="5">
+        <v>3265.2436</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3258.4234</v>
+      </c>
+      <c r="M5" s="5">
+        <v>3233.217</v>
+      </c>
+      <c r="N5" s="5">
+        <v>3216.7392</v>
+      </c>
+      <c r="O5" s="5">
+        <v>3216.7391</v>
+      </c>
+      <c r="P5" s="5">
+        <v>3216.7391</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>3216.7391</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3223.5583</v>
+      </c>
+      <c r="S5" s="5">
+        <v>3223.5583</v>
+      </c>
+      <c r="T5" s="5">
+        <v>3223.5583</v>
+      </c>
+      <c r="U5" s="5">
+        <v>3223.5583</v>
+      </c>
+      <c r="V5" s="5">
+        <v>3223.5583</v>
+      </c>
+      <c r="W5" s="5">
+        <v>3223.5583</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
+      <c r="A6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" s="5">
+        <v>1172.3435</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1263.6591</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1395.2806</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1455.3763</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1641.8764</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1650.9895</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1681.4597</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1694.3798</v>
+      </c>
+      <c r="J6" s="5">
+        <v>1734.6258</v>
+      </c>
+      <c r="K6" s="5">
+        <v>1719.1458</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1758.8212</v>
+      </c>
+      <c r="M6" s="5">
+        <v>1738.9466</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1739.6468</v>
+      </c>
+      <c r="O6" s="5">
+        <v>1740.152</v>
+      </c>
+      <c r="P6" s="5">
+        <v>1740.151</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>1746.8131</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1746.8131</v>
+      </c>
+      <c r="S6" s="5">
+        <v>1746.8131</v>
+      </c>
+      <c r="T6" s="5">
+        <v>1746.8131</v>
+      </c>
+      <c r="U6" s="5">
+        <v>1746.8655</v>
+      </c>
+      <c r="V6" s="5">
+        <v>1746.8655</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" s="5">
+        <v>1993.7326</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2538.8382</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2768.881</v>
+      </c>
+      <c r="E7" s="5">
+        <v>2706.5528</v>
+      </c>
+      <c r="F7" s="5">
+        <v>2807.1297</v>
+      </c>
+      <c r="G7" s="5">
+        <v>2852.9634</v>
+      </c>
+      <c r="H7" s="5">
+        <v>2911.0234</v>
+      </c>
+      <c r="I7" s="5">
+        <v>2927.4654</v>
+      </c>
+      <c r="J7" s="5">
+        <v>2965.2737</v>
+      </c>
+      <c r="K7" s="5">
+        <v>3046.2327</v>
+      </c>
+      <c r="L7" s="5">
+        <v>3081.9362</v>
+      </c>
+      <c r="M7" s="5">
+        <v>3449.9444</v>
+      </c>
+      <c r="N7" s="5">
+        <v>3449.963</v>
+      </c>
+      <c r="O7" s="5">
+        <v>3386.3438</v>
+      </c>
+      <c r="P7" s="5">
+        <v>3420.0517</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>3443.969</v>
+      </c>
+      <c r="R7" s="5">
+        <v>3496.1167</v>
+      </c>
+      <c r="S7" s="5">
+        <v>3496.1167</v>
+      </c>
+      <c r="T7" s="5">
+        <v>3496.1167</v>
+      </c>
+      <c r="U7" s="5">
+        <v>3496.1167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
+      <c r="A8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="5">
+        <v>1599.0849</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2327.8896</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2023.4351</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2163.9389</v>
+      </c>
+      <c r="F8" s="5">
+        <v>2183.4454</v>
+      </c>
+      <c r="G8" s="5">
+        <v>2293.584</v>
+      </c>
+      <c r="H8" s="5">
+        <v>2394.6572</v>
+      </c>
+      <c r="I8" s="5">
+        <v>2350.5597</v>
+      </c>
+      <c r="J8" s="5">
+        <v>2411.7895</v>
+      </c>
+      <c r="K8" s="5">
+        <v>2501.2918</v>
+      </c>
+      <c r="L8" s="5">
+        <v>2709.3077</v>
+      </c>
+      <c r="M8" s="5">
+        <v>2872.1777</v>
+      </c>
+      <c r="N8" s="5">
+        <v>2951.2085</v>
+      </c>
+      <c r="O8" s="5">
+        <v>2982.9877</v>
+      </c>
+      <c r="P8" s="5">
+        <v>2984.7119</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>3019.1946</v>
+      </c>
+      <c r="R8" s="5">
+        <v>3028.4784</v>
+      </c>
+      <c r="S8" s="5">
+        <v>3050.5924</v>
+      </c>
+      <c r="T8" s="5">
+        <v>3050.5924</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
+      <c r="A9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="5">
+        <v>3777.3245</v>
+      </c>
+      <c r="C9" s="5">
+        <v>3941.769</v>
+      </c>
+      <c r="D9" s="5">
+        <v>4293.0553</v>
+      </c>
+      <c r="E9" s="5">
+        <v>4810.1306</v>
+      </c>
+      <c r="F9" s="5">
+        <v>5361.7176</v>
+      </c>
+      <c r="G9" s="5">
+        <v>6400.5666</v>
+      </c>
+      <c r="H9" s="5">
+        <v>6807.7258</v>
+      </c>
+      <c r="I9" s="5">
+        <v>7553.3299</v>
+      </c>
+      <c r="J9" s="5">
+        <v>8094.4377</v>
+      </c>
+      <c r="K9" s="5">
+        <v>8917.1247</v>
+      </c>
+      <c r="L9" s="5">
+        <v>9190.731299999999</v>
+      </c>
+      <c r="M9" s="5">
+        <v>9456.272800000001</v>
+      </c>
+      <c r="N9" s="5">
+        <v>9608.6579</v>
+      </c>
+      <c r="O9" s="5">
+        <v>9617.6212</v>
+      </c>
+      <c r="P9" s="5">
+        <v>10037.1822</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>10037.1822</v>
+      </c>
+      <c r="R9" s="5">
+        <v>10073.235</v>
+      </c>
+      <c r="S9" s="5">
+        <v>10098.7007</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
+      <c r="A10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="5">
+        <v>1809.473</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2355.6596</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2839.9925</v>
+      </c>
+      <c r="E10" s="5">
+        <v>3950.3476</v>
+      </c>
+      <c r="F10" s="5">
+        <v>3828.9536</v>
+      </c>
+      <c r="G10" s="5">
+        <v>3893.4618</v>
+      </c>
+      <c r="H10" s="5">
+        <v>3914.5485</v>
+      </c>
+      <c r="I10" s="5">
+        <v>3966.0723</v>
+      </c>
+      <c r="J10" s="5">
+        <v>3988.739</v>
+      </c>
+      <c r="K10" s="5">
+        <v>4127.0241</v>
+      </c>
+      <c r="L10" s="5">
+        <v>4147.332</v>
+      </c>
+      <c r="M10" s="5">
+        <v>4148.0168</v>
+      </c>
+      <c r="N10" s="5">
+        <v>4087.6122</v>
+      </c>
+      <c r="O10" s="5">
+        <v>4088.6162</v>
+      </c>
+      <c r="P10" s="5">
+        <v>4088.6162</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>4108.6965</v>
+      </c>
+      <c r="R10" s="5">
+        <v>4195.1009</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" s="5">
+        <v>1167.6749</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2721.0436</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2553.6801</v>
+      </c>
+      <c r="E11" s="5">
+        <v>2617.3913</v>
+      </c>
+      <c r="F11" s="5">
+        <v>2791.3361</v>
+      </c>
+      <c r="G11" s="5">
+        <v>2934.6002</v>
+      </c>
+      <c r="H11" s="5">
+        <v>3041.3852</v>
+      </c>
+      <c r="I11" s="5">
+        <v>3479.5492</v>
+      </c>
+      <c r="J11" s="5">
+        <v>3479.5697</v>
+      </c>
+      <c r="K11" s="5">
+        <v>3479.575</v>
+      </c>
+      <c r="L11" s="5">
+        <v>3479.575</v>
+      </c>
+      <c r="M11" s="5">
+        <v>3526.7061</v>
+      </c>
+      <c r="N11" s="5">
+        <v>3632.438</v>
+      </c>
+      <c r="O11" s="5">
+        <v>3632.438</v>
+      </c>
+      <c r="P11" s="5">
+        <v>3632.438</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>3632.438</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="A12" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="5">
+        <v>1384.9391</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2687.5986</v>
+      </c>
+      <c r="D12" s="5">
+        <v>3499.5972</v>
+      </c>
+      <c r="E12" s="5">
+        <v>4066.1699</v>
+      </c>
+      <c r="F12" s="5">
+        <v>4547.5156</v>
+      </c>
+      <c r="G12" s="5">
+        <v>4498.6408</v>
+      </c>
+      <c r="H12" s="5">
+        <v>4676.9369</v>
+      </c>
+      <c r="I12" s="5">
+        <v>4682.4417</v>
+      </c>
+      <c r="J12" s="5">
+        <v>4660.2165</v>
+      </c>
+      <c r="K12" s="5">
+        <v>4663.1575</v>
+      </c>
+      <c r="L12" s="5">
+        <v>4666.8177</v>
+      </c>
+      <c r="M12" s="5">
+        <v>4667.0895</v>
+      </c>
+      <c r="N12" s="5">
+        <v>4673.1575</v>
+      </c>
+      <c r="O12" s="5">
+        <v>4672.1618</v>
+      </c>
+      <c r="P12" s="5">
+        <v>4700.13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="A13" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1313.2806</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2565.3152</v>
+      </c>
+      <c r="D13" s="5">
+        <v>3783.2939</v>
+      </c>
+      <c r="E13" s="5">
+        <v>4368.5282</v>
+      </c>
+      <c r="F13" s="5">
+        <v>4661.1947</v>
+      </c>
+      <c r="G13" s="5">
+        <v>5034.2137</v>
+      </c>
+      <c r="H13" s="5">
+        <v>5312.4542</v>
+      </c>
+      <c r="I13" s="5">
+        <v>5312.7876</v>
+      </c>
+      <c r="J13" s="5">
+        <v>5386.0395</v>
+      </c>
+      <c r="K13" s="5">
+        <v>5406.7113</v>
+      </c>
+      <c r="L13" s="5">
+        <v>5559.1271</v>
+      </c>
+      <c r="M13" s="5">
+        <v>5542.0495</v>
+      </c>
+      <c r="N13" s="5">
+        <v>5542.0495</v>
+      </c>
+      <c r="O13" s="5">
+        <v>5542.0495</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
+      <c r="A14" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="5">
+        <v>1368.4788</v>
+      </c>
+      <c r="C14" s="5">
+        <v>2612.096</v>
+      </c>
+      <c r="D14" s="5">
+        <v>3413.9935</v>
+      </c>
+      <c r="E14" s="5">
+        <v>3710.1818</v>
+      </c>
+      <c r="F14" s="5">
+        <v>3698.5859</v>
+      </c>
+      <c r="G14" s="5">
+        <v>3730.9798</v>
+      </c>
+      <c r="H14" s="5">
+        <v>3745.9265</v>
+      </c>
+      <c r="I14" s="5">
+        <v>3939.0426</v>
+      </c>
+      <c r="J14" s="5">
+        <v>4159.1215</v>
+      </c>
+      <c r="K14" s="5">
+        <v>4394.3121</v>
+      </c>
+      <c r="L14" s="5">
+        <v>4427.1404</v>
+      </c>
+      <c r="M14" s="5">
+        <v>5219.4933</v>
+      </c>
+      <c r="N14" s="5">
+        <v>5219.4933</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
+      <c r="A15" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="5">
+        <v>988.3224</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1755.5463</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1908.7091</v>
+      </c>
+      <c r="E15" s="5">
+        <v>2290.7285</v>
+      </c>
+      <c r="F15" s="5">
+        <v>2429.9367</v>
+      </c>
+      <c r="G15" s="5">
+        <v>2423.6216</v>
+      </c>
+      <c r="H15" s="5">
+        <v>2424.8165</v>
+      </c>
+      <c r="I15" s="5">
+        <v>2424.8165</v>
+      </c>
+      <c r="J15" s="5">
+        <v>2429.4993</v>
+      </c>
+      <c r="K15" s="5">
+        <v>2429.4993</v>
+      </c>
+      <c r="L15" s="5">
+        <v>2429.5378</v>
+      </c>
+      <c r="M15" s="5">
+        <v>2429.5378</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
+      <c r="A16" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16" s="5">
+        <v>1334.6909</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1743.9971</v>
+      </c>
+      <c r="D16" s="5">
+        <v>2454.6058</v>
+      </c>
+      <c r="E16" s="5">
+        <v>2838.1826</v>
+      </c>
+      <c r="F16" s="5">
+        <v>2878.7598</v>
+      </c>
+      <c r="G16" s="5">
+        <v>2977.9598</v>
+      </c>
+      <c r="H16" s="5">
+        <v>2892.6972</v>
+      </c>
+      <c r="I16" s="5">
+        <v>2892.6972</v>
+      </c>
+      <c r="J16" s="5">
+        <v>3011.5377</v>
+      </c>
+      <c r="K16" s="5">
+        <v>3073.6631</v>
+      </c>
+      <c r="L16" s="5">
+        <v>3052.3164</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
+      <c r="A17" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B17" s="5">
+        <v>1671.1066</v>
+      </c>
+      <c r="C17" s="5">
+        <v>3212.9841</v>
+      </c>
+      <c r="D17" s="5">
+        <v>4752.8672</v>
+      </c>
+      <c r="E17" s="5">
+        <v>6314.127</v>
+      </c>
+      <c r="F17" s="5">
+        <v>6982.9534</v>
+      </c>
+      <c r="G17" s="5">
+        <v>7934.0749</v>
+      </c>
+      <c r="H17" s="5">
+        <v>9044.3287</v>
+      </c>
+      <c r="I17" s="5">
+        <v>9105.656800000001</v>
+      </c>
+      <c r="J17" s="5">
+        <v>9135.714599999999</v>
+      </c>
+      <c r="K17" s="5">
+        <v>10132.9162</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
+      <c r="A18" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" s="5">
+        <v>1989.3893</v>
+      </c>
+      <c r="C18" s="5">
+        <v>3443.4912</v>
+      </c>
+      <c r="D18" s="5">
+        <v>4437.949</v>
+      </c>
+      <c r="E18" s="5">
+        <v>4824.0141</v>
+      </c>
+      <c r="F18" s="5">
+        <v>5510.515</v>
+      </c>
+      <c r="G18" s="5">
+        <v>5684.6093</v>
+      </c>
+      <c r="H18" s="5">
+        <v>6409.6524</v>
+      </c>
+      <c r="I18" s="5">
+        <v>6408.127</v>
+      </c>
+      <c r="J18" s="5">
+        <v>6416.5729</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
+      <c r="A19" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" s="5">
+        <v>1672.7081</v>
+      </c>
+      <c r="C19" s="5">
+        <v>1982.7823</v>
+      </c>
+      <c r="D19" s="5">
+        <v>2042.2188</v>
+      </c>
+      <c r="E19" s="5">
+        <v>2662.7754</v>
+      </c>
+      <c r="F19" s="5">
+        <v>2874.8102</v>
+      </c>
+      <c r="G19" s="5">
+        <v>3256.3421</v>
+      </c>
+      <c r="H19" s="5">
+        <v>3753.5543</v>
+      </c>
+      <c r="I19" s="5">
+        <v>3888.386</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
+      <c r="A20" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" s="5">
+        <v>1757.7757</v>
+      </c>
+      <c r="C20" s="5">
+        <v>3598.2446</v>
+      </c>
+      <c r="D20" s="5">
+        <v>5140.9339</v>
+      </c>
+      <c r="E20" s="5">
+        <v>7136.9854</v>
+      </c>
+      <c r="F20" s="5">
+        <v>7067.2812</v>
+      </c>
+      <c r="G20" s="5">
+        <v>7159.8047</v>
+      </c>
+      <c r="H20" s="5">
+        <v>7349.3269</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
+      <c r="A21" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="5">
+        <v>1298.8238</v>
+      </c>
+      <c r="C21" s="5">
+        <v>3133.2107</v>
+      </c>
+      <c r="D21" s="5">
+        <v>4847.8776</v>
+      </c>
+      <c r="E21" s="5">
+        <v>5573.6672</v>
+      </c>
+      <c r="F21" s="5">
+        <v>5926.9818</v>
+      </c>
+      <c r="G21" s="5">
+        <v>7270.1301</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
+      <c r="A22" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B22" s="5">
+        <v>1493.0271</v>
+      </c>
+      <c r="C22" s="5">
+        <v>2513.205</v>
+      </c>
+      <c r="D22" s="5">
+        <v>2471.0707</v>
+      </c>
+      <c r="E22" s="5">
+        <v>2614.478</v>
+      </c>
+      <c r="F22" s="5">
+        <v>2639.9122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
+      <c r="A23" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" s="5">
+        <v>1901.2855</v>
+      </c>
+      <c r="C23" s="5">
+        <v>2427.8119</v>
+      </c>
+      <c r="D23" s="5">
+        <v>2971.5574</v>
+      </c>
+      <c r="E23" s="5">
+        <v>3065.5146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
+      <c r="A24" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B24" s="5">
+        <v>2658.5306</v>
+      </c>
+      <c r="C24" s="5">
+        <v>2855.7054</v>
+      </c>
+      <c r="D24" s="5">
+        <v>2774.4265</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
+      <c r="A25" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B25" s="5">
+        <v>3569.3743</v>
+      </c>
+      <c r="C25" s="5">
+        <v>5418.6585</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
+      <c r="A26" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" s="5">
+        <v>3477.1362</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
+      <c r="A28" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
+    </row>
+    <row r="29" spans="1:25">
+      <c r="A29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N29" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="O29" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="P29" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q29" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="R29" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="S29" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="T29" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="U29" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="V29" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="W29" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="X29" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="Y29" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
+      <c r="A30" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" s="6">
+        <v>0.5747</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.6738</v>
+      </c>
+      <c r="D30" s="6">
+        <v>0.8126</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.9127999999999999</v>
+      </c>
+      <c r="F30" s="6">
+        <v>0.9882</v>
+      </c>
+      <c r="G30" s="6">
+        <v>0.9504</v>
+      </c>
+      <c r="H30" s="6">
+        <v>0.9435</v>
+      </c>
+      <c r="I30" s="6">
+        <v>0.9474</v>
+      </c>
+      <c r="J30" s="6">
+        <v>0.9496</v>
+      </c>
+      <c r="K30" s="6">
+        <v>0.953</v>
+      </c>
+      <c r="L30" s="6">
+        <v>0.9553</v>
+      </c>
+      <c r="M30" s="6">
+        <v>0.9582000000000001</v>
+      </c>
+      <c r="N30" s="6">
+        <v>0.9749</v>
+      </c>
+      <c r="O30" s="6">
+        <v>0.9772999999999999</v>
+      </c>
+      <c r="P30" s="6">
+        <v>0.9816</v>
+      </c>
+      <c r="Q30" s="6">
+        <v>0.9606</v>
+      </c>
+      <c r="R30" s="6">
+        <v>0.9691</v>
+      </c>
+      <c r="S30" s="6">
+        <v>0.9655</v>
+      </c>
+      <c r="T30" s="6">
+        <v>0.9848</v>
+      </c>
+      <c r="U30" s="6">
+        <v>0.9848</v>
+      </c>
+      <c r="V30" s="6">
+        <v>0.9694</v>
+      </c>
+      <c r="W30" s="6">
+        <v>0.9631999999999999</v>
+      </c>
+      <c r="X30" s="6">
+        <v>0.9693000000000001</v>
+      </c>
+      <c r="Y30" s="6">
+        <v>0.9616</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25">
+      <c r="A31" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" s="6">
+        <v>0.3852</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.6865</v>
+      </c>
+      <c r="D31" s="6">
+        <v>0.9088000000000001</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.8218</v>
+      </c>
+      <c r="F31" s="6">
+        <v>0.9127</v>
+      </c>
+      <c r="G31" s="6">
+        <v>0.9389</v>
+      </c>
+      <c r="H31" s="6">
+        <v>0.9422</v>
+      </c>
+      <c r="I31" s="6">
+        <v>0.9587</v>
+      </c>
+      <c r="J31" s="6">
+        <v>0.9614</v>
+      </c>
+      <c r="K31" s="6">
+        <v>0.9636</v>
+      </c>
+      <c r="L31" s="6">
+        <v>0.9706</v>
+      </c>
+      <c r="M31" s="6">
+        <v>0.9563</v>
+      </c>
+      <c r="N31" s="6">
+        <v>0.977</v>
+      </c>
+      <c r="O31" s="6">
+        <v>0.9633</v>
+      </c>
+      <c r="P31" s="6">
+        <v>0.9584</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>0.9629</v>
+      </c>
+      <c r="R31" s="6">
+        <v>0.9406</v>
+      </c>
+      <c r="S31" s="6">
+        <v>0.9585</v>
+      </c>
+      <c r="T31" s="6">
+        <v>0.9737</v>
+      </c>
+      <c r="U31" s="6">
+        <v>0.9455</v>
+      </c>
+      <c r="V31" s="6">
+        <v>0.961</v>
+      </c>
+      <c r="W31" s="6">
+        <v>0.9366</v>
+      </c>
+      <c r="X31" s="6">
+        <v>0.945</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25">
+      <c r="A32" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32" s="6">
+        <v>0.4594</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.7896</v>
+      </c>
+      <c r="D32" s="6">
+        <v>0.8421</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.7722</v>
+      </c>
+      <c r="F32" s="6">
+        <v>0.9843</v>
+      </c>
+      <c r="G32" s="6">
+        <v>0.9677</v>
+      </c>
+      <c r="H32" s="6">
+        <v>0.9718</v>
+      </c>
+      <c r="I32" s="6">
+        <v>0.9861</v>
+      </c>
+      <c r="J32" s="6">
+        <v>0.9865</v>
+      </c>
+      <c r="K32" s="6">
+        <v>0.9867</v>
+      </c>
+      <c r="L32" s="6">
+        <v>0.9869</v>
+      </c>
+      <c r="M32" s="6">
+        <v>0.9948</v>
+      </c>
+      <c r="N32" s="6">
+        <v>1</v>
+      </c>
+      <c r="O32" s="6">
+        <v>1</v>
+      </c>
+      <c r="P32" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="6">
+        <v>1</v>
+      </c>
+      <c r="R32" s="6">
+        <v>1</v>
+      </c>
+      <c r="S32" s="6">
+        <v>1</v>
+      </c>
+      <c r="T32" s="6">
+        <v>1</v>
+      </c>
+      <c r="U32" s="6">
+        <v>1</v>
+      </c>
+      <c r="V32" s="6">
+        <v>1</v>
+      </c>
+      <c r="W32" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
+      <c r="A33" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" s="6">
+        <v>0.3634</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.7756</v>
+      </c>
+      <c r="D33" s="6">
+        <v>0.9055</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.9681</v>
+      </c>
+      <c r="F33" s="6">
+        <v>1</v>
+      </c>
+      <c r="G33" s="6">
+        <v>0.9981</v>
+      </c>
+      <c r="H33" s="6">
+        <v>0.996</v>
+      </c>
+      <c r="I33" s="6">
+        <v>0.9961</v>
+      </c>
+      <c r="J33" s="6">
+        <v>0.991</v>
+      </c>
+      <c r="K33" s="6">
+        <v>0.9938</v>
+      </c>
+      <c r="L33" s="6">
+        <v>0.9748</v>
+      </c>
+      <c r="M33" s="6">
+        <v>0.9923</v>
+      </c>
+      <c r="N33" s="6">
+        <v>0.9923</v>
+      </c>
+      <c r="O33" s="6">
+        <v>0.9938</v>
+      </c>
+      <c r="P33" s="6">
+        <v>0.9944</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>1</v>
+      </c>
+      <c r="R33" s="6">
+        <v>1</v>
+      </c>
+      <c r="S33" s="6">
+        <v>1</v>
+      </c>
+      <c r="T33" s="6">
+        <v>1</v>
+      </c>
+      <c r="U33" s="6">
+        <v>1</v>
+      </c>
+      <c r="V33" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22">
+      <c r="A34" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="6">
+        <v>0.4873</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.7597</v>
+      </c>
+      <c r="D34" s="6">
+        <v>0.881</v>
+      </c>
+      <c r="E34" s="6">
+        <v>0.9428</v>
+      </c>
+      <c r="F34" s="6">
+        <v>0.9769</v>
+      </c>
+      <c r="G34" s="6">
+        <v>0.9811</v>
+      </c>
+      <c r="H34" s="6">
+        <v>0.9818</v>
+      </c>
+      <c r="I34" s="6">
+        <v>0.9865</v>
+      </c>
+      <c r="J34" s="6">
+        <v>0.978</v>
+      </c>
+      <c r="K34" s="6">
+        <v>0.9805</v>
+      </c>
+      <c r="L34" s="6">
+        <v>0.9967</v>
+      </c>
+      <c r="M34" s="6">
+        <v>0.9084</v>
+      </c>
+      <c r="N34" s="6">
+        <v>0.9382</v>
+      </c>
+      <c r="O34" s="6">
+        <v>0.9738</v>
+      </c>
+      <c r="P34" s="6">
+        <v>0.9933</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>0.9942</v>
+      </c>
+      <c r="R34" s="6">
+        <v>0.9983</v>
+      </c>
+      <c r="S34" s="6">
+        <v>1</v>
+      </c>
+      <c r="T34" s="6">
+        <v>1</v>
+      </c>
+      <c r="U34" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22">
+      <c r="A35" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" s="6">
+        <v>0.3718</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.6041</v>
+      </c>
+      <c r="D35" s="6">
+        <v>0.8874</v>
+      </c>
+      <c r="E35" s="6">
+        <v>0.9036999999999999</v>
+      </c>
+      <c r="F35" s="6">
+        <v>0.9504</v>
+      </c>
+      <c r="G35" s="6">
+        <v>0.9469</v>
+      </c>
+      <c r="H35" s="6">
+        <v>0.9444</v>
+      </c>
+      <c r="I35" s="6">
+        <v>0.9687</v>
+      </c>
+      <c r="J35" s="6">
+        <v>0.9739</v>
+      </c>
+      <c r="K35" s="6">
+        <v>0.9776</v>
+      </c>
+      <c r="L35" s="6">
+        <v>0.9857</v>
+      </c>
+      <c r="M35" s="6">
+        <v>0.9555</v>
+      </c>
+      <c r="N35" s="6">
+        <v>0.9396</v>
+      </c>
+      <c r="O35" s="6">
+        <v>0.947</v>
+      </c>
+      <c r="P35" s="6">
+        <v>0.9529</v>
+      </c>
+      <c r="Q35" s="6">
+        <v>0.9499</v>
+      </c>
+      <c r="R35" s="6">
+        <v>0.9578</v>
+      </c>
+      <c r="S35" s="6">
+        <v>0.9582000000000001</v>
+      </c>
+      <c r="T35" s="6">
+        <v>0.9634</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22">
+      <c r="A36" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" s="6">
+        <v>0.292</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.5875</v>
+      </c>
+      <c r="D36" s="6">
+        <v>0.6985</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.7939000000000001</v>
+      </c>
+      <c r="F36" s="6">
+        <v>0.8448</v>
+      </c>
+      <c r="G36" s="6">
+        <v>0.8595</v>
+      </c>
+      <c r="H36" s="6">
+        <v>0.9016999999999999</v>
+      </c>
+      <c r="I36" s="6">
+        <v>0.8758</v>
+      </c>
+      <c r="J36" s="6">
+        <v>0.8831</v>
+      </c>
+      <c r="K36" s="6">
+        <v>0.8697</v>
+      </c>
+      <c r="L36" s="6">
+        <v>0.9132</v>
+      </c>
+      <c r="M36" s="6">
+        <v>0.9319</v>
+      </c>
+      <c r="N36" s="6">
+        <v>0.9548</v>
+      </c>
+      <c r="O36" s="6">
+        <v>0.9815</v>
+      </c>
+      <c r="P36" s="6">
+        <v>0.9657</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.9937</v>
+      </c>
+      <c r="R36" s="6">
+        <v>0.9964</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.9958</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22">
+      <c r="A37" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" s="6">
+        <v>0.6354</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.8387</v>
+      </c>
+      <c r="D37" s="6">
+        <v>0.9319</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0.9155</v>
+      </c>
+      <c r="F37" s="6">
+        <v>0.9775</v>
+      </c>
+      <c r="G37" s="6">
+        <v>0.991</v>
+      </c>
+      <c r="H37" s="6">
+        <v>0.9925</v>
+      </c>
+      <c r="I37" s="6">
+        <v>0.9859</v>
+      </c>
+      <c r="J37" s="6">
+        <v>0.9918</v>
+      </c>
+      <c r="K37" s="6">
+        <v>0.9714</v>
+      </c>
+      <c r="L37" s="6">
+        <v>0.977</v>
+      </c>
+      <c r="M37" s="6">
+        <v>0.9787</v>
+      </c>
+      <c r="N37" s="6">
+        <v>0.9955000000000001</v>
+      </c>
+      <c r="O37" s="6">
+        <v>0.9964</v>
+      </c>
+      <c r="P37" s="6">
+        <v>0.997</v>
+      </c>
+      <c r="Q37" s="6">
+        <v>0.9948</v>
+      </c>
+      <c r="R37" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22">
+      <c r="A38" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B38" s="6">
+        <v>0.6397</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.8507</v>
+      </c>
+      <c r="D38" s="6">
+        <v>0.9875</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0.9897</v>
+      </c>
+      <c r="F38" s="6">
+        <v>0.9958</v>
+      </c>
+      <c r="G38" s="6">
+        <v>0.996</v>
+      </c>
+      <c r="H38" s="6">
+        <v>0.9899</v>
+      </c>
+      <c r="I38" s="6">
+        <v>0.9089</v>
+      </c>
+      <c r="J38" s="6">
+        <v>0.9422</v>
+      </c>
+      <c r="K38" s="6">
+        <v>0.956</v>
+      </c>
+      <c r="L38" s="6">
+        <v>0.965</v>
+      </c>
+      <c r="M38" s="6">
+        <v>0.9812</v>
+      </c>
+      <c r="N38" s="6">
+        <v>1</v>
+      </c>
+      <c r="O38" s="6">
+        <v>1</v>
+      </c>
+      <c r="P38" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22">
+      <c r="A39" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" s="6">
+        <v>0.6767</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.9214</v>
+      </c>
+      <c r="D39" s="6">
+        <v>0.9621</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0.9743000000000001</v>
+      </c>
+      <c r="F39" s="6">
+        <v>0.9520999999999999</v>
+      </c>
+      <c r="G39" s="6">
+        <v>0.9825</v>
+      </c>
+      <c r="H39" s="6">
+        <v>0.9913</v>
+      </c>
+      <c r="I39" s="6">
+        <v>0.9919</v>
+      </c>
+      <c r="J39" s="6">
+        <v>1</v>
+      </c>
+      <c r="K39" s="6">
+        <v>1</v>
+      </c>
+      <c r="L39" s="6">
+        <v>0.9997</v>
+      </c>
+      <c r="M39" s="6">
+        <v>0.9997</v>
+      </c>
+      <c r="N39" s="6">
+        <v>0.9991</v>
+      </c>
+      <c r="O39" s="6">
+        <v>1</v>
+      </c>
+      <c r="P39" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22">
+      <c r="A40" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40" s="6">
+        <v>0.8018999999999999</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.946</v>
+      </c>
+      <c r="D40" s="6">
+        <v>1</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0.9315</v>
+      </c>
+      <c r="F40" s="6">
+        <v>0.9453</v>
+      </c>
+      <c r="G40" s="6">
+        <v>0.9530999999999999</v>
+      </c>
+      <c r="H40" s="6">
+        <v>0.9921</v>
+      </c>
+      <c r="I40" s="6">
+        <v>0.994</v>
+      </c>
+      <c r="J40" s="6">
+        <v>0.9849</v>
+      </c>
+      <c r="K40" s="6">
+        <v>0.9887</v>
+      </c>
+      <c r="L40" s="6">
+        <v>0.9666</v>
+      </c>
+      <c r="M40" s="6">
+        <v>0.9796</v>
+      </c>
+      <c r="N40" s="6">
+        <v>0.9846</v>
+      </c>
+      <c r="O40" s="6">
+        <v>0.9878</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22">
+      <c r="A41" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B41" s="6">
+        <v>0.6782</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.9298</v>
+      </c>
+      <c r="D41" s="6">
+        <v>0.8961</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.9816</v>
+      </c>
+      <c r="F41" s="6">
+        <v>0.9946</v>
+      </c>
+      <c r="G41" s="6">
+        <v>0.9923999999999999</v>
+      </c>
+      <c r="H41" s="6">
+        <v>0.9989</v>
+      </c>
+      <c r="I41" s="6">
+        <v>0.9874000000000001</v>
+      </c>
+      <c r="J41" s="6">
+        <v>0.9646</v>
+      </c>
+      <c r="K41" s="6">
+        <v>0.9172</v>
+      </c>
+      <c r="L41" s="6">
+        <v>0.9374</v>
+      </c>
+      <c r="M41" s="6">
+        <v>0.84</v>
+      </c>
+      <c r="N41" s="6">
+        <v>0.8757</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22">
+      <c r="A42" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" s="6">
+        <v>0.7258</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.9146</v>
+      </c>
+      <c r="D42" s="6">
+        <v>0.9831</v>
+      </c>
+      <c r="E42" s="6">
+        <v>0.8945</v>
+      </c>
+      <c r="F42" s="6">
+        <v>1</v>
+      </c>
+      <c r="G42" s="6">
+        <v>1</v>
+      </c>
+      <c r="H42" s="6">
+        <v>1</v>
+      </c>
+      <c r="I42" s="6">
+        <v>1</v>
+      </c>
+      <c r="J42" s="6">
+        <v>1</v>
+      </c>
+      <c r="K42" s="6">
+        <v>1</v>
+      </c>
+      <c r="L42" s="6">
+        <v>1</v>
+      </c>
+      <c r="M42" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22">
+      <c r="A43" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B43" s="6">
+        <v>0.7105</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.9325</v>
+      </c>
+      <c r="D43" s="6">
+        <v>0.8289</v>
+      </c>
+      <c r="E43" s="6">
+        <v>0.9129</v>
+      </c>
+      <c r="F43" s="6">
+        <v>0.9603</v>
+      </c>
+      <c r="G43" s="6">
+        <v>0.9437</v>
+      </c>
+      <c r="H43" s="6">
+        <v>0.9775</v>
+      </c>
+      <c r="I43" s="6">
+        <v>0.9804</v>
+      </c>
+      <c r="J43" s="6">
+        <v>0.9476</v>
+      </c>
+      <c r="K43" s="6">
+        <v>0.9857</v>
+      </c>
+      <c r="L43" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22">
+      <c r="A44" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" s="6">
+        <v>0.707</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.7906</v>
+      </c>
+      <c r="D44" s="6">
+        <v>0.8845</v>
+      </c>
+      <c r="E44" s="6">
+        <v>0.9756</v>
+      </c>
+      <c r="F44" s="6">
+        <v>0.9473</v>
+      </c>
+      <c r="G44" s="6">
+        <v>0.9283</v>
+      </c>
+      <c r="H44" s="6">
+        <v>0.9045</v>
+      </c>
+      <c r="I44" s="6">
+        <v>0.9476</v>
+      </c>
+      <c r="J44" s="6">
+        <v>0.958</v>
+      </c>
+      <c r="K44" s="6">
+        <v>0.9945000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22">
+      <c r="A45" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" s="6">
+        <v>0.4938</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.8754999999999999</v>
+      </c>
+      <c r="D45" s="6">
+        <v>0.9181</v>
+      </c>
+      <c r="E45" s="6">
+        <v>0.9506</v>
+      </c>
+      <c r="F45" s="6">
+        <v>0.8948</v>
+      </c>
+      <c r="G45" s="6">
+        <v>0.956</v>
+      </c>
+      <c r="H45" s="6">
+        <v>0.9663</v>
+      </c>
+      <c r="I45" s="6">
+        <v>0.9729</v>
+      </c>
+      <c r="J45" s="6">
+        <v>0.9824000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22">
+      <c r="A46" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B46" s="6">
+        <v>0.7297</v>
+      </c>
+      <c r="C46" s="6">
+        <v>0.9510999999999999</v>
+      </c>
+      <c r="D46" s="6">
+        <v>0.9908</v>
+      </c>
+      <c r="E46" s="6">
+        <v>0.8532999999999999</v>
+      </c>
+      <c r="F46" s="6">
+        <v>0.863</v>
+      </c>
+      <c r="G46" s="6">
+        <v>0.8438</v>
+      </c>
+      <c r="H46" s="6">
+        <v>0.9454</v>
+      </c>
+      <c r="I46" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22">
+      <c r="A47" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B47" s="6">
+        <v>0.68</v>
+      </c>
+      <c r="C47" s="6">
+        <v>0.8502</v>
+      </c>
+      <c r="D47" s="6">
+        <v>0.8831</v>
+      </c>
+      <c r="E47" s="6">
+        <v>0.8737</v>
+      </c>
+      <c r="F47" s="6">
+        <v>0.9292</v>
+      </c>
+      <c r="G47" s="6">
+        <v>0.9688</v>
+      </c>
+      <c r="H47" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22">
+      <c r="A48" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B48" s="6">
+        <v>0.7092000000000001</v>
+      </c>
+      <c r="C48" s="6">
+        <v>0.6879</v>
+      </c>
+      <c r="D48" s="6">
+        <v>0.778</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0.8001</v>
+      </c>
+      <c r="F48" s="6">
+        <v>0.9264</v>
+      </c>
+      <c r="G48" s="6">
+        <v>0.9213</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25">
+      <c r="A49" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B49" s="6">
+        <v>0.5476</v>
+      </c>
+      <c r="C49" s="6">
+        <v>0.7834</v>
+      </c>
+      <c r="D49" s="6">
+        <v>0.9404</v>
+      </c>
+      <c r="E49" s="6">
+        <v>0.9964</v>
+      </c>
+      <c r="F49" s="6">
+        <v>0.9971</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25">
+      <c r="A50" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B50" s="6">
+        <v>0.4982</v>
+      </c>
+      <c r="C50" s="6">
+        <v>0.6828</v>
+      </c>
+      <c r="D50" s="6">
+        <v>0.9297</v>
+      </c>
+      <c r="E50" s="6">
+        <v>0.9641</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25">
+      <c r="A51" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B51" s="6">
+        <v>0.4425</v>
+      </c>
+      <c r="C51" s="6">
+        <v>0.8767</v>
+      </c>
+      <c r="D51" s="6">
+        <v>0.9560999999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25">
+      <c r="A52" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B52" s="6">
+        <v>0.3767</v>
+      </c>
+      <c r="C52" s="6">
+        <v>0.726</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25">
+      <c r="A53" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B53" s="6">
+        <v>0.3991</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25">
+      <c r="A55" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="1"/>
+      <c r="R55" s="1"/>
+      <c r="S55" s="1"/>
+      <c r="T55" s="1"/>
+      <c r="U55" s="1"/>
+      <c r="V55" s="1"/>
+      <c r="W55" s="1"/>
+      <c r="X55" s="1"/>
+      <c r="Y55" s="1"/>
+    </row>
+    <row r="56" spans="1:25">
+      <c r="A56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="L56" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="M56" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N56" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="O56" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="P56" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q56" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="R56" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="S56" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="T56" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="U56" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="V56" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="W56" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="X56" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="Y56" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25">
+      <c r="A57" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B57" s="5">
+        <v>241287.5404</v>
+      </c>
+      <c r="C57" s="5">
+        <v>507032.5472</v>
+      </c>
+      <c r="D57" s="5">
+        <v>356561.1984</v>
+      </c>
+      <c r="E57" s="5">
+        <v>182475.6076</v>
+      </c>
+      <c r="F57" s="5">
+        <v>26448.7428</v>
+      </c>
+      <c r="G57" s="5">
+        <v>119212.1625</v>
+      </c>
+      <c r="H57" s="5">
+        <v>135560.5682</v>
+      </c>
+      <c r="I57" s="5">
+        <v>127376.7521</v>
+      </c>
+      <c r="J57" s="5">
+        <v>122762.2165</v>
+      </c>
+      <c r="K57" s="5">
+        <v>115449.8906</v>
+      </c>
+      <c r="L57" s="5">
+        <v>112336.3604</v>
+      </c>
+      <c r="M57" s="5">
+        <v>107056.0337</v>
+      </c>
+      <c r="N57" s="5">
+        <v>64267.1592</v>
+      </c>
+      <c r="O57" s="5">
+        <v>59425.9163</v>
+      </c>
+      <c r="P57" s="5">
+        <v>49003.346</v>
+      </c>
+      <c r="Q57" s="5">
+        <v>110426.7672</v>
+      </c>
+      <c r="R57" s="5">
+        <v>88625.6556</v>
+      </c>
+      <c r="S57" s="5">
+        <v>102153.0336</v>
+      </c>
+      <c r="T57" s="5">
+        <v>45924.5344</v>
+      </c>
+      <c r="U57" s="5">
+        <v>45924.5344</v>
+      </c>
+      <c r="V57" s="5">
+        <v>94432.9512</v>
+      </c>
+      <c r="W57" s="5">
+        <v>115096.185</v>
+      </c>
+      <c r="X57" s="5">
+        <v>96100.76730000001</v>
+      </c>
+      <c r="Y57" s="5">
+        <v>121479.0374</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25">
+      <c r="A58" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B58" s="5">
+        <v>570477.5956</v>
+      </c>
+      <c r="C58" s="5">
+        <v>416134.5404</v>
+      </c>
+      <c r="D58" s="5">
+        <v>122452.282</v>
+      </c>
+      <c r="E58" s="5">
+        <v>285899.2576</v>
+      </c>
+      <c r="F58" s="5">
+        <v>141953.9247</v>
+      </c>
+      <c r="G58" s="5">
+        <v>105558.3141</v>
+      </c>
+      <c r="H58" s="5">
+        <v>101772.4609</v>
+      </c>
+      <c r="I58" s="5">
+        <v>72762.40089999999</v>
+      </c>
+      <c r="J58" s="5">
+        <v>69459.8116</v>
+      </c>
+      <c r="K58" s="5">
+        <v>66177.22749999999</v>
+      </c>
+      <c r="L58" s="5">
+        <v>54004.9995</v>
+      </c>
+      <c r="M58" s="5">
+        <v>82818.09600000001</v>
+      </c>
+      <c r="N58" s="5">
+        <v>43710.3644</v>
+      </c>
+      <c r="O58" s="5">
+        <v>72556.8864</v>
+      </c>
+      <c r="P58" s="5">
+        <v>84420.0904</v>
+      </c>
+      <c r="Q58" s="5">
+        <v>76315.1072</v>
+      </c>
+      <c r="R58" s="5">
+        <v>128714.8397</v>
+      </c>
+      <c r="S58" s="5">
+        <v>89992.77439999999</v>
+      </c>
+      <c r="T58" s="5">
+        <v>56966.0763</v>
+      </c>
+      <c r="U58" s="5">
+        <v>123262.49</v>
+      </c>
+      <c r="V58" s="5">
+        <v>87668.23299999999</v>
+      </c>
+      <c r="W58" s="5">
+        <v>147682.6117</v>
+      </c>
+      <c r="X58" s="5">
+        <v>128087.5282</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25">
+      <c r="A59" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B59" s="5">
+        <v>545628.208</v>
+      </c>
+      <c r="C59" s="5">
+        <v>306912.568</v>
+      </c>
+      <c r="D59" s="5">
+        <v>249264.5224</v>
+      </c>
+      <c r="E59" s="5">
+        <v>427585.8973</v>
+      </c>
+      <c r="F59" s="5">
+        <v>26723.6947</v>
+      </c>
+      <c r="G59" s="5">
+        <v>58838.7339</v>
+      </c>
+      <c r="H59" s="5">
+        <v>51156.788</v>
+      </c>
+      <c r="I59" s="5">
+        <v>25100.2963</v>
+      </c>
+      <c r="J59" s="5">
+        <v>24291.8302</v>
+      </c>
+      <c r="K59" s="5">
+        <v>23901.6773</v>
+      </c>
+      <c r="L59" s="5">
+        <v>23511.3132</v>
+      </c>
+      <c r="M59" s="5">
+        <v>9218.8971</v>
+      </c>
+      <c r="N59" s="5">
+        <v>0</v>
+      </c>
+      <c r="O59" s="5">
+        <v>-0.607</v>
+      </c>
+      <c r="P59" s="5">
+        <v>-0.607</v>
+      </c>
+      <c r="Q59" s="5">
+        <v>0</v>
+      </c>
+      <c r="R59" s="5">
+        <v>0</v>
+      </c>
+      <c r="S59" s="5">
+        <v>0</v>
+      </c>
+      <c r="T59" s="5">
+        <v>0</v>
+      </c>
+      <c r="U59" s="5">
+        <v>0</v>
+      </c>
+      <c r="V59" s="5">
+        <v>0</v>
+      </c>
+      <c r="W59" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25">
+      <c r="A60" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B60" s="5">
+        <v>450102.364</v>
+      </c>
+      <c r="C60" s="5">
+        <v>181099.2648</v>
+      </c>
+      <c r="D60" s="5">
+        <v>84182.9979</v>
+      </c>
+      <c r="E60" s="5">
+        <v>29743.111</v>
+      </c>
+      <c r="F60" s="5">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5">
+        <v>1979.3736</v>
+      </c>
+      <c r="H60" s="5">
+        <v>4337.1161</v>
+      </c>
+      <c r="I60" s="5">
+        <v>4242.8439</v>
+      </c>
+      <c r="J60" s="5">
+        <v>10060.538</v>
+      </c>
+      <c r="K60" s="5">
+        <v>6885.6728</v>
+      </c>
+      <c r="L60" s="5">
+        <v>28441.7742</v>
+      </c>
+      <c r="M60" s="5">
+        <v>8623.585999999999</v>
+      </c>
+      <c r="N60" s="5">
+        <v>8613.029200000001</v>
+      </c>
+      <c r="O60" s="5">
+        <v>6922.6216</v>
+      </c>
+      <c r="P60" s="5">
+        <v>6275.9648</v>
+      </c>
+      <c r="Q60" s="5">
+        <v>0</v>
+      </c>
+      <c r="R60" s="5">
+        <v>0</v>
+      </c>
+      <c r="S60" s="5">
+        <v>0</v>
+      </c>
+      <c r="T60" s="5">
+        <v>0</v>
+      </c>
+      <c r="U60" s="5">
+        <v>0</v>
+      </c>
+      <c r="V60" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25">
+      <c r="A61" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B61" s="5">
+        <v>640698.79</v>
+      </c>
+      <c r="C61" s="5">
+        <v>391326.4562</v>
+      </c>
+      <c r="D61" s="5">
+        <v>211776.6394</v>
+      </c>
+      <c r="E61" s="5">
+        <v>99356.18090000001</v>
+      </c>
+      <c r="F61" s="5">
+        <v>41646.2461</v>
+      </c>
+      <c r="G61" s="5">
+        <v>34545.0694</v>
+      </c>
+      <c r="H61" s="5">
+        <v>33913.0998</v>
+      </c>
+      <c r="I61" s="5">
+        <v>25370.9727</v>
+      </c>
+      <c r="J61" s="5">
+        <v>41895.9804</v>
+      </c>
+      <c r="K61" s="5">
+        <v>38007.3568</v>
+      </c>
+      <c r="L61" s="5">
+        <v>6489.7928</v>
+      </c>
+      <c r="M61" s="5">
+        <v>202590.2704</v>
+      </c>
+      <c r="N61" s="5">
+        <v>136833.2828</v>
+      </c>
+      <c r="O61" s="5">
+        <v>56870.1414</v>
+      </c>
+      <c r="P61" s="5">
+        <v>14780.1138</v>
+      </c>
+      <c r="Q61" s="5">
+        <v>12771.8673</v>
+      </c>
+      <c r="R61" s="5">
+        <v>3751.4248</v>
+      </c>
+      <c r="S61" s="5">
+        <v>0</v>
+      </c>
+      <c r="T61" s="5">
+        <v>0</v>
+      </c>
+      <c r="U61" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25">
+      <c r="A62" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B62" s="5">
+        <v>481198.9096</v>
+      </c>
+      <c r="C62" s="5">
+        <v>458517.7435</v>
+      </c>
+      <c r="D62" s="5">
+        <v>113376.7462</v>
+      </c>
+      <c r="E62" s="5">
+        <v>103692.281</v>
+      </c>
+      <c r="F62" s="5">
+        <v>53871.6539</v>
+      </c>
+      <c r="G62" s="5">
+        <v>60597.5627</v>
+      </c>
+      <c r="H62" s="5">
+        <v>66204.10769999999</v>
+      </c>
+      <c r="I62" s="5">
+        <v>36626.8176</v>
+      </c>
+      <c r="J62" s="5">
+        <v>31300.1202</v>
+      </c>
+      <c r="K62" s="5">
+        <v>27931.9732</v>
+      </c>
+      <c r="L62" s="5">
+        <v>19226.572</v>
+      </c>
+      <c r="M62" s="5">
+        <v>63534.7812</v>
+      </c>
+      <c r="N62" s="5">
+        <v>88618.18670000001</v>
+      </c>
+      <c r="O62" s="5">
+        <v>78644.7555</v>
+      </c>
+      <c r="P62" s="5">
+        <v>69930.38099999999</v>
+      </c>
+      <c r="Q62" s="5">
+        <v>75266.57950000001</v>
+      </c>
+      <c r="R62" s="5">
+        <v>63520.5692</v>
+      </c>
+      <c r="S62" s="5">
+        <v>63503.7179</v>
+      </c>
+      <c r="T62" s="5">
+        <v>55495.7648</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25">
+      <c r="A63" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B63" s="5">
+        <v>1221079.0071</v>
+      </c>
+      <c r="C63" s="5">
+        <v>774524.8100000001</v>
+      </c>
+      <c r="D63" s="5">
+        <v>616580.7378999999</v>
+      </c>
+      <c r="E63" s="5">
+        <v>472292.0318</v>
+      </c>
+      <c r="F63" s="5">
+        <v>396530.4045</v>
+      </c>
+      <c r="G63" s="5">
+        <v>428271.8649</v>
+      </c>
+      <c r="H63" s="5">
+        <v>318887.938</v>
+      </c>
+      <c r="I63" s="5">
+        <v>447037.4875</v>
+      </c>
+      <c r="J63" s="5">
+        <v>450591.9356</v>
+      </c>
+      <c r="K63" s="5">
+        <v>553461.3536</v>
+      </c>
+      <c r="L63" s="5">
+        <v>380042.1608</v>
+      </c>
+      <c r="M63" s="5">
+        <v>306630.3847</v>
+      </c>
+      <c r="N63" s="5">
+        <v>206938.0753</v>
+      </c>
+      <c r="O63" s="5">
+        <v>84869.00509999999</v>
+      </c>
+      <c r="P63" s="5">
+        <v>164157.6462</v>
+      </c>
+      <c r="Q63" s="5">
+        <v>30002.6104</v>
+      </c>
+      <c r="R63" s="5">
+        <v>17313.825</v>
+      </c>
+      <c r="S63" s="5">
+        <v>20081.4616</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25">
+      <c r="A64" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B64" s="5">
+        <v>202836.1251</v>
+      </c>
+      <c r="C64" s="5">
+        <v>124339.9962</v>
+      </c>
+      <c r="D64" s="5">
+        <v>63528.4339</v>
+      </c>
+      <c r="E64" s="5">
+        <v>109651.0404</v>
+      </c>
+      <c r="F64" s="5">
+        <v>28266.571</v>
+      </c>
+      <c r="G64" s="5">
+        <v>11563.6548</v>
+      </c>
+      <c r="H64" s="5">
+        <v>9628.395500000001</v>
+      </c>
+      <c r="I64" s="5">
+        <v>18396.5436</v>
+      </c>
+      <c r="J64" s="5">
+        <v>10752.1008</v>
+      </c>
+      <c r="K64" s="5">
+        <v>38765.8892</v>
+      </c>
+      <c r="L64" s="5">
+        <v>31350.0671</v>
+      </c>
+      <c r="M64" s="5">
+        <v>28990.4903</v>
+      </c>
+      <c r="N64" s="5">
+        <v>6049.0332</v>
+      </c>
+      <c r="O64" s="5">
+        <v>4859.7569</v>
+      </c>
+      <c r="P64" s="5">
+        <v>3982.2757</v>
+      </c>
+      <c r="Q64" s="5">
+        <v>7035.9356</v>
+      </c>
+      <c r="R64" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17">
+      <c r="A65" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B65" s="5">
+        <v>128812.754</v>
+      </c>
+      <c r="C65" s="5">
+        <v>130290.1518</v>
+      </c>
+      <c r="D65" s="5">
+        <v>10289.2247</v>
+      </c>
+      <c r="E65" s="5">
+        <v>8691.9941</v>
+      </c>
+      <c r="F65" s="5">
+        <v>3776.6952</v>
+      </c>
+      <c r="G65" s="5">
+        <v>3804.6971</v>
+      </c>
+      <c r="H65" s="5">
+        <v>9881.1648</v>
+      </c>
+      <c r="I65" s="5">
+        <v>102097.452</v>
+      </c>
+      <c r="J65" s="5">
+        <v>64750.1328</v>
+      </c>
+      <c r="K65" s="5">
+        <v>49255.8911</v>
+      </c>
+      <c r="L65" s="5">
+        <v>39179.5178</v>
+      </c>
+      <c r="M65" s="5">
+        <v>21331.6507</v>
+      </c>
+      <c r="N65" s="5">
+        <v>0</v>
+      </c>
+      <c r="O65" s="5">
+        <v>0</v>
+      </c>
+      <c r="P65" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17">
+      <c r="A66" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B66" s="5">
+        <v>116407.2868</v>
+      </c>
+      <c r="C66" s="5">
+        <v>57439.7996</v>
+      </c>
+      <c r="D66" s="5">
+        <v>36069.3262</v>
+      </c>
+      <c r="E66" s="5">
+        <v>28417.586</v>
+      </c>
+      <c r="F66" s="5">
+        <v>59201.3995</v>
+      </c>
+      <c r="G66" s="5">
+        <v>21364.324</v>
+      </c>
+      <c r="H66" s="5">
+        <v>11058.248</v>
+      </c>
+      <c r="I66" s="5">
+        <v>10361.4992</v>
+      </c>
+      <c r="J66" s="5">
+        <v>0</v>
+      </c>
+      <c r="K66" s="5">
+        <v>0</v>
+      </c>
+      <c r="L66" s="5">
+        <v>352.4651</v>
+      </c>
+      <c r="M66" s="5">
+        <v>352.4651</v>
+      </c>
+      <c r="N66" s="5">
+        <v>1195.1353</v>
+      </c>
+      <c r="O66" s="5">
+        <v>0</v>
+      </c>
+      <c r="P66" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17">
+      <c r="A67" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B67" s="5">
+        <v>89969.2987</v>
+      </c>
+      <c r="C67" s="5">
+        <v>47873.7288</v>
+      </c>
+      <c r="D67" s="5">
+        <v>0</v>
+      </c>
+      <c r="E67" s="5">
+        <v>103527.5817</v>
+      </c>
+      <c r="F67" s="5">
+        <v>88124.20759999999</v>
+      </c>
+      <c r="G67" s="5">
+        <v>81689.838</v>
+      </c>
+      <c r="H67" s="5">
+        <v>14535.394</v>
+      </c>
+      <c r="I67" s="5">
+        <v>11061.6394</v>
+      </c>
+      <c r="J67" s="5">
+        <v>28079.2538</v>
+      </c>
+      <c r="K67" s="5">
+        <v>21164.8797</v>
+      </c>
+      <c r="L67" s="5">
+        <v>64240.5297</v>
+      </c>
+      <c r="M67" s="5">
+        <v>39139.943</v>
+      </c>
+      <c r="N67" s="5">
+        <v>29469.0037</v>
+      </c>
+      <c r="O67" s="5">
+        <v>23423.2827</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17">
+      <c r="A68" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B68" s="5">
+        <v>108077.1139</v>
+      </c>
+      <c r="C68" s="5">
+        <v>47913.3564</v>
+      </c>
+      <c r="D68" s="5">
+        <v>92667.2341</v>
+      </c>
+      <c r="E68" s="5">
+        <v>17829.1156</v>
+      </c>
+      <c r="F68" s="5">
+        <v>5191.3064</v>
+      </c>
+      <c r="G68" s="5">
+        <v>7397.6776</v>
+      </c>
+      <c r="H68" s="5">
+        <v>1076.6616</v>
+      </c>
+      <c r="I68" s="5">
+        <v>13014.5418</v>
+      </c>
+      <c r="J68" s="5">
+        <v>38458.0133</v>
+      </c>
+      <c r="K68" s="5">
+        <v>95108.7448</v>
+      </c>
+      <c r="L68" s="5">
+        <v>72406.97990000001</v>
+      </c>
+      <c r="M68" s="5">
+        <v>218177.8606</v>
+      </c>
+      <c r="N68" s="5">
+        <v>169516.5022</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17">
+      <c r="A69" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B69" s="5">
+        <v>76538.11960000001</v>
+      </c>
+      <c r="C69" s="5">
+        <v>43545.8894</v>
+      </c>
+      <c r="D69" s="5">
+        <v>9379.7168</v>
+      </c>
+      <c r="E69" s="5">
+        <v>70450.8048</v>
+      </c>
+      <c r="F69" s="5">
+        <v>0</v>
+      </c>
+      <c r="G69" s="5">
+        <v>0</v>
+      </c>
+      <c r="H69" s="5">
+        <v>0</v>
+      </c>
+      <c r="I69" s="5">
+        <v>0</v>
+      </c>
+      <c r="J69" s="5">
+        <v>0</v>
+      </c>
+      <c r="K69" s="5">
+        <v>0</v>
+      </c>
+      <c r="L69" s="5">
+        <v>0</v>
+      </c>
+      <c r="M69" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17">
+      <c r="A70" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B70" s="5">
+        <v>167732.7461</v>
+      </c>
+      <c r="C70" s="5">
+        <v>53437.202</v>
+      </c>
+      <c r="D70" s="5">
+        <v>191170.452</v>
+      </c>
+      <c r="E70" s="5">
+        <v>112584.3132</v>
+      </c>
+      <c r="F70" s="5">
+        <v>52042.068</v>
+      </c>
+      <c r="G70" s="5">
+        <v>76314.9224</v>
+      </c>
+      <c r="H70" s="5">
+        <v>29679.5195</v>
+      </c>
+      <c r="I70" s="5">
+        <v>25857.8523</v>
+      </c>
+      <c r="J70" s="5">
+        <v>71793.0096</v>
+      </c>
+      <c r="K70" s="5">
+        <v>20004.0012</v>
+      </c>
+      <c r="L70" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17">
+      <c r="A71" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B71" s="5">
+        <v>157642.0552</v>
+      </c>
+      <c r="C71" s="5">
+        <v>223747.4172</v>
+      </c>
+      <c r="D71" s="5">
+        <v>185459.2232</v>
+      </c>
+      <c r="E71" s="5">
+        <v>52148.8765</v>
+      </c>
+      <c r="F71" s="5">
+        <v>124342.5562</v>
+      </c>
+      <c r="G71" s="5">
+        <v>192202.3</v>
+      </c>
+      <c r="H71" s="5">
+        <v>291651.7502</v>
+      </c>
+      <c r="I71" s="5">
+        <v>161110.6633</v>
+      </c>
+      <c r="J71" s="5">
+        <v>129471.8546</v>
+      </c>
+      <c r="K71" s="5">
+        <v>18731.9596</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17">
+      <c r="A72" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B72" s="5">
+        <v>348179.0992</v>
+      </c>
+      <c r="C72" s="5">
+        <v>160058.2428</v>
+      </c>
+      <c r="D72" s="5">
+        <v>141976.8592</v>
+      </c>
+      <c r="E72" s="5">
+        <v>93144.09789999999</v>
+      </c>
+      <c r="F72" s="5">
+        <v>226526.0593</v>
+      </c>
+      <c r="G72" s="5">
+        <v>97588.9727</v>
+      </c>
+      <c r="H72" s="5">
+        <v>84454.1229</v>
+      </c>
+      <c r="I72" s="5">
+        <v>67834.82980000001</v>
+      </c>
+      <c r="J72" s="5">
+        <v>44114.967</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17">
+      <c r="A73" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B73" s="5">
+        <v>124674.4884</v>
+      </c>
+      <c r="C73" s="5">
+        <v>30082.3934</v>
+      </c>
+      <c r="D73" s="5">
+        <v>5872.0616</v>
+      </c>
+      <c r="E73" s="5">
+        <v>122203.0228</v>
+      </c>
+      <c r="F73" s="5">
+        <v>122613.9066</v>
+      </c>
+      <c r="G73" s="5">
+        <v>158378.1545</v>
+      </c>
+      <c r="H73" s="5">
+        <v>63865.1167</v>
+      </c>
+      <c r="I73" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17">
+      <c r="A74" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B74" s="5">
+        <v>162564.6514</v>
+      </c>
+      <c r="C74" s="5">
+        <v>174947.8042</v>
+      </c>
+      <c r="D74" s="5">
+        <v>195135.85</v>
+      </c>
+      <c r="E74" s="5">
+        <v>292716.4563</v>
+      </c>
+      <c r="F74" s="5">
+        <v>163113.0244</v>
+      </c>
+      <c r="G74" s="5">
+        <v>72826.03200000001</v>
+      </c>
+      <c r="H74" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17">
+      <c r="A75" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B75" s="5">
+        <v>118634.9695</v>
+      </c>
+      <c r="C75" s="5">
+        <v>350939.2933</v>
+      </c>
+      <c r="D75" s="5">
+        <v>386371.068</v>
+      </c>
+      <c r="E75" s="5">
+        <v>399867.2638</v>
+      </c>
+      <c r="F75" s="5">
+        <v>156538.2098</v>
+      </c>
+      <c r="G75" s="5">
+        <v>204693.0398</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17">
+      <c r="A76" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B76" s="5">
+        <v>236186.4682</v>
+      </c>
+      <c r="C76" s="5">
+        <v>201827.5548</v>
+      </c>
+      <c r="D76" s="5">
+        <v>54587.946</v>
+      </c>
+      <c r="E76" s="5">
+        <v>3532.2525</v>
+      </c>
+      <c r="F76" s="5">
+        <v>2848.6469</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17">
+      <c r="A77" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B77" s="5">
+        <v>275744.962</v>
+      </c>
+      <c r="C77" s="5">
+        <v>254023.2771</v>
+      </c>
+      <c r="D77" s="5">
+        <v>68937.55349999999</v>
+      </c>
+      <c r="E77" s="5">
+        <v>36333.8664</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17">
+      <c r="A78" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B78" s="5">
+        <v>387282.1198</v>
+      </c>
+      <c r="C78" s="5">
+        <v>105011.3135</v>
+      </c>
+      <c r="D78" s="5">
+        <v>36312.3965</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17">
+      <c r="A79" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B79" s="5">
+        <v>607733.0706</v>
+      </c>
+      <c r="C79" s="5">
+        <v>452514.606</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17">
+      <c r="A80" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B80" s="5">
+        <v>534907.4608999999</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25">
+      <c r="A82" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="1"/>
+      <c r="M82" s="1"/>
+      <c r="N82" s="1"/>
+      <c r="O82" s="1"/>
+      <c r="P82" s="1"/>
+      <c r="Q82" s="1"/>
+      <c r="R82" s="1"/>
+      <c r="S82" s="1"/>
+      <c r="T82" s="1"/>
+      <c r="U82" s="1"/>
+      <c r="V82" s="1"/>
+      <c r="W82" s="1"/>
+      <c r="X82" s="1"/>
+      <c r="Y82" s="1"/>
+    </row>
+    <row r="83" spans="1:25">
+      <c r="A83" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="H83" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="J83" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="K83" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="L83" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="M83" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N83" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="O83" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="P83" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q83" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="R83" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="S83" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="T83" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="U83" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="V83" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="W83" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="X83" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="Y83" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25">
+      <c r="A84" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B84" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="C84" s="5">
+        <v>0.0049</v>
+      </c>
+      <c r="D84" s="5">
+        <v>0.006</v>
+      </c>
+      <c r="E84" s="5">
+        <v>0.0066</v>
+      </c>
+      <c r="F84" s="5">
+        <v>0.0071</v>
+      </c>
+      <c r="G84" s="5">
+        <v>0.0076</v>
+      </c>
+      <c r="H84" s="5">
+        <v>0.0076</v>
+      </c>
+      <c r="I84" s="5">
+        <v>0.0076</v>
+      </c>
+      <c r="J84" s="5">
+        <v>0.0077</v>
+      </c>
+      <c r="K84" s="5">
+        <v>0.0078</v>
+      </c>
+      <c r="L84" s="5">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="M84" s="5">
+        <v>0.0081</v>
+      </c>
+      <c r="N84" s="5">
+        <v>0.0081</v>
+      </c>
+      <c r="O84" s="5">
+        <v>0.0083</v>
+      </c>
+      <c r="P84" s="5">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="Q84" s="5">
+        <v>0.0089</v>
+      </c>
+      <c r="R84" s="5">
+        <v>0.0091</v>
+      </c>
+      <c r="S84" s="5">
+        <v>0.0094</v>
+      </c>
+      <c r="T84" s="5">
+        <v>0.0095</v>
+      </c>
+      <c r="U84" s="5">
+        <v>0.0095</v>
+      </c>
+      <c r="V84" s="5">
+        <v>0.0097</v>
+      </c>
+      <c r="W84" s="5">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="X84" s="5">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="Y84" s="5">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25">
+      <c r="A85" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B85" s="5">
+        <v>0.0029</v>
+      </c>
+      <c r="C85" s="5">
+        <v>0.0041</v>
+      </c>
+      <c r="D85" s="5">
+        <v>0.0042</v>
+      </c>
+      <c r="E85" s="5">
+        <v>0.005</v>
+      </c>
+      <c r="F85" s="5">
+        <v>0.005</v>
+      </c>
+      <c r="G85" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="H85" s="5">
+        <v>0.0055</v>
+      </c>
+      <c r="I85" s="5">
+        <v>0.0055</v>
+      </c>
+      <c r="J85" s="5">
+        <v>0.0056</v>
+      </c>
+      <c r="K85" s="5">
+        <v>0.0056</v>
+      </c>
+      <c r="L85" s="5">
+        <v>0.0057</v>
+      </c>
+      <c r="M85" s="5">
+        <v>0.0059</v>
+      </c>
+      <c r="N85" s="5">
+        <v>0.0059</v>
+      </c>
+      <c r="O85" s="5">
+        <v>0.0061</v>
+      </c>
+      <c r="P85" s="5">
+        <v>0.0063</v>
+      </c>
+      <c r="Q85" s="5">
+        <v>0.0064</v>
+      </c>
+      <c r="R85" s="5">
+        <v>0.0067</v>
+      </c>
+      <c r="S85" s="5">
+        <v>0.0067</v>
+      </c>
+      <c r="T85" s="5">
+        <v>0.0067</v>
+      </c>
+      <c r="U85" s="5">
+        <v>0.007</v>
+      </c>
+      <c r="V85" s="5">
+        <v>0.007</v>
+      </c>
+      <c r="W85" s="5">
+        <v>0.0072</v>
+      </c>
+      <c r="X85" s="5">
+        <v>0.0072</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25">
+      <c r="A86" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B86" s="5">
+        <v>0.0031</v>
+      </c>
+      <c r="C86" s="5">
+        <v>0.0044</v>
+      </c>
+      <c r="D86" s="5">
+        <v>0.0048</v>
+      </c>
+      <c r="E86" s="5">
+        <v>0.0057</v>
+      </c>
+      <c r="F86" s="5">
+        <v>0.0052</v>
+      </c>
+      <c r="G86" s="5">
+        <v>0.0055</v>
+      </c>
+      <c r="H86" s="5">
+        <v>0.0055</v>
+      </c>
+      <c r="I86" s="5">
+        <v>0.0055</v>
+      </c>
+      <c r="J86" s="5">
+        <v>0.0055</v>
+      </c>
+      <c r="K86" s="5">
+        <v>0.0055</v>
+      </c>
+      <c r="L86" s="5">
+        <v>0.0055</v>
+      </c>
+      <c r="M86" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="N86" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="O86" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="P86" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="Q86" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="R86" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="S86" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="T86" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="U86" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="V86" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="W86" s="5">
+        <v>0.0054</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25">
+      <c r="A87" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B87" s="5">
+        <v>0.0021</v>
+      </c>
+      <c r="C87" s="5">
+        <v>0.0024</v>
+      </c>
+      <c r="D87" s="5">
+        <v>0.0027</v>
+      </c>
+      <c r="E87" s="5">
+        <v>0.0028</v>
+      </c>
+      <c r="F87" s="5">
+        <v>0.0031</v>
+      </c>
+      <c r="G87" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="H87" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="I87" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="J87" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="K87" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="L87" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="M87" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="N87" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="O87" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="P87" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="Q87" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="R87" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="S87" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="T87" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="U87" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="V87" s="5">
+        <v>0.0033</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25">
+      <c r="A88" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B88" s="5">
+        <v>0.0036</v>
+      </c>
+      <c r="C88" s="5">
+        <v>0.0048</v>
+      </c>
+      <c r="D88" s="5">
+        <v>0.0052</v>
+      </c>
+      <c r="E88" s="5">
+        <v>0.0051</v>
+      </c>
+      <c r="F88" s="5">
+        <v>0.0053</v>
+      </c>
+      <c r="G88" s="5">
+        <v>0.0053</v>
+      </c>
+      <c r="H88" s="5">
+        <v>0.0055</v>
+      </c>
+      <c r="I88" s="5">
+        <v>0.0055</v>
+      </c>
+      <c r="J88" s="5">
+        <v>0.0056</v>
+      </c>
+      <c r="K88" s="5">
+        <v>0.0057</v>
+      </c>
+      <c r="L88" s="5">
+        <v>0.0058</v>
+      </c>
+      <c r="M88" s="5">
+        <v>0.0065</v>
+      </c>
+      <c r="N88" s="5">
+        <v>0.0065</v>
+      </c>
+      <c r="O88" s="5">
+        <v>0.0063</v>
+      </c>
+      <c r="P88" s="5">
+        <v>0.0064</v>
+      </c>
+      <c r="Q88" s="5">
+        <v>0.0064</v>
+      </c>
+      <c r="R88" s="5">
+        <v>0.0065</v>
+      </c>
+      <c r="S88" s="5">
+        <v>0.0065</v>
+      </c>
+      <c r="T88" s="5">
+        <v>0.0065</v>
+      </c>
+      <c r="U88" s="5">
+        <v>0.0065</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25">
+      <c r="A89" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B89" s="5">
+        <v>0.0022</v>
+      </c>
+      <c r="C89" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="D89" s="5">
+        <v>0.0029</v>
+      </c>
+      <c r="E89" s="5">
+        <v>0.0031</v>
+      </c>
+      <c r="F89" s="5">
+        <v>0.0031</v>
+      </c>
+      <c r="G89" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="H89" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="I89" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="J89" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="K89" s="5">
+        <v>0.0036</v>
+      </c>
+      <c r="L89" s="5">
+        <v>0.0039</v>
+      </c>
+      <c r="M89" s="5">
+        <v>0.0041</v>
+      </c>
+      <c r="N89" s="5">
+        <v>0.0042</v>
+      </c>
+      <c r="O89" s="5">
+        <v>0.0042</v>
+      </c>
+      <c r="P89" s="5">
+        <v>0.0043</v>
+      </c>
+      <c r="Q89" s="5">
+        <v>0.0043</v>
+      </c>
+      <c r="R89" s="5">
+        <v>0.0043</v>
+      </c>
+      <c r="S89" s="5">
+        <v>0.0043</v>
+      </c>
+      <c r="T89" s="5">
+        <v>0.0043</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25">
+      <c r="A90" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B90" s="5">
+        <v>0.0048</v>
+      </c>
+      <c r="C90" s="5">
+        <v>0.0053</v>
+      </c>
+      <c r="D90" s="5">
+        <v>0.0057</v>
+      </c>
+      <c r="E90" s="5">
+        <v>0.0064</v>
+      </c>
+      <c r="F90" s="5">
+        <v>0.0072</v>
+      </c>
+      <c r="G90" s="5">
+        <v>0.0086</v>
+      </c>
+      <c r="H90" s="5">
+        <v>0.0091</v>
+      </c>
+      <c r="I90" s="5">
+        <v>0.0101</v>
+      </c>
+      <c r="J90" s="5">
+        <v>0.0108</v>
+      </c>
+      <c r="K90" s="5">
+        <v>0.0119</v>
+      </c>
+      <c r="L90" s="5">
+        <v>0.0123</v>
+      </c>
+      <c r="M90" s="5">
+        <v>0.0126</v>
+      </c>
+      <c r="N90" s="5">
+        <v>0.0128</v>
+      </c>
+      <c r="O90" s="5">
+        <v>0.0129</v>
+      </c>
+      <c r="P90" s="5">
+        <v>0.0134</v>
+      </c>
+      <c r="Q90" s="5">
+        <v>0.0134</v>
+      </c>
+      <c r="R90" s="5">
+        <v>0.0135</v>
+      </c>
+      <c r="S90" s="5">
+        <v>0.0135</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25">
+      <c r="A91" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B91" s="5">
+        <v>0.0015</v>
+      </c>
+      <c r="C91" s="5">
+        <v>0.0021</v>
+      </c>
+      <c r="D91" s="5">
+        <v>0.0026</v>
+      </c>
+      <c r="E91" s="5">
+        <v>0.0036</v>
+      </c>
+      <c r="F91" s="5">
+        <v>0.0035</v>
+      </c>
+      <c r="G91" s="5">
+        <v>0.0035</v>
+      </c>
+      <c r="H91" s="5">
+        <v>0.0035</v>
+      </c>
+      <c r="I91" s="5">
+        <v>0.0036</v>
+      </c>
+      <c r="J91" s="5">
+        <v>0.0036</v>
+      </c>
+      <c r="K91" s="5">
+        <v>0.0037</v>
+      </c>
+      <c r="L91" s="5">
+        <v>0.0037</v>
+      </c>
+      <c r="M91" s="5">
+        <v>0.0038</v>
+      </c>
+      <c r="N91" s="5">
+        <v>0.0037</v>
+      </c>
+      <c r="O91" s="5">
+        <v>0.0037</v>
+      </c>
+      <c r="P91" s="5">
+        <v>0.0037</v>
+      </c>
+      <c r="Q91" s="5">
+        <v>0.0037</v>
+      </c>
+      <c r="R91" s="5">
+        <v>0.0038</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25">
+      <c r="A92" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B92" s="5">
+        <v>0.001</v>
+      </c>
+      <c r="C92" s="5">
+        <v>0.0024</v>
+      </c>
+      <c r="D92" s="5">
+        <v>0.0022</v>
+      </c>
+      <c r="E92" s="5">
+        <v>0.0023</v>
+      </c>
+      <c r="F92" s="5">
+        <v>0.0024</v>
+      </c>
+      <c r="G92" s="5">
+        <v>0.0025</v>
+      </c>
+      <c r="H92" s="5">
+        <v>0.0026</v>
+      </c>
+      <c r="I92" s="5">
+        <v>0.003</v>
+      </c>
+      <c r="J92" s="5">
+        <v>0.003</v>
+      </c>
+      <c r="K92" s="5">
+        <v>0.003</v>
+      </c>
+      <c r="L92" s="5">
+        <v>0.003</v>
+      </c>
+      <c r="M92" s="5">
+        <v>0.0031</v>
+      </c>
+      <c r="N92" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="O92" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="P92" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="Q92" s="5">
+        <v>0.0032</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25">
+      <c r="A93" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B93" s="5">
+        <v>0.001</v>
+      </c>
+      <c r="C93" s="5">
+        <v>0.0019</v>
+      </c>
+      <c r="D93" s="5">
+        <v>0.0025</v>
+      </c>
+      <c r="E93" s="5">
+        <v>0.0029</v>
+      </c>
+      <c r="F93" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="G93" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="H93" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="I93" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="J93" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="K93" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="L93" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="M93" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="N93" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="O93" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="P93" s="5">
+        <v>0.0034</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25">
+      <c r="A94" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B94" s="5">
+        <v>0.0012</v>
+      </c>
+      <c r="C94" s="5">
+        <v>0.0023</v>
+      </c>
+      <c r="D94" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="E94" s="5">
+        <v>0.0039</v>
+      </c>
+      <c r="F94" s="5">
+        <v>0.0042</v>
+      </c>
+      <c r="G94" s="5">
+        <v>0.0045</v>
+      </c>
+      <c r="H94" s="5">
+        <v>0.0048</v>
+      </c>
+      <c r="I94" s="5">
+        <v>0.0048</v>
+      </c>
+      <c r="J94" s="5">
+        <v>0.0048</v>
+      </c>
+      <c r="K94" s="5">
+        <v>0.0048</v>
+      </c>
+      <c r="L94" s="5">
+        <v>0.005</v>
+      </c>
+      <c r="M94" s="5">
+        <v>0.005</v>
+      </c>
+      <c r="N94" s="5">
+        <v>0.005</v>
+      </c>
+      <c r="O94" s="5">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25">
+      <c r="A95" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B95" s="5">
+        <v>0.0009</v>
+      </c>
+      <c r="C95" s="5">
+        <v>0.0017</v>
+      </c>
+      <c r="D95" s="5">
+        <v>0.0023</v>
+      </c>
+      <c r="E95" s="5">
+        <v>0.0025</v>
+      </c>
+      <c r="F95" s="5">
+        <v>0.0025</v>
+      </c>
+      <c r="G95" s="5">
+        <v>0.0025</v>
+      </c>
+      <c r="H95" s="5">
+        <v>0.0025</v>
+      </c>
+      <c r="I95" s="5">
+        <v>0.0026</v>
+      </c>
+      <c r="J95" s="5">
+        <v>0.0028</v>
+      </c>
+      <c r="K95" s="5">
+        <v>0.0029</v>
+      </c>
+      <c r="L95" s="5">
+        <v>0.0029</v>
+      </c>
+      <c r="M95" s="5">
+        <v>0.0035</v>
+      </c>
+      <c r="N95" s="5">
+        <v>0.0035</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25">
+      <c r="A96" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B96" s="5">
+        <v>0.0007</v>
+      </c>
+      <c r="C96" s="5">
+        <v>0.0013</v>
+      </c>
+      <c r="D96" s="5">
+        <v>0.0014</v>
+      </c>
+      <c r="E96" s="5">
+        <v>0.0017</v>
+      </c>
+      <c r="F96" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="G96" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="H96" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="I96" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="J96" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="K96" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="L96" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="M96" s="5">
+        <v>0.0018</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25">
+      <c r="A97" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B97" s="5">
+        <v>0.0014</v>
+      </c>
+      <c r="C97" s="5">
+        <v>0.0019</v>
+      </c>
+      <c r="D97" s="5">
+        <v>0.0027</v>
+      </c>
+      <c r="E97" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="F97" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="G97" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="H97" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="I97" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="J97" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="K97" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="L97" s="5">
+        <v>0.0034</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25">
+      <c r="A98" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B98" s="5">
+        <v>0.0013</v>
+      </c>
+      <c r="C98" s="5">
+        <v>0.0026</v>
+      </c>
+      <c r="D98" s="5">
+        <v>0.0038</v>
+      </c>
+      <c r="E98" s="5">
+        <v>0.0051</v>
+      </c>
+      <c r="F98" s="5">
+        <v>0.0057</v>
+      </c>
+      <c r="G98" s="5">
+        <v>0.0064</v>
+      </c>
+      <c r="H98" s="5">
+        <v>0.0073</v>
+      </c>
+      <c r="I98" s="5">
+        <v>0.0074</v>
+      </c>
+      <c r="J98" s="5">
+        <v>0.0074</v>
+      </c>
+      <c r="K98" s="5">
+        <v>0.0081</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25">
+      <c r="A99" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B99" s="5">
+        <v>0.0016</v>
+      </c>
+      <c r="C99" s="5">
+        <v>0.003</v>
+      </c>
+      <c r="D99" s="5">
+        <v>0.0041</v>
+      </c>
+      <c r="E99" s="5">
+        <v>0.0044</v>
+      </c>
+      <c r="F99" s="5">
+        <v>0.0051</v>
+      </c>
+      <c r="G99" s="5">
+        <v>0.0052</v>
+      </c>
+      <c r="H99" s="5">
+        <v>0.0059</v>
+      </c>
+      <c r="I99" s="5">
+        <v>0.0059</v>
+      </c>
+      <c r="J99" s="5">
+        <v>0.0059</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25">
+      <c r="A100" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B100" s="5">
+        <v>0.0011</v>
+      </c>
+      <c r="C100" s="5">
+        <v>0.0014</v>
+      </c>
+      <c r="D100" s="5">
+        <v>0.0015</v>
+      </c>
+      <c r="E100" s="5">
+        <v>0.0019</v>
+      </c>
+      <c r="F100" s="5">
+        <v>0.0021</v>
+      </c>
+      <c r="G100" s="5">
+        <v>0.0023</v>
+      </c>
+      <c r="H100" s="5">
+        <v>0.0027</v>
+      </c>
+      <c r="I100" s="5">
+        <v>0.0028</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25">
+      <c r="A101" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B101" s="5">
+        <v>0.0011</v>
+      </c>
+      <c r="C101" s="5">
+        <v>0.0026</v>
+      </c>
+      <c r="D101" s="5">
+        <v>0.0038</v>
+      </c>
+      <c r="E101" s="5">
+        <v>0.0052</v>
+      </c>
+      <c r="F101" s="5">
+        <v>0.0052</v>
+      </c>
+      <c r="G101" s="5">
+        <v>0.0053</v>
+      </c>
+      <c r="H101" s="5">
+        <v>0.0054</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25">
+      <c r="A102" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B102" s="5">
+        <v>0.0009</v>
+      </c>
+      <c r="C102" s="5">
+        <v>0.0025</v>
+      </c>
+      <c r="D102" s="5">
+        <v>0.0039</v>
+      </c>
+      <c r="E102" s="5">
+        <v>0.0044</v>
+      </c>
+      <c r="F102" s="5">
+        <v>0.0047</v>
+      </c>
+      <c r="G102" s="5">
+        <v>0.0058</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25">
+      <c r="A103" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B103" s="5">
+        <v>0.0011</v>
+      </c>
+      <c r="C103" s="5">
+        <v>0.002</v>
+      </c>
+      <c r="D103" s="5">
+        <v>0.002</v>
+      </c>
+      <c r="E103" s="5">
+        <v>0.0021</v>
+      </c>
+      <c r="F103" s="5">
+        <v>0.0021</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25">
+      <c r="A104" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B104" s="5">
+        <v>0.0012</v>
+      </c>
+      <c r="C104" s="5">
+        <v>0.0017</v>
+      </c>
+      <c r="D104" s="5">
+        <v>0.0021</v>
+      </c>
+      <c r="E104" s="5">
+        <v>0.0022</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25">
+      <c r="A105" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B105" s="5">
+        <v>0.0014</v>
+      </c>
+      <c r="C105" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="D105" s="5">
+        <v>0.0017</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25">
+      <c r="A106" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B106" s="5">
+        <v>0.002</v>
+      </c>
+      <c r="C106" s="5">
+        <v>0.0034</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25">
+      <c r="A107" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B107" s="5">
+        <v>0.0018</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25">
+      <c r="A109" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
+      <c r="E109" s="1"/>
+      <c r="F109" s="1"/>
+      <c r="G109" s="1"/>
+      <c r="H109" s="1"/>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1"/>
+      <c r="K109" s="1"/>
+      <c r="L109" s="1"/>
+      <c r="M109" s="1"/>
+      <c r="N109" s="1"/>
+      <c r="O109" s="1"/>
+      <c r="P109" s="1"/>
+      <c r="Q109" s="1"/>
+      <c r="R109" s="1"/>
+      <c r="S109" s="1"/>
+      <c r="T109" s="1"/>
+      <c r="U109" s="1"/>
+      <c r="V109" s="1"/>
+      <c r="W109" s="1"/>
+      <c r="X109" s="1"/>
+      <c r="Y109" s="1"/>
+    </row>
+    <row r="110" spans="1:25">
+      <c r="A110" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D110" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E110" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="G110" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="H110" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I110" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="J110" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="K110" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="L110" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="M110" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N110" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="O110" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="P110" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q110" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="R110" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="S110" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="T110" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="U110" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="V110" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="W110" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="X110" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="Y110" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25">
+      <c r="A111" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B111" s="5">
+        <v>0.001</v>
+      </c>
+      <c r="C111" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="D111" s="5">
+        <v>0.0049</v>
+      </c>
+      <c r="E111" s="5">
+        <v>0.006</v>
+      </c>
+      <c r="F111" s="5">
+        <v>0.007</v>
+      </c>
+      <c r="G111" s="5">
+        <v>0.0072</v>
+      </c>
+      <c r="H111" s="5">
+        <v>0.0071</v>
+      </c>
+      <c r="I111" s="5">
+        <v>0.0072</v>
+      </c>
+      <c r="J111" s="5">
+        <v>0.0073</v>
+      </c>
+      <c r="K111" s="5">
+        <v>0.0074</v>
+      </c>
+      <c r="L111" s="5">
+        <v>0.0076</v>
+      </c>
+      <c r="M111" s="5">
+        <v>0.0078</v>
+      </c>
+      <c r="N111" s="5">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="O111" s="5">
+        <v>0.0081</v>
+      </c>
+      <c r="P111" s="5">
+        <v>0.0083</v>
+      </c>
+      <c r="Q111" s="5">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="R111" s="5">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="S111" s="5">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="T111" s="5">
+        <v>0.0094</v>
+      </c>
+      <c r="U111" s="5">
+        <v>0.0094</v>
+      </c>
+      <c r="V111" s="5">
+        <v>0.0094</v>
+      </c>
+      <c r="W111" s="5">
+        <v>0.0095</v>
+      </c>
+      <c r="X111" s="5">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="Y111" s="5">
+        <v>0.009599999999999999</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25">
+      <c r="A112" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B112" s="5">
+        <v>0.0011</v>
+      </c>
+      <c r="C112" s="5">
+        <v>0.0028</v>
+      </c>
+      <c r="D112" s="5">
+        <v>0.0038</v>
+      </c>
+      <c r="E112" s="5">
+        <v>0.0041</v>
+      </c>
+      <c r="F112" s="5">
+        <v>0.0046</v>
+      </c>
+      <c r="G112" s="5">
+        <v>0.005</v>
+      </c>
+      <c r="H112" s="5">
+        <v>0.0051</v>
+      </c>
+      <c r="I112" s="5">
+        <v>0.0052</v>
+      </c>
+      <c r="J112" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="K112" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="L112" s="5">
+        <v>0.0055</v>
+      </c>
+      <c r="M112" s="5">
+        <v>0.0056</v>
+      </c>
+      <c r="N112" s="5">
+        <v>0.0058</v>
+      </c>
+      <c r="O112" s="5">
+        <v>0.0059</v>
+      </c>
+      <c r="P112" s="5">
+        <v>0.006</v>
+      </c>
+      <c r="Q112" s="5">
+        <v>0.0061</v>
+      </c>
+      <c r="R112" s="5">
+        <v>0.0063</v>
+      </c>
+      <c r="S112" s="5">
+        <v>0.0064</v>
+      </c>
+      <c r="T112" s="5">
+        <v>0.0065</v>
+      </c>
+      <c r="U112" s="5">
+        <v>0.0066</v>
+      </c>
+      <c r="V112" s="5">
+        <v>0.0067</v>
+      </c>
+      <c r="W112" s="5">
+        <v>0.0068</v>
+      </c>
+      <c r="X112" s="5">
+        <v>0.0068</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23">
+      <c r="A113" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B113" s="5">
+        <v>0.0014</v>
+      </c>
+      <c r="C113" s="5">
+        <v>0.0035</v>
+      </c>
+      <c r="D113" s="5">
+        <v>0.004</v>
+      </c>
+      <c r="E113" s="5">
+        <v>0.0044</v>
+      </c>
+      <c r="F113" s="5">
+        <v>0.0051</v>
+      </c>
+      <c r="G113" s="5">
+        <v>0.0053</v>
+      </c>
+      <c r="H113" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="I113" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="J113" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="K113" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="L113" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="M113" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="N113" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="O113" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="P113" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="Q113" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="R113" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="S113" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="T113" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="U113" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="V113" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="W113" s="5">
+        <v>0.0054</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23">
+      <c r="A114" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B114" s="5">
+        <v>0.0008</v>
+      </c>
+      <c r="C114" s="5">
+        <v>0.0019</v>
+      </c>
+      <c r="D114" s="5">
+        <v>0.0024</v>
+      </c>
+      <c r="E114" s="5">
+        <v>0.0027</v>
+      </c>
+      <c r="F114" s="5">
+        <v>0.0031</v>
+      </c>
+      <c r="G114" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="H114" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="I114" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="J114" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="K114" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="L114" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="M114" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="N114" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="O114" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="P114" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="Q114" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="R114" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="S114" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="T114" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="U114" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="V114" s="5">
+        <v>0.0033</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23">
+      <c r="A115" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B115" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="C115" s="5">
+        <v>0.0036</v>
+      </c>
+      <c r="D115" s="5">
+        <v>0.0046</v>
+      </c>
+      <c r="E115" s="5">
+        <v>0.0048</v>
+      </c>
+      <c r="F115" s="5">
+        <v>0.0051</v>
+      </c>
+      <c r="G115" s="5">
+        <v>0.0052</v>
+      </c>
+      <c r="H115" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="I115" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="J115" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="K115" s="5">
+        <v>0.0056</v>
+      </c>
+      <c r="L115" s="5">
+        <v>0.0058</v>
+      </c>
+      <c r="M115" s="5">
+        <v>0.0059</v>
+      </c>
+      <c r="N115" s="5">
+        <v>0.0061</v>
+      </c>
+      <c r="O115" s="5">
+        <v>0.0062</v>
+      </c>
+      <c r="P115" s="5">
+        <v>0.0064</v>
+      </c>
+      <c r="Q115" s="5">
+        <v>0.0064</v>
+      </c>
+      <c r="R115" s="5">
+        <v>0.0065</v>
+      </c>
+      <c r="S115" s="5">
+        <v>0.0065</v>
+      </c>
+      <c r="T115" s="5">
+        <v>0.0065</v>
+      </c>
+      <c r="U115" s="5">
+        <v>0.0065</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23">
+      <c r="A116" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B116" s="5">
+        <v>0.0008</v>
+      </c>
+      <c r="C116" s="5">
+        <v>0.002</v>
+      </c>
+      <c r="D116" s="5">
+        <v>0.0026</v>
+      </c>
+      <c r="E116" s="5">
+        <v>0.0028</v>
+      </c>
+      <c r="F116" s="5">
+        <v>0.003</v>
+      </c>
+      <c r="G116" s="5">
+        <v>0.0031</v>
+      </c>
+      <c r="H116" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="I116" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="J116" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="K116" s="5">
+        <v>0.0035</v>
+      </c>
+      <c r="L116" s="5">
+        <v>0.0038</v>
+      </c>
+      <c r="M116" s="5">
+        <v>0.0039</v>
+      </c>
+      <c r="N116" s="5">
+        <v>0.0039</v>
+      </c>
+      <c r="O116" s="5">
+        <v>0.004</v>
+      </c>
+      <c r="P116" s="5">
+        <v>0.0041</v>
+      </c>
+      <c r="Q116" s="5">
+        <v>0.0041</v>
+      </c>
+      <c r="R116" s="5">
+        <v>0.0041</v>
+      </c>
+      <c r="S116" s="5">
+        <v>0.0042</v>
+      </c>
+      <c r="T116" s="5">
+        <v>0.0042</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23">
+      <c r="A117" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B117" s="5">
+        <v>0.0014</v>
+      </c>
+      <c r="C117" s="5">
+        <v>0.0031</v>
+      </c>
+      <c r="D117" s="5">
+        <v>0.004</v>
+      </c>
+      <c r="E117" s="5">
+        <v>0.0051</v>
+      </c>
+      <c r="F117" s="5">
+        <v>0.0061</v>
+      </c>
+      <c r="G117" s="5">
+        <v>0.0074</v>
+      </c>
+      <c r="H117" s="5">
+        <v>0.008200000000000001</v>
+      </c>
+      <c r="I117" s="5">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="J117" s="5">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="K117" s="5">
+        <v>0.0104</v>
+      </c>
+      <c r="L117" s="5">
+        <v>0.0112</v>
+      </c>
+      <c r="M117" s="5">
+        <v>0.0118</v>
+      </c>
+      <c r="N117" s="5">
+        <v>0.0123</v>
+      </c>
+      <c r="O117" s="5">
+        <v>0.0126</v>
+      </c>
+      <c r="P117" s="5">
+        <v>0.013</v>
+      </c>
+      <c r="Q117" s="5">
+        <v>0.0133</v>
+      </c>
+      <c r="R117" s="5">
+        <v>0.0134</v>
+      </c>
+      <c r="S117" s="5">
+        <v>0.0134</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23">
+      <c r="A118" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B118" s="5">
+        <v>0.001</v>
+      </c>
+      <c r="C118" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="D118" s="5">
+        <v>0.0024</v>
+      </c>
+      <c r="E118" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="F118" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="G118" s="5">
+        <v>0.0035</v>
+      </c>
+      <c r="H118" s="5">
+        <v>0.0035</v>
+      </c>
+      <c r="I118" s="5">
+        <v>0.0035</v>
+      </c>
+      <c r="J118" s="5">
+        <v>0.0036</v>
+      </c>
+      <c r="K118" s="5">
+        <v>0.0036</v>
+      </c>
+      <c r="L118" s="5">
+        <v>0.0037</v>
+      </c>
+      <c r="M118" s="5">
+        <v>0.0037</v>
+      </c>
+      <c r="N118" s="5">
+        <v>0.0037</v>
+      </c>
+      <c r="O118" s="5">
+        <v>0.0037</v>
+      </c>
+      <c r="P118" s="5">
+        <v>0.0037</v>
+      </c>
+      <c r="Q118" s="5">
+        <v>0.0037</v>
+      </c>
+      <c r="R118" s="5">
+        <v>0.0038</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23">
+      <c r="A119" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B119" s="5">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="C119" s="5">
+        <v>0.002</v>
+      </c>
+      <c r="D119" s="5">
+        <v>0.0022</v>
+      </c>
+      <c r="E119" s="5">
+        <v>0.0023</v>
+      </c>
+      <c r="F119" s="5">
+        <v>0.0024</v>
+      </c>
+      <c r="G119" s="5">
+        <v>0.0025</v>
+      </c>
+      <c r="H119" s="5">
+        <v>0.0026</v>
+      </c>
+      <c r="I119" s="5">
+        <v>0.0027</v>
+      </c>
+      <c r="J119" s="5">
+        <v>0.0028</v>
+      </c>
+      <c r="K119" s="5">
+        <v>0.0029</v>
+      </c>
+      <c r="L119" s="5">
+        <v>0.0029</v>
+      </c>
+      <c r="M119" s="5">
+        <v>0.003</v>
+      </c>
+      <c r="N119" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="O119" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="P119" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="Q119" s="5">
+        <v>0.0032</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23">
+      <c r="A120" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B120" s="5">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="C120" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="D120" s="5">
+        <v>0.0024</v>
+      </c>
+      <c r="E120" s="5">
+        <v>0.0028</v>
+      </c>
+      <c r="F120" s="5">
+        <v>0.0031</v>
+      </c>
+      <c r="G120" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="H120" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="I120" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="J120" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="K120" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="L120" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="M120" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="N120" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="O120" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="P120" s="5">
+        <v>0.0034</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23">
+      <c r="A121" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B121" s="5">
+        <v>0.0009</v>
+      </c>
+      <c r="C121" s="5">
+        <v>0.0022</v>
+      </c>
+      <c r="D121" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="E121" s="5">
+        <v>0.0036</v>
+      </c>
+      <c r="F121" s="5">
+        <v>0.004</v>
+      </c>
+      <c r="G121" s="5">
+        <v>0.0043</v>
+      </c>
+      <c r="H121" s="5">
+        <v>0.0047</v>
+      </c>
+      <c r="I121" s="5">
+        <v>0.0047</v>
+      </c>
+      <c r="J121" s="5">
+        <v>0.0048</v>
+      </c>
+      <c r="K121" s="5">
+        <v>0.0048</v>
+      </c>
+      <c r="L121" s="5">
+        <v>0.0048</v>
+      </c>
+      <c r="M121" s="5">
+        <v>0.0049</v>
+      </c>
+      <c r="N121" s="5">
+        <v>0.0049</v>
+      </c>
+      <c r="O121" s="5">
+        <v>0.0049</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23">
+      <c r="A122" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B122" s="5">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="C122" s="5">
+        <v>0.0016</v>
+      </c>
+      <c r="D122" s="5">
+        <v>0.002</v>
+      </c>
+      <c r="E122" s="5">
+        <v>0.0024</v>
+      </c>
+      <c r="F122" s="5">
+        <v>0.0024</v>
+      </c>
+      <c r="G122" s="5">
+        <v>0.0025</v>
+      </c>
+      <c r="H122" s="5">
+        <v>0.0025</v>
+      </c>
+      <c r="I122" s="5">
+        <v>0.0026</v>
+      </c>
+      <c r="J122" s="5">
+        <v>0.0027</v>
+      </c>
+      <c r="K122" s="5">
+        <v>0.0027</v>
+      </c>
+      <c r="L122" s="5">
+        <v>0.0028</v>
+      </c>
+      <c r="M122" s="5">
+        <v>0.0029</v>
+      </c>
+      <c r="N122" s="5">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23">
+      <c r="A123" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B123" s="5">
+        <v>0.0005</v>
+      </c>
+      <c r="C123" s="5">
+        <v>0.0012</v>
+      </c>
+      <c r="D123" s="5">
+        <v>0.0014</v>
+      </c>
+      <c r="E123" s="5">
+        <v>0.0015</v>
+      </c>
+      <c r="F123" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="G123" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="H123" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="I123" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="J123" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="K123" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="L123" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="M123" s="5">
+        <v>0.0018</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23">
+      <c r="A124" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B124" s="5">
+        <v>0.001</v>
+      </c>
+      <c r="C124" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="D124" s="5">
+        <v>0.0023</v>
+      </c>
+      <c r="E124" s="5">
+        <v>0.0029</v>
+      </c>
+      <c r="F124" s="5">
+        <v>0.0031</v>
+      </c>
+      <c r="G124" s="5">
+        <v>0.0031</v>
+      </c>
+      <c r="H124" s="5">
+        <v>0.0031</v>
+      </c>
+      <c r="I124" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="J124" s="5">
+        <v>0.0032</v>
+      </c>
+      <c r="K124" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="L124" s="5">
+        <v>0.0034</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23">
+      <c r="A125" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B125" s="5">
+        <v>0.0009</v>
+      </c>
+      <c r="C125" s="5">
+        <v>0.002</v>
+      </c>
+      <c r="D125" s="5">
+        <v>0.0034</v>
+      </c>
+      <c r="E125" s="5">
+        <v>0.005</v>
+      </c>
+      <c r="F125" s="5">
+        <v>0.0054</v>
+      </c>
+      <c r="G125" s="5">
+        <v>0.006</v>
+      </c>
+      <c r="H125" s="5">
+        <v>0.0066</v>
+      </c>
+      <c r="I125" s="5">
+        <v>0.007</v>
+      </c>
+      <c r="J125" s="5">
+        <v>0.0071</v>
+      </c>
+      <c r="K125" s="5">
+        <v>0.0081</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23">
+      <c r="A126" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B126" s="5">
+        <v>0.0008</v>
+      </c>
+      <c r="C126" s="5">
+        <v>0.0026</v>
+      </c>
+      <c r="D126" s="5">
+        <v>0.0037</v>
+      </c>
+      <c r="E126" s="5">
+        <v>0.0042</v>
+      </c>
+      <c r="F126" s="5">
+        <v>0.0045</v>
+      </c>
+      <c r="G126" s="5">
+        <v>0.005</v>
+      </c>
+      <c r="H126" s="5">
+        <v>0.0057</v>
+      </c>
+      <c r="I126" s="5">
+        <v>0.0057</v>
+      </c>
+      <c r="J126" s="5">
+        <v>0.0058</v>
+      </c>
+    </row>
+    <row r="127" spans="1:23">
+      <c r="A127" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B127" s="5">
+        <v>0.0008</v>
+      </c>
+      <c r="C127" s="5">
+        <v>0.0013</v>
+      </c>
+      <c r="D127" s="5">
+        <v>0.0015</v>
+      </c>
+      <c r="E127" s="5">
+        <v>0.0016</v>
+      </c>
+      <c r="F127" s="5">
+        <v>0.0018</v>
+      </c>
+      <c r="G127" s="5">
+        <v>0.002</v>
+      </c>
+      <c r="H127" s="5">
+        <v>0.0025</v>
+      </c>
+      <c r="I127" s="5">
+        <v>0.0028</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23">
+      <c r="A128" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B128" s="5">
+        <v>0.0008</v>
+      </c>
+      <c r="C128" s="5">
+        <v>0.0022</v>
+      </c>
+      <c r="D128" s="5">
+        <v>0.0033</v>
+      </c>
+      <c r="E128" s="5">
+        <v>0.0046</v>
+      </c>
+      <c r="F128" s="5">
+        <v>0.0048</v>
+      </c>
+      <c r="G128" s="5">
+        <v>0.0051</v>
+      </c>
+      <c r="H128" s="5">
+        <v>0.0054</v>
+      </c>
+    </row>
+    <row r="129" spans="1:25">
+      <c r="A129" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B129" s="5">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="C129" s="5">
+        <v>0.0017</v>
+      </c>
+      <c r="D129" s="5">
+        <v>0.003</v>
+      </c>
+      <c r="E129" s="5">
+        <v>0.0035</v>
+      </c>
+      <c r="F129" s="5">
+        <v>0.0044</v>
+      </c>
+      <c r="G129" s="5">
+        <v>0.0053</v>
+      </c>
+    </row>
+    <row r="130" spans="1:25">
+      <c r="A130" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B130" s="5">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="C130" s="5">
+        <v>0.0016</v>
+      </c>
+      <c r="D130" s="5">
+        <v>0.0019</v>
+      </c>
+      <c r="E130" s="5">
+        <v>0.0021</v>
+      </c>
+      <c r="F130" s="5">
+        <v>0.0021</v>
+      </c>
+    </row>
+    <row r="131" spans="1:25">
+      <c r="A131" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B131" s="5">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="C131" s="5">
+        <v>0.0012</v>
+      </c>
+      <c r="D131" s="5">
+        <v>0.0019</v>
+      </c>
+      <c r="E131" s="5">
+        <v>0.0021</v>
+      </c>
+    </row>
+    <row r="132" spans="1:25">
+      <c r="A132" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B132" s="5">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="C132" s="5">
+        <v>0.0016</v>
+      </c>
+      <c r="D132" s="5">
+        <v>0.0016</v>
+      </c>
+    </row>
+    <row r="133" spans="1:25">
+      <c r="A133" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B133" s="5">
+        <v>0.0008</v>
+      </c>
+      <c r="C133" s="5">
+        <v>0.0025</v>
+      </c>
+    </row>
+    <row r="134" spans="1:25">
+      <c r="A134" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B134" s="5">
+        <v>0.0007</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25">
+      <c r="A136" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
+      <c r="E136" s="1"/>
+      <c r="F136" s="1"/>
+      <c r="G136" s="1"/>
+      <c r="H136" s="1"/>
+      <c r="I136" s="1"/>
+      <c r="J136" s="1"/>
+      <c r="K136" s="1"/>
+      <c r="L136" s="1"/>
+      <c r="M136" s="1"/>
+      <c r="N136" s="1"/>
+      <c r="O136" s="1"/>
+      <c r="P136" s="1"/>
+      <c r="Q136" s="1"/>
+      <c r="R136" s="1"/>
+      <c r="S136" s="1"/>
+      <c r="T136" s="1"/>
+      <c r="U136" s="1"/>
+      <c r="V136" s="1"/>
+      <c r="W136" s="1"/>
+      <c r="X136" s="1"/>
+      <c r="Y136" s="1"/>
+    </row>
+    <row r="137" spans="1:25">
+      <c r="A137" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B137" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C137" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D137" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E137" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="H137" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I137" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="J137" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="K137" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="L137" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="M137" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N137" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="O137" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="P137" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q137" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="R137" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="S137" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="T137" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="U137" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="V137" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="W137" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="X137" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="Y137" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="138" spans="1:25">
+      <c r="A138" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B138" s="6">
+        <v>0</v>
+      </c>
+      <c r="C138" s="6">
+        <v>0</v>
+      </c>
+      <c r="D138" s="6">
+        <v>0</v>
+      </c>
+      <c r="E138" s="6">
+        <v>0</v>
+      </c>
+      <c r="F138" s="6">
+        <v>0</v>
+      </c>
+      <c r="G138" s="6">
+        <v>0</v>
+      </c>
+      <c r="H138" s="6">
+        <v>0</v>
+      </c>
+      <c r="I138" s="6">
+        <v>0</v>
+      </c>
+      <c r="J138" s="6">
+        <v>0</v>
+      </c>
+      <c r="K138" s="6">
+        <v>0</v>
+      </c>
+      <c r="L138" s="6">
+        <v>0</v>
+      </c>
+      <c r="M138" s="6">
+        <v>0</v>
+      </c>
+      <c r="N138" s="6">
+        <v>0</v>
+      </c>
+      <c r="O138" s="6">
+        <v>0</v>
+      </c>
+      <c r="P138" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q138" s="6">
+        <v>0</v>
+      </c>
+      <c r="R138" s="6">
+        <v>0</v>
+      </c>
+      <c r="S138" s="6">
+        <v>0</v>
+      </c>
+      <c r="T138" s="6">
+        <v>0</v>
+      </c>
+      <c r="U138" s="6">
+        <v>0</v>
+      </c>
+      <c r="V138" s="6">
+        <v>0</v>
+      </c>
+      <c r="W138" s="6">
+        <v>0</v>
+      </c>
+      <c r="X138" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y138" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:25">
+      <c r="A139" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B139" s="6">
+        <v>0</v>
+      </c>
+      <c r="C139" s="6">
+        <v>0</v>
+      </c>
+      <c r="D139" s="6">
+        <v>0</v>
+      </c>
+      <c r="E139" s="6">
+        <v>0</v>
+      </c>
+      <c r="F139" s="6">
+        <v>0</v>
+      </c>
+      <c r="G139" s="6">
+        <v>0</v>
+      </c>
+      <c r="H139" s="6">
+        <v>0</v>
+      </c>
+      <c r="I139" s="6">
+        <v>0</v>
+      </c>
+      <c r="J139" s="6">
+        <v>0</v>
+      </c>
+      <c r="K139" s="6">
+        <v>0</v>
+      </c>
+      <c r="L139" s="6">
+        <v>0</v>
+      </c>
+      <c r="M139" s="6">
+        <v>0</v>
+      </c>
+      <c r="N139" s="6">
+        <v>0</v>
+      </c>
+      <c r="O139" s="6">
+        <v>0</v>
+      </c>
+      <c r="P139" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q139" s="6">
+        <v>0</v>
+      </c>
+      <c r="R139" s="6">
+        <v>0</v>
+      </c>
+      <c r="S139" s="6">
+        <v>0</v>
+      </c>
+      <c r="T139" s="6">
+        <v>0</v>
+      </c>
+      <c r="U139" s="6">
+        <v>0</v>
+      </c>
+      <c r="V139" s="6">
+        <v>0</v>
+      </c>
+      <c r="W139" s="6">
+        <v>0</v>
+      </c>
+      <c r="X139" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:25">
+      <c r="A140" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B140" s="6">
+        <v>0</v>
+      </c>
+      <c r="C140" s="6">
+        <v>0</v>
+      </c>
+      <c r="D140" s="6">
+        <v>0</v>
+      </c>
+      <c r="E140" s="6">
+        <v>0</v>
+      </c>
+      <c r="F140" s="6">
+        <v>0</v>
+      </c>
+      <c r="G140" s="6">
+        <v>0</v>
+      </c>
+      <c r="H140" s="6">
+        <v>0</v>
+      </c>
+      <c r="I140" s="6">
+        <v>0</v>
+      </c>
+      <c r="J140" s="6">
+        <v>0</v>
+      </c>
+      <c r="K140" s="6">
+        <v>0</v>
+      </c>
+      <c r="L140" s="6">
+        <v>0</v>
+      </c>
+      <c r="M140" s="6">
+        <v>0</v>
+      </c>
+      <c r="N140" s="6">
+        <v>0</v>
+      </c>
+      <c r="O140" s="6">
+        <v>0</v>
+      </c>
+      <c r="P140" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q140" s="6">
+        <v>0</v>
+      </c>
+      <c r="R140" s="6">
+        <v>0</v>
+      </c>
+      <c r="S140" s="6">
+        <v>0</v>
+      </c>
+      <c r="T140" s="6">
+        <v>0</v>
+      </c>
+      <c r="U140" s="6">
+        <v>0</v>
+      </c>
+      <c r="V140" s="6">
+        <v>0</v>
+      </c>
+      <c r="W140" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:25">
+      <c r="A141" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B141" s="6">
+        <v>0</v>
+      </c>
+      <c r="C141" s="6">
+        <v>0</v>
+      </c>
+      <c r="D141" s="6">
+        <v>0</v>
+      </c>
+      <c r="E141" s="6">
+        <v>0</v>
+      </c>
+      <c r="F141" s="6">
+        <v>0</v>
+      </c>
+      <c r="G141" s="6">
+        <v>0</v>
+      </c>
+      <c r="H141" s="6">
+        <v>0</v>
+      </c>
+      <c r="I141" s="6">
+        <v>0</v>
+      </c>
+      <c r="J141" s="6">
+        <v>0</v>
+      </c>
+      <c r="K141" s="6">
+        <v>0</v>
+      </c>
+      <c r="L141" s="6">
+        <v>0</v>
+      </c>
+      <c r="M141" s="6">
+        <v>0</v>
+      </c>
+      <c r="N141" s="6">
+        <v>0</v>
+      </c>
+      <c r="O141" s="6">
+        <v>0</v>
+      </c>
+      <c r="P141" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q141" s="6">
+        <v>0</v>
+      </c>
+      <c r="R141" s="6">
+        <v>0</v>
+      </c>
+      <c r="S141" s="6">
+        <v>0</v>
+      </c>
+      <c r="T141" s="6">
+        <v>0</v>
+      </c>
+      <c r="U141" s="6">
+        <v>0</v>
+      </c>
+      <c r="V141" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:25">
+      <c r="A142" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B142" s="6">
+        <v>0</v>
+      </c>
+      <c r="C142" s="6">
+        <v>0</v>
+      </c>
+      <c r="D142" s="6">
+        <v>0</v>
+      </c>
+      <c r="E142" s="6">
+        <v>0</v>
+      </c>
+      <c r="F142" s="6">
+        <v>0</v>
+      </c>
+      <c r="G142" s="6">
+        <v>0</v>
+      </c>
+      <c r="H142" s="6">
+        <v>0</v>
+      </c>
+      <c r="I142" s="6">
+        <v>0</v>
+      </c>
+      <c r="J142" s="6">
+        <v>0</v>
+      </c>
+      <c r="K142" s="6">
+        <v>0</v>
+      </c>
+      <c r="L142" s="6">
+        <v>0</v>
+      </c>
+      <c r="M142" s="6">
+        <v>0</v>
+      </c>
+      <c r="N142" s="6">
+        <v>0</v>
+      </c>
+      <c r="O142" s="6">
+        <v>0</v>
+      </c>
+      <c r="P142" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q142" s="6">
+        <v>0</v>
+      </c>
+      <c r="R142" s="6">
+        <v>0</v>
+      </c>
+      <c r="S142" s="6">
+        <v>0</v>
+      </c>
+      <c r="T142" s="6">
+        <v>0</v>
+      </c>
+      <c r="U142" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:25">
+      <c r="A143" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B143" s="6">
+        <v>0</v>
+      </c>
+      <c r="C143" s="6">
+        <v>0</v>
+      </c>
+      <c r="D143" s="6">
+        <v>0</v>
+      </c>
+      <c r="E143" s="6">
+        <v>0</v>
+      </c>
+      <c r="F143" s="6">
+        <v>0</v>
+      </c>
+      <c r="G143" s="6">
+        <v>0</v>
+      </c>
+      <c r="H143" s="6">
+        <v>0</v>
+      </c>
+      <c r="I143" s="6">
+        <v>0</v>
+      </c>
+      <c r="J143" s="6">
+        <v>0</v>
+      </c>
+      <c r="K143" s="6">
+        <v>0</v>
+      </c>
+      <c r="L143" s="6">
+        <v>0</v>
+      </c>
+      <c r="M143" s="6">
+        <v>0</v>
+      </c>
+      <c r="N143" s="6">
+        <v>0</v>
+      </c>
+      <c r="O143" s="6">
+        <v>0</v>
+      </c>
+      <c r="P143" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q143" s="6">
+        <v>0</v>
+      </c>
+      <c r="R143" s="6">
+        <v>0</v>
+      </c>
+      <c r="S143" s="6">
+        <v>0</v>
+      </c>
+      <c r="T143" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:25">
+      <c r="A144" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B144" s="6">
+        <v>0</v>
+      </c>
+      <c r="C144" s="6">
+        <v>0</v>
+      </c>
+      <c r="D144" s="6">
+        <v>0</v>
+      </c>
+      <c r="E144" s="6">
+        <v>0</v>
+      </c>
+      <c r="F144" s="6">
+        <v>0</v>
+      </c>
+      <c r="G144" s="6">
+        <v>0</v>
+      </c>
+      <c r="H144" s="6">
+        <v>0</v>
+      </c>
+      <c r="I144" s="6">
+        <v>0</v>
+      </c>
+      <c r="J144" s="6">
+        <v>0</v>
+      </c>
+      <c r="K144" s="6">
+        <v>0</v>
+      </c>
+      <c r="L144" s="6">
+        <v>0</v>
+      </c>
+      <c r="M144" s="6">
+        <v>0</v>
+      </c>
+      <c r="N144" s="6">
+        <v>0</v>
+      </c>
+      <c r="O144" s="6">
+        <v>0</v>
+      </c>
+      <c r="P144" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q144" s="6">
+        <v>0</v>
+      </c>
+      <c r="R144" s="6">
+        <v>0</v>
+      </c>
+      <c r="S144" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18">
+      <c r="A145" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B145" s="6">
+        <v>0</v>
+      </c>
+      <c r="C145" s="6">
+        <v>0</v>
+      </c>
+      <c r="D145" s="6">
+        <v>0</v>
+      </c>
+      <c r="E145" s="6">
+        <v>0</v>
+      </c>
+      <c r="F145" s="6">
+        <v>0</v>
+      </c>
+      <c r="G145" s="6">
+        <v>0</v>
+      </c>
+      <c r="H145" s="6">
+        <v>0</v>
+      </c>
+      <c r="I145" s="6">
+        <v>0</v>
+      </c>
+      <c r="J145" s="6">
+        <v>0</v>
+      </c>
+      <c r="K145" s="6">
+        <v>0</v>
+      </c>
+      <c r="L145" s="6">
+        <v>0</v>
+      </c>
+      <c r="M145" s="6">
+        <v>0</v>
+      </c>
+      <c r="N145" s="6">
+        <v>0</v>
+      </c>
+      <c r="O145" s="6">
+        <v>0</v>
+      </c>
+      <c r="P145" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q145" s="6">
+        <v>0</v>
+      </c>
+      <c r="R145" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18">
+      <c r="A146" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B146" s="6">
+        <v>0</v>
+      </c>
+      <c r="C146" s="6">
+        <v>0</v>
+      </c>
+      <c r="D146" s="6">
+        <v>0</v>
+      </c>
+      <c r="E146" s="6">
+        <v>0</v>
+      </c>
+      <c r="F146" s="6">
+        <v>0</v>
+      </c>
+      <c r="G146" s="6">
+        <v>0</v>
+      </c>
+      <c r="H146" s="6">
+        <v>0</v>
+      </c>
+      <c r="I146" s="6">
+        <v>0</v>
+      </c>
+      <c r="J146" s="6">
+        <v>0</v>
+      </c>
+      <c r="K146" s="6">
+        <v>0</v>
+      </c>
+      <c r="L146" s="6">
+        <v>0</v>
+      </c>
+      <c r="M146" s="6">
+        <v>0</v>
+      </c>
+      <c r="N146" s="6">
+        <v>0</v>
+      </c>
+      <c r="O146" s="6">
+        <v>0</v>
+      </c>
+      <c r="P146" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q146" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18">
+      <c r="A147" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B147" s="6">
+        <v>0</v>
+      </c>
+      <c r="C147" s="6">
+        <v>0</v>
+      </c>
+      <c r="D147" s="6">
+        <v>0</v>
+      </c>
+      <c r="E147" s="6">
+        <v>0</v>
+      </c>
+      <c r="F147" s="6">
+        <v>0</v>
+      </c>
+      <c r="G147" s="6">
+        <v>0</v>
+      </c>
+      <c r="H147" s="6">
+        <v>0</v>
+      </c>
+      <c r="I147" s="6">
+        <v>0</v>
+      </c>
+      <c r="J147" s="6">
+        <v>0</v>
+      </c>
+      <c r="K147" s="6">
+        <v>0</v>
+      </c>
+      <c r="L147" s="6">
+        <v>0</v>
+      </c>
+      <c r="M147" s="6">
+        <v>0</v>
+      </c>
+      <c r="N147" s="6">
+        <v>0</v>
+      </c>
+      <c r="O147" s="6">
+        <v>0</v>
+      </c>
+      <c r="P147" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18">
+      <c r="A148" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B148" s="6">
+        <v>0</v>
+      </c>
+      <c r="C148" s="6">
+        <v>0</v>
+      </c>
+      <c r="D148" s="6">
+        <v>0</v>
+      </c>
+      <c r="E148" s="6">
+        <v>0</v>
+      </c>
+      <c r="F148" s="6">
+        <v>0</v>
+      </c>
+      <c r="G148" s="6">
+        <v>0</v>
+      </c>
+      <c r="H148" s="6">
+        <v>0</v>
+      </c>
+      <c r="I148" s="6">
+        <v>0</v>
+      </c>
+      <c r="J148" s="6">
+        <v>0</v>
+      </c>
+      <c r="K148" s="6">
+        <v>0</v>
+      </c>
+      <c r="L148" s="6">
+        <v>0</v>
+      </c>
+      <c r="M148" s="6">
+        <v>0</v>
+      </c>
+      <c r="N148" s="6">
+        <v>0</v>
+      </c>
+      <c r="O148" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18">
+      <c r="A149" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B149" s="6">
+        <v>0</v>
+      </c>
+      <c r="C149" s="6">
+        <v>0</v>
+      </c>
+      <c r="D149" s="6">
+        <v>0</v>
+      </c>
+      <c r="E149" s="6">
+        <v>0</v>
+      </c>
+      <c r="F149" s="6">
+        <v>0</v>
+      </c>
+      <c r="G149" s="6">
+        <v>0</v>
+      </c>
+      <c r="H149" s="6">
+        <v>0</v>
+      </c>
+      <c r="I149" s="6">
+        <v>0</v>
+      </c>
+      <c r="J149" s="6">
+        <v>0</v>
+      </c>
+      <c r="K149" s="6">
+        <v>0</v>
+      </c>
+      <c r="L149" s="6">
+        <v>0</v>
+      </c>
+      <c r="M149" s="6">
+        <v>0</v>
+      </c>
+      <c r="N149" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18">
+      <c r="A150" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B150" s="6">
+        <v>0</v>
+      </c>
+      <c r="C150" s="6">
+        <v>0</v>
+      </c>
+      <c r="D150" s="6">
+        <v>0</v>
+      </c>
+      <c r="E150" s="6">
+        <v>0</v>
+      </c>
+      <c r="F150" s="6">
+        <v>0</v>
+      </c>
+      <c r="G150" s="6">
+        <v>0</v>
+      </c>
+      <c r="H150" s="6">
+        <v>0</v>
+      </c>
+      <c r="I150" s="6">
+        <v>0</v>
+      </c>
+      <c r="J150" s="6">
+        <v>0</v>
+      </c>
+      <c r="K150" s="6">
+        <v>0</v>
+      </c>
+      <c r="L150" s="6">
+        <v>0</v>
+      </c>
+      <c r="M150" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18">
+      <c r="A151" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B151" s="6">
+        <v>0</v>
+      </c>
+      <c r="C151" s="6">
+        <v>0</v>
+      </c>
+      <c r="D151" s="6">
+        <v>0</v>
+      </c>
+      <c r="E151" s="6">
+        <v>0</v>
+      </c>
+      <c r="F151" s="6">
+        <v>0</v>
+      </c>
+      <c r="G151" s="6">
+        <v>0</v>
+      </c>
+      <c r="H151" s="6">
+        <v>0</v>
+      </c>
+      <c r="I151" s="6">
+        <v>0</v>
+      </c>
+      <c r="J151" s="6">
+        <v>0</v>
+      </c>
+      <c r="K151" s="6">
+        <v>0</v>
+      </c>
+      <c r="L151" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18">
+      <c r="A152" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B152" s="6">
+        <v>0</v>
+      </c>
+      <c r="C152" s="6">
+        <v>0</v>
+      </c>
+      <c r="D152" s="6">
+        <v>0</v>
+      </c>
+      <c r="E152" s="6">
+        <v>0</v>
+      </c>
+      <c r="F152" s="6">
+        <v>0</v>
+      </c>
+      <c r="G152" s="6">
+        <v>0</v>
+      </c>
+      <c r="H152" s="6">
+        <v>0</v>
+      </c>
+      <c r="I152" s="6">
+        <v>0</v>
+      </c>
+      <c r="J152" s="6">
+        <v>0</v>
+      </c>
+      <c r="K152" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18">
+      <c r="A153" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B153" s="6">
+        <v>0</v>
+      </c>
+      <c r="C153" s="6">
+        <v>0</v>
+      </c>
+      <c r="D153" s="6">
+        <v>0</v>
+      </c>
+      <c r="E153" s="6">
+        <v>0</v>
+      </c>
+      <c r="F153" s="6">
+        <v>0</v>
+      </c>
+      <c r="G153" s="6">
+        <v>0</v>
+      </c>
+      <c r="H153" s="6">
+        <v>0</v>
+      </c>
+      <c r="I153" s="6">
+        <v>0</v>
+      </c>
+      <c r="J153" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18">
+      <c r="A154" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B154" s="6">
+        <v>0</v>
+      </c>
+      <c r="C154" s="6">
+        <v>0</v>
+      </c>
+      <c r="D154" s="6">
+        <v>0</v>
+      </c>
+      <c r="E154" s="6">
+        <v>0</v>
+      </c>
+      <c r="F154" s="6">
+        <v>0</v>
+      </c>
+      <c r="G154" s="6">
+        <v>0</v>
+      </c>
+      <c r="H154" s="6">
+        <v>0</v>
+      </c>
+      <c r="I154" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18">
+      <c r="A155" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B155" s="6">
+        <v>0</v>
+      </c>
+      <c r="C155" s="6">
+        <v>0</v>
+      </c>
+      <c r="D155" s="6">
+        <v>0</v>
+      </c>
+      <c r="E155" s="6">
+        <v>0</v>
+      </c>
+      <c r="F155" s="6">
+        <v>0</v>
+      </c>
+      <c r="G155" s="6">
+        <v>0</v>
+      </c>
+      <c r="H155" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18">
+      <c r="A156" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B156" s="6">
+        <v>0</v>
+      </c>
+      <c r="C156" s="6">
+        <v>0</v>
+      </c>
+      <c r="D156" s="6">
+        <v>0</v>
+      </c>
+      <c r="E156" s="6">
+        <v>0</v>
+      </c>
+      <c r="F156" s="6">
+        <v>0</v>
+      </c>
+      <c r="G156" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18">
+      <c r="A157" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B157" s="6">
+        <v>0</v>
+      </c>
+      <c r="C157" s="6">
+        <v>0</v>
+      </c>
+      <c r="D157" s="6">
+        <v>0</v>
+      </c>
+      <c r="E157" s="6">
+        <v>0</v>
+      </c>
+      <c r="F157" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:18">
+      <c r="A158" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B158" s="6">
+        <v>0</v>
+      </c>
+      <c r="C158" s="6">
+        <v>0</v>
+      </c>
+      <c r="D158" s="6">
+        <v>0</v>
+      </c>
+      <c r="E158" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18">
+      <c r="A159" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B159" s="6">
+        <v>0</v>
+      </c>
+      <c r="C159" s="6">
+        <v>0</v>
+      </c>
+      <c r="D159" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18">
+      <c r="A160" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B160" s="6">
+        <v>0</v>
+      </c>
+      <c r="C160" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B161" s="6">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A28:Y28"/>
+    <mergeCell ref="A55:Y55"/>
+    <mergeCell ref="A82:Y82"/>
+    <mergeCell ref="A109:Y109"/>
+    <mergeCell ref="A136:Y136"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -18431,10 +24873,10 @@
         <v>40</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>39</v>

--- a/sample-data/sample-run/Analysis.xlsx
+++ b/sample-data/sample-run/Analysis.xlsx
@@ -20,14 +20,15 @@
     <sheet name="Paid" sheetId="11" r:id="rId11"/>
     <sheet name="Reported" sheetId="12" r:id="rId12"/>
     <sheet name="Exposure" sheetId="13" r:id="rId13"/>
-    <sheet name="Diagnostics" sheetId="14" r:id="rId14"/>
+    <sheet name="Pre-Method Diagnostics" sheetId="14" r:id="rId14"/>
+    <sheet name="Post-Method Diagnostics" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="189">
   <si>
     <t>Accident Period</t>
   </si>
@@ -530,6 +531,30 @@
     <t>REPORTED FREQUENCY</t>
   </si>
   <si>
+    <t>Ultimate Severity</t>
+  </si>
+  <si>
+    <t>Ultimate Loss Rate</t>
+  </si>
+  <si>
+    <t>Ultimate Frequency</t>
+  </si>
+  <si>
+    <t>INCURRED-TO-ULTIMATE</t>
+  </si>
+  <si>
+    <t>PAID-TO-ULTIMATE</t>
+  </si>
+  <si>
+    <t>REPORTED-TO-ULTIMATE</t>
+  </si>
+  <si>
+    <t>AVERAGE IBNR</t>
+  </si>
+  <si>
+    <t>AVERAGE UNPAID</t>
+  </si>
+  <si>
     <t>Sheet</t>
   </si>
   <si>
@@ -566,10 +591,10 @@
     <t>Exposure development triangle with age-to-age factors, averages, and selected LDFs.</t>
   </si>
   <si>
-    <t>Diagnostics</t>
+    <t>Pre-Method Diagnostics</t>
   </si>
   <si>
-    <t>Post-selection diagnostic metrics including ultimate severity, loss rate, and frequency.</t>
+    <t>Post-Method Diagnostics</t>
   </si>
 </sst>
 </file>
@@ -944,7 +969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -953,18 +978,18 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -972,7 +997,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -980,7 +1005,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -988,7 +1013,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -996,15 +1021,15 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1012,7 +1037,7 @@
         <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1020,7 +1045,7 @@
         <v>45</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1028,7 +1053,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1036,7 +1061,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1044,7 +1069,7 @@
         <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1052,15 +1077,23 @@
         <v>136</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -19519,6 +19552,6007 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Y161"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="2" max="25" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2">
+        <v>2001</v>
+      </c>
+      <c r="B2" s="6">
+        <v>4561.602617345264</v>
+      </c>
+      <c r="C2" s="6">
+        <v>0.01010300000380942</v>
+      </c>
+      <c r="D2" s="6">
+        <v>2.214791785104925E-06</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2">
+        <v>2002</v>
+      </c>
+      <c r="B3" s="6">
+        <v>3650.510462048229</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0.007374212885173717</v>
+      </c>
+      <c r="D3" s="6">
+        <v>2.020049788060651E-06</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B4" s="6">
+        <v>3334.750031726463</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.005588225393396084</v>
+      </c>
+      <c r="D4" s="6">
+        <v>1.675755406021528E-06</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2">
+        <v>2004</v>
+      </c>
+      <c r="B5" s="6">
+        <v>1807.098264996499</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.00345899834407469</v>
+      </c>
+      <c r="D5" s="6">
+        <v>1.91411746172054E-06</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2">
+        <v>2005</v>
+      </c>
+      <c r="B6" s="6">
+        <v>3666.938346872904</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.006867190027689312</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1.872731248275696E-06</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2">
+        <v>2006</v>
+      </c>
+      <c r="B7" s="6">
+        <v>3199.662405274478</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.004557033737021419</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1.424223296029414E-06</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B8" s="6">
+        <v>10592.10210336286</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.01416215151909411</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1.337048244143889E-06</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2">
+        <v>2008</v>
+      </c>
+      <c r="B9" s="6">
+        <v>4409.791009799745</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.003987057685496641</v>
+      </c>
+      <c r="D9" s="6">
+        <v>9.041375604050904E-07</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2">
+        <v>2009</v>
+      </c>
+      <c r="B10" s="6">
+        <v>3861.886079880738</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.003354451901309865</v>
+      </c>
+      <c r="D10" s="6">
+        <v>8.68604570907865E-07</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B11" s="6">
+        <v>5026.920725426721</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.003614168868624826</v>
+      </c>
+      <c r="D11" s="6">
+        <v>7.189627738396509E-07</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2">
+        <v>2011</v>
+      </c>
+      <c r="B12" s="6">
+        <v>5971.802279169317</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.005353624648238385</v>
+      </c>
+      <c r="D12" s="6">
+        <v>8.964839085367507E-07</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B13" s="6">
+        <v>5646.263969687692</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.003750248487772091</v>
+      </c>
+      <c r="D13" s="6">
+        <v>6.641999927572508E-07</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2">
+        <v>2013</v>
+      </c>
+      <c r="B14" s="6">
+        <v>2638.707540376505</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.001917855946344958</v>
+      </c>
+      <c r="D14" s="6">
+        <v>7.268164118223227E-07</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B15" s="6">
+        <v>3395.325791855204</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.003776881005952719</v>
+      </c>
+      <c r="D15" s="6">
+        <v>1.112376613464546E-06</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B16" s="6">
+        <v>11400.02569939496</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.009117219344256643</v>
+      </c>
+      <c r="D16" s="6">
+        <v>7.997542799171524E-07</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
+      <c r="A17" s="2">
+        <v>2016</v>
+      </c>
+      <c r="B17" s="6">
+        <v>7383.606963645672</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.006773183189107037</v>
+      </c>
+      <c r="D17" s="6">
+        <v>9.17327157642037E-07</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
+      <c r="A18" s="2">
+        <v>2017</v>
+      </c>
+      <c r="B18" s="6">
+        <v>4542.333688046177</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.003243296448208928</v>
+      </c>
+      <c r="D18" s="6">
+        <v>7.140154534978667E-07</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
+      <c r="A19" s="2">
+        <v>2018</v>
+      </c>
+      <c r="B19" s="6">
+        <v>8716.834816223845</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.006413397320690939</v>
+      </c>
+      <c r="D19" s="6">
+        <v>7.357484059184271E-07</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
+      <c r="A20" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B20" s="6">
+        <v>8941.930468575263</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.007078112192328222</v>
+      </c>
+      <c r="D20" s="6">
+        <v>7.915642172798054E-07</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
+      <c r="A21" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B21" s="6">
+        <v>3431.711389128559</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.002761439262416636</v>
+      </c>
+      <c r="D21" s="6">
+        <v>8.046828387622275E-07</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
+      <c r="A22" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B22" s="6">
+        <v>4188.925781131618</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.002940141794494372</v>
+      </c>
+      <c r="D22" s="6">
+        <v>7.018844324570743E-07</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
+      <c r="A23" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B23" s="6">
+        <v>4360.341107090202</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.002713741512120429</v>
+      </c>
+      <c r="D23" s="6">
+        <v>6.223690866083173E-07</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
+      <c r="A24" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B24" s="6">
+        <v>10147.83267768161</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.006328793125555113</v>
+      </c>
+      <c r="D24" s="6">
+        <v>6.236595859009567E-07</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
+      <c r="A25" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="6">
+        <v>8701.6860292851</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.005062514447684894</v>
+      </c>
+      <c r="D25" s="6">
+        <v>5.817854644085352E-07</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
+      <c r="A28" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
+    </row>
+    <row r="29" spans="1:25">
+      <c r="A29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="8">
+        <v>11</v>
+      </c>
+      <c r="C29" s="8">
+        <v>23</v>
+      </c>
+      <c r="D29" s="8">
+        <v>35</v>
+      </c>
+      <c r="E29" s="8">
+        <v>47</v>
+      </c>
+      <c r="F29" s="8">
+        <v>59</v>
+      </c>
+      <c r="G29" s="8">
+        <v>71</v>
+      </c>
+      <c r="H29" s="8">
+        <v>83</v>
+      </c>
+      <c r="I29" s="8">
+        <v>95</v>
+      </c>
+      <c r="J29" s="8">
+        <v>107</v>
+      </c>
+      <c r="K29" s="8">
+        <v>119</v>
+      </c>
+      <c r="L29" s="8">
+        <v>131</v>
+      </c>
+      <c r="M29" s="8">
+        <v>143</v>
+      </c>
+      <c r="N29" s="8">
+        <v>155</v>
+      </c>
+      <c r="O29" s="8">
+        <v>167</v>
+      </c>
+      <c r="P29" s="8">
+        <v>179</v>
+      </c>
+      <c r="Q29" s="8">
+        <v>191</v>
+      </c>
+      <c r="R29" s="8">
+        <v>203</v>
+      </c>
+      <c r="S29" s="8">
+        <v>215</v>
+      </c>
+      <c r="T29" s="8">
+        <v>227</v>
+      </c>
+      <c r="U29" s="8">
+        <v>239</v>
+      </c>
+      <c r="V29" s="8">
+        <v>251</v>
+      </c>
+      <c r="W29" s="8">
+        <v>263</v>
+      </c>
+      <c r="X29" s="8">
+        <v>275</v>
+      </c>
+      <c r="Y29" s="8">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
+      <c r="A30" s="2">
+        <v>2001</v>
+      </c>
+      <c r="B30" s="6">
+        <v>0.1774930133116991</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.4863044426805704</v>
+      </c>
+      <c r="D30" s="6">
+        <v>0.5951418223132443</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.6549452434272771</v>
+      </c>
+      <c r="F30" s="6">
+        <v>0.7041348443364136</v>
+      </c>
+      <c r="G30" s="6">
+        <v>0.7517888245768218</v>
+      </c>
+      <c r="H30" s="6">
+        <v>0.7500197527076867</v>
+      </c>
+      <c r="I30" s="6">
+        <v>0.75701438366323</v>
+      </c>
+      <c r="J30" s="6">
+        <v>0.7625258582338226</v>
+      </c>
+      <c r="K30" s="6">
+        <v>0.7689478160181409</v>
+      </c>
+      <c r="L30" s="6">
+        <v>0.785435910315963</v>
+      </c>
+      <c r="M30" s="6">
+        <v>0.8017748480109679</v>
+      </c>
+      <c r="N30" s="6">
+        <v>0.800908080905278</v>
+      </c>
+      <c r="O30" s="6">
+        <v>0.8192262943939395</v>
+      </c>
+      <c r="P30" s="6">
+        <v>0.8331875695738545</v>
+      </c>
+      <c r="Q30" s="6">
+        <v>0.8774907425416026</v>
+      </c>
+      <c r="R30" s="6">
+        <v>0.8982209052841621</v>
+      </c>
+      <c r="S30" s="6">
+        <v>0.9259903894034086</v>
+      </c>
+      <c r="T30" s="6">
+        <v>0.9426334490266849</v>
+      </c>
+      <c r="U30" s="6">
+        <v>0.9426334490266849</v>
+      </c>
+      <c r="V30" s="6">
+        <v>0.9647206317627677</v>
+      </c>
+      <c r="W30" s="6">
+        <v>0.9781380792192665</v>
+      </c>
+      <c r="X30" s="6">
+        <v>0.9781380792192665</v>
+      </c>
+      <c r="Y30" s="6">
+        <v>0.9898050080401287</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25">
+      <c r="A31" s="2">
+        <v>2002</v>
+      </c>
+      <c r="B31" s="6">
+        <v>0.3898981025616916</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.5577217365474219</v>
+      </c>
+      <c r="D31" s="6">
+        <v>0.5642834296949918</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.6741386941575651</v>
+      </c>
+      <c r="F31" s="6">
+        <v>0.6830270906088814</v>
+      </c>
+      <c r="G31" s="6">
+        <v>0.7258466217305956</v>
+      </c>
+      <c r="H31" s="6">
+        <v>0.7396332087162306</v>
+      </c>
+      <c r="I31" s="6">
+        <v>0.739786784387423</v>
+      </c>
+      <c r="J31" s="6">
+        <v>0.7559959243058553</v>
+      </c>
+      <c r="K31" s="6">
+        <v>0.7632811338173474</v>
+      </c>
+      <c r="L31" s="6">
+        <v>0.7711082250616043</v>
+      </c>
+      <c r="M31" s="6">
+        <v>0.7972626304392082</v>
+      </c>
+      <c r="N31" s="6">
+        <v>0.7983198654334981</v>
+      </c>
+      <c r="O31" s="6">
+        <v>0.8303367136043954</v>
+      </c>
+      <c r="P31" s="6">
+        <v>0.8522265840514774</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>0.8647682737259968</v>
+      </c>
+      <c r="R31" s="6">
+        <v>0.9105137333041824</v>
+      </c>
+      <c r="S31" s="6">
+        <v>0.9115478945173625</v>
+      </c>
+      <c r="T31" s="6">
+        <v>0.9115478945173625</v>
+      </c>
+      <c r="U31" s="6">
+        <v>0.9501608385606566</v>
+      </c>
+      <c r="V31" s="6">
+        <v>0.9442625512777951</v>
+      </c>
+      <c r="W31" s="6">
+        <v>0.9781648451081177</v>
+      </c>
+      <c r="X31" s="6">
+        <v>0.9781648451081177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25">
+      <c r="A32" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B32" s="6">
+        <v>0.5487415758872046</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.7930205744732604</v>
+      </c>
+      <c r="D32" s="6">
+        <v>0.8583873832871312</v>
+      </c>
+      <c r="E32" s="6">
+        <v>1.020395836536639</v>
+      </c>
+      <c r="F32" s="6">
+        <v>0.9261821031675201</v>
+      </c>
+      <c r="G32" s="6">
+        <v>0.989023455752723</v>
+      </c>
+      <c r="H32" s="6">
+        <v>0.9862895153027395</v>
+      </c>
+      <c r="I32" s="6">
+        <v>0.9788441657603956</v>
+      </c>
+      <c r="J32" s="6">
+        <v>0.9770172295985208</v>
+      </c>
+      <c r="K32" s="6">
+        <v>0.9791619031459665</v>
+      </c>
+      <c r="L32" s="6">
+        <v>0.9771167117463128</v>
+      </c>
+      <c r="M32" s="6">
+        <v>0.9695579552816138</v>
+      </c>
+      <c r="N32" s="6">
+        <v>0.9646166977337037</v>
+      </c>
+      <c r="O32" s="6">
+        <v>0.9646166475155573</v>
+      </c>
+      <c r="P32" s="6">
+        <v>0.9646166475155573</v>
+      </c>
+      <c r="Q32" s="6">
+        <v>0.9646166475155573</v>
+      </c>
+      <c r="R32" s="6">
+        <v>0.9666615734764373</v>
+      </c>
+      <c r="S32" s="6">
+        <v>0.9666615734764374</v>
+      </c>
+      <c r="T32" s="6">
+        <v>0.9666615734764374</v>
+      </c>
+      <c r="U32" s="6">
+        <v>0.9666615734764374</v>
+      </c>
+      <c r="V32" s="6">
+        <v>0.9666615734764374</v>
+      </c>
+      <c r="W32" s="6">
+        <v>0.9666615734764374</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
+      <c r="A33" s="2">
+        <v>2004</v>
+      </c>
+      <c r="B33" s="6">
+        <v>0.6087754390928967</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.6949624087588413</v>
+      </c>
+      <c r="D33" s="6">
+        <v>0.7673490094862636</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.8037067298171574</v>
+      </c>
+      <c r="F33" s="6">
+        <v>0.908563831057053</v>
+      </c>
+      <c r="G33" s="6">
+        <v>0.9136067403033948</v>
+      </c>
+      <c r="H33" s="6">
+        <v>0.93046802498201</v>
+      </c>
+      <c r="I33" s="6">
+        <v>0.9376176232922946</v>
+      </c>
+      <c r="J33" s="6">
+        <v>0.9598884953334178</v>
+      </c>
+      <c r="K33" s="6">
+        <v>0.9513223400342901</v>
+      </c>
+      <c r="L33" s="6">
+        <v>0.9732775075579183</v>
+      </c>
+      <c r="M33" s="6">
+        <v>0.9622795048133106</v>
+      </c>
+      <c r="N33" s="6">
+        <v>0.9626669768852431</v>
+      </c>
+      <c r="O33" s="6">
+        <v>0.962946502192268</v>
+      </c>
+      <c r="P33" s="6">
+        <v>0.962945968139852</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>0.9666326001434391</v>
+      </c>
+      <c r="R33" s="6">
+        <v>0.9666326001434391</v>
+      </c>
+      <c r="S33" s="6">
+        <v>0.9666326001434391</v>
+      </c>
+      <c r="T33" s="6">
+        <v>0.9666326001434391</v>
+      </c>
+      <c r="U33" s="6">
+        <v>0.9666615753277039</v>
+      </c>
+      <c r="V33" s="6">
+        <v>0.9666615753277039</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22">
+      <c r="A34" s="2">
+        <v>2005</v>
+      </c>
+      <c r="B34" s="6">
+        <v>0.5313952520242472</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.6923543763156901</v>
+      </c>
+      <c r="D34" s="6">
+        <v>0.7566419047453902</v>
+      </c>
+      <c r="E34" s="6">
+        <v>0.7380910103656708</v>
+      </c>
+      <c r="F34" s="6">
+        <v>0.7655188572597177</v>
+      </c>
+      <c r="G34" s="6">
+        <v>0.7780179295611591</v>
+      </c>
+      <c r="H34" s="6">
+        <v>0.793851193219601</v>
+      </c>
+      <c r="I34" s="6">
+        <v>0.7983350333688243</v>
+      </c>
+      <c r="J34" s="6">
+        <v>0.8086455342509519</v>
+      </c>
+      <c r="K34" s="6">
+        <v>0.8307234719397025</v>
+      </c>
+      <c r="L34" s="6">
+        <v>0.8404600181645112</v>
+      </c>
+      <c r="M34" s="6">
+        <v>0.9408177746445974</v>
+      </c>
+      <c r="N34" s="6">
+        <v>0.940822824740813</v>
+      </c>
+      <c r="O34" s="6">
+        <v>0.9234735390321552</v>
+      </c>
+      <c r="P34" s="6">
+        <v>0.9326658812775719</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>0.9391882264314588</v>
+      </c>
+      <c r="R34" s="6">
+        <v>0.9534091851497288</v>
+      </c>
+      <c r="S34" s="6">
+        <v>0.9534091851497288</v>
+      </c>
+      <c r="T34" s="6">
+        <v>0.9534091851497288</v>
+      </c>
+      <c r="U34" s="6">
+        <v>0.9534091851497288</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22">
+      <c r="A35" s="2">
+        <v>2006</v>
+      </c>
+      <c r="B35" s="6">
+        <v>0.4812070054100073</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.7275410935211367</v>
+      </c>
+      <c r="D35" s="6">
+        <v>0.6323891574145887</v>
+      </c>
+      <c r="E35" s="6">
+        <v>0.6763011796663784</v>
+      </c>
+      <c r="F35" s="6">
+        <v>0.6823975855711275</v>
+      </c>
+      <c r="G35" s="6">
+        <v>0.7168194557727272</v>
+      </c>
+      <c r="H35" s="6">
+        <v>0.7484081320967417</v>
+      </c>
+      <c r="I35" s="6">
+        <v>0.7346262211764599</v>
+      </c>
+      <c r="J35" s="6">
+        <v>0.7537625179418734</v>
+      </c>
+      <c r="K35" s="6">
+        <v>0.7817348951584717</v>
+      </c>
+      <c r="L35" s="6">
+        <v>0.8467466227306627</v>
+      </c>
+      <c r="M35" s="6">
+        <v>0.8976487942691044</v>
+      </c>
+      <c r="N35" s="6">
+        <v>0.9223484674246619</v>
+      </c>
+      <c r="O35" s="6">
+        <v>0.9322805171742522</v>
+      </c>
+      <c r="P35" s="6">
+        <v>0.9328193662589724</v>
+      </c>
+      <c r="Q35" s="6">
+        <v>0.9435963479533755</v>
+      </c>
+      <c r="R35" s="6">
+        <v>0.9464978430249456</v>
+      </c>
+      <c r="S35" s="6">
+        <v>0.9534091877054536</v>
+      </c>
+      <c r="T35" s="6">
+        <v>0.9534091877054536</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22">
+      <c r="A36" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B36" s="6">
+        <v>0.3417960401252068</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.3721388378953257</v>
+      </c>
+      <c r="D36" s="6">
+        <v>0.4053034581063753</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.4541200704878069</v>
+      </c>
+      <c r="F36" s="6">
+        <v>0.5061949054631976</v>
+      </c>
+      <c r="G36" s="6">
+        <v>0.60427169867069</v>
+      </c>
+      <c r="H36" s="6">
+        <v>0.6427112217178358</v>
+      </c>
+      <c r="I36" s="6">
+        <v>0.7131030371391581</v>
+      </c>
+      <c r="J36" s="6">
+        <v>0.7641885275739411</v>
+      </c>
+      <c r="K36" s="6">
+        <v>0.8418576601009747</v>
+      </c>
+      <c r="L36" s="6">
+        <v>0.8676886158838636</v>
+      </c>
+      <c r="M36" s="6">
+        <v>0.8927581453243625</v>
+      </c>
+      <c r="N36" s="6">
+        <v>0.9071446842745871</v>
+      </c>
+      <c r="O36" s="6">
+        <v>0.9079909009673187</v>
+      </c>
+      <c r="P36" s="6">
+        <v>0.9476012798454244</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.9476012798454244</v>
+      </c>
+      <c r="R36" s="6">
+        <v>0.951004986591795</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.9534091860900933</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22">
+      <c r="A37" s="2">
+        <v>2008</v>
+      </c>
+      <c r="B37" s="6">
+        <v>0.3839646242235679</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.5320438014907882</v>
+      </c>
+      <c r="D37" s="6">
+        <v>0.6440205308915037</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0.8958139627060242</v>
+      </c>
+      <c r="F37" s="6">
+        <v>0.8682856550712024</v>
+      </c>
+      <c r="G37" s="6">
+        <v>0.8829140833386838</v>
+      </c>
+      <c r="H37" s="6">
+        <v>0.8876958728361591</v>
+      </c>
+      <c r="I37" s="6">
+        <v>0.8993798364772617</v>
+      </c>
+      <c r="J37" s="6">
+        <v>0.9045199200344594</v>
+      </c>
+      <c r="K37" s="6">
+        <v>0.9358786190289645</v>
+      </c>
+      <c r="L37" s="6">
+        <v>0.9404838206097602</v>
+      </c>
+      <c r="M37" s="6">
+        <v>0.9406390977618677</v>
+      </c>
+      <c r="N37" s="6">
+        <v>0.9269412395473177</v>
+      </c>
+      <c r="O37" s="6">
+        <v>0.9271689186559817</v>
+      </c>
+      <c r="P37" s="6">
+        <v>0.9271689186559817</v>
+      </c>
+      <c r="Q37" s="6">
+        <v>0.931722500829261</v>
+      </c>
+      <c r="R37" s="6">
+        <v>0.9513162917059513</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22">
+      <c r="A38" s="2">
+        <v>2009</v>
+      </c>
+      <c r="B38" s="6">
+        <v>0.2874907468516951</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.7017068617374652</v>
+      </c>
+      <c r="D38" s="6">
+        <v>0.6612569775410686</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0.6777545287640336</v>
+      </c>
+      <c r="F38" s="6">
+        <v>0.7227962747004689</v>
+      </c>
+      <c r="G38" s="6">
+        <v>0.7598934974663397</v>
+      </c>
+      <c r="H38" s="6">
+        <v>0.7875447004675893</v>
+      </c>
+      <c r="I38" s="6">
+        <v>0.9010040805176514</v>
+      </c>
+      <c r="J38" s="6">
+        <v>0.9010093867218216</v>
+      </c>
+      <c r="K38" s="6">
+        <v>0.9010107557224977</v>
+      </c>
+      <c r="L38" s="6">
+        <v>0.9010107557224979</v>
+      </c>
+      <c r="M38" s="6">
+        <v>0.9132150253140845</v>
+      </c>
+      <c r="N38" s="6">
+        <v>0.9405935212582079</v>
+      </c>
+      <c r="O38" s="6">
+        <v>0.9405935212582079</v>
+      </c>
+      <c r="P38" s="6">
+        <v>0.9405935212582079</v>
+      </c>
+      <c r="Q38" s="6">
+        <v>0.9405935212582079</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22">
+      <c r="A39" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B39" s="6">
+        <v>0.2634655421629862</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.5346364224761512</v>
+      </c>
+      <c r="D39" s="6">
+        <v>0.6961650041130447</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0.8088717180795838</v>
+      </c>
+      <c r="F39" s="6">
+        <v>0.9046244670840922</v>
+      </c>
+      <c r="G39" s="6">
+        <v>0.894901930060745</v>
+      </c>
+      <c r="H39" s="6">
+        <v>0.9303698739803768</v>
+      </c>
+      <c r="I39" s="6">
+        <v>0.9314649391442762</v>
+      </c>
+      <c r="J39" s="6">
+        <v>0.9270437245966141</v>
+      </c>
+      <c r="K39" s="6">
+        <v>0.9276287732999199</v>
+      </c>
+      <c r="L39" s="6">
+        <v>0.928356885410661</v>
+      </c>
+      <c r="M39" s="6">
+        <v>0.9284109627027054</v>
+      </c>
+      <c r="N39" s="6">
+        <v>0.929618045114411</v>
+      </c>
+      <c r="O39" s="6">
+        <v>0.9294199870322983</v>
+      </c>
+      <c r="P39" s="6">
+        <v>0.934983623001036</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22">
+      <c r="A40" s="2">
+        <v>2011</v>
+      </c>
+      <c r="B40" s="6">
+        <v>0.2199105591029577</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.4295653901398472</v>
+      </c>
+      <c r="D40" s="6">
+        <v>0.6335175198038844</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0.7315157723675174</v>
+      </c>
+      <c r="F40" s="6">
+        <v>0.7805231529763303</v>
+      </c>
+      <c r="G40" s="6">
+        <v>0.8429856873686451</v>
+      </c>
+      <c r="H40" s="6">
+        <v>0.889577416652755</v>
+      </c>
+      <c r="I40" s="6">
+        <v>0.889633250799592</v>
+      </c>
+      <c r="J40" s="6">
+        <v>0.9018993788455271</v>
+      </c>
+      <c r="K40" s="6">
+        <v>0.9053608914287276</v>
+      </c>
+      <c r="L40" s="6">
+        <v>0.9308831235020881</v>
+      </c>
+      <c r="M40" s="6">
+        <v>0.9280234449890445</v>
+      </c>
+      <c r="N40" s="6">
+        <v>0.9280234449890445</v>
+      </c>
+      <c r="O40" s="6">
+        <v>0.9280234449890445</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22">
+      <c r="A41" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B41" s="6">
+        <v>0.2276805778306183</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.4626251927758835</v>
+      </c>
+      <c r="D41" s="6">
+        <v>0.6046483048455629</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.6571058664841085</v>
+      </c>
+      <c r="F41" s="6">
+        <v>0.6550521199424493</v>
+      </c>
+      <c r="G41" s="6">
+        <v>0.6607893718231993</v>
+      </c>
+      <c r="H41" s="6">
+        <v>0.6634365580885512</v>
+      </c>
+      <c r="I41" s="6">
+        <v>0.6976391306118181</v>
+      </c>
+      <c r="J41" s="6">
+        <v>0.7366170395297865</v>
+      </c>
+      <c r="K41" s="6">
+        <v>0.7782713576658575</v>
+      </c>
+      <c r="L41" s="6">
+        <v>0.7840855355930287</v>
+      </c>
+      <c r="M41" s="6">
+        <v>0.9244182156823841</v>
+      </c>
+      <c r="N41" s="6">
+        <v>0.9244182156823841</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22">
+      <c r="A42" s="2">
+        <v>2013</v>
+      </c>
+      <c r="B42" s="6">
+        <v>0.3626864044201323</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.6622985631211972</v>
+      </c>
+      <c r="D42" s="6">
+        <v>0.7200808705324528</v>
+      </c>
+      <c r="E42" s="6">
+        <v>0.868129961201585</v>
+      </c>
+      <c r="F42" s="6">
+        <v>0.9208864362630995</v>
+      </c>
+      <c r="G42" s="6">
+        <v>0.9184931803134782</v>
+      </c>
+      <c r="H42" s="6">
+        <v>0.9189460303032143</v>
+      </c>
+      <c r="I42" s="6">
+        <v>0.9189460303032146</v>
+      </c>
+      <c r="J42" s="6">
+        <v>0.9207206987914692</v>
+      </c>
+      <c r="K42" s="6">
+        <v>0.9207206987914692</v>
+      </c>
+      <c r="L42" s="6">
+        <v>0.9207352747719024</v>
+      </c>
+      <c r="M42" s="6">
+        <v>0.9207352747719024</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22">
+      <c r="A43" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B43" s="6">
+        <v>0.3748676311051987</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.5121598853614686</v>
+      </c>
+      <c r="D43" s="6">
+        <v>0.7229399270914696</v>
+      </c>
+      <c r="E43" s="6">
+        <v>0.8359124428963894</v>
+      </c>
+      <c r="F43" s="6">
+        <v>0.8478633922758393</v>
+      </c>
+      <c r="G43" s="6">
+        <v>0.8770801572864003</v>
+      </c>
+      <c r="H43" s="6">
+        <v>0.8519682777570552</v>
+      </c>
+      <c r="I43" s="6">
+        <v>0.8519682777570552</v>
+      </c>
+      <c r="J43" s="6">
+        <v>0.8869696617400203</v>
+      </c>
+      <c r="K43" s="6">
+        <v>0.9052670706001843</v>
+      </c>
+      <c r="L43" s="6">
+        <v>0.8989799598076287</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22">
+      <c r="A44" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B44" s="6">
+        <v>0.1413728643009372</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.2807250761110201</v>
+      </c>
+      <c r="D44" s="6">
+        <v>0.421859400790525</v>
+      </c>
+      <c r="E44" s="6">
+        <v>0.5604351522642629</v>
+      </c>
+      <c r="F44" s="6">
+        <v>0.6197994642392909</v>
+      </c>
+      <c r="G44" s="6">
+        <v>0.7042199884510106</v>
+      </c>
+      <c r="H44" s="6">
+        <v>0.8027649255809873</v>
+      </c>
+      <c r="I44" s="6">
+        <v>0.8082083442677432</v>
+      </c>
+      <c r="J44" s="6">
+        <v>0.8108762400433268</v>
+      </c>
+      <c r="K44" s="6">
+        <v>0.8888471036204514</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22">
+      <c r="A45" s="2">
+        <v>2016</v>
+      </c>
+      <c r="B45" s="6">
+        <v>0.2384858240786435</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.4458891513204228</v>
+      </c>
+      <c r="D45" s="6">
+        <v>0.6010568034192406</v>
+      </c>
+      <c r="E45" s="6">
+        <v>0.6533438022928472</v>
+      </c>
+      <c r="F45" s="6">
+        <v>0.746320540335115</v>
+      </c>
+      <c r="G45" s="6">
+        <v>0.7698991298127917</v>
+      </c>
+      <c r="H45" s="6">
+        <v>0.8680958577617076</v>
+      </c>
+      <c r="I45" s="6">
+        <v>0.8678892633883374</v>
+      </c>
+      <c r="J45" s="6">
+        <v>0.869033146125371</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22">
+      <c r="A46" s="2">
+        <v>2017</v>
+      </c>
+      <c r="B46" s="6">
+        <v>0.3275019993637759</v>
+      </c>
+      <c r="C46" s="6">
+        <v>0.4365061791646041</v>
+      </c>
+      <c r="D46" s="6">
+        <v>0.4515041718029474</v>
+      </c>
+      <c r="E46" s="6">
+        <v>0.5911944877916602</v>
+      </c>
+      <c r="F46" s="6">
+        <v>0.6355777368126367</v>
+      </c>
+      <c r="G46" s="6">
+        <v>0.7199287716522612</v>
+      </c>
+      <c r="H46" s="6">
+        <v>0.8298549794306229</v>
+      </c>
+      <c r="I46" s="6">
+        <v>0.8560216206279738</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22">
+      <c r="A47" s="2">
+        <v>2018</v>
+      </c>
+      <c r="B47" s="6">
+        <v>0.1787941902060645</v>
+      </c>
+      <c r="C47" s="6">
+        <v>0.4111228526237655</v>
+      </c>
+      <c r="D47" s="6">
+        <v>0.5873851465388595</v>
+      </c>
+      <c r="E47" s="6">
+        <v>0.8154470158788449</v>
+      </c>
+      <c r="F47" s="6">
+        <v>0.8107652998375169</v>
+      </c>
+      <c r="G47" s="6">
+        <v>0.8213796920273352</v>
+      </c>
+      <c r="H47" s="6">
+        <v>0.8431218550372614</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22">
+      <c r="A48" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B48" s="6">
+        <v>0.1275391594769614</v>
+      </c>
+      <c r="C48" s="6">
+        <v>0.3516210457525049</v>
+      </c>
+      <c r="D48" s="6">
+        <v>0.5440476214194079</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0.6254985349685137</v>
+      </c>
+      <c r="F48" s="6">
+        <v>0.6651488725674647</v>
+      </c>
+      <c r="G48" s="6">
+        <v>0.8128826195649668</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25">
+      <c r="A49" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B49" s="6">
+        <v>0.410215143320175</v>
+      </c>
+      <c r="C49" s="6">
+        <v>0.7322044678672637</v>
+      </c>
+      <c r="D49" s="6">
+        <v>0.7199289364554846</v>
+      </c>
+      <c r="E49" s="6">
+        <v>0.7617096250968136</v>
+      </c>
+      <c r="F49" s="6">
+        <v>0.7691197091451638</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25">
+      <c r="A50" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B50" s="6">
+        <v>0.3975178557616419</v>
+      </c>
+      <c r="C50" s="6">
+        <v>0.5794556909326378</v>
+      </c>
+      <c r="D50" s="6">
+        <v>0.7092336239798147</v>
+      </c>
+      <c r="E50" s="6">
+        <v>0.7316587784877983</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25">
+      <c r="A51" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B51" s="6">
+        <v>0.5337915137306519</v>
+      </c>
+      <c r="C51" s="6">
+        <v>0.6544653406124129</v>
+      </c>
+      <c r="D51" s="6">
+        <v>0.6358379923740892</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25">
+      <c r="A52" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B52" s="6">
+        <v>0.3149739671363954</v>
+      </c>
+      <c r="C52" s="6">
+        <v>0.5336001958924254</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25">
+      <c r="A53" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B53" s="6">
+        <v>0.3524439875706842</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25">
+      <c r="A55" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="1"/>
+      <c r="R55" s="1"/>
+      <c r="S55" s="1"/>
+      <c r="T55" s="1"/>
+      <c r="U55" s="1"/>
+      <c r="V55" s="1"/>
+      <c r="W55" s="1"/>
+      <c r="X55" s="1"/>
+      <c r="Y55" s="1"/>
+    </row>
+    <row r="56" spans="1:25">
+      <c r="A56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B56" s="8">
+        <v>11</v>
+      </c>
+      <c r="C56" s="8">
+        <v>23</v>
+      </c>
+      <c r="D56" s="8">
+        <v>35</v>
+      </c>
+      <c r="E56" s="8">
+        <v>47</v>
+      </c>
+      <c r="F56" s="8">
+        <v>59</v>
+      </c>
+      <c r="G56" s="8">
+        <v>71</v>
+      </c>
+      <c r="H56" s="8">
+        <v>83</v>
+      </c>
+      <c r="I56" s="8">
+        <v>95</v>
+      </c>
+      <c r="J56" s="8">
+        <v>107</v>
+      </c>
+      <c r="K56" s="8">
+        <v>119</v>
+      </c>
+      <c r="L56" s="8">
+        <v>131</v>
+      </c>
+      <c r="M56" s="8">
+        <v>143</v>
+      </c>
+      <c r="N56" s="8">
+        <v>155</v>
+      </c>
+      <c r="O56" s="8">
+        <v>167</v>
+      </c>
+      <c r="P56" s="8">
+        <v>179</v>
+      </c>
+      <c r="Q56" s="8">
+        <v>191</v>
+      </c>
+      <c r="R56" s="8">
+        <v>203</v>
+      </c>
+      <c r="S56" s="8">
+        <v>215</v>
+      </c>
+      <c r="T56" s="8">
+        <v>227</v>
+      </c>
+      <c r="U56" s="8">
+        <v>239</v>
+      </c>
+      <c r="V56" s="8">
+        <v>251</v>
+      </c>
+      <c r="W56" s="8">
+        <v>263</v>
+      </c>
+      <c r="X56" s="8">
+        <v>275</v>
+      </c>
+      <c r="Y56" s="8">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25">
+      <c r="A57" s="2">
+        <v>2001</v>
+      </c>
+      <c r="B57" s="6">
+        <v>0.1020048025432875</v>
+      </c>
+      <c r="C57" s="6">
+        <v>0.3276763604927088</v>
+      </c>
+      <c r="D57" s="6">
+        <v>0.4835895770044493</v>
+      </c>
+      <c r="E57" s="6">
+        <v>0.5978566879893654</v>
+      </c>
+      <c r="F57" s="6">
+        <v>0.6958602012788564</v>
+      </c>
+      <c r="G57" s="6">
+        <v>0.7144926059740502</v>
+      </c>
+      <c r="H57" s="6">
+        <v>0.7076088402905059</v>
+      </c>
+      <c r="I57" s="6">
+        <v>0.7171638257257067</v>
+      </c>
+      <c r="J57" s="6">
+        <v>0.7241189846150555</v>
+      </c>
+      <c r="K57" s="6">
+        <v>0.7328286460898247</v>
+      </c>
+      <c r="L57" s="6">
+        <v>0.7502908264307616</v>
+      </c>
+      <c r="M57" s="6">
+        <v>0.7682817450272829</v>
+      </c>
+      <c r="N57" s="6">
+        <v>0.7808017262583115</v>
+      </c>
+      <c r="O57" s="6">
+        <v>0.800634550757207</v>
+      </c>
+      <c r="P57" s="6">
+        <v>0.8178565876877902</v>
+      </c>
+      <c r="Q57" s="6">
+        <v>0.8429430859860721</v>
+      </c>
+      <c r="R57" s="6">
+        <v>0.8704938533264414</v>
+      </c>
+      <c r="S57" s="6">
+        <v>0.8940312185542948</v>
+      </c>
+      <c r="T57" s="6">
+        <v>0.9282656912439637</v>
+      </c>
+      <c r="U57" s="6">
+        <v>0.9282656912439637</v>
+      </c>
+      <c r="V57" s="6">
+        <v>0.9351767335660757</v>
+      </c>
+      <c r="W57" s="6">
+        <v>0.9421295681406807</v>
+      </c>
+      <c r="X57" s="6">
+        <v>0.9480723950689955</v>
+      </c>
+      <c r="Y57" s="6">
+        <v>0.9517995844492602</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25">
+      <c r="A58" s="2">
+        <v>2002</v>
+      </c>
+      <c r="B58" s="6">
+        <v>0.1501708883033386</v>
+      </c>
+      <c r="C58" s="6">
+        <v>0.3828528637008892</v>
+      </c>
+      <c r="D58" s="6">
+        <v>0.5128262915534597</v>
+      </c>
+      <c r="E58" s="6">
+        <v>0.5539975473156903</v>
+      </c>
+      <c r="F58" s="6">
+        <v>0.6233749339516133</v>
+      </c>
+      <c r="G58" s="6">
+        <v>0.6814886999036802</v>
+      </c>
+      <c r="H58" s="6">
+        <v>0.6968661855573445</v>
+      </c>
+      <c r="I58" s="6">
+        <v>0.7092104255505443</v>
+      </c>
+      <c r="J58" s="6">
+        <v>0.726807386027946</v>
+      </c>
+      <c r="K58" s="6">
+        <v>0.7354720095009161</v>
+      </c>
+      <c r="L58" s="6">
+        <v>0.7484141382418308</v>
+      </c>
+      <c r="M58" s="6">
+        <v>0.7624606476840754</v>
+      </c>
+      <c r="N58" s="6">
+        <v>0.7799518103557115</v>
+      </c>
+      <c r="O58" s="6">
+        <v>0.7998467164755199</v>
+      </c>
+      <c r="P58" s="6">
+        <v>0.8167514080671423</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>0.8326989896805086</v>
+      </c>
+      <c r="R58" s="6">
+        <v>0.8564249308898761</v>
+      </c>
+      <c r="S58" s="6">
+        <v>0.8737309543329836</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0.8876094981828682</v>
+      </c>
+      <c r="U58" s="6">
+        <v>0.898363233220718</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.907422434431885</v>
+      </c>
+      <c r="W58" s="6">
+        <v>0.9161053683170696</v>
+      </c>
+      <c r="X58" s="6">
+        <v>0.9243396527410097</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25">
+      <c r="A59" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B59" s="6">
+        <v>0.2521101597982711</v>
+      </c>
+      <c r="C59" s="6">
+        <v>0.6261671964284597</v>
+      </c>
+      <c r="D59" s="6">
+        <v>0.7228744329371674</v>
+      </c>
+      <c r="E59" s="6">
+        <v>0.7879382613264545</v>
+      </c>
+      <c r="F59" s="6">
+        <v>0.9116537351823047</v>
+      </c>
+      <c r="G59" s="6">
+        <v>0.9570357089782421</v>
+      </c>
+      <c r="H59" s="6">
+        <v>0.9584780674018401</v>
+      </c>
+      <c r="I59" s="6">
+        <v>0.9651983601740897</v>
+      </c>
+      <c r="J59" s="6">
+        <v>0.9638109475765492</v>
+      </c>
+      <c r="K59" s="6">
+        <v>0.9661677282258639</v>
+      </c>
+      <c r="L59" s="6">
+        <v>0.9643347587124138</v>
+      </c>
+      <c r="M59" s="6">
+        <v>0.964546091020026</v>
+      </c>
+      <c r="N59" s="6">
+        <v>0.9646166977337037</v>
+      </c>
+      <c r="O59" s="6">
+        <v>0.9646169775205187</v>
+      </c>
+      <c r="P59" s="6">
+        <v>0.9646169775205187</v>
+      </c>
+      <c r="Q59" s="6">
+        <v>0.9646166475155573</v>
+      </c>
+      <c r="R59" s="6">
+        <v>0.9666615734764373</v>
+      </c>
+      <c r="S59" s="6">
+        <v>0.9666615734764374</v>
+      </c>
+      <c r="T59" s="6">
+        <v>0.9666615734764374</v>
+      </c>
+      <c r="U59" s="6">
+        <v>0.9666615734764374</v>
+      </c>
+      <c r="V59" s="6">
+        <v>0.9666615734764374</v>
+      </c>
+      <c r="W59" s="6">
+        <v>0.9666615734764374</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25">
+      <c r="A60" s="2">
+        <v>2004</v>
+      </c>
+      <c r="B60" s="6">
+        <v>0.2212011018040755</v>
+      </c>
+      <c r="C60" s="6">
+        <v>0.539021375891143</v>
+      </c>
+      <c r="D60" s="6">
+        <v>0.6948606774550276</v>
+      </c>
+      <c r="E60" s="6">
+        <v>0.778095518994272</v>
+      </c>
+      <c r="F60" s="6">
+        <v>0.908563831057053</v>
+      </c>
+      <c r="G60" s="6">
+        <v>0.9119023404252207</v>
+      </c>
+      <c r="H60" s="6">
+        <v>0.9267334191635346</v>
+      </c>
+      <c r="I60" s="6">
+        <v>0.9339641934410299</v>
+      </c>
+      <c r="J60" s="6">
+        <v>0.9512255629188456</v>
+      </c>
+      <c r="K60" s="6">
+        <v>0.9453932219365062</v>
+      </c>
+      <c r="L60" s="6">
+        <v>0.9487868523316811</v>
+      </c>
+      <c r="M60" s="6">
+        <v>0.9548539036693825</v>
+      </c>
+      <c r="N60" s="6">
+        <v>0.9552504659952019</v>
+      </c>
+      <c r="O60" s="6">
+        <v>0.9569855682058795</v>
+      </c>
+      <c r="P60" s="6">
+        <v>0.9575418576553107</v>
+      </c>
+      <c r="Q60" s="6">
+        <v>0.9666326001434391</v>
+      </c>
+      <c r="R60" s="6">
+        <v>0.9666326001434391</v>
+      </c>
+      <c r="S60" s="6">
+        <v>0.9666326001434391</v>
+      </c>
+      <c r="T60" s="6">
+        <v>0.9666326001434391</v>
+      </c>
+      <c r="U60" s="6">
+        <v>0.9666615753277039</v>
+      </c>
+      <c r="V60" s="6">
+        <v>0.9666615753277039</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25">
+      <c r="A61" s="2">
+        <v>2005</v>
+      </c>
+      <c r="B61" s="6">
+        <v>0.2589565892472369</v>
+      </c>
+      <c r="C61" s="6">
+        <v>0.5259540988027742</v>
+      </c>
+      <c r="D61" s="6">
+        <v>0.6665900030589134</v>
+      </c>
+      <c r="E61" s="6">
+        <v>0.6958426629418771</v>
+      </c>
+      <c r="F61" s="6">
+        <v>0.7478099934780861</v>
+      </c>
+      <c r="G61" s="6">
+        <v>0.7633286361423069</v>
+      </c>
+      <c r="H61" s="6">
+        <v>0.7794306266428075</v>
+      </c>
+      <c r="I61" s="6">
+        <v>0.7875467597174095</v>
+      </c>
+      <c r="J61" s="6">
+        <v>0.7908304781683458</v>
+      </c>
+      <c r="K61" s="6">
+        <v>0.8145619408048221</v>
+      </c>
+      <c r="L61" s="6">
+        <v>0.8377004211436837</v>
+      </c>
+      <c r="M61" s="6">
+        <v>0.8546721111583141</v>
+      </c>
+      <c r="N61" s="6">
+        <v>0.8826384217557215</v>
+      </c>
+      <c r="O61" s="6">
+        <v>0.8992911533046037</v>
+      </c>
+      <c r="P61" s="6">
+        <v>0.9263810645935686</v>
+      </c>
+      <c r="Q61" s="6">
+        <v>0.9337573585726112</v>
+      </c>
+      <c r="R61" s="6">
+        <v>0.9518140000357271</v>
+      </c>
+      <c r="S61" s="6">
+        <v>0.9534091851497288</v>
+      </c>
+      <c r="T61" s="6">
+        <v>0.9534091851497288</v>
+      </c>
+      <c r="U61" s="6">
+        <v>0.9534091851497288</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25">
+      <c r="A62" s="2">
+        <v>2006</v>
+      </c>
+      <c r="B62" s="6">
+        <v>0.178908416119223</v>
+      </c>
+      <c r="C62" s="6">
+        <v>0.4394912574176638</v>
+      </c>
+      <c r="D62" s="6">
+        <v>0.5611636626069965</v>
+      </c>
+      <c r="E62" s="6">
+        <v>0.6111596557846573</v>
+      </c>
+      <c r="F62" s="6">
+        <v>0.6485543563866579</v>
+      </c>
+      <c r="G62" s="6">
+        <v>0.6787508787953613</v>
+      </c>
+      <c r="H62" s="6">
+        <v>0.7068174136720249</v>
+      </c>
+      <c r="I62" s="6">
+        <v>0.7116165362603174</v>
+      </c>
+      <c r="J62" s="6">
+        <v>0.7340991687417022</v>
+      </c>
+      <c r="K62" s="6">
+        <v>0.7641874819642077</v>
+      </c>
+      <c r="L62" s="6">
+        <v>0.8346681132470125</v>
+      </c>
+      <c r="M62" s="6">
+        <v>0.8577349990659945</v>
+      </c>
+      <c r="N62" s="6">
+        <v>0.8666767851276296</v>
+      </c>
+      <c r="O62" s="6">
+        <v>0.8828743399147397</v>
+      </c>
+      <c r="P62" s="6">
+        <v>0.8888877299004988</v>
+      </c>
+      <c r="Q62" s="6">
+        <v>0.8963124070890689</v>
+      </c>
+      <c r="R62" s="6">
+        <v>0.9065929761366701</v>
+      </c>
+      <c r="S62" s="6">
+        <v>0.9135149071291965</v>
+      </c>
+      <c r="T62" s="6">
+        <v>0.9185456602140453</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25">
+      <c r="A63" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B63" s="6">
+        <v>0.09980009653606313</v>
+      </c>
+      <c r="C63" s="6">
+        <v>0.2186419215351277</v>
+      </c>
+      <c r="D63" s="6">
+        <v>0.2831082220866129</v>
+      </c>
+      <c r="E63" s="6">
+        <v>0.3605202663590564</v>
+      </c>
+      <c r="F63" s="6">
+        <v>0.4276096961290448</v>
+      </c>
+      <c r="G63" s="6">
+        <v>0.5193959015610722</v>
+      </c>
+      <c r="H63" s="6">
+        <v>0.5795133557263199</v>
+      </c>
+      <c r="I63" s="6">
+        <v>0.6245082304459318</v>
+      </c>
+      <c r="J63" s="6">
+        <v>0.6748892930481543</v>
+      </c>
+      <c r="K63" s="6">
+        <v>0.7321715532018928</v>
+      </c>
+      <c r="L63" s="6">
+        <v>0.7923710805139164</v>
+      </c>
+      <c r="M63" s="6">
+        <v>0.8319895063943042</v>
+      </c>
+      <c r="N63" s="6">
+        <v>0.8661332718255518</v>
+      </c>
+      <c r="O63" s="6">
+        <v>0.8911713873591877</v>
+      </c>
+      <c r="P63" s="6">
+        <v>0.9150681806324766</v>
+      </c>
+      <c r="Q63" s="6">
+        <v>0.9416553009545084</v>
+      </c>
+      <c r="R63" s="6">
+        <v>0.9475736972217413</v>
+      </c>
+      <c r="S63" s="6">
+        <v>0.9494294008052852</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25">
+      <c r="A64" s="2">
+        <v>2008</v>
+      </c>
+      <c r="B64" s="6">
+        <v>0.2439781187305212</v>
+      </c>
+      <c r="C64" s="6">
+        <v>0.446231071862794</v>
+      </c>
+      <c r="D64" s="6">
+        <v>0.6001766472581787</v>
+      </c>
+      <c r="E64" s="6">
+        <v>0.820138754677265</v>
+      </c>
+      <c r="F64" s="6">
+        <v>0.8487775990396705</v>
+      </c>
+      <c r="G64" s="6">
+        <v>0.8749334752217945</v>
+      </c>
+      <c r="H64" s="6">
+        <v>0.8810508759065144</v>
+      </c>
+      <c r="I64" s="6">
+        <v>0.8866835386617244</v>
+      </c>
+      <c r="J64" s="6">
+        <v>0.8970994025248835</v>
+      </c>
+      <c r="K64" s="6">
+        <v>0.9091245023280794</v>
+      </c>
+      <c r="L64" s="6">
+        <v>0.9188477025925322</v>
+      </c>
+      <c r="M64" s="6">
+        <v>0.9206314318014481</v>
+      </c>
+      <c r="N64" s="6">
+        <v>0.9227665245180195</v>
+      </c>
+      <c r="O64" s="6">
+        <v>0.9238149777062528</v>
+      </c>
+      <c r="P64" s="6">
+        <v>0.9244205677066414</v>
+      </c>
+      <c r="Q64" s="6">
+        <v>0.9268666791928123</v>
+      </c>
+      <c r="R64" s="6">
+        <v>0.9513162917059513</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17">
+      <c r="A65" s="2">
+        <v>2009</v>
+      </c>
+      <c r="B65" s="6">
+        <v>0.1838977228358054</v>
+      </c>
+      <c r="C65" s="6">
+        <v>0.5969256937085886</v>
+      </c>
+      <c r="D65" s="6">
+        <v>0.652982238672581</v>
+      </c>
+      <c r="E65" s="6">
+        <v>0.6707643051886731</v>
+      </c>
+      <c r="F65" s="6">
+        <v>0.7197590034334148</v>
+      </c>
+      <c r="G65" s="6">
+        <v>0.7568337066687872</v>
+      </c>
+      <c r="H65" s="6">
+        <v>0.7795981291022154</v>
+      </c>
+      <c r="I65" s="6">
+        <v>0.8188958771871244</v>
+      </c>
+      <c r="J65" s="6">
+        <v>0.8489364214766065</v>
+      </c>
+      <c r="K65" s="6">
+        <v>0.8613984770791925</v>
+      </c>
+      <c r="L65" s="6">
+        <v>0.8695020378011478</v>
+      </c>
+      <c r="M65" s="6">
+        <v>0.8960598125338495</v>
+      </c>
+      <c r="N65" s="6">
+        <v>0.9405935212582079</v>
+      </c>
+      <c r="O65" s="6">
+        <v>0.9405935212582079</v>
+      </c>
+      <c r="P65" s="6">
+        <v>0.9405935212582079</v>
+      </c>
+      <c r="Q65" s="6">
+        <v>0.9405935212582079</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17">
+      <c r="A66" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B66" s="6">
+        <v>0.1782802202734039</v>
+      </c>
+      <c r="C66" s="6">
+        <v>0.4926027324262431</v>
+      </c>
+      <c r="D66" s="6">
+        <v>0.66976994546278</v>
+      </c>
+      <c r="E66" s="6">
+        <v>0.7880761022907177</v>
+      </c>
+      <c r="F66" s="6">
+        <v>0.8613016613017789</v>
+      </c>
+      <c r="G66" s="6">
+        <v>0.8792677986643325</v>
+      </c>
+      <c r="H66" s="6">
+        <v>0.9222775934923017</v>
+      </c>
+      <c r="I66" s="6">
+        <v>0.9238825302669056</v>
+      </c>
+      <c r="J66" s="6">
+        <v>0.9270437245966141</v>
+      </c>
+      <c r="K66" s="6">
+        <v>0.9276287732999199</v>
+      </c>
+      <c r="L66" s="6">
+        <v>0.9280989560409275</v>
+      </c>
+      <c r="M66" s="6">
+        <v>0.9281530333329719</v>
+      </c>
+      <c r="N66" s="6">
+        <v>0.9287434607955042</v>
+      </c>
+      <c r="O66" s="6">
+        <v>0.9294199870322983</v>
+      </c>
+      <c r="P66" s="6">
+        <v>0.934983623001036</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17">
+      <c r="A67" s="2">
+        <v>2011</v>
+      </c>
+      <c r="B67" s="6">
+        <v>0.1763353693055424</v>
+      </c>
+      <c r="C67" s="6">
+        <v>0.4063785158487548</v>
+      </c>
+      <c r="D67" s="6">
+        <v>0.6335175198038844</v>
+      </c>
+      <c r="E67" s="6">
+        <v>0.6813738452184407</v>
+      </c>
+      <c r="F67" s="6">
+        <v>0.7378416035267885</v>
+      </c>
+      <c r="G67" s="6">
+        <v>0.8034205218474058</v>
+      </c>
+      <c r="H67" s="6">
+        <v>0.8825374312199717</v>
+      </c>
+      <c r="I67" s="6">
+        <v>0.8842757228205373</v>
+      </c>
+      <c r="J67" s="6">
+        <v>0.8882996417207084</v>
+      </c>
+      <c r="K67" s="6">
+        <v>0.8951100207289137</v>
+      </c>
+      <c r="L67" s="6">
+        <v>0.8997692511787672</v>
+      </c>
+      <c r="M67" s="6">
+        <v>0.9090666400567112</v>
+      </c>
+      <c r="N67" s="6">
+        <v>0.9137506047268323</v>
+      </c>
+      <c r="O67" s="6">
+        <v>0.9166787529302448</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17">
+      <c r="A68" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B68" s="6">
+        <v>0.154420665774008</v>
+      </c>
+      <c r="C68" s="6">
+        <v>0.430147194874706</v>
+      </c>
+      <c r="D68" s="6">
+        <v>0.5418339570102365</v>
+      </c>
+      <c r="E68" s="6">
+        <v>0.6450204267957995</v>
+      </c>
+      <c r="F68" s="6">
+        <v>0.651533200563143</v>
+      </c>
+      <c r="G68" s="6">
+        <v>0.6557748669832423</v>
+      </c>
+      <c r="H68" s="6">
+        <v>0.6627067445853545</v>
+      </c>
+      <c r="I68" s="6">
+        <v>0.688817242663365</v>
+      </c>
+      <c r="J68" s="6">
+        <v>0.7105483319737379</v>
+      </c>
+      <c r="K68" s="6">
+        <v>0.7138020353906741</v>
+      </c>
+      <c r="L68" s="6">
+        <v>0.7350045712030213</v>
+      </c>
+      <c r="M68" s="6">
+        <v>0.7765266749330286</v>
+      </c>
+      <c r="N68" s="6">
+        <v>0.809511704929012</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17">
+      <c r="A69" s="2">
+        <v>2013</v>
+      </c>
+      <c r="B69" s="6">
+        <v>0.2632250584086615</v>
+      </c>
+      <c r="C69" s="6">
+        <v>0.6057106458430505</v>
+      </c>
+      <c r="D69" s="6">
+        <v>0.7078919212479657</v>
+      </c>
+      <c r="E69" s="6">
+        <v>0.7765790855121932</v>
+      </c>
+      <c r="F69" s="6">
+        <v>0.9208864362630995</v>
+      </c>
+      <c r="G69" s="6">
+        <v>0.9184931803134782</v>
+      </c>
+      <c r="H69" s="6">
+        <v>0.9189460303032143</v>
+      </c>
+      <c r="I69" s="6">
+        <v>0.9189460303032146</v>
+      </c>
+      <c r="J69" s="6">
+        <v>0.9207206987914692</v>
+      </c>
+      <c r="K69" s="6">
+        <v>0.9207206987914692</v>
+      </c>
+      <c r="L69" s="6">
+        <v>0.9207352747719024</v>
+      </c>
+      <c r="M69" s="6">
+        <v>0.9207352747719024</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17">
+      <c r="A70" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B70" s="6">
+        <v>0.2663558453396805</v>
+      </c>
+      <c r="C70" s="6">
+        <v>0.4775896159860986</v>
+      </c>
+      <c r="D70" s="6">
+        <v>0.5992655247106849</v>
+      </c>
+      <c r="E70" s="6">
+        <v>0.7630779775970078</v>
+      </c>
+      <c r="F70" s="6">
+        <v>0.8141956805395461</v>
+      </c>
+      <c r="G70" s="6">
+        <v>0.8277095441569106</v>
+      </c>
+      <c r="H70" s="6">
+        <v>0.8327676283039805</v>
+      </c>
+      <c r="I70" s="6">
+        <v>0.8352399894777703</v>
+      </c>
+      <c r="J70" s="6">
+        <v>0.8405244215992123</v>
+      </c>
+      <c r="K70" s="6">
+        <v>0.8923258296247814</v>
+      </c>
+      <c r="L70" s="6">
+        <v>0.8989799598076287</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17">
+      <c r="A71" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B71" s="6">
+        <v>0.09995364881321543</v>
+      </c>
+      <c r="C71" s="6">
+        <v>0.2219371944377546</v>
+      </c>
+      <c r="D71" s="6">
+        <v>0.3731314422507768</v>
+      </c>
+      <c r="E71" s="6">
+        <v>0.5467334433434795</v>
+      </c>
+      <c r="F71" s="6">
+        <v>0.5871294313367722</v>
+      </c>
+      <c r="G71" s="6">
+        <v>0.6537203392816954</v>
+      </c>
+      <c r="H71" s="6">
+        <v>0.7261357121557389</v>
+      </c>
+      <c r="I71" s="6">
+        <v>0.7658777791417605</v>
+      </c>
+      <c r="J71" s="6">
+        <v>0.7768585241554828</v>
+      </c>
+      <c r="K71" s="6">
+        <v>0.8839254279469568</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17">
+      <c r="A72" s="2">
+        <v>2016</v>
+      </c>
+      <c r="B72" s="6">
+        <v>0.1177595249059367</v>
+      </c>
+      <c r="C72" s="6">
+        <v>0.3903911637912204</v>
+      </c>
+      <c r="D72" s="6">
+        <v>0.5518282861791977</v>
+      </c>
+      <c r="E72" s="6">
+        <v>0.6210473713401334</v>
+      </c>
+      <c r="F72" s="6">
+        <v>0.6677757544126824</v>
+      </c>
+      <c r="G72" s="6">
+        <v>0.7360614998931631</v>
+      </c>
+      <c r="H72" s="6">
+        <v>0.8388125557797995</v>
+      </c>
+      <c r="I72" s="6">
+        <v>0.8443684720175973</v>
+      </c>
+      <c r="J72" s="6">
+        <v>0.8537368899360257</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17">
+      <c r="A73" s="2">
+        <v>2017</v>
+      </c>
+      <c r="B73" s="6">
+        <v>0.2389939460740066</v>
+      </c>
+      <c r="C73" s="6">
+        <v>0.4151502938607212</v>
+      </c>
+      <c r="D73" s="6">
+        <v>0.4473355182802272</v>
+      </c>
+      <c r="E73" s="6">
+        <v>0.5044409603534119</v>
+      </c>
+      <c r="F73" s="6">
+        <v>0.5485325175428405</v>
+      </c>
+      <c r="G73" s="6">
+        <v>0.6074940441002283</v>
+      </c>
+      <c r="H73" s="6">
+        <v>0.7845162960965218</v>
+      </c>
+      <c r="I73" s="6">
+        <v>0.8560216206279738</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17">
+      <c r="A74" s="2">
+        <v>2018</v>
+      </c>
+      <c r="B74" s="6">
+        <v>0.1215765898760816</v>
+      </c>
+      <c r="C74" s="6">
+        <v>0.3495467753373885</v>
+      </c>
+      <c r="D74" s="6">
+        <v>0.5187035175646283</v>
+      </c>
+      <c r="E74" s="6">
+        <v>0.7124201089824721</v>
+      </c>
+      <c r="F74" s="6">
+        <v>0.7533546896158243</v>
+      </c>
+      <c r="G74" s="6">
+        <v>0.7957472389922399</v>
+      </c>
+      <c r="H74" s="6">
+        <v>0.8431218550372614</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17">
+      <c r="A75" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B75" s="6">
+        <v>0.09044660206120246</v>
+      </c>
+      <c r="C75" s="6">
+        <v>0.2418959289457807</v>
+      </c>
+      <c r="D75" s="6">
+        <v>0.4232443617958485</v>
+      </c>
+      <c r="E75" s="6">
+        <v>0.500475537945321</v>
+      </c>
+      <c r="F75" s="6">
+        <v>0.616205440806568</v>
+      </c>
+      <c r="G75" s="6">
+        <v>0.7488830386423445</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17">
+      <c r="A76" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B76" s="6">
+        <v>0.2246438298135933</v>
+      </c>
+      <c r="C76" s="6">
+        <v>0.573628895256607</v>
+      </c>
+      <c r="D76" s="6">
+        <v>0.6770392784957383</v>
+      </c>
+      <c r="E76" s="6">
+        <v>0.7589343402120278</v>
+      </c>
+      <c r="F76" s="6">
+        <v>0.7668815320256295</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17">
+      <c r="A77" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B77" s="6">
+        <v>0.1980235683753461</v>
+      </c>
+      <c r="C77" s="6">
+        <v>0.3956764759591354</v>
+      </c>
+      <c r="D77" s="6">
+        <v>0.6593591022105426</v>
+      </c>
+      <c r="E77" s="6">
+        <v>0.7053721738909493</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17">
+      <c r="A78" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B78" s="6">
+        <v>0.2361798482533083</v>
+      </c>
+      <c r="C78" s="6">
+        <v>0.5737681167558415</v>
+      </c>
+      <c r="D78" s="6">
+        <v>0.6079332886723602</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17">
+      <c r="A79" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B79" s="6">
+        <v>0.1186457242545981</v>
+      </c>
+      <c r="C79" s="6">
+        <v>0.3874152970190023</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17">
+      <c r="A80" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B80" s="6">
+        <v>0.1406551738036357</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25">
+      <c r="A82" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="1"/>
+      <c r="M82" s="1"/>
+      <c r="N82" s="1"/>
+      <c r="O82" s="1"/>
+      <c r="P82" s="1"/>
+      <c r="Q82" s="1"/>
+      <c r="R82" s="1"/>
+      <c r="S82" s="1"/>
+      <c r="T82" s="1"/>
+      <c r="U82" s="1"/>
+      <c r="V82" s="1"/>
+      <c r="W82" s="1"/>
+      <c r="X82" s="1"/>
+      <c r="Y82" s="1"/>
+    </row>
+    <row r="83" spans="1:25">
+      <c r="A83" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B83" s="8">
+        <v>11</v>
+      </c>
+      <c r="C83" s="8">
+        <v>23</v>
+      </c>
+      <c r="D83" s="8">
+        <v>35</v>
+      </c>
+      <c r="E83" s="8">
+        <v>47</v>
+      </c>
+      <c r="F83" s="8">
+        <v>59</v>
+      </c>
+      <c r="G83" s="8">
+        <v>71</v>
+      </c>
+      <c r="H83" s="8">
+        <v>83</v>
+      </c>
+      <c r="I83" s="8">
+        <v>95</v>
+      </c>
+      <c r="J83" s="8">
+        <v>107</v>
+      </c>
+      <c r="K83" s="8">
+        <v>119</v>
+      </c>
+      <c r="L83" s="8">
+        <v>131</v>
+      </c>
+      <c r="M83" s="8">
+        <v>143</v>
+      </c>
+      <c r="N83" s="8">
+        <v>155</v>
+      </c>
+      <c r="O83" s="8">
+        <v>167</v>
+      </c>
+      <c r="P83" s="8">
+        <v>179</v>
+      </c>
+      <c r="Q83" s="8">
+        <v>191</v>
+      </c>
+      <c r="R83" s="8">
+        <v>203</v>
+      </c>
+      <c r="S83" s="8">
+        <v>215</v>
+      </c>
+      <c r="T83" s="8">
+        <v>227</v>
+      </c>
+      <c r="U83" s="8">
+        <v>239</v>
+      </c>
+      <c r="V83" s="8">
+        <v>251</v>
+      </c>
+      <c r="W83" s="8">
+        <v>263</v>
+      </c>
+      <c r="X83" s="8">
+        <v>275</v>
+      </c>
+      <c r="Y83" s="8">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25">
+      <c r="A84" s="2">
+        <v>2001</v>
+      </c>
+      <c r="B84" s="6">
+        <v>0.9096014042899344</v>
+      </c>
+      <c r="C84" s="6">
+        <v>0.9736313168072384</v>
+      </c>
+      <c r="D84" s="6">
+        <v>0.9755145495283356</v>
+      </c>
+      <c r="E84" s="6">
+        <v>0.9755145495283356</v>
+      </c>
+      <c r="F84" s="6">
+        <v>0.9755145495283356</v>
+      </c>
+      <c r="G84" s="6">
+        <v>0.9755145495283356</v>
+      </c>
+      <c r="H84" s="6">
+        <v>0.9999965749025989</v>
+      </c>
+      <c r="I84" s="6">
+        <v>0.9999965749025989</v>
+      </c>
+      <c r="J84" s="6">
+        <v>0.9999965749025989</v>
+      </c>
+      <c r="K84" s="6">
+        <v>0.9999965749025989</v>
+      </c>
+      <c r="L84" s="6">
+        <v>0.9999965749025989</v>
+      </c>
+      <c r="M84" s="6">
+        <v>0.9999965749025989</v>
+      </c>
+      <c r="N84" s="6">
+        <v>0.9999965749025989</v>
+      </c>
+      <c r="O84" s="6">
+        <v>0.9999965749025989</v>
+      </c>
+      <c r="P84" s="6">
+        <v>0.9999965749025989</v>
+      </c>
+      <c r="Q84" s="6">
+        <v>0.9999965749025989</v>
+      </c>
+      <c r="R84" s="6">
+        <v>0.9999965749025989</v>
+      </c>
+      <c r="S84" s="6">
+        <v>0.9999965749025989</v>
+      </c>
+      <c r="T84" s="6">
+        <v>0.9999965749025989</v>
+      </c>
+      <c r="U84" s="6">
+        <v>0.9999965749025989</v>
+      </c>
+      <c r="V84" s="6">
+        <v>0.9999965749025989</v>
+      </c>
+      <c r="W84" s="6">
+        <v>0.9999965749025989</v>
+      </c>
+      <c r="X84" s="6">
+        <v>0.9999965749025989</v>
+      </c>
+      <c r="Y84" s="6">
+        <v>0.9999965749025989</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25">
+      <c r="A85" s="2">
+        <v>2002</v>
+      </c>
+      <c r="B85" s="6">
+        <v>0.9412990120881144</v>
+      </c>
+      <c r="C85" s="6">
+        <v>0.9736877952997485</v>
+      </c>
+      <c r="D85" s="6">
+        <v>0.9736877952997485</v>
+      </c>
+      <c r="E85" s="6">
+        <v>0.9736877952997485</v>
+      </c>
+      <c r="F85" s="6">
+        <v>0.9736877952997485</v>
+      </c>
+      <c r="G85" s="6">
+        <v>1.000003681659201</v>
+      </c>
+      <c r="H85" s="6">
+        <v>1.000003681659201</v>
+      </c>
+      <c r="I85" s="6">
+        <v>1.000003681659201</v>
+      </c>
+      <c r="J85" s="6">
+        <v>1.000003681659201</v>
+      </c>
+      <c r="K85" s="6">
+        <v>1.000003681659201</v>
+      </c>
+      <c r="L85" s="6">
+        <v>1.000003681659201</v>
+      </c>
+      <c r="M85" s="6">
+        <v>1.000003681659201</v>
+      </c>
+      <c r="N85" s="6">
+        <v>1.000003681659201</v>
+      </c>
+      <c r="O85" s="6">
+        <v>1.000003681659201</v>
+      </c>
+      <c r="P85" s="6">
+        <v>1.000003681659201</v>
+      </c>
+      <c r="Q85" s="6">
+        <v>1.000003681659201</v>
+      </c>
+      <c r="R85" s="6">
+        <v>1.000003681659201</v>
+      </c>
+      <c r="S85" s="6">
+        <v>1.000003681659201</v>
+      </c>
+      <c r="T85" s="6">
+        <v>1.000003681659201</v>
+      </c>
+      <c r="U85" s="6">
+        <v>1.000003681659201</v>
+      </c>
+      <c r="V85" s="6">
+        <v>1.000003681659201</v>
+      </c>
+      <c r="W85" s="6">
+        <v>1.000003681659201</v>
+      </c>
+      <c r="X85" s="6">
+        <v>1.000003681659201</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25">
+      <c r="A86" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B86" s="6">
+        <v>0.9689044398919486</v>
+      </c>
+      <c r="C86" s="6">
+        <v>1.002397432875868</v>
+      </c>
+      <c r="D86" s="6">
+        <v>1.002397432875868</v>
+      </c>
+      <c r="E86" s="6">
+        <v>1.002397432875868</v>
+      </c>
+      <c r="F86" s="6">
+        <v>0.997612719592451</v>
+      </c>
+      <c r="G86" s="6">
+        <v>0.997612719592451</v>
+      </c>
+      <c r="H86" s="6">
+        <v>1.000005076234159</v>
+      </c>
+      <c r="I86" s="6">
+        <v>1.000005076234159</v>
+      </c>
+      <c r="J86" s="6">
+        <v>1.000005076234159</v>
+      </c>
+      <c r="K86" s="6">
+        <v>1.000005076234159</v>
+      </c>
+      <c r="L86" s="6">
+        <v>1.000005076234159</v>
+      </c>
+      <c r="M86" s="6">
+        <v>1.000005076234159</v>
+      </c>
+      <c r="N86" s="6">
+        <v>1.000005076234159</v>
+      </c>
+      <c r="O86" s="6">
+        <v>1.000005076234159</v>
+      </c>
+      <c r="P86" s="6">
+        <v>1.000005076234159</v>
+      </c>
+      <c r="Q86" s="6">
+        <v>1.000005076234159</v>
+      </c>
+      <c r="R86" s="6">
+        <v>1.000005076234159</v>
+      </c>
+      <c r="S86" s="6">
+        <v>1.000005076234159</v>
+      </c>
+      <c r="T86" s="6">
+        <v>1.000005076234159</v>
+      </c>
+      <c r="U86" s="6">
+        <v>1.000005076234159</v>
+      </c>
+      <c r="V86" s="6">
+        <v>1.000005076234159</v>
+      </c>
+      <c r="W86" s="6">
+        <v>1.000005076234159</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25">
+      <c r="A87" s="2">
+        <v>2004</v>
+      </c>
+      <c r="B87" s="6">
+        <v>0.9383913483233488</v>
+      </c>
+      <c r="C87" s="6">
+        <v>0.9938324126663037</v>
+      </c>
+      <c r="D87" s="6">
+        <v>0.9938324126663037</v>
+      </c>
+      <c r="E87" s="6">
+        <v>0.9979391581731892</v>
+      </c>
+      <c r="F87" s="6">
+        <v>0.999992530926632</v>
+      </c>
+      <c r="G87" s="6">
+        <v>0.999992530926632</v>
+      </c>
+      <c r="H87" s="6">
+        <v>0.999992530926632</v>
+      </c>
+      <c r="I87" s="6">
+        <v>0.999992530926632</v>
+      </c>
+      <c r="J87" s="6">
+        <v>0.999992530926632</v>
+      </c>
+      <c r="K87" s="6">
+        <v>0.999992530926632</v>
+      </c>
+      <c r="L87" s="6">
+        <v>0.999992530926632</v>
+      </c>
+      <c r="M87" s="6">
+        <v>0.999992530926632</v>
+      </c>
+      <c r="N87" s="6">
+        <v>0.999992530926632</v>
+      </c>
+      <c r="O87" s="6">
+        <v>0.999992530926632</v>
+      </c>
+      <c r="P87" s="6">
+        <v>0.999992530926632</v>
+      </c>
+      <c r="Q87" s="6">
+        <v>0.999992530926632</v>
+      </c>
+      <c r="R87" s="6">
+        <v>0.999992530926632</v>
+      </c>
+      <c r="S87" s="6">
+        <v>0.999992530926632</v>
+      </c>
+      <c r="T87" s="6">
+        <v>0.999992530926632</v>
+      </c>
+      <c r="U87" s="6">
+        <v>0.999992530926632</v>
+      </c>
+      <c r="V87" s="6">
+        <v>0.999992530926632</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25">
+      <c r="A88" s="2">
+        <v>2005</v>
+      </c>
+      <c r="B88" s="6">
+        <v>0.9773595496858092</v>
+      </c>
+      <c r="C88" s="6">
+        <v>0.9999931392574805</v>
+      </c>
+      <c r="D88" s="6">
+        <v>1.002050738309451</v>
+      </c>
+      <c r="E88" s="6">
+        <v>0.9999931392574805</v>
+      </c>
+      <c r="F88" s="6">
+        <v>0.9999931392574805</v>
+      </c>
+      <c r="G88" s="6">
+        <v>0.9999931392574805</v>
+      </c>
+      <c r="H88" s="6">
+        <v>0.9999931392574805</v>
+      </c>
+      <c r="I88" s="6">
+        <v>0.9999931392574805</v>
+      </c>
+      <c r="J88" s="6">
+        <v>0.9999931392574805</v>
+      </c>
+      <c r="K88" s="6">
+        <v>0.9999931392574805</v>
+      </c>
+      <c r="L88" s="6">
+        <v>0.9999931392574805</v>
+      </c>
+      <c r="M88" s="6">
+        <v>0.9999931392574805</v>
+      </c>
+      <c r="N88" s="6">
+        <v>0.9999931392574805</v>
+      </c>
+      <c r="O88" s="6">
+        <v>0.9999931392574805</v>
+      </c>
+      <c r="P88" s="6">
+        <v>0.9999931392574805</v>
+      </c>
+      <c r="Q88" s="6">
+        <v>0.9999931392574805</v>
+      </c>
+      <c r="R88" s="6">
+        <v>0.9999931392574805</v>
+      </c>
+      <c r="S88" s="6">
+        <v>0.9999931392574805</v>
+      </c>
+      <c r="T88" s="6">
+        <v>0.9999931392574805</v>
+      </c>
+      <c r="U88" s="6">
+        <v>0.9999931392574805</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25">
+      <c r="A89" s="2">
+        <v>2006</v>
+      </c>
+      <c r="B89" s="6">
+        <v>0.9628631731291082</v>
+      </c>
+      <c r="C89" s="6">
+        <v>0.999998391927476</v>
+      </c>
+      <c r="D89" s="6">
+        <v>0.999998391927476</v>
+      </c>
+      <c r="E89" s="6">
+        <v>0.999998391927476</v>
+      </c>
+      <c r="F89" s="6">
+        <v>0.999998391927476</v>
+      </c>
+      <c r="G89" s="6">
+        <v>0.999998391927476</v>
+      </c>
+      <c r="H89" s="6">
+        <v>0.999998391927476</v>
+      </c>
+      <c r="I89" s="6">
+        <v>0.999998391927476</v>
+      </c>
+      <c r="J89" s="6">
+        <v>0.999998391927476</v>
+      </c>
+      <c r="K89" s="6">
+        <v>0.999998391927476</v>
+      </c>
+      <c r="L89" s="6">
+        <v>0.999998391927476</v>
+      </c>
+      <c r="M89" s="6">
+        <v>0.999998391927476</v>
+      </c>
+      <c r="N89" s="6">
+        <v>0.999998391927476</v>
+      </c>
+      <c r="O89" s="6">
+        <v>0.999998391927476</v>
+      </c>
+      <c r="P89" s="6">
+        <v>0.999998391927476</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>0.999998391927476</v>
+      </c>
+      <c r="R89" s="6">
+        <v>0.999998391927476</v>
+      </c>
+      <c r="S89" s="6">
+        <v>0.999998391927476</v>
+      </c>
+      <c r="T89" s="6">
+        <v>0.999998391927476</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25">
+      <c r="A90" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B90" s="6">
+        <v>0.9584399009194342</v>
+      </c>
+      <c r="C90" s="6">
+        <v>0.999990763676057</v>
+      </c>
+      <c r="D90" s="6">
+        <v>0.999990763676057</v>
+      </c>
+      <c r="E90" s="6">
+        <v>0.999990763676057</v>
+      </c>
+      <c r="F90" s="6">
+        <v>0.999990763676057</v>
+      </c>
+      <c r="G90" s="6">
+        <v>0.999990763676057</v>
+      </c>
+      <c r="H90" s="6">
+        <v>0.999990763676057</v>
+      </c>
+      <c r="I90" s="6">
+        <v>0.999990763676057</v>
+      </c>
+      <c r="J90" s="6">
+        <v>0.999990763676057</v>
+      </c>
+      <c r="K90" s="6">
+        <v>0.999990763676057</v>
+      </c>
+      <c r="L90" s="6">
+        <v>0.999990763676057</v>
+      </c>
+      <c r="M90" s="6">
+        <v>0.999990763676057</v>
+      </c>
+      <c r="N90" s="6">
+        <v>0.999990763676057</v>
+      </c>
+      <c r="O90" s="6">
+        <v>0.999990763676057</v>
+      </c>
+      <c r="P90" s="6">
+        <v>0.999990763676057</v>
+      </c>
+      <c r="Q90" s="6">
+        <v>0.999990763676057</v>
+      </c>
+      <c r="R90" s="6">
+        <v>0.999990763676057</v>
+      </c>
+      <c r="S90" s="6">
+        <v>0.999990763676057</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25">
+      <c r="A91" s="2">
+        <v>2008</v>
+      </c>
+      <c r="B91" s="6">
+        <v>0.9357441110231909</v>
+      </c>
+      <c r="C91" s="6">
+        <v>0.995985148213525</v>
+      </c>
+      <c r="D91" s="6">
+        <v>1.000001217359547</v>
+      </c>
+      <c r="E91" s="6">
+        <v>1.000001217359547</v>
+      </c>
+      <c r="F91" s="6">
+        <v>1.000001217359547</v>
+      </c>
+      <c r="G91" s="6">
+        <v>1.000001217359547</v>
+      </c>
+      <c r="H91" s="6">
+        <v>1.000001217359547</v>
+      </c>
+      <c r="I91" s="6">
+        <v>1.000001217359547</v>
+      </c>
+      <c r="J91" s="6">
+        <v>1.000001217359547</v>
+      </c>
+      <c r="K91" s="6">
+        <v>1.000001217359547</v>
+      </c>
+      <c r="L91" s="6">
+        <v>1.000001217359547</v>
+      </c>
+      <c r="M91" s="6">
+        <v>1.000001217359547</v>
+      </c>
+      <c r="N91" s="6">
+        <v>1.000001217359547</v>
+      </c>
+      <c r="O91" s="6">
+        <v>1.000001217359547</v>
+      </c>
+      <c r="P91" s="6">
+        <v>1.000001217359547</v>
+      </c>
+      <c r="Q91" s="6">
+        <v>1.000001217359547</v>
+      </c>
+      <c r="R91" s="6">
+        <v>1.000001217359547</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25">
+      <c r="A92" s="2">
+        <v>2009</v>
+      </c>
+      <c r="B92" s="6">
+        <v>0.9508267594260512</v>
+      </c>
+      <c r="C92" s="6">
+        <v>0.9959090626747003</v>
+      </c>
+      <c r="D92" s="6">
+        <v>1.000007453879123</v>
+      </c>
+      <c r="E92" s="6">
+        <v>1.000007453879123</v>
+      </c>
+      <c r="F92" s="6">
+        <v>1.000007453879123</v>
+      </c>
+      <c r="G92" s="6">
+        <v>1.000007453879123</v>
+      </c>
+      <c r="H92" s="6">
+        <v>1.000007453879123</v>
+      </c>
+      <c r="I92" s="6">
+        <v>1.000007453879123</v>
+      </c>
+      <c r="J92" s="6">
+        <v>1.000007453879123</v>
+      </c>
+      <c r="K92" s="6">
+        <v>1.000007453879123</v>
+      </c>
+      <c r="L92" s="6">
+        <v>1.000007453879123</v>
+      </c>
+      <c r="M92" s="6">
+        <v>1.000007453879123</v>
+      </c>
+      <c r="N92" s="6">
+        <v>1.000007453879123</v>
+      </c>
+      <c r="O92" s="6">
+        <v>1.000007453879123</v>
+      </c>
+      <c r="P92" s="6">
+        <v>1.000007453879123</v>
+      </c>
+      <c r="Q92" s="6">
+        <v>1.000007453879123</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25">
+      <c r="A93" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B93" s="6">
+        <v>0.9563022366097707</v>
+      </c>
+      <c r="C93" s="6">
+        <v>0.999991171277222</v>
+      </c>
+      <c r="D93" s="6">
+        <v>0.999991171277222</v>
+      </c>
+      <c r="E93" s="6">
+        <v>0.999991171277222</v>
+      </c>
+      <c r="F93" s="6">
+        <v>0.999991171277222</v>
+      </c>
+      <c r="G93" s="6">
+        <v>0.999991171277222</v>
+      </c>
+      <c r="H93" s="6">
+        <v>0.999991171277222</v>
+      </c>
+      <c r="I93" s="6">
+        <v>0.999991171277222</v>
+      </c>
+      <c r="J93" s="6">
+        <v>0.999991171277222</v>
+      </c>
+      <c r="K93" s="6">
+        <v>0.999991171277222</v>
+      </c>
+      <c r="L93" s="6">
+        <v>0.999991171277222</v>
+      </c>
+      <c r="M93" s="6">
+        <v>0.999991171277222</v>
+      </c>
+      <c r="N93" s="6">
+        <v>0.999991171277222</v>
+      </c>
+      <c r="O93" s="6">
+        <v>0.999991171277222</v>
+      </c>
+      <c r="P93" s="6">
+        <v>0.999991171277222</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25">
+      <c r="A94" s="2">
+        <v>2011</v>
+      </c>
+      <c r="B94" s="6">
+        <v>0.9999861167351189</v>
+      </c>
+      <c r="C94" s="6">
+        <v>0.9999861167351189</v>
+      </c>
+      <c r="D94" s="6">
+        <v>0.9999861167351189</v>
+      </c>
+      <c r="E94" s="6">
+        <v>0.9999861167351189</v>
+      </c>
+      <c r="F94" s="6">
+        <v>0.9999861167351189</v>
+      </c>
+      <c r="G94" s="6">
+        <v>0.9999861167351189</v>
+      </c>
+      <c r="H94" s="6">
+        <v>0.9999861167351189</v>
+      </c>
+      <c r="I94" s="6">
+        <v>0.9999861167351189</v>
+      </c>
+      <c r="J94" s="6">
+        <v>0.9999861167351189</v>
+      </c>
+      <c r="K94" s="6">
+        <v>0.9999861167351189</v>
+      </c>
+      <c r="L94" s="6">
+        <v>0.9999861167351189</v>
+      </c>
+      <c r="M94" s="6">
+        <v>0.9999861167351189</v>
+      </c>
+      <c r="N94" s="6">
+        <v>0.9999861167351189</v>
+      </c>
+      <c r="O94" s="6">
+        <v>0.9999861167351189</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25">
+      <c r="A95" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B95" s="6">
+        <v>0.9393968156766689</v>
+      </c>
+      <c r="C95" s="6">
+        <v>1.000003061849357</v>
+      </c>
+      <c r="D95" s="6">
+        <v>1.000003061849357</v>
+      </c>
+      <c r="E95" s="6">
+        <v>1.000003061849357</v>
+      </c>
+      <c r="F95" s="6">
+        <v>1.000003061849357</v>
+      </c>
+      <c r="G95" s="6">
+        <v>1.000003061849357</v>
+      </c>
+      <c r="H95" s="6">
+        <v>1.000003061849357</v>
+      </c>
+      <c r="I95" s="6">
+        <v>1.000003061849357</v>
+      </c>
+      <c r="J95" s="6">
+        <v>1.000003061849357</v>
+      </c>
+      <c r="K95" s="6">
+        <v>1.000003061849357</v>
+      </c>
+      <c r="L95" s="6">
+        <v>1.000003061849357</v>
+      </c>
+      <c r="M95" s="6">
+        <v>1.000003061849357</v>
+      </c>
+      <c r="N95" s="6">
+        <v>1.000003061849357</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25">
+      <c r="A96" s="2">
+        <v>2013</v>
+      </c>
+      <c r="B96" s="6">
+        <v>0.9683311044817063</v>
+      </c>
+      <c r="C96" s="6">
+        <v>0.9954805747008196</v>
+      </c>
+      <c r="D96" s="6">
+        <v>0.9954805747008196</v>
+      </c>
+      <c r="E96" s="6">
+        <v>1.000005486404005</v>
+      </c>
+      <c r="F96" s="6">
+        <v>1.000005486404005</v>
+      </c>
+      <c r="G96" s="6">
+        <v>1.000005486404005</v>
+      </c>
+      <c r="H96" s="6">
+        <v>1.000005486404005</v>
+      </c>
+      <c r="I96" s="6">
+        <v>1.000005486404005</v>
+      </c>
+      <c r="J96" s="6">
+        <v>1.000005486404005</v>
+      </c>
+      <c r="K96" s="6">
+        <v>1.000005486404005</v>
+      </c>
+      <c r="L96" s="6">
+        <v>1.000005486404005</v>
+      </c>
+      <c r="M96" s="6">
+        <v>1.000005486404005</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25">
+      <c r="A97" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B97" s="6">
+        <v>0.953627377762158</v>
+      </c>
+      <c r="C97" s="6">
+        <v>0.9971058296358125</v>
+      </c>
+      <c r="D97" s="6">
+        <v>1.000004393094056</v>
+      </c>
+      <c r="E97" s="6">
+        <v>1.000004393094056</v>
+      </c>
+      <c r="F97" s="6">
+        <v>1.000004393094056</v>
+      </c>
+      <c r="G97" s="6">
+        <v>1.000004393094056</v>
+      </c>
+      <c r="H97" s="6">
+        <v>1.000004393094056</v>
+      </c>
+      <c r="I97" s="6">
+        <v>1.000004393094056</v>
+      </c>
+      <c r="J97" s="6">
+        <v>1.000004393094056</v>
+      </c>
+      <c r="K97" s="6">
+        <v>1.000004393094056</v>
+      </c>
+      <c r="L97" s="6">
+        <v>1.000004393094056</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25">
+      <c r="A98" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B98" s="6">
+        <v>0.9644234110106034</v>
+      </c>
+      <c r="C98" s="6">
+        <v>0.996043850715869</v>
+      </c>
+      <c r="D98" s="6">
+        <v>1.011854070568502</v>
+      </c>
+      <c r="E98" s="6">
+        <v>1.011854070568502</v>
+      </c>
+      <c r="F98" s="6">
+        <v>1.011854070568502</v>
+      </c>
+      <c r="G98" s="6">
+        <v>1.011854070568502</v>
+      </c>
+      <c r="H98" s="6">
+        <v>1.011854070568502</v>
+      </c>
+      <c r="I98" s="6">
+        <v>1.011854070568502</v>
+      </c>
+      <c r="J98" s="6">
+        <v>1.011854070568502</v>
+      </c>
+      <c r="K98" s="6">
+        <v>0.9999964056790271</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25">
+      <c r="A99" s="2">
+        <v>2016</v>
+      </c>
+      <c r="B99" s="6">
+        <v>0.8851387608806963</v>
+      </c>
+      <c r="C99" s="6">
+        <v>0.9560849974398362</v>
+      </c>
+      <c r="D99" s="6">
+        <v>1.000004096262161</v>
+      </c>
+      <c r="E99" s="6">
+        <v>1.000004096262161</v>
+      </c>
+      <c r="F99" s="6">
+        <v>1.000004096262161</v>
+      </c>
+      <c r="G99" s="6">
+        <v>1.000004096262161</v>
+      </c>
+      <c r="H99" s="6">
+        <v>1.000004096262161</v>
+      </c>
+      <c r="I99" s="6">
+        <v>1.000004096262161</v>
+      </c>
+      <c r="J99" s="6">
+        <v>1.000004096262161</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25">
+      <c r="A100" s="2">
+        <v>2017</v>
+      </c>
+      <c r="B100" s="6">
+        <v>0.8893502305633485</v>
+      </c>
+      <c r="C100" s="6">
+        <v>0.9999871013511336</v>
+      </c>
+      <c r="D100" s="6">
+        <v>1.004242365612202</v>
+      </c>
+      <c r="E100" s="6">
+        <v>1.008497629873271</v>
+      </c>
+      <c r="F100" s="6">
+        <v>1.004242365612202</v>
+      </c>
+      <c r="G100" s="6">
+        <v>1.004242365612202</v>
+      </c>
+      <c r="H100" s="6">
+        <v>1.004242365612202</v>
+      </c>
+      <c r="I100" s="6">
+        <v>0.9999871013511336</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25">
+      <c r="A101" s="2">
+        <v>2018</v>
+      </c>
+      <c r="B101" s="6">
+        <v>0.886642940418482</v>
+      </c>
+      <c r="C101" s="6">
+        <v>0.9959550837577469</v>
+      </c>
+      <c r="D101" s="6">
+        <v>0.9959550837577469</v>
+      </c>
+      <c r="E101" s="6">
+        <v>0.9959550837577469</v>
+      </c>
+      <c r="F101" s="6">
+        <v>1.000003681659201</v>
+      </c>
+      <c r="G101" s="6">
+        <v>1.000003681659201</v>
+      </c>
+      <c r="H101" s="6">
+        <v>1.000003681659201</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25">
+      <c r="A102" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B102" s="6">
+        <v>0.8780608365019013</v>
+      </c>
+      <c r="C102" s="6">
+        <v>1.003498098859316</v>
+      </c>
+      <c r="D102" s="6">
+        <v>1.003498098859316</v>
+      </c>
+      <c r="E102" s="6">
+        <v>1.003498098859316</v>
+      </c>
+      <c r="F102" s="6">
+        <v>1.003498098859316</v>
+      </c>
+      <c r="G102" s="6">
+        <v>0.9998087676135093</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25">
+      <c r="A103" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B103" s="6">
+        <v>0.9428764020707507</v>
+      </c>
+      <c r="C103" s="6">
+        <v>0.9998047886108715</v>
+      </c>
+      <c r="D103" s="6">
+        <v>0.9998047886108715</v>
+      </c>
+      <c r="E103" s="6">
+        <v>0.9998047886108715</v>
+      </c>
+      <c r="F103" s="6">
+        <v>0.9998047886108715</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25">
+      <c r="A104" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B104" s="6">
+        <v>0.875814164924084</v>
+      </c>
+      <c r="C104" s="6">
+        <v>0.999787859502379</v>
+      </c>
+      <c r="D104" s="6">
+        <v>0.999787859502379</v>
+      </c>
+      <c r="E104" s="6">
+        <v>0.999787859502379</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25">
+      <c r="A105" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B105" s="6">
+        <v>0.8754885404101327</v>
+      </c>
+      <c r="C105" s="6">
+        <v>0.9992950006701514</v>
+      </c>
+      <c r="D105" s="6">
+        <v>0.9992950006701514</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25">
+      <c r="A106" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B106" s="6">
+        <v>0.8954799370574352</v>
+      </c>
+      <c r="C106" s="6">
+        <v>0.9993036978756884</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25">
+      <c r="A107" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B107" s="6">
+        <v>0.8820065460809647</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25">
+      <c r="A109" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
+      <c r="E109" s="1"/>
+      <c r="F109" s="1"/>
+      <c r="G109" s="1"/>
+      <c r="H109" s="1"/>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1"/>
+      <c r="K109" s="1"/>
+      <c r="L109" s="1"/>
+      <c r="M109" s="1"/>
+      <c r="N109" s="1"/>
+      <c r="O109" s="1"/>
+      <c r="P109" s="1"/>
+      <c r="Q109" s="1"/>
+      <c r="R109" s="1"/>
+      <c r="S109" s="1"/>
+      <c r="T109" s="1"/>
+      <c r="U109" s="1"/>
+      <c r="V109" s="1"/>
+      <c r="W109" s="1"/>
+      <c r="X109" s="1"/>
+      <c r="Y109" s="1"/>
+    </row>
+    <row r="110" spans="1:25">
+      <c r="A110" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B110" s="8">
+        <v>11</v>
+      </c>
+      <c r="C110" s="8">
+        <v>23</v>
+      </c>
+      <c r="D110" s="8">
+        <v>35</v>
+      </c>
+      <c r="E110" s="8">
+        <v>47</v>
+      </c>
+      <c r="F110" s="8">
+        <v>59</v>
+      </c>
+      <c r="G110" s="8">
+        <v>71</v>
+      </c>
+      <c r="H110" s="8">
+        <v>83</v>
+      </c>
+      <c r="I110" s="8">
+        <v>95</v>
+      </c>
+      <c r="J110" s="8">
+        <v>107</v>
+      </c>
+      <c r="K110" s="8">
+        <v>119</v>
+      </c>
+      <c r="L110" s="8">
+        <v>131</v>
+      </c>
+      <c r="M110" s="8">
+        <v>143</v>
+      </c>
+      <c r="N110" s="8">
+        <v>155</v>
+      </c>
+      <c r="O110" s="8">
+        <v>167</v>
+      </c>
+      <c r="P110" s="8">
+        <v>179</v>
+      </c>
+      <c r="Q110" s="8">
+        <v>191</v>
+      </c>
+      <c r="R110" s="8">
+        <v>203</v>
+      </c>
+      <c r="S110" s="8">
+        <v>215</v>
+      </c>
+      <c r="T110" s="8">
+        <v>227</v>
+      </c>
+      <c r="U110" s="8">
+        <v>239</v>
+      </c>
+      <c r="V110" s="8">
+        <v>251</v>
+      </c>
+      <c r="W110" s="8">
+        <v>263</v>
+      </c>
+      <c r="X110" s="8">
+        <v>275</v>
+      </c>
+      <c r="Y110" s="8">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25">
+      <c r="A111" s="2">
+        <v>2001</v>
+      </c>
+      <c r="B111" s="5">
+        <v>2629028.9008</v>
+      </c>
+      <c r="C111" s="5">
+        <v>1641956.2244</v>
+      </c>
+      <c r="D111" s="5">
+        <v>1294072.7156</v>
+      </c>
+      <c r="E111" s="5">
+        <v>1102919.4184</v>
+      </c>
+      <c r="F111" s="5">
+        <v>945691.7175999996</v>
+      </c>
+      <c r="G111" s="5">
+        <v>793372.4141559997</v>
+      </c>
+      <c r="H111" s="5">
+        <v>799027.0057239993</v>
+      </c>
+      <c r="I111" s="5">
+        <v>776669.6431359993</v>
+      </c>
+      <c r="J111" s="5">
+        <v>759052.9831359996</v>
+      </c>
+      <c r="K111" s="5">
+        <v>738526.0904919999</v>
+      </c>
+      <c r="L111" s="5">
+        <v>685824.1960039996</v>
+      </c>
+      <c r="M111" s="5">
+        <v>633599.0597999995</v>
+      </c>
+      <c r="N111" s="5">
+        <v>636369.5599999996</v>
+      </c>
+      <c r="O111" s="5">
+        <v>577817.9446919998</v>
+      </c>
+      <c r="P111" s="5">
+        <v>533192.6751999995</v>
+      </c>
+      <c r="Q111" s="5">
+        <v>391583.7599999998</v>
+      </c>
+      <c r="R111" s="5">
+        <v>325322.6851999997</v>
+      </c>
+      <c r="S111" s="5">
+        <v>236561.4011119991</v>
+      </c>
+      <c r="T111" s="5">
+        <v>183364.1815679995</v>
+      </c>
+      <c r="U111" s="5">
+        <v>183364.1815679995</v>
+      </c>
+      <c r="V111" s="5">
+        <v>112765.5815679999</v>
+      </c>
+      <c r="W111" s="5">
+        <v>69878.58156799991</v>
+      </c>
+      <c r="X111" s="5">
+        <v>69878.58156799991</v>
+      </c>
+      <c r="Y111" s="5">
+        <v>32586.87031199969</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25">
+      <c r="A112" s="2">
+        <v>2002</v>
+      </c>
+      <c r="B112" s="5">
+        <v>1451856.2884</v>
+      </c>
+      <c r="C112" s="5">
+        <v>1052487.266</v>
+      </c>
+      <c r="D112" s="5">
+        <v>1036872.4392</v>
+      </c>
+      <c r="E112" s="5">
+        <v>775450.4419999996</v>
+      </c>
+      <c r="F112" s="5">
+        <v>754298.7715399996</v>
+      </c>
+      <c r="G112" s="5">
+        <v>652401.3577039996</v>
+      </c>
+      <c r="H112" s="5">
+        <v>619593.4888959997</v>
+      </c>
+      <c r="I112" s="5">
+        <v>619228.0256759997</v>
+      </c>
+      <c r="J112" s="5">
+        <v>580655.2203479996</v>
+      </c>
+      <c r="K112" s="5">
+        <v>563318.6454479995</v>
+      </c>
+      <c r="L112" s="5">
+        <v>544692.5574279996</v>
+      </c>
+      <c r="M112" s="5">
+        <v>482453.0559999996</v>
+      </c>
+      <c r="N112" s="5">
+        <v>479937.1594239995</v>
+      </c>
+      <c r="O112" s="5">
+        <v>403746.8335999995</v>
+      </c>
+      <c r="P112" s="5">
+        <v>351655.6235999996</v>
+      </c>
+      <c r="Q112" s="5">
+        <v>321810.2303999995</v>
+      </c>
+      <c r="R112" s="5">
+        <v>212949.9999479996</v>
+      </c>
+      <c r="S112" s="5">
+        <v>210489.0119279996</v>
+      </c>
+      <c r="T112" s="5">
+        <v>210489.0119279996</v>
+      </c>
+      <c r="U112" s="5">
+        <v>118601.9913199996</v>
+      </c>
+      <c r="V112" s="5">
+        <v>132638.1146599995</v>
+      </c>
+      <c r="W112" s="5">
+        <v>51961.00368000055</v>
+      </c>
+      <c r="X112" s="5">
+        <v>51961.00368000055</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23">
+      <c r="A113" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B113" s="5">
+        <v>830051.4103999999</v>
+      </c>
+      <c r="C113" s="5">
+        <v>380721.0123999999</v>
+      </c>
+      <c r="D113" s="5">
+        <v>260484.3387999998</v>
+      </c>
+      <c r="E113" s="5">
+        <v>-37516.40297200019</v>
+      </c>
+      <c r="F113" s="5">
+        <v>135781.7297239997</v>
+      </c>
+      <c r="G113" s="5">
+        <v>20190.4176119999</v>
+      </c>
+      <c r="H113" s="5">
+        <v>25219.26805600012</v>
+      </c>
+      <c r="I113" s="5">
+        <v>38914.35397200007</v>
+      </c>
+      <c r="J113" s="5">
+        <v>42274.8473319998</v>
+      </c>
+      <c r="K113" s="5">
+        <v>38329.90313199977</v>
+      </c>
+      <c r="L113" s="5">
+        <v>42091.85839999979</v>
+      </c>
+      <c r="M113" s="5">
+        <v>55995.54668399994</v>
+      </c>
+      <c r="N113" s="5">
+        <v>65084.56879999978</v>
+      </c>
+      <c r="O113" s="5">
+        <v>65084.66117199999</v>
+      </c>
+      <c r="P113" s="5">
+        <v>65084.66117199999</v>
+      </c>
+      <c r="Q113" s="5">
+        <v>65084.66117199999</v>
+      </c>
+      <c r="R113" s="5">
+        <v>61323.19415600086</v>
+      </c>
+      <c r="S113" s="5">
+        <v>61323.19415600062</v>
+      </c>
+      <c r="T113" s="5">
+        <v>61323.19415600062</v>
+      </c>
+      <c r="U113" s="5">
+        <v>61323.19415600062</v>
+      </c>
+      <c r="V113" s="5">
+        <v>61323.19415600062</v>
+      </c>
+      <c r="W113" s="5">
+        <v>61323.19415600062</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23">
+      <c r="A114" s="2">
+        <v>2004</v>
+      </c>
+      <c r="B114" s="5">
+        <v>454341.4843999998</v>
+      </c>
+      <c r="C114" s="5">
+        <v>354249.8243999999</v>
+      </c>
+      <c r="D114" s="5">
+        <v>270184.9703200014</v>
+      </c>
+      <c r="E114" s="5">
+        <v>227961.5971599999</v>
+      </c>
+      <c r="F114" s="5">
+        <v>106187.7215199999</v>
+      </c>
+      <c r="G114" s="5">
+        <v>100331.2311519999</v>
+      </c>
+      <c r="H114" s="5">
+        <v>80749.68675199989</v>
+      </c>
+      <c r="I114" s="5">
+        <v>72446.6315919999</v>
+      </c>
+      <c r="J114" s="5">
+        <v>46582.76190399984</v>
+      </c>
+      <c r="K114" s="5">
+        <v>56530.9095999999</v>
+      </c>
+      <c r="L114" s="5">
+        <v>31033.67757599987</v>
+      </c>
+      <c r="M114" s="5">
+        <v>43806.00679999986</v>
+      </c>
+      <c r="N114" s="5">
+        <v>43356.02319999994</v>
+      </c>
+      <c r="O114" s="5">
+        <v>43031.40159999975</v>
+      </c>
+      <c r="P114" s="5">
+        <v>43032.02181199985</v>
+      </c>
+      <c r="Q114" s="5">
+        <v>38750.61919999961</v>
+      </c>
+      <c r="R114" s="5">
+        <v>38750.61919999961</v>
+      </c>
+      <c r="S114" s="5">
+        <v>38750.61919999961</v>
+      </c>
+      <c r="T114" s="5">
+        <v>38750.61919999961</v>
+      </c>
+      <c r="U114" s="5">
+        <v>38716.96939999959</v>
+      </c>
+      <c r="V114" s="5">
+        <v>38716.96939999959</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23">
+      <c r="A115" s="2">
+        <v>2005</v>
+      </c>
+      <c r="B115" s="5">
+        <v>1102026.0192</v>
+      </c>
+      <c r="C115" s="5">
+        <v>723495.6185519998</v>
+      </c>
+      <c r="D115" s="5">
+        <v>572309.5084119996</v>
+      </c>
+      <c r="E115" s="5">
+        <v>615935.9726639998</v>
+      </c>
+      <c r="F115" s="5">
+        <v>551433.4232159997</v>
+      </c>
+      <c r="G115" s="5">
+        <v>522039.1352759998</v>
+      </c>
+      <c r="H115" s="5">
+        <v>484803.7709399995</v>
+      </c>
+      <c r="I115" s="5">
+        <v>474259.0452799997</v>
+      </c>
+      <c r="J115" s="5">
+        <v>450011.6591999996</v>
+      </c>
+      <c r="K115" s="5">
+        <v>398090.5852279996</v>
+      </c>
+      <c r="L115" s="5">
+        <v>375192.9783999997</v>
+      </c>
+      <c r="M115" s="5">
+        <v>139179.8791999999</v>
+      </c>
+      <c r="N115" s="5">
+        <v>139168.0027999994</v>
+      </c>
+      <c r="O115" s="5">
+        <v>179968.6228279998</v>
+      </c>
+      <c r="P115" s="5">
+        <v>158350.8300600001</v>
+      </c>
+      <c r="Q115" s="5">
+        <v>143012.1163639999</v>
+      </c>
+      <c r="R115" s="5">
+        <v>109568.4378839997</v>
+      </c>
+      <c r="S115" s="5">
+        <v>109568.4378839997</v>
+      </c>
+      <c r="T115" s="5">
+        <v>109568.4378839997</v>
+      </c>
+      <c r="U115" s="5">
+        <v>109568.4378839997</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23">
+      <c r="A116" s="2">
+        <v>2006</v>
+      </c>
+      <c r="B116" s="5">
+        <v>825814.7147280001</v>
+      </c>
+      <c r="C116" s="5">
+        <v>433700.1009559999</v>
+      </c>
+      <c r="D116" s="5">
+        <v>585162.9576079999</v>
+      </c>
+      <c r="E116" s="5">
+        <v>515263.7983919999</v>
+      </c>
+      <c r="F116" s="5">
+        <v>505559.539168</v>
+      </c>
+      <c r="G116" s="5">
+        <v>450766.80446</v>
+      </c>
+      <c r="H116" s="5">
+        <v>400483.9479079999</v>
+      </c>
+      <c r="I116" s="5">
+        <v>422421.9944</v>
+      </c>
+      <c r="J116" s="5">
+        <v>391960.836252</v>
+      </c>
+      <c r="K116" s="5">
+        <v>347434.4047999999</v>
+      </c>
+      <c r="L116" s="5">
+        <v>243948.7335999999</v>
+      </c>
+      <c r="M116" s="5">
+        <v>162922.6543999999</v>
+      </c>
+      <c r="N116" s="5">
+        <v>123605.7134359998</v>
+      </c>
+      <c r="O116" s="5">
+        <v>107795.8761479994</v>
+      </c>
+      <c r="P116" s="5">
+        <v>106938.1361479994</v>
+      </c>
+      <c r="Q116" s="5">
+        <v>89783.33614799939</v>
+      </c>
+      <c r="R116" s="5">
+        <v>85164.73614799953</v>
+      </c>
+      <c r="S116" s="5">
+        <v>74163.25733999955</v>
+      </c>
+      <c r="T116" s="5">
+        <v>74163.25733999955</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23">
+      <c r="A117" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B117" s="5">
+        <v>3321208.718915999</v>
+      </c>
+      <c r="C117" s="5">
+        <v>3168103.039439999</v>
+      </c>
+      <c r="D117" s="5">
+        <v>3000758.823179999</v>
+      </c>
+      <c r="E117" s="5">
+        <v>2754436.758055999</v>
+      </c>
+      <c r="F117" s="5">
+        <v>2491674.139627999</v>
+      </c>
+      <c r="G117" s="5">
+        <v>1996791.822623999</v>
+      </c>
+      <c r="H117" s="5">
+        <v>1802831.155599999</v>
+      </c>
+      <c r="I117" s="5">
+        <v>1447643.515643999</v>
+      </c>
+      <c r="J117" s="5">
+        <v>1189872.996799999</v>
+      </c>
+      <c r="K117" s="5">
+        <v>797964.9927999992</v>
+      </c>
+      <c r="L117" s="5">
+        <v>667625.4615999991</v>
+      </c>
+      <c r="M117" s="5">
+        <v>541127.9853879986</v>
+      </c>
+      <c r="N117" s="5">
+        <v>468535.4433960002</v>
+      </c>
+      <c r="O117" s="5">
+        <v>464265.547696</v>
+      </c>
+      <c r="P117" s="5">
+        <v>264396.8995119995</v>
+      </c>
+      <c r="Q117" s="5">
+        <v>264396.8995119995</v>
+      </c>
+      <c r="R117" s="5">
+        <v>247222.2527280003</v>
+      </c>
+      <c r="S117" s="5">
+        <v>235090.9851839999</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23">
+      <c r="A118" s="2">
+        <v>2008</v>
+      </c>
+      <c r="B118" s="5">
+        <v>892616.2424879998</v>
+      </c>
+      <c r="C118" s="5">
+        <v>678054.0858319999</v>
+      </c>
+      <c r="D118" s="5">
+        <v>515803.2616519998</v>
+      </c>
+      <c r="E118" s="5">
+        <v>150962.3518159997</v>
+      </c>
+      <c r="F118" s="5">
+        <v>190850.0197799997</v>
+      </c>
+      <c r="G118" s="5">
+        <v>169653.8787999998</v>
+      </c>
+      <c r="H118" s="5">
+        <v>162725.2134319998</v>
+      </c>
+      <c r="I118" s="5">
+        <v>145795.5107999998</v>
+      </c>
+      <c r="J118" s="5">
+        <v>138347.6883999999</v>
+      </c>
+      <c r="K118" s="5">
+        <v>92909.90159999975</v>
+      </c>
+      <c r="L118" s="5">
+        <v>86237.10667199967</v>
+      </c>
+      <c r="M118" s="5">
+        <v>86012.11487200158</v>
+      </c>
+      <c r="N118" s="5">
+        <v>105859.8885720016</v>
+      </c>
+      <c r="O118" s="5">
+        <v>105529.9885720015</v>
+      </c>
+      <c r="P118" s="5">
+        <v>105529.9885720015</v>
+      </c>
+      <c r="Q118" s="5">
+        <v>98931.98857200146</v>
+      </c>
+      <c r="R118" s="5">
+        <v>70541.19045200152</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23">
+      <c r="A119" s="2">
+        <v>2009</v>
+      </c>
+      <c r="B119" s="5">
+        <v>885969.6878280001</v>
+      </c>
+      <c r="C119" s="5">
+        <v>370912.626636</v>
+      </c>
+      <c r="D119" s="5">
+        <v>421210.0383760001</v>
+      </c>
+      <c r="E119" s="5">
+        <v>400696.156988</v>
+      </c>
+      <c r="F119" s="5">
+        <v>344688.9944</v>
+      </c>
+      <c r="G119" s="5">
+        <v>298560.4497840001</v>
+      </c>
+      <c r="H119" s="5">
+        <v>264177.5592</v>
+      </c>
+      <c r="I119" s="5">
+        <v>123096.4839999999</v>
+      </c>
+      <c r="J119" s="5">
+        <v>123089.8859999999</v>
+      </c>
+      <c r="K119" s="5">
+        <v>123088.1837159998</v>
+      </c>
+      <c r="L119" s="5">
+        <v>123088.1837159996</v>
+      </c>
+      <c r="M119" s="5">
+        <v>107912.7837159997</v>
+      </c>
+      <c r="N119" s="5">
+        <v>73868.9907439996</v>
+      </c>
+      <c r="O119" s="5">
+        <v>73868.9907439996</v>
+      </c>
+      <c r="P119" s="5">
+        <v>73868.9907439996</v>
+      </c>
+      <c r="Q119" s="5">
+        <v>73868.9907439996</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23">
+      <c r="A120" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B120" s="5">
+        <v>1006487.690004</v>
+      </c>
+      <c r="C120" s="5">
+        <v>635927.7657279999</v>
+      </c>
+      <c r="D120" s="5">
+        <v>415196.0304079998</v>
+      </c>
+      <c r="E120" s="5">
+        <v>261180.2623999999</v>
+      </c>
+      <c r="F120" s="5">
+        <v>130332.3948879999</v>
+      </c>
+      <c r="G120" s="5">
+        <v>143618.4179999998</v>
+      </c>
+      <c r="H120" s="5">
+        <v>95150.82959999982</v>
+      </c>
+      <c r="I120" s="5">
+        <v>93654.40319999983</v>
+      </c>
+      <c r="J120" s="5">
+        <v>99696.0730359999</v>
+      </c>
+      <c r="K120" s="5">
+        <v>98896.59337599948</v>
+      </c>
+      <c r="L120" s="5">
+        <v>97901.61497599934</v>
+      </c>
+      <c r="M120" s="5">
+        <v>97827.71737599932</v>
+      </c>
+      <c r="N120" s="5">
+        <v>96178.21737599932</v>
+      </c>
+      <c r="O120" s="5">
+        <v>96448.86733599938</v>
+      </c>
+      <c r="P120" s="5">
+        <v>88846.05791599932</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23">
+      <c r="A121" s="2">
+        <v>2011</v>
+      </c>
+      <c r="B121" s="5">
+        <v>1610643.585408</v>
+      </c>
+      <c r="C121" s="5">
+        <v>1177771.159432</v>
+      </c>
+      <c r="D121" s="5">
+        <v>756673.0491999998</v>
+      </c>
+      <c r="E121" s="5">
+        <v>554336.9469559998</v>
+      </c>
+      <c r="F121" s="5">
+        <v>453151.8531999998</v>
+      </c>
+      <c r="G121" s="5">
+        <v>324186.0255999998</v>
+      </c>
+      <c r="H121" s="5">
+        <v>227988.5051999998</v>
+      </c>
+      <c r="I121" s="5">
+        <v>227873.2249439997</v>
+      </c>
+      <c r="J121" s="5">
+        <v>202547.4617440002</v>
+      </c>
+      <c r="K121" s="5">
+        <v>195400.5081440003</v>
+      </c>
+      <c r="L121" s="5">
+        <v>142704.9873240001</v>
+      </c>
+      <c r="M121" s="5">
+        <v>148609.3395840002</v>
+      </c>
+      <c r="N121" s="5">
+        <v>148609.3395840002</v>
+      </c>
+      <c r="O121" s="5">
+        <v>148609.3395840002</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23">
+      <c r="A122" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B122" s="5">
+        <v>1139368.745624</v>
+      </c>
+      <c r="C122" s="5">
+        <v>792765.3280000001</v>
+      </c>
+      <c r="D122" s="5">
+        <v>583244.9010840001</v>
+      </c>
+      <c r="E122" s="5">
+        <v>505856.5764</v>
+      </c>
+      <c r="F122" s="5">
+        <v>508886.378</v>
+      </c>
+      <c r="G122" s="5">
+        <v>500422.4636</v>
+      </c>
+      <c r="H122" s="5">
+        <v>496517.1865760001</v>
+      </c>
+      <c r="I122" s="5">
+        <v>446059.6413760013</v>
+      </c>
+      <c r="J122" s="5">
+        <v>388557.2532240013</v>
+      </c>
+      <c r="K122" s="5">
+        <v>327106.4767160013</v>
+      </c>
+      <c r="L122" s="5">
+        <v>318529.0767160011</v>
+      </c>
+      <c r="M122" s="5">
+        <v>111502.469468001</v>
+      </c>
+      <c r="N122" s="5">
+        <v>111502.469468001</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23">
+      <c r="A123" s="2">
+        <v>2013</v>
+      </c>
+      <c r="B123" s="5">
+        <v>490429.5604</v>
+      </c>
+      <c r="C123" s="5">
+        <v>259870.130472</v>
+      </c>
+      <c r="D123" s="5">
+        <v>215405.1264</v>
+      </c>
+      <c r="E123" s="5">
+        <v>101477.4604</v>
+      </c>
+      <c r="F123" s="5">
+        <v>60879.96639999992</v>
+      </c>
+      <c r="G123" s="5">
+        <v>62721.63974799996</v>
+      </c>
+      <c r="H123" s="5">
+        <v>62373.15978000022</v>
+      </c>
+      <c r="I123" s="5">
+        <v>62373.15977999999</v>
+      </c>
+      <c r="J123" s="5">
+        <v>61007.50574000017</v>
+      </c>
+      <c r="K123" s="5">
+        <v>61007.50574000017</v>
+      </c>
+      <c r="L123" s="5">
+        <v>60996.28914000012</v>
+      </c>
+      <c r="M123" s="5">
+        <v>60996.28914000012</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23">
+      <c r="A124" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B124" s="5">
+        <v>966302.1225159999</v>
+      </c>
+      <c r="C124" s="5">
+        <v>754081.794</v>
+      </c>
+      <c r="D124" s="5">
+        <v>428267.2755999998</v>
+      </c>
+      <c r="E124" s="5">
+        <v>253639.3291999998</v>
+      </c>
+      <c r="F124" s="5">
+        <v>235166.0772519999</v>
+      </c>
+      <c r="G124" s="5">
+        <v>190004.0868519999</v>
+      </c>
+      <c r="H124" s="5">
+        <v>228820.9258079999</v>
+      </c>
+      <c r="I124" s="5">
+        <v>228820.9258079999</v>
+      </c>
+      <c r="J124" s="5">
+        <v>174717.3258079998</v>
+      </c>
+      <c r="K124" s="5">
+        <v>146433.9959120001</v>
+      </c>
+      <c r="L124" s="5">
+        <v>156152.3352679999</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23">
+      <c r="A125" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B125" s="5">
+        <v>3267945.68</v>
+      </c>
+      <c r="C125" s="5">
+        <v>2737569.4088</v>
+      </c>
+      <c r="D125" s="5">
+        <v>2200410.3936</v>
+      </c>
+      <c r="E125" s="5">
+        <v>1672989.340208</v>
+      </c>
+      <c r="F125" s="5">
+        <v>1447048.022027999</v>
+      </c>
+      <c r="G125" s="5">
+        <v>1125742.444867999</v>
+      </c>
+      <c r="H125" s="5">
+        <v>750679.1744559985</v>
+      </c>
+      <c r="I125" s="5">
+        <v>729961.4544559983</v>
+      </c>
+      <c r="J125" s="5">
+        <v>719807.4095719983</v>
+      </c>
+      <c r="K125" s="5">
+        <v>423049.3219239987</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23">
+      <c r="A126" s="2">
+        <v>2016</v>
+      </c>
+      <c r="B126" s="5">
+        <v>2196234.968</v>
+      </c>
+      <c r="C126" s="5">
+        <v>1598076.1232</v>
+      </c>
+      <c r="D126" s="5">
+        <v>1150566.891964</v>
+      </c>
+      <c r="E126" s="5">
+        <v>999769.2588680002</v>
+      </c>
+      <c r="F126" s="5">
+        <v>731620.9173720009</v>
+      </c>
+      <c r="G126" s="5">
+        <v>663619.395740001</v>
+      </c>
+      <c r="H126" s="5">
+        <v>380416.410840001</v>
+      </c>
+      <c r="I126" s="5">
+        <v>381012.2366320011</v>
+      </c>
+      <c r="J126" s="5">
+        <v>377713.2366320011</v>
+      </c>
+    </row>
+    <row r="127" spans="1:23">
+      <c r="A127" s="2">
+        <v>2017</v>
+      </c>
+      <c r="B127" s="5">
+        <v>947296.2184000001</v>
+      </c>
+      <c r="C127" s="5">
+        <v>793750.412736</v>
+      </c>
+      <c r="D127" s="5">
+        <v>772623.8938519997</v>
+      </c>
+      <c r="E127" s="5">
+        <v>575852.8879039995</v>
+      </c>
+      <c r="F127" s="5">
+        <v>513333.6180799996</v>
+      </c>
+      <c r="G127" s="5">
+        <v>394514.8018959997</v>
+      </c>
+      <c r="H127" s="5">
+        <v>239670.2063239997</v>
+      </c>
+      <c r="I127" s="5">
+        <v>202811.2710839997</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23">
+      <c r="A128" s="2">
+        <v>2018</v>
+      </c>
+      <c r="B128" s="5">
+        <v>2333181.319552</v>
+      </c>
+      <c r="C128" s="5">
+        <v>1673097.222868</v>
+      </c>
+      <c r="D128" s="5">
+        <v>1172306.937900001</v>
+      </c>
+      <c r="E128" s="5">
+        <v>524345.5049679992</v>
+      </c>
+      <c r="F128" s="5">
+        <v>537647.0333799995</v>
+      </c>
+      <c r="G128" s="5">
+        <v>507489.7923079995</v>
+      </c>
+      <c r="H128" s="5">
+        <v>445716.7166959993</v>
+      </c>
+    </row>
+    <row r="129" spans="1:25">
+      <c r="A129" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B129" s="5">
+        <v>2790434.858824</v>
+      </c>
+      <c r="C129" s="5">
+        <v>2073742.62732</v>
+      </c>
+      <c r="D129" s="5">
+        <v>1458295.148687999</v>
+      </c>
+      <c r="E129" s="5">
+        <v>1197786.644588</v>
+      </c>
+      <c r="F129" s="5">
+        <v>1070970.99962</v>
+      </c>
+      <c r="G129" s="5">
+        <v>598466.8157080007</v>
+      </c>
+    </row>
+    <row r="130" spans="1:25">
+      <c r="A130" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B130" s="5">
+        <v>750650.5164680001</v>
+      </c>
+      <c r="C130" s="5">
+        <v>340837.5990440004</v>
+      </c>
+      <c r="D130" s="5">
+        <v>356461.3199480003</v>
+      </c>
+      <c r="E130" s="5">
+        <v>303284.8181240002</v>
+      </c>
+      <c r="F130" s="5">
+        <v>293853.6105320002</v>
+      </c>
+    </row>
+    <row r="131" spans="1:25">
+      <c r="A131" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B131" s="5">
+        <v>832762.7730120003</v>
+      </c>
+      <c r="C131" s="5">
+        <v>581284.687592</v>
+      </c>
+      <c r="D131" s="5">
+        <v>401903.0537400004</v>
+      </c>
+      <c r="E131" s="5">
+        <v>370906.5602640001</v>
+      </c>
+    </row>
+    <row r="132" spans="1:25">
+      <c r="A132" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B132" s="5">
+        <v>606677.1964239998</v>
+      </c>
+      <c r="C132" s="5">
+        <v>449644.321367999</v>
+      </c>
+      <c r="D132" s="5">
+        <v>473884.0933559992</v>
+      </c>
+    </row>
+    <row r="133" spans="1:25">
+      <c r="A133" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B133" s="5">
+        <v>2120494.577396</v>
+      </c>
+      <c r="C133" s="5">
+        <v>1443738.205648</v>
+      </c>
+    </row>
+    <row r="134" spans="1:25">
+      <c r="A134" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B134" s="5">
+        <v>1635509.148172</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25">
+      <c r="A136" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
+      <c r="E136" s="1"/>
+      <c r="F136" s="1"/>
+      <c r="G136" s="1"/>
+      <c r="H136" s="1"/>
+      <c r="I136" s="1"/>
+      <c r="J136" s="1"/>
+      <c r="K136" s="1"/>
+      <c r="L136" s="1"/>
+      <c r="M136" s="1"/>
+      <c r="N136" s="1"/>
+      <c r="O136" s="1"/>
+      <c r="P136" s="1"/>
+      <c r="Q136" s="1"/>
+      <c r="R136" s="1"/>
+      <c r="S136" s="1"/>
+      <c r="T136" s="1"/>
+      <c r="U136" s="1"/>
+      <c r="V136" s="1"/>
+      <c r="W136" s="1"/>
+      <c r="X136" s="1"/>
+      <c r="Y136" s="1"/>
+    </row>
+    <row r="137" spans="1:25">
+      <c r="A137" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B137" s="8">
+        <v>11</v>
+      </c>
+      <c r="C137" s="8">
+        <v>23</v>
+      </c>
+      <c r="D137" s="8">
+        <v>35</v>
+      </c>
+      <c r="E137" s="8">
+        <v>47</v>
+      </c>
+      <c r="F137" s="8">
+        <v>59</v>
+      </c>
+      <c r="G137" s="8">
+        <v>71</v>
+      </c>
+      <c r="H137" s="8">
+        <v>83</v>
+      </c>
+      <c r="I137" s="8">
+        <v>95</v>
+      </c>
+      <c r="J137" s="8">
+        <v>107</v>
+      </c>
+      <c r="K137" s="8">
+        <v>119</v>
+      </c>
+      <c r="L137" s="8">
+        <v>131</v>
+      </c>
+      <c r="M137" s="8">
+        <v>143</v>
+      </c>
+      <c r="N137" s="8">
+        <v>155</v>
+      </c>
+      <c r="O137" s="8">
+        <v>167</v>
+      </c>
+      <c r="P137" s="8">
+        <v>179</v>
+      </c>
+      <c r="Q137" s="8">
+        <v>191</v>
+      </c>
+      <c r="R137" s="8">
+        <v>203</v>
+      </c>
+      <c r="S137" s="8">
+        <v>215</v>
+      </c>
+      <c r="T137" s="8">
+        <v>227</v>
+      </c>
+      <c r="U137" s="8">
+        <v>239</v>
+      </c>
+      <c r="V137" s="8">
+        <v>251</v>
+      </c>
+      <c r="W137" s="8">
+        <v>263</v>
+      </c>
+      <c r="X137" s="8">
+        <v>275</v>
+      </c>
+      <c r="Y137" s="8">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="138" spans="1:25">
+      <c r="A138" s="2">
+        <v>2001</v>
+      </c>
+      <c r="B138" s="5">
+        <v>2870316.4412</v>
+      </c>
+      <c r="C138" s="5">
+        <v>2148988.7716</v>
+      </c>
+      <c r="D138" s="5">
+        <v>1650633.914</v>
+      </c>
+      <c r="E138" s="5">
+        <v>1285395.026</v>
+      </c>
+      <c r="F138" s="5">
+        <v>972140.4603999997</v>
+      </c>
+      <c r="G138" s="5">
+        <v>912584.5767079997</v>
+      </c>
+      <c r="H138" s="5">
+        <v>934587.5739119998</v>
+      </c>
+      <c r="I138" s="5">
+        <v>904046.3952199994</v>
+      </c>
+      <c r="J138" s="5">
+        <v>881815.1995879998</v>
+      </c>
+      <c r="K138" s="5">
+        <v>853975.9810719998</v>
+      </c>
+      <c r="L138" s="5">
+        <v>798160.5563639998</v>
+      </c>
+      <c r="M138" s="5">
+        <v>740655.0935439994</v>
+      </c>
+      <c r="N138" s="5">
+        <v>700636.7191999997</v>
+      </c>
+      <c r="O138" s="5">
+        <v>637243.8609799999</v>
+      </c>
+      <c r="P138" s="5">
+        <v>582196.0211999998</v>
+      </c>
+      <c r="Q138" s="5">
+        <v>502010.5271999994</v>
+      </c>
+      <c r="R138" s="5">
+        <v>413948.3407999994</v>
+      </c>
+      <c r="S138" s="5">
+        <v>338714.4346639998</v>
+      </c>
+      <c r="T138" s="5">
+        <v>229288.7160240002</v>
+      </c>
+      <c r="U138" s="5">
+        <v>229288.7160240002</v>
+      </c>
+      <c r="V138" s="5">
+        <v>207198.5328480001</v>
+      </c>
+      <c r="W138" s="5">
+        <v>184974.7665639999</v>
+      </c>
+      <c r="X138" s="5">
+        <v>165979.3488960001</v>
+      </c>
+      <c r="Y138" s="5">
+        <v>154065.9077239996</v>
+      </c>
+    </row>
+    <row r="139" spans="1:25">
+      <c r="A139" s="2">
+        <v>2002</v>
+      </c>
+      <c r="B139" s="5">
+        <v>2022333.884</v>
+      </c>
+      <c r="C139" s="5">
+        <v>1468621.8064</v>
+      </c>
+      <c r="D139" s="5">
+        <v>1159324.7212</v>
+      </c>
+      <c r="E139" s="5">
+        <v>1061349.6996</v>
+      </c>
+      <c r="F139" s="5">
+        <v>896252.6961599998</v>
+      </c>
+      <c r="G139" s="5">
+        <v>757959.6718399995</v>
+      </c>
+      <c r="H139" s="5">
+        <v>721365.9498079997</v>
+      </c>
+      <c r="I139" s="5">
+        <v>691990.4265799997</v>
+      </c>
+      <c r="J139" s="5">
+        <v>650115.0319399994</v>
+      </c>
+      <c r="K139" s="5">
+        <v>629495.8728639998</v>
+      </c>
+      <c r="L139" s="5">
+        <v>598697.5569159996</v>
+      </c>
+      <c r="M139" s="5">
+        <v>565271.1519999995</v>
+      </c>
+      <c r="N139" s="5">
+        <v>523647.5238439995</v>
+      </c>
+      <c r="O139" s="5">
+        <v>476303.7199999997</v>
+      </c>
+      <c r="P139" s="5">
+        <v>436075.7139999997</v>
+      </c>
+      <c r="Q139" s="5">
+        <v>398125.3375999995</v>
+      </c>
+      <c r="R139" s="5">
+        <v>341664.8396279996</v>
+      </c>
+      <c r="S139" s="5">
+        <v>300481.7863239995</v>
+      </c>
+      <c r="T139" s="5">
+        <v>267455.0882479991</v>
+      </c>
+      <c r="U139" s="5">
+        <v>241864.4813279994</v>
+      </c>
+      <c r="V139" s="5">
+        <v>220306.3476759996</v>
+      </c>
+      <c r="W139" s="5">
+        <v>199643.6154079996</v>
+      </c>
+      <c r="X139" s="5">
+        <v>180048.5319119995</v>
+      </c>
+    </row>
+    <row r="140" spans="1:25">
+      <c r="A140" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B140" s="5">
+        <v>1375679.6184</v>
+      </c>
+      <c r="C140" s="5">
+        <v>687633.5803999999</v>
+      </c>
+      <c r="D140" s="5">
+        <v>509748.8611999999</v>
+      </c>
+      <c r="E140" s="5">
+        <v>390069.4942679999</v>
+      </c>
+      <c r="F140" s="5">
+        <v>162505.42438</v>
+      </c>
+      <c r="G140" s="5">
+        <v>79029.15148799983</v>
+      </c>
+      <c r="H140" s="5">
+        <v>76376.05609999993</v>
+      </c>
+      <c r="I140" s="5">
+        <v>64014.65031599975</v>
+      </c>
+      <c r="J140" s="5">
+        <v>66566.67753999983</v>
+      </c>
+      <c r="K140" s="5">
+        <v>62231.58040399989</v>
+      </c>
+      <c r="L140" s="5">
+        <v>65603.17159999977</v>
+      </c>
+      <c r="M140" s="5">
+        <v>65214.44383199979</v>
+      </c>
+      <c r="N140" s="5">
+        <v>65084.56879999978</v>
+      </c>
+      <c r="O140" s="5">
+        <v>65084.05415600003</v>
+      </c>
+      <c r="P140" s="5">
+        <v>65084.05415600003</v>
+      </c>
+      <c r="Q140" s="5">
+        <v>65084.66117199999</v>
+      </c>
+      <c r="R140" s="5">
+        <v>61323.19415600086</v>
+      </c>
+      <c r="S140" s="5">
+        <v>61323.19415600062</v>
+      </c>
+      <c r="T140" s="5">
+        <v>61323.19415600062</v>
+      </c>
+      <c r="U140" s="5">
+        <v>61323.19415600062</v>
+      </c>
+      <c r="V140" s="5">
+        <v>61323.19415600062</v>
+      </c>
+      <c r="W140" s="5">
+        <v>61323.19415600062</v>
+      </c>
+    </row>
+    <row r="141" spans="1:25">
+      <c r="A141" s="2">
+        <v>2004</v>
+      </c>
+      <c r="B141" s="5">
+        <v>904443.8483999999</v>
+      </c>
+      <c r="C141" s="5">
+        <v>535349.0891999999</v>
+      </c>
+      <c r="D141" s="5">
+        <v>354367.9681880012</v>
+      </c>
+      <c r="E141" s="5">
+        <v>257704.7081639998</v>
+      </c>
+      <c r="F141" s="5">
+        <v>106187.7215199999</v>
+      </c>
+      <c r="G141" s="5">
+        <v>102310.6047599998</v>
+      </c>
+      <c r="H141" s="5">
+        <v>85086.80287599983</v>
+      </c>
+      <c r="I141" s="5">
+        <v>76689.47549199988</v>
+      </c>
+      <c r="J141" s="5">
+        <v>56643.29993199999</v>
+      </c>
+      <c r="K141" s="5">
+        <v>63416.58239999996</v>
+      </c>
+      <c r="L141" s="5">
+        <v>59475.45184399979</v>
+      </c>
+      <c r="M141" s="5">
+        <v>52429.59279999975</v>
+      </c>
+      <c r="N141" s="5">
+        <v>51969.05239999993</v>
+      </c>
+      <c r="O141" s="5">
+        <v>49954.02319999994</v>
+      </c>
+      <c r="P141" s="5">
+        <v>49307.98662799993</v>
+      </c>
+      <c r="Q141" s="5">
+        <v>38750.61919999961</v>
+      </c>
+      <c r="R141" s="5">
+        <v>38750.61919999961</v>
+      </c>
+      <c r="S141" s="5">
+        <v>38750.61919999961</v>
+      </c>
+      <c r="T141" s="5">
+        <v>38750.61919999961</v>
+      </c>
+      <c r="U141" s="5">
+        <v>38716.96939999959</v>
+      </c>
+      <c r="V141" s="5">
+        <v>38716.96939999959</v>
+      </c>
+    </row>
+    <row r="142" spans="1:25">
+      <c r="A142" s="2">
+        <v>2005</v>
+      </c>
+      <c r="B142" s="5">
+        <v>1742724.8092</v>
+      </c>
+      <c r="C142" s="5">
+        <v>1114822.074832</v>
+      </c>
+      <c r="D142" s="5">
+        <v>784086.1478199996</v>
+      </c>
+      <c r="E142" s="5">
+        <v>715292.1536039996</v>
+      </c>
+      <c r="F142" s="5">
+        <v>593079.6693159996</v>
+      </c>
+      <c r="G142" s="5">
+        <v>556584.2046999997</v>
+      </c>
+      <c r="H142" s="5">
+        <v>518716.8707279996</v>
+      </c>
+      <c r="I142" s="5">
+        <v>499630.0179759997</v>
+      </c>
+      <c r="J142" s="5">
+        <v>491907.6395999996</v>
+      </c>
+      <c r="K142" s="5">
+        <v>436097.9419559997</v>
+      </c>
+      <c r="L142" s="5">
+        <v>381682.7711999996</v>
+      </c>
+      <c r="M142" s="5">
+        <v>341770.1495999997</v>
+      </c>
+      <c r="N142" s="5">
+        <v>276001.2855999996</v>
+      </c>
+      <c r="O142" s="5">
+        <v>236838.7642279998</v>
+      </c>
+      <c r="P142" s="5">
+        <v>173130.9438799997</v>
+      </c>
+      <c r="Q142" s="5">
+        <v>155783.983728</v>
+      </c>
+      <c r="R142" s="5">
+        <v>113319.8627439998</v>
+      </c>
+      <c r="S142" s="5">
+        <v>109568.4378839997</v>
+      </c>
+      <c r="T142" s="5">
+        <v>109568.4378839997</v>
+      </c>
+      <c r="U142" s="5">
+        <v>109568.4378839997</v>
+      </c>
+    </row>
+    <row r="143" spans="1:25">
+      <c r="A143" s="2">
+        <v>2006</v>
+      </c>
+      <c r="B143" s="5">
+        <v>1307013.624276</v>
+      </c>
+      <c r="C143" s="5">
+        <v>892217.8444679999</v>
+      </c>
+      <c r="D143" s="5">
+        <v>698539.7038039999</v>
+      </c>
+      <c r="E143" s="5">
+        <v>618956.0793639999</v>
+      </c>
+      <c r="F143" s="5">
+        <v>559431.1930760001</v>
+      </c>
+      <c r="G143" s="5">
+        <v>511364.3671959999</v>
+      </c>
+      <c r="H143" s="5">
+        <v>466688.0555760001</v>
+      </c>
+      <c r="I143" s="5">
+        <v>459048.8119999999</v>
+      </c>
+      <c r="J143" s="5">
+        <v>423260.956492</v>
+      </c>
+      <c r="K143" s="5">
+        <v>375366.378</v>
+      </c>
+      <c r="L143" s="5">
+        <v>263175.3055999998</v>
+      </c>
+      <c r="M143" s="5">
+        <v>226457.4356</v>
+      </c>
+      <c r="N143" s="5">
+        <v>212223.9001</v>
+      </c>
+      <c r="O143" s="5">
+        <v>186440.6315800003</v>
+      </c>
+      <c r="P143" s="5">
+        <v>176868.5170999996</v>
+      </c>
+      <c r="Q143" s="5">
+        <v>165049.9155799998</v>
+      </c>
+      <c r="R143" s="5">
+        <v>148685.3052559998</v>
+      </c>
+      <c r="S143" s="5">
+        <v>137666.9751559997</v>
+      </c>
+      <c r="T143" s="5">
+        <v>129659.0221439998</v>
+      </c>
+    </row>
+    <row r="144" spans="1:25">
+      <c r="A144" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B144" s="5">
+        <v>4542287.726012</v>
+      </c>
+      <c r="C144" s="5">
+        <v>3942627.849408</v>
+      </c>
+      <c r="D144" s="5">
+        <v>3617339.561096</v>
+      </c>
+      <c r="E144" s="5">
+        <v>3226728.789876</v>
+      </c>
+      <c r="F144" s="5">
+        <v>2888204.544075999</v>
+      </c>
+      <c r="G144" s="5">
+        <v>2425063.687531999</v>
+      </c>
+      <c r="H144" s="5">
+        <v>2121719.093599999</v>
+      </c>
+      <c r="I144" s="5">
+        <v>1894681.003076</v>
+      </c>
+      <c r="J144" s="5">
+        <v>1640464.932399999</v>
+      </c>
+      <c r="K144" s="5">
+        <v>1351426.346399999</v>
+      </c>
+      <c r="L144" s="5">
+        <v>1047667.622399999</v>
+      </c>
+      <c r="M144" s="5">
+        <v>847758.3701240001</v>
+      </c>
+      <c r="N144" s="5">
+        <v>675473.5186799988</v>
+      </c>
+      <c r="O144" s="5">
+        <v>549134.5528199999</v>
+      </c>
+      <c r="P144" s="5">
+        <v>428554.5456919996</v>
+      </c>
+      <c r="Q144" s="5">
+        <v>294399.5098559987</v>
+      </c>
+      <c r="R144" s="5">
+        <v>264536.0777239995</v>
+      </c>
+      <c r="S144" s="5">
+        <v>255172.4468479995</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18">
+      <c r="A145" s="2">
+        <v>2008</v>
+      </c>
+      <c r="B145" s="5">
+        <v>1095452.367564</v>
+      </c>
+      <c r="C145" s="5">
+        <v>802394.0820239999</v>
+      </c>
+      <c r="D145" s="5">
+        <v>579331.6955759999</v>
+      </c>
+      <c r="E145" s="5">
+        <v>260613.3921559998</v>
+      </c>
+      <c r="F145" s="5">
+        <v>219116.5907559998</v>
+      </c>
+      <c r="G145" s="5">
+        <v>181217.5335999997</v>
+      </c>
+      <c r="H145" s="5">
+        <v>172353.6088519997</v>
+      </c>
+      <c r="I145" s="5">
+        <v>164192.0543999998</v>
+      </c>
+      <c r="J145" s="5">
+        <v>149099.7891999998</v>
+      </c>
+      <c r="K145" s="5">
+        <v>131675.7907999998</v>
+      </c>
+      <c r="L145" s="5">
+        <v>117587.1737719998</v>
+      </c>
+      <c r="M145" s="5">
+        <v>115002.6052120014</v>
+      </c>
+      <c r="N145" s="5">
+        <v>111908.9217760016</v>
+      </c>
+      <c r="O145" s="5">
+        <v>110389.7454720016</v>
+      </c>
+      <c r="P145" s="5">
+        <v>109512.2642560017</v>
+      </c>
+      <c r="Q145" s="5">
+        <v>105967.9242240016</v>
+      </c>
+      <c r="R145" s="5">
+        <v>70541.19045200152</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18">
+      <c r="A146" s="2">
+        <v>2009</v>
+      </c>
+      <c r="B146" s="5">
+        <v>1014782.441828</v>
+      </c>
+      <c r="C146" s="5">
+        <v>501202.778404</v>
+      </c>
+      <c r="D146" s="5">
+        <v>431499.2630840001</v>
+      </c>
+      <c r="E146" s="5">
+        <v>409388.151052</v>
+      </c>
+      <c r="F146" s="5">
+        <v>348465.6896</v>
+      </c>
+      <c r="G146" s="5">
+        <v>302365.146896</v>
+      </c>
+      <c r="H146" s="5">
+        <v>274058.724</v>
+      </c>
+      <c r="I146" s="5">
+        <v>225193.936</v>
+      </c>
+      <c r="J146" s="5">
+        <v>187840.0188</v>
+      </c>
+      <c r="K146" s="5">
+        <v>172344.074764</v>
+      </c>
+      <c r="L146" s="5">
+        <v>162267.7015359998</v>
+      </c>
+      <c r="M146" s="5">
+        <v>129244.4344199998</v>
+      </c>
+      <c r="N146" s="5">
+        <v>73868.9907439996</v>
+      </c>
+      <c r="O146" s="5">
+        <v>73868.9907439996</v>
+      </c>
+      <c r="P146" s="5">
+        <v>73868.9907439996</v>
+      </c>
+      <c r="Q146" s="5">
+        <v>73868.9907439996</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18">
+      <c r="A147" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B147" s="5">
+        <v>1122894.976776</v>
+      </c>
+      <c r="C147" s="5">
+        <v>693367.5652519999</v>
+      </c>
+      <c r="D147" s="5">
+        <v>451265.3565959998</v>
+      </c>
+      <c r="E147" s="5">
+        <v>289597.8483999998</v>
+      </c>
+      <c r="F147" s="5">
+        <v>189533.7944319998</v>
+      </c>
+      <c r="G147" s="5">
+        <v>164982.7419999999</v>
+      </c>
+      <c r="H147" s="5">
+        <v>106209.0775999997</v>
+      </c>
+      <c r="I147" s="5">
+        <v>104015.9023999998</v>
+      </c>
+      <c r="J147" s="5">
+        <v>99696.0730359999</v>
+      </c>
+      <c r="K147" s="5">
+        <v>98896.59337599948</v>
+      </c>
+      <c r="L147" s="5">
+        <v>98254.08013599948</v>
+      </c>
+      <c r="M147" s="5">
+        <v>98180.18253599945</v>
+      </c>
+      <c r="N147" s="5">
+        <v>97373.35270399926</v>
+      </c>
+      <c r="O147" s="5">
+        <v>96448.86733599938</v>
+      </c>
+      <c r="P147" s="5">
+        <v>88846.05791599932</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18">
+      <c r="A148" s="2">
+        <v>2011</v>
+      </c>
+      <c r="B148" s="5">
+        <v>1700612.88412</v>
+      </c>
+      <c r="C148" s="5">
+        <v>1225644.888244</v>
+      </c>
+      <c r="D148" s="5">
+        <v>756673.0491999998</v>
+      </c>
+      <c r="E148" s="5">
+        <v>657864.528652</v>
+      </c>
+      <c r="F148" s="5">
+        <v>541276.0607999999</v>
+      </c>
+      <c r="G148" s="5">
+        <v>405875.8635999998</v>
+      </c>
+      <c r="H148" s="5">
+        <v>242523.8991999999</v>
+      </c>
+      <c r="I148" s="5">
+        <v>238934.8643159997</v>
+      </c>
+      <c r="J148" s="5">
+        <v>230626.7155000002</v>
+      </c>
+      <c r="K148" s="5">
+        <v>216565.3878000001</v>
+      </c>
+      <c r="L148" s="5">
+        <v>206945.5169960002</v>
+      </c>
+      <c r="M148" s="5">
+        <v>187749.2826</v>
+      </c>
+      <c r="N148" s="5">
+        <v>178078.3432760001</v>
+      </c>
+      <c r="O148" s="5">
+        <v>172032.6222680002</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18">
+      <c r="A149" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B149" s="5">
+        <v>1247445.859456</v>
+      </c>
+      <c r="C149" s="5">
+        <v>840678.6844</v>
+      </c>
+      <c r="D149" s="5">
+        <v>675912.1351920001</v>
+      </c>
+      <c r="E149" s="5">
+        <v>523685.692</v>
+      </c>
+      <c r="F149" s="5">
+        <v>514077.6844</v>
+      </c>
+      <c r="G149" s="5">
+        <v>507820.1412000001</v>
+      </c>
+      <c r="H149" s="5">
+        <v>497593.848216</v>
+      </c>
+      <c r="I149" s="5">
+        <v>459074.1831800013</v>
+      </c>
+      <c r="J149" s="5">
+        <v>427015.2665480012</v>
+      </c>
+      <c r="K149" s="5">
+        <v>422215.221548001</v>
+      </c>
+      <c r="L149" s="5">
+        <v>390936.0565560013</v>
+      </c>
+      <c r="M149" s="5">
+        <v>329680.3301240013</v>
+      </c>
+      <c r="N149" s="5">
+        <v>281018.9716600012</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18">
+      <c r="A150" s="2">
+        <v>2013</v>
+      </c>
+      <c r="B150" s="5">
+        <v>566967.6800000001</v>
+      </c>
+      <c r="C150" s="5">
+        <v>303416.019948</v>
+      </c>
+      <c r="D150" s="5">
+        <v>224784.8432</v>
+      </c>
+      <c r="E150" s="5">
+        <v>171928.2652</v>
+      </c>
+      <c r="F150" s="5">
+        <v>60879.96639999992</v>
+      </c>
+      <c r="G150" s="5">
+        <v>62721.63974799996</v>
+      </c>
+      <c r="H150" s="5">
+        <v>62373.15978000022</v>
+      </c>
+      <c r="I150" s="5">
+        <v>62373.15977999999</v>
+      </c>
+      <c r="J150" s="5">
+        <v>61007.50574000017</v>
+      </c>
+      <c r="K150" s="5">
+        <v>61007.50574000017</v>
+      </c>
+      <c r="L150" s="5">
+        <v>60996.28914000012</v>
+      </c>
+      <c r="M150" s="5">
+        <v>60996.28914000012</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18">
+      <c r="A151" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B151" s="5">
+        <v>1134034.868604</v>
+      </c>
+      <c r="C151" s="5">
+        <v>807518.9959999999</v>
+      </c>
+      <c r="D151" s="5">
+        <v>619437.7276</v>
+      </c>
+      <c r="E151" s="5">
+        <v>366223.6424</v>
+      </c>
+      <c r="F151" s="5">
+        <v>287208.1453479999</v>
+      </c>
+      <c r="G151" s="5">
+        <v>266319.0093079996</v>
+      </c>
+      <c r="H151" s="5">
+        <v>258500.4452879997</v>
+      </c>
+      <c r="I151" s="5">
+        <v>254678.7781199999</v>
+      </c>
+      <c r="J151" s="5">
+        <v>246510.3353559996</v>
+      </c>
+      <c r="K151" s="5">
+        <v>166437.9970559999</v>
+      </c>
+      <c r="L151" s="5">
+        <v>156152.3352679999</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18">
+      <c r="A152" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B152" s="5">
+        <v>3425587.7352</v>
+      </c>
+      <c r="C152" s="5">
+        <v>2961316.826</v>
+      </c>
+      <c r="D152" s="5">
+        <v>2385869.6168</v>
+      </c>
+      <c r="E152" s="5">
+        <v>1725138.216728</v>
+      </c>
+      <c r="F152" s="5">
+        <v>1571390.578243999</v>
+      </c>
+      <c r="G152" s="5">
+        <v>1317944.744891999</v>
+      </c>
+      <c r="H152" s="5">
+        <v>1042330.924747999</v>
+      </c>
+      <c r="I152" s="5">
+        <v>891072.1178439981</v>
+      </c>
+      <c r="J152" s="5">
+        <v>849279.2641839986</v>
+      </c>
+      <c r="K152" s="5">
+        <v>441781.2814519987</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18">
+      <c r="A153" s="2">
+        <v>2016</v>
+      </c>
+      <c r="B153" s="5">
+        <v>2544414.0672</v>
+      </c>
+      <c r="C153" s="5">
+        <v>1758134.366</v>
+      </c>
+      <c r="D153" s="5">
+        <v>1292543.751232</v>
+      </c>
+      <c r="E153" s="5">
+        <v>1092913.356828</v>
+      </c>
+      <c r="F153" s="5">
+        <v>958146.976704001</v>
+      </c>
+      <c r="G153" s="5">
+        <v>761208.3683600016</v>
+      </c>
+      <c r="H153" s="5">
+        <v>464870.5337240011</v>
+      </c>
+      <c r="I153" s="5">
+        <v>448847.0663920012</v>
+      </c>
+      <c r="J153" s="5">
+        <v>421828.2036080011</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18">
+      <c r="A154" s="2">
+        <v>2017</v>
+      </c>
+      <c r="B154" s="5">
+        <v>1071970.7068</v>
+      </c>
+      <c r="C154" s="5">
+        <v>823832.806096</v>
+      </c>
+      <c r="D154" s="5">
+        <v>778495.9554999997</v>
+      </c>
+      <c r="E154" s="5">
+        <v>698055.9106599998</v>
+      </c>
+      <c r="F154" s="5">
+        <v>635947.5246879997</v>
+      </c>
+      <c r="G154" s="5">
+        <v>552892.9563679997</v>
+      </c>
+      <c r="H154" s="5">
+        <v>303535.3229919996</v>
+      </c>
+      <c r="I154" s="5">
+        <v>202811.2710839997</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18">
+      <c r="A155" s="2">
+        <v>2018</v>
+      </c>
+      <c r="B155" s="5">
+        <v>2495745.971004</v>
+      </c>
+      <c r="C155" s="5">
+        <v>1848045.027112</v>
+      </c>
+      <c r="D155" s="5">
+        <v>1367442.7879</v>
+      </c>
+      <c r="E155" s="5">
+        <v>817061.9613239996</v>
+      </c>
+      <c r="F155" s="5">
+        <v>700760.0578080001</v>
+      </c>
+      <c r="G155" s="5">
+        <v>580315.8243239992</v>
+      </c>
+      <c r="H155" s="5">
+        <v>445716.7166959993</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18">
+      <c r="A156" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B156" s="5">
+        <v>2909069.828336</v>
+      </c>
+      <c r="C156" s="5">
+        <v>2424681.920644</v>
+      </c>
+      <c r="D156" s="5">
+        <v>1844666.216656</v>
+      </c>
+      <c r="E156" s="5">
+        <v>1597653.908359999</v>
+      </c>
+      <c r="F156" s="5">
+        <v>1227509.20942</v>
+      </c>
+      <c r="G156" s="5">
+        <v>803159.8555119992</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18">
+      <c r="A157" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B157" s="5">
+        <v>986836.9847160003</v>
+      </c>
+      <c r="C157" s="5">
+        <v>542665.1538400003</v>
+      </c>
+      <c r="D157" s="5">
+        <v>411049.2659320002</v>
+      </c>
+      <c r="E157" s="5">
+        <v>306817.0706200002</v>
+      </c>
+      <c r="F157" s="5">
+        <v>296702.2574440002</v>
+      </c>
+    </row>
+    <row r="158" spans="1:18">
+      <c r="A158" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B158" s="5">
+        <v>1108507.735004</v>
+      </c>
+      <c r="C158" s="5">
+        <v>835307.9647080001</v>
+      </c>
+      <c r="D158" s="5">
+        <v>470840.6072400002</v>
+      </c>
+      <c r="E158" s="5">
+        <v>407240.4266639999</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18">
+      <c r="A159" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B159" s="5">
+        <v>993959.3162320002</v>
+      </c>
+      <c r="C159" s="5">
+        <v>554655.634912</v>
+      </c>
+      <c r="D159" s="5">
+        <v>510196.4898639999</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18">
+      <c r="A160" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B160" s="5">
+        <v>2728227.648035999</v>
+      </c>
+      <c r="C160" s="5">
+        <v>1896252.811643999</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B161" s="5">
+        <v>2170416.609068</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A28:Y28"/>
+    <mergeCell ref="A55:Y55"/>
+    <mergeCell ref="A82:Y82"/>
+    <mergeCell ref="A109:Y109"/>
+    <mergeCell ref="A136:Y136"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M27"/>

--- a/sample-data/sample-run/Analysis.xlsx
+++ b/sample-data/sample-run/Analysis.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="189">
   <si>
     <t>Accident Period</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>Selected Reasoning</t>
+  </si>
+  <si>
+    <t>Ultimate Loss Rate</t>
   </si>
   <si>
     <t>Incurred CL selected. At 287 months maturity (tail-exposed), CDF 1.0103 and 98.98% developed indicate full maturity. Incurred CL ultimate of 3.196M reflects final case reserves and estimated IBNR. Paid CL 3.054M is only marginally different (1.4% variance), both reasonable. Incurred preferred at this maturity per framework Â§2. Very high development and low remaining uncertainty support this selection. Loss ratio (3.20M / premium) consistent with historical portfolio.</t>
@@ -166,6 +169,12 @@
   </si>
   <si>
     <t>Reported BF</t>
+  </si>
+  <si>
+    <t>Ultimate Severity</t>
+  </si>
+  <si>
+    <t>Ultimate Frequency</t>
   </si>
   <si>
     <t>Reported CL selected. At 287 months maturity, CDF 1.0 and 100% developed indicate full closure. Reported Count ultimate equals actual (700.71). Closed CL would show similar result. Reported Count is simplest, most direct at complete maturity. IBNR 0 is appropriate. No development expected.</t>
@@ -529,15 +538,6 @@
   </si>
   <si>
     <t>REPORTED FREQUENCY</t>
-  </si>
-  <si>
-    <t>Ultimate Severity</t>
-  </si>
-  <si>
-    <t>Ultimate Loss Rate</t>
-  </si>
-  <si>
-    <t>Ultimate Frequency</t>
   </si>
   <si>
     <t>INCURRED-TO-ULTIMATE</t>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>179</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>180</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>185</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>186</v>
@@ -1112,7 +1112,7 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B1" s="3">
         <v>11</v>
@@ -2485,81 +2485,81 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B28" s="6">
         <v>2.7399</v>
@@ -2634,7 +2634,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B29" s="6">
         <v>1.4304</v>
@@ -2707,7 +2707,7 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B30" s="6">
         <v>1.4452</v>
@@ -2778,7 +2778,7 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B31" s="6">
         <v>1.1416</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B32" s="6">
         <v>1.3029</v>
@@ -2914,7 +2914,7 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B33" s="6">
         <v>1.5119</v>
@@ -2979,7 +2979,7 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B34" s="6">
         <v>1.0888</v>
@@ -3042,7 +3042,7 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B35" s="6">
         <v>1.3857</v>
@@ -3103,7 +3103,7 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B36" s="6">
         <v>2.4408</v>
@@ -3162,7 +3162,7 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B37" s="6">
         <v>2.0292</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B38" s="6">
         <v>1.9534</v>
@@ -3274,7 +3274,7 @@
     </row>
     <row r="39" spans="1:25">
       <c r="A39" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B39" s="6">
         <v>2.0319</v>
@@ -3327,7 +3327,7 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B40" s="6">
         <v>1.8261</v>
@@ -3378,7 +3378,7 @@
     </row>
     <row r="41" spans="1:25">
       <c r="A41" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B41" s="6">
         <v>1.3662</v>
@@ -3427,7 +3427,7 @@
     </row>
     <row r="42" spans="1:25">
       <c r="A42" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B42" s="6">
         <v>1.9857</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="43" spans="1:25">
       <c r="A43" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B43" s="6">
         <v>1.8697</v>
@@ -3519,7 +3519,7 @@
     </row>
     <row r="44" spans="1:25">
       <c r="A44" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B44" s="6">
         <v>1.3328</v>
@@ -3562,7 +3562,7 @@
     </row>
     <row r="45" spans="1:25">
       <c r="A45" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B45" s="6">
         <v>2.2994</v>
@@ -3603,7 +3603,7 @@
     </row>
     <row r="46" spans="1:25">
       <c r="A46" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B46" s="6">
         <v>2.757</v>
@@ -3642,7 +3642,7 @@
     </row>
     <row r="47" spans="1:25">
       <c r="A47" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B47" s="6">
         <v>1.7849</v>
@@ -3679,7 +3679,7 @@
     </row>
     <row r="48" spans="1:25">
       <c r="A48" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B48" s="6">
         <v>1.4577</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="49" spans="1:25">
       <c r="A49" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B49" s="6">
         <v>1.2261</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="50" spans="1:25">
       <c r="A50" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B50" s="6">
         <v>1.6941</v>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="51" spans="1:25">
       <c r="A51" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -3807,84 +3807,84 @@
     </row>
     <row r="53" spans="1:25">
       <c r="A53" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="X53" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="54" spans="1:25">
       <c r="A54" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B54" s="6">
         <v>1.7435</v>
@@ -3959,7 +3959,7 @@
     </row>
     <row r="55" spans="1:25">
       <c r="A55" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B55" s="6">
         <v>1.6135</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="56" spans="1:25">
       <c r="A56" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B56" s="6">
         <v>1.7265</v>
@@ -4109,7 +4109,7 @@
     </row>
     <row r="57" spans="1:25">
       <c r="A57" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B57" s="6">
         <v>1.4593</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="58" spans="1:25">
       <c r="A58" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B58" s="6">
         <v>1.4891</v>
@@ -4259,7 +4259,7 @@
     </row>
     <row r="59" spans="1:25">
       <c r="A59" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B59" s="6">
         <v>1.784</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="60" spans="1:25">
       <c r="A60" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B60" s="6">
         <v>1.7024</v>
@@ -4409,7 +4409,7 @@
     </row>
     <row r="61" spans="1:25">
       <c r="A61" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B61" s="6">
         <v>1.6456</v>
@@ -4484,7 +4484,7 @@
     </row>
     <row r="62" spans="1:25">
       <c r="A62" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B62" s="6">
         <v>1.7774</v>
@@ -4559,7 +4559,7 @@
     </row>
     <row r="63" spans="1:25">
       <c r="A63" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B63" s="6">
         <v>1.7371</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="64" spans="1:25">
       <c r="A64" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B64" s="6">
         <v>1.7238</v>
@@ -4709,81 +4709,81 @@
     </row>
     <row r="66" spans="1:25">
       <c r="A66" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q66" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T66" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="V66" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="W66" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="X66" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:25">
       <c r="A67" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="70" spans="1:25">
       <c r="A70" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B70" s="6">
         <v>2.837330291099596</v>
@@ -4932,7 +4932,7 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B1" s="3">
         <v>11</v>
@@ -6305,81 +6305,81 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B28" s="6">
         <v>3.2124</v>
@@ -6454,7 +6454,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B29" s="6">
         <v>2.5494</v>
@@ -6527,7 +6527,7 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B30" s="6">
         <v>2.4837</v>
@@ -6598,7 +6598,7 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B31" s="6">
         <v>2.4368</v>
@@ -6667,7 +6667,7 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B32" s="6">
         <v>2.0311</v>
@@ -6734,7 +6734,7 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B33" s="6">
         <v>2.4565</v>
@@ -6799,7 +6799,7 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B34" s="6">
         <v>2.1908</v>
@@ -6862,7 +6862,7 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B35" s="6">
         <v>1.829</v>
@@ -6923,7 +6923,7 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B36" s="6">
         <v>3.246</v>
@@ -6982,7 +6982,7 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B37" s="6">
         <v>2.7631</v>
@@ -7039,7 +7039,7 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B38" s="6">
         <v>2.3046</v>
@@ -7094,7 +7094,7 @@
     </row>
     <row r="39" spans="1:25">
       <c r="A39" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B39" s="6">
         <v>2.7856</v>
@@ -7147,7 +7147,7 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B40" s="6">
         <v>2.3011</v>
@@ -7198,7 +7198,7 @@
     </row>
     <row r="41" spans="1:25">
       <c r="A41" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B41" s="6">
         <v>1.7931</v>
@@ -7247,7 +7247,7 @@
     </row>
     <row r="42" spans="1:25">
       <c r="A42" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B42" s="6">
         <v>2.2204</v>
@@ -7294,7 +7294,7 @@
     </row>
     <row r="43" spans="1:25">
       <c r="A43" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B43" s="6">
         <v>3.3152</v>
@@ -7339,7 +7339,7 @@
     </row>
     <row r="44" spans="1:25">
       <c r="A44" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B44" s="6">
         <v>1.7371</v>
@@ -7382,7 +7382,7 @@
     </row>
     <row r="45" spans="1:25">
       <c r="A45" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B45" s="6">
         <v>2.8751</v>
@@ -7423,7 +7423,7 @@
     </row>
     <row r="46" spans="1:25">
       <c r="A46" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B46" s="6">
         <v>2.6745</v>
@@ -7462,7 +7462,7 @@
     </row>
     <row r="47" spans="1:25">
       <c r="A47" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B47" s="6">
         <v>2.5535</v>
@@ -7499,7 +7499,7 @@
     </row>
     <row r="48" spans="1:25">
       <c r="A48" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B48" s="6">
         <v>1.9981</v>
@@ -7534,7 +7534,7 @@
     </row>
     <row r="49" spans="1:25">
       <c r="A49" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B49" s="6">
         <v>2.4294</v>
@@ -7567,7 +7567,7 @@
     </row>
     <row r="50" spans="1:25">
       <c r="A50" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B50" s="6">
         <v>3.2653</v>
@@ -7598,7 +7598,7 @@
     </row>
     <row r="51" spans="1:25">
       <c r="A51" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -7627,84 +7627,84 @@
     </row>
     <row r="53" spans="1:25">
       <c r="A53" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="X53" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="54" spans="1:25">
       <c r="A54" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B54" s="6">
         <v>2.4979</v>
@@ -7779,7 +7779,7 @@
     </row>
     <row r="55" spans="1:25">
       <c r="A55" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B55" s="6">
         <v>2.4566</v>
@@ -7854,7 +7854,7 @@
     </row>
     <row r="56" spans="1:25">
       <c r="A56" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B56" s="6">
         <v>2.4952</v>
@@ -7929,7 +7929,7 @@
     </row>
     <row r="57" spans="1:25">
       <c r="A57" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B57" s="6">
         <v>2.5643</v>
@@ -8004,7 +8004,7 @@
     </row>
     <row r="58" spans="1:25">
       <c r="A58" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B58" s="6">
         <v>2.6286</v>
@@ -8079,7 +8079,7 @@
     </row>
     <row r="59" spans="1:25">
       <c r="A59" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B59" s="6">
         <v>2.5842</v>
@@ -8154,7 +8154,7 @@
     </row>
     <row r="60" spans="1:25">
       <c r="A60" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B60" s="6">
         <v>2.6232</v>
@@ -8229,7 +8229,7 @@
     </row>
     <row r="61" spans="1:25">
       <c r="A61" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B61" s="6">
         <v>2.5525</v>
@@ -8304,7 +8304,7 @@
     </row>
     <row r="62" spans="1:25">
       <c r="A62" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B62" s="6">
         <v>2.4862</v>
@@ -8379,7 +8379,7 @@
     </row>
     <row r="63" spans="1:25">
       <c r="A63" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B63" s="6">
         <v>2.482</v>
@@ -8454,7 +8454,7 @@
     </row>
     <row r="64" spans="1:25">
       <c r="A64" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B64" s="6">
         <v>2.4762</v>
@@ -8529,81 +8529,81 @@
     </row>
     <row r="66" spans="1:25">
       <c r="A66" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q66" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T66" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="V66" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="W66" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="X66" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:25">
       <c r="A67" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -8661,7 +8661,7 @@
     </row>
     <row r="70" spans="1:25">
       <c r="A70" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B70" s="6">
         <v>6.356087136500853</v>
@@ -8752,7 +8752,7 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B1" s="3">
         <v>11</v>
@@ -10125,81 +10125,81 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B28" s="6">
         <v>1.0704</v>
@@ -10274,7 +10274,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B29" s="6">
         <v>1.0344</v>
@@ -10347,7 +10347,7 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B30" s="6">
         <v>1.0346</v>
@@ -10418,7 +10418,7 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B31" s="6">
         <v>1.0591</v>
@@ -10487,7 +10487,7 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B32" s="6">
         <v>1.0232</v>
@@ -10554,7 +10554,7 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B33" s="6">
         <v>1.0386</v>
@@ -10619,7 +10619,7 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B34" s="6">
         <v>1.0434</v>
@@ -10682,7 +10682,7 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B35" s="6">
         <v>1.0644</v>
@@ -10743,7 +10743,7 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B36" s="6">
         <v>1.0474</v>
@@ -10802,7 +10802,7 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B37" s="6">
         <v>1.0457</v>
@@ -10859,7 +10859,7 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B38" s="6">
         <v>1</v>
@@ -10914,7 +10914,7 @@
     </row>
     <row r="39" spans="1:25">
       <c r="A39" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B39" s="6">
         <v>1.0645</v>
@@ -10967,7 +10967,7 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B40" s="6">
         <v>1.028</v>
@@ -11018,7 +11018,7 @@
     </row>
     <row r="41" spans="1:25">
       <c r="A41" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B41" s="6">
         <v>1.0456</v>
@@ -11067,7 +11067,7 @@
     </row>
     <row r="42" spans="1:25">
       <c r="A42" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B42" s="6">
         <v>1.0328</v>
@@ -11114,7 +11114,7 @@
     </row>
     <row r="43" spans="1:25">
       <c r="A43" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B43" s="6">
         <v>1.0802</v>
@@ -11159,7 +11159,7 @@
     </row>
     <row r="44" spans="1:25">
       <c r="A44" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B44" s="6">
         <v>1.1244</v>
@@ -11202,7 +11202,7 @@
     </row>
     <row r="45" spans="1:25">
       <c r="A45" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B45" s="6">
         <v>1.1233</v>
@@ -11243,7 +11243,7 @@
     </row>
     <row r="46" spans="1:25">
       <c r="A46" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B46" s="6">
         <v>1.1429</v>
@@ -11282,7 +11282,7 @@
     </row>
     <row r="47" spans="1:25">
       <c r="A47" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B47" s="6">
         <v>1.0604</v>
@@ -11319,7 +11319,7 @@
     </row>
     <row r="48" spans="1:25">
       <c r="A48" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B48" s="6">
         <v>1.1416</v>
@@ -11354,7 +11354,7 @@
     </row>
     <row r="49" spans="1:25">
       <c r="A49" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B49" s="6">
         <v>1.1414</v>
@@ -11387,7 +11387,7 @@
     </row>
     <row r="50" spans="1:25">
       <c r="A50" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B50" s="6">
         <v>1.1159</v>
@@ -11418,7 +11418,7 @@
     </row>
     <row r="51" spans="1:25">
       <c r="A51" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -11447,84 +11447,84 @@
     </row>
     <row r="53" spans="1:25">
       <c r="A53" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="X53" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="54" spans="1:25">
       <c r="A54" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B54" s="6">
         <v>1.0679</v>
@@ -11599,7 +11599,7 @@
     </row>
     <row r="55" spans="1:25">
       <c r="A55" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B55" s="6">
         <v>1.0617</v>
@@ -11674,7 +11674,7 @@
     </row>
     <row r="56" spans="1:25">
       <c r="A56" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B56" s="6">
         <v>1.0676</v>
@@ -11749,7 +11749,7 @@
     </row>
     <row r="57" spans="1:25">
       <c r="A57" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B57" s="6">
         <v>1.133</v>
@@ -11824,7 +11824,7 @@
     </row>
     <row r="58" spans="1:25">
       <c r="A58" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B58" s="6">
         <v>1.133</v>
@@ -11899,7 +11899,7 @@
     </row>
     <row r="59" spans="1:25">
       <c r="A59" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B59" s="6">
         <v>1.1204</v>
@@ -11974,7 +11974,7 @@
     </row>
     <row r="60" spans="1:25">
       <c r="A60" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B60" s="6">
         <v>1.118</v>
@@ -12049,7 +12049,7 @@
     </row>
     <row r="61" spans="1:25">
       <c r="A61" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B61" s="6">
         <v>1.133</v>
@@ -12124,7 +12124,7 @@
     </row>
     <row r="62" spans="1:25">
       <c r="A62" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B62" s="6">
         <v>1.1009</v>
@@ -12199,7 +12199,7 @@
     </row>
     <row r="63" spans="1:25">
       <c r="A63" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B63" s="6">
         <v>1.0962</v>
@@ -12274,7 +12274,7 @@
     </row>
     <row r="64" spans="1:25">
       <c r="A64" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B64" s="6">
         <v>1.1041</v>
@@ -12349,81 +12349,81 @@
     </row>
     <row r="66" spans="1:25">
       <c r="A66" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q66" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="T66" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="V66" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="W66" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="X66" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:25">
       <c r="A67" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -12481,7 +12481,7 @@
     </row>
     <row r="70" spans="1:25">
       <c r="A70" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B70" s="6">
         <v>1.1337932133</v>
@@ -12571,10 +12571,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -12785,7 +12785,7 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -12814,84 +12814,84 @@
     </row>
     <row r="2" spans="1:25">
       <c r="A2" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="R2" s="8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="T2" s="8" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="U2" s="8" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="V2" s="8" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="W2" s="8" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="X2" s="8" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Y2" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:25">
       <c r="A3" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B3" s="5">
         <v>890.1180000000001</v>
@@ -12968,7 +12968,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B4" s="5">
         <v>1512.0882</v>
@@ -13042,7 +13042,7 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B5" s="5">
         <v>1888.6444</v>
@@ -13113,7 +13113,7 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B6" s="5">
         <v>1172.3435</v>
@@ -13181,7 +13181,7 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B7" s="5">
         <v>1993.7326</v>
@@ -13246,7 +13246,7 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B8" s="5">
         <v>1599.0849</v>
@@ -13308,7 +13308,7 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B9" s="5">
         <v>3777.3245</v>
@@ -13367,7 +13367,7 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B10" s="5">
         <v>1809.473</v>
@@ -13423,7 +13423,7 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B11" s="5">
         <v>1167.6749</v>
@@ -13476,7 +13476,7 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B12" s="5">
         <v>1384.9391</v>
@@ -13526,7 +13526,7 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B13" s="5">
         <v>1313.2806</v>
@@ -13573,7 +13573,7 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B14" s="5">
         <v>1368.4788</v>
@@ -13617,7 +13617,7 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B15" s="5">
         <v>988.3224</v>
@@ -13658,7 +13658,7 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B16" s="5">
         <v>1334.6909</v>
@@ -13696,7 +13696,7 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B17" s="5">
         <v>1671.1066</v>
@@ -13731,7 +13731,7 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B18" s="5">
         <v>1989.3893</v>
@@ -13763,7 +13763,7 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B19" s="5">
         <v>1672.7081</v>
@@ -13792,7 +13792,7 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B20" s="5">
         <v>1757.7757</v>
@@ -13818,7 +13818,7 @@
     </row>
     <row r="21" spans="1:25">
       <c r="A21" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B21" s="5">
         <v>1298.8238</v>
@@ -13841,7 +13841,7 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B22" s="5">
         <v>1493.0271</v>
@@ -13861,7 +13861,7 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B23" s="5">
         <v>1901.2855</v>
@@ -13878,7 +13878,7 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B24" s="5">
         <v>2658.5306</v>
@@ -13892,7 +13892,7 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B25" s="5">
         <v>3569.3743</v>
@@ -13903,7 +13903,7 @@
     </row>
     <row r="26" spans="1:25">
       <c r="A26" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B26" s="5">
         <v>3477.1362</v>
@@ -13911,7 +13911,7 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -13940,84 +13940,84 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="O29" s="8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="P29" s="8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q29" s="8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="R29" s="8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="S29" s="8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="T29" s="8" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="U29" s="8" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="V29" s="8" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="W29" s="8" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="X29" s="8" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Y29" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:25">
       <c r="A30" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B30" s="6">
         <v>0.5747</v>
@@ -14094,7 +14094,7 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B31" s="6">
         <v>0.3852</v>
@@ -14168,7 +14168,7 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B32" s="6">
         <v>0.4594</v>
@@ -14239,7 +14239,7 @@
     </row>
     <row r="33" spans="1:22">
       <c r="A33" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B33" s="6">
         <v>0.3634</v>
@@ -14307,7 +14307,7 @@
     </row>
     <row r="34" spans="1:22">
       <c r="A34" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B34" s="6">
         <v>0.4873</v>
@@ -14372,7 +14372,7 @@
     </row>
     <row r="35" spans="1:22">
       <c r="A35" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B35" s="6">
         <v>0.3718</v>
@@ -14434,7 +14434,7 @@
     </row>
     <row r="36" spans="1:22">
       <c r="A36" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B36" s="6">
         <v>0.292</v>
@@ -14493,7 +14493,7 @@
     </row>
     <row r="37" spans="1:22">
       <c r="A37" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B37" s="6">
         <v>0.6354</v>
@@ -14549,7 +14549,7 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B38" s="6">
         <v>0.6397</v>
@@ -14602,7 +14602,7 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B39" s="6">
         <v>0.6767</v>
@@ -14652,7 +14652,7 @@
     </row>
     <row r="40" spans="1:22">
       <c r="A40" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B40" s="6">
         <v>0.8018999999999999</v>
@@ -14699,7 +14699,7 @@
     </row>
     <row r="41" spans="1:22">
       <c r="A41" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B41" s="6">
         <v>0.6782</v>
@@ -14743,7 +14743,7 @@
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B42" s="6">
         <v>0.7258</v>
@@ -14784,7 +14784,7 @@
     </row>
     <row r="43" spans="1:22">
       <c r="A43" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B43" s="6">
         <v>0.7105</v>
@@ -14822,7 +14822,7 @@
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B44" s="6">
         <v>0.707</v>
@@ -14857,7 +14857,7 @@
     </row>
     <row r="45" spans="1:22">
       <c r="A45" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B45" s="6">
         <v>0.4938</v>
@@ -14889,7 +14889,7 @@
     </row>
     <row r="46" spans="1:22">
       <c r="A46" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B46" s="6">
         <v>0.7297</v>
@@ -14918,7 +14918,7 @@
     </row>
     <row r="47" spans="1:22">
       <c r="A47" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B47" s="6">
         <v>0.68</v>
@@ -14944,7 +14944,7 @@
     </row>
     <row r="48" spans="1:22">
       <c r="A48" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B48" s="6">
         <v>0.7092000000000001</v>
@@ -14967,7 +14967,7 @@
     </row>
     <row r="49" spans="1:25">
       <c r="A49" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B49" s="6">
         <v>0.5476</v>
@@ -14987,7 +14987,7 @@
     </row>
     <row r="50" spans="1:25">
       <c r="A50" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B50" s="6">
         <v>0.4982</v>
@@ -15004,7 +15004,7 @@
     </row>
     <row r="51" spans="1:25">
       <c r="A51" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B51" s="6">
         <v>0.4425</v>
@@ -15018,7 +15018,7 @@
     </row>
     <row r="52" spans="1:25">
       <c r="A52" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B52" s="6">
         <v>0.3767</v>
@@ -15029,7 +15029,7 @@
     </row>
     <row r="53" spans="1:25">
       <c r="A53" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B53" s="6">
         <v>0.3991</v>
@@ -15037,7 +15037,7 @@
     </row>
     <row r="55" spans="1:25">
       <c r="A55" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -15066,84 +15066,84 @@
     </row>
     <row r="56" spans="1:25">
       <c r="A56" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L56" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="M56" s="8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="N56" s="8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="O56" s="8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="P56" s="8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q56" s="8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="R56" s="8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="S56" s="8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="T56" s="8" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="U56" s="8" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="V56" s="8" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="W56" s="8" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="X56" s="8" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Y56" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57" spans="1:25">
       <c r="A57" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B57" s="5">
         <v>241287.5404</v>
@@ -15220,7 +15220,7 @@
     </row>
     <row r="58" spans="1:25">
       <c r="A58" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B58" s="5">
         <v>570477.5956</v>
@@ -15294,7 +15294,7 @@
     </row>
     <row r="59" spans="1:25">
       <c r="A59" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B59" s="5">
         <v>545628.208</v>
@@ -15365,7 +15365,7 @@
     </row>
     <row r="60" spans="1:25">
       <c r="A60" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B60" s="5">
         <v>450102.364</v>
@@ -15433,7 +15433,7 @@
     </row>
     <row r="61" spans="1:25">
       <c r="A61" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B61" s="5">
         <v>640698.79</v>
@@ -15498,7 +15498,7 @@
     </row>
     <row r="62" spans="1:25">
       <c r="A62" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B62" s="5">
         <v>481198.9096</v>
@@ -15560,7 +15560,7 @@
     </row>
     <row r="63" spans="1:25">
       <c r="A63" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B63" s="5">
         <v>1221079.0071</v>
@@ -15619,7 +15619,7 @@
     </row>
     <row r="64" spans="1:25">
       <c r="A64" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B64" s="5">
         <v>202836.1251</v>
@@ -15675,7 +15675,7 @@
     </row>
     <row r="65" spans="1:17">
       <c r="A65" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B65" s="5">
         <v>128812.754</v>
@@ -15728,7 +15728,7 @@
     </row>
     <row r="66" spans="1:17">
       <c r="A66" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B66" s="5">
         <v>116407.2868</v>
@@ -15778,7 +15778,7 @@
     </row>
     <row r="67" spans="1:17">
       <c r="A67" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B67" s="5">
         <v>89969.2987</v>
@@ -15825,7 +15825,7 @@
     </row>
     <row r="68" spans="1:17">
       <c r="A68" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B68" s="5">
         <v>108077.1139</v>
@@ -15869,7 +15869,7 @@
     </row>
     <row r="69" spans="1:17">
       <c r="A69" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B69" s="5">
         <v>76538.11960000001</v>
@@ -15910,7 +15910,7 @@
     </row>
     <row r="70" spans="1:17">
       <c r="A70" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B70" s="5">
         <v>167732.7461</v>
@@ -15948,7 +15948,7 @@
     </row>
     <row r="71" spans="1:17">
       <c r="A71" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B71" s="5">
         <v>157642.0552</v>
@@ -15983,7 +15983,7 @@
     </row>
     <row r="72" spans="1:17">
       <c r="A72" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B72" s="5">
         <v>348179.0992</v>
@@ -16015,7 +16015,7 @@
     </row>
     <row r="73" spans="1:17">
       <c r="A73" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B73" s="5">
         <v>124674.4884</v>
@@ -16044,7 +16044,7 @@
     </row>
     <row r="74" spans="1:17">
       <c r="A74" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B74" s="5">
         <v>162564.6514</v>
@@ -16070,7 +16070,7 @@
     </row>
     <row r="75" spans="1:17">
       <c r="A75" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B75" s="5">
         <v>118634.9695</v>
@@ -16093,7 +16093,7 @@
     </row>
     <row r="76" spans="1:17">
       <c r="A76" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B76" s="5">
         <v>236186.4682</v>
@@ -16113,7 +16113,7 @@
     </row>
     <row r="77" spans="1:17">
       <c r="A77" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B77" s="5">
         <v>275744.962</v>
@@ -16130,7 +16130,7 @@
     </row>
     <row r="78" spans="1:17">
       <c r="A78" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B78" s="5">
         <v>387282.1198</v>
@@ -16144,7 +16144,7 @@
     </row>
     <row r="79" spans="1:17">
       <c r="A79" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B79" s="5">
         <v>607733.0706</v>
@@ -16155,7 +16155,7 @@
     </row>
     <row r="80" spans="1:17">
       <c r="A80" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B80" s="5">
         <v>534907.4608999999</v>
@@ -16163,7 +16163,7 @@
     </row>
     <row r="82" spans="1:25">
       <c r="A82" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -16192,84 +16192,84 @@
     </row>
     <row r="83" spans="1:25">
       <c r="A83" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J83" s="8" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K83" s="8" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L83" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="M83" s="8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="N83" s="8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="O83" s="8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="P83" s="8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q83" s="8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="R83" s="8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="S83" s="8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="T83" s="8" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="U83" s="8" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="V83" s="8" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="W83" s="8" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="X83" s="8" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Y83" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="84" spans="1:25">
       <c r="A84" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B84" s="5">
         <v>0.0018</v>
@@ -16346,7 +16346,7 @@
     </row>
     <row r="85" spans="1:25">
       <c r="A85" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B85" s="5">
         <v>0.0029</v>
@@ -16420,7 +16420,7 @@
     </row>
     <row r="86" spans="1:25">
       <c r="A86" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B86" s="5">
         <v>0.0031</v>
@@ -16491,7 +16491,7 @@
     </row>
     <row r="87" spans="1:25">
       <c r="A87" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B87" s="5">
         <v>0.0021</v>
@@ -16559,7 +16559,7 @@
     </row>
     <row r="88" spans="1:25">
       <c r="A88" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B88" s="5">
         <v>0.0036</v>
@@ -16624,7 +16624,7 @@
     </row>
     <row r="89" spans="1:25">
       <c r="A89" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B89" s="5">
         <v>0.0022</v>
@@ -16686,7 +16686,7 @@
     </row>
     <row r="90" spans="1:25">
       <c r="A90" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B90" s="5">
         <v>0.0048</v>
@@ -16745,7 +16745,7 @@
     </row>
     <row r="91" spans="1:25">
       <c r="A91" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B91" s="5">
         <v>0.0015</v>
@@ -16801,7 +16801,7 @@
     </row>
     <row r="92" spans="1:25">
       <c r="A92" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B92" s="5">
         <v>0.001</v>
@@ -16854,7 +16854,7 @@
     </row>
     <row r="93" spans="1:25">
       <c r="A93" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B93" s="5">
         <v>0.001</v>
@@ -16904,7 +16904,7 @@
     </row>
     <row r="94" spans="1:25">
       <c r="A94" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B94" s="5">
         <v>0.0012</v>
@@ -16951,7 +16951,7 @@
     </row>
     <row r="95" spans="1:25">
       <c r="A95" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B95" s="5">
         <v>0.0009</v>
@@ -16995,7 +16995,7 @@
     </row>
     <row r="96" spans="1:25">
       <c r="A96" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B96" s="5">
         <v>0.0007</v>
@@ -17036,7 +17036,7 @@
     </row>
     <row r="97" spans="1:25">
       <c r="A97" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B97" s="5">
         <v>0.0014</v>
@@ -17074,7 +17074,7 @@
     </row>
     <row r="98" spans="1:25">
       <c r="A98" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B98" s="5">
         <v>0.0013</v>
@@ -17109,7 +17109,7 @@
     </row>
     <row r="99" spans="1:25">
       <c r="A99" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B99" s="5">
         <v>0.0016</v>
@@ -17141,7 +17141,7 @@
     </row>
     <row r="100" spans="1:25">
       <c r="A100" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B100" s="5">
         <v>0.0011</v>
@@ -17170,7 +17170,7 @@
     </row>
     <row r="101" spans="1:25">
       <c r="A101" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B101" s="5">
         <v>0.0011</v>
@@ -17196,7 +17196,7 @@
     </row>
     <row r="102" spans="1:25">
       <c r="A102" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B102" s="5">
         <v>0.0009</v>
@@ -17219,7 +17219,7 @@
     </row>
     <row r="103" spans="1:25">
       <c r="A103" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B103" s="5">
         <v>0.0011</v>
@@ -17239,7 +17239,7 @@
     </row>
     <row r="104" spans="1:25">
       <c r="A104" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B104" s="5">
         <v>0.0012</v>
@@ -17256,7 +17256,7 @@
     </row>
     <row r="105" spans="1:25">
       <c r="A105" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B105" s="5">
         <v>0.0014</v>
@@ -17270,7 +17270,7 @@
     </row>
     <row r="106" spans="1:25">
       <c r="A106" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B106" s="5">
         <v>0.002</v>
@@ -17281,7 +17281,7 @@
     </row>
     <row r="107" spans="1:25">
       <c r="A107" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B107" s="5">
         <v>0.0018</v>
@@ -17289,7 +17289,7 @@
     </row>
     <row r="109" spans="1:25">
       <c r="A109" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -17318,84 +17318,84 @@
     </row>
     <row r="110" spans="1:25">
       <c r="A110" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H110" s="8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K110" s="8" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L110" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="M110" s="8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="N110" s="8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="O110" s="8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="P110" s="8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q110" s="8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="R110" s="8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="S110" s="8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="T110" s="8" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="U110" s="8" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="V110" s="8" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="W110" s="8" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="X110" s="8" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Y110" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="111" spans="1:25">
       <c r="A111" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B111" s="5">
         <v>0.001</v>
@@ -17472,7 +17472,7 @@
     </row>
     <row r="112" spans="1:25">
       <c r="A112" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B112" s="5">
         <v>0.0011</v>
@@ -17546,7 +17546,7 @@
     </row>
     <row r="113" spans="1:23">
       <c r="A113" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B113" s="5">
         <v>0.0014</v>
@@ -17617,7 +17617,7 @@
     </row>
     <row r="114" spans="1:23">
       <c r="A114" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B114" s="5">
         <v>0.0008</v>
@@ -17685,7 +17685,7 @@
     </row>
     <row r="115" spans="1:23">
       <c r="A115" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B115" s="5">
         <v>0.0018</v>
@@ -17750,7 +17750,7 @@
     </row>
     <row r="116" spans="1:23">
       <c r="A116" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B116" s="5">
         <v>0.0008</v>
@@ -17812,7 +17812,7 @@
     </row>
     <row r="117" spans="1:23">
       <c r="A117" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B117" s="5">
         <v>0.0014</v>
@@ -17871,7 +17871,7 @@
     </row>
     <row r="118" spans="1:23">
       <c r="A118" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B118" s="5">
         <v>0.001</v>
@@ -17927,7 +17927,7 @@
     </row>
     <row r="119" spans="1:23">
       <c r="A119" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B119" s="5">
         <v>0.0005999999999999999</v>
@@ -17980,7 +17980,7 @@
     </row>
     <row r="120" spans="1:23">
       <c r="A120" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B120" s="5">
         <v>0.0005999999999999999</v>
@@ -18030,7 +18030,7 @@
     </row>
     <row r="121" spans="1:23">
       <c r="A121" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B121" s="5">
         <v>0.0009</v>
@@ -18077,7 +18077,7 @@
     </row>
     <row r="122" spans="1:23">
       <c r="A122" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B122" s="5">
         <v>0.0005999999999999999</v>
@@ -18121,7 +18121,7 @@
     </row>
     <row r="123" spans="1:23">
       <c r="A123" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B123" s="5">
         <v>0.0005</v>
@@ -18162,7 +18162,7 @@
     </row>
     <row r="124" spans="1:23">
       <c r="A124" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B124" s="5">
         <v>0.001</v>
@@ -18200,7 +18200,7 @@
     </row>
     <row r="125" spans="1:23">
       <c r="A125" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B125" s="5">
         <v>0.0009</v>
@@ -18235,7 +18235,7 @@
     </row>
     <row r="126" spans="1:23">
       <c r="A126" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B126" s="5">
         <v>0.0008</v>
@@ -18267,7 +18267,7 @@
     </row>
     <row r="127" spans="1:23">
       <c r="A127" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B127" s="5">
         <v>0.0008</v>
@@ -18296,7 +18296,7 @@
     </row>
     <row r="128" spans="1:23">
       <c r="A128" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B128" s="5">
         <v>0.0008</v>
@@ -18322,7 +18322,7 @@
     </row>
     <row r="129" spans="1:25">
       <c r="A129" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B129" s="5">
         <v>0.0005999999999999999</v>
@@ -18345,7 +18345,7 @@
     </row>
     <row r="130" spans="1:25">
       <c r="A130" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B130" s="5">
         <v>0.0005999999999999999</v>
@@ -18365,7 +18365,7 @@
     </row>
     <row r="131" spans="1:25">
       <c r="A131" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B131" s="5">
         <v>0.0005999999999999999</v>
@@ -18382,7 +18382,7 @@
     </row>
     <row r="132" spans="1:25">
       <c r="A132" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B132" s="5">
         <v>0.0005999999999999999</v>
@@ -18396,7 +18396,7 @@
     </row>
     <row r="133" spans="1:25">
       <c r="A133" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B133" s="5">
         <v>0.0008</v>
@@ -18407,7 +18407,7 @@
     </row>
     <row r="134" spans="1:25">
       <c r="A134" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B134" s="5">
         <v>0.0007</v>
@@ -18415,7 +18415,7 @@
     </row>
     <row r="136" spans="1:25">
       <c r="A136" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -18444,84 +18444,84 @@
     </row>
     <row r="137" spans="1:25">
       <c r="A137" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H137" s="8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J137" s="8" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K137" s="8" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L137" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="M137" s="8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="N137" s="8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="O137" s="8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="P137" s="8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q137" s="8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="R137" s="8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="S137" s="8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="T137" s="8" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="U137" s="8" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="V137" s="8" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="W137" s="8" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="X137" s="8" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Y137" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="138" spans="1:25">
       <c r="A138" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B138" s="6">
         <v>0</v>
@@ -18598,7 +18598,7 @@
     </row>
     <row r="139" spans="1:25">
       <c r="A139" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B139" s="6">
         <v>0</v>
@@ -18672,7 +18672,7 @@
     </row>
     <row r="140" spans="1:25">
       <c r="A140" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B140" s="6">
         <v>0</v>
@@ -18743,7 +18743,7 @@
     </row>
     <row r="141" spans="1:25">
       <c r="A141" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B141" s="6">
         <v>0</v>
@@ -18811,7 +18811,7 @@
     </row>
     <row r="142" spans="1:25">
       <c r="A142" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B142" s="6">
         <v>0</v>
@@ -18876,7 +18876,7 @@
     </row>
     <row r="143" spans="1:25">
       <c r="A143" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B143" s="6">
         <v>0</v>
@@ -18938,7 +18938,7 @@
     </row>
     <row r="144" spans="1:25">
       <c r="A144" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B144" s="6">
         <v>0</v>
@@ -18997,7 +18997,7 @@
     </row>
     <row r="145" spans="1:18">
       <c r="A145" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B145" s="6">
         <v>0</v>
@@ -19053,7 +19053,7 @@
     </row>
     <row r="146" spans="1:18">
       <c r="A146" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B146" s="6">
         <v>0</v>
@@ -19106,7 +19106,7 @@
     </row>
     <row r="147" spans="1:18">
       <c r="A147" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B147" s="6">
         <v>0</v>
@@ -19156,7 +19156,7 @@
     </row>
     <row r="148" spans="1:18">
       <c r="A148" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B148" s="6">
         <v>0</v>
@@ -19203,7 +19203,7 @@
     </row>
     <row r="149" spans="1:18">
       <c r="A149" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B149" s="6">
         <v>0</v>
@@ -19247,7 +19247,7 @@
     </row>
     <row r="150" spans="1:18">
       <c r="A150" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B150" s="6">
         <v>0</v>
@@ -19288,7 +19288,7 @@
     </row>
     <row r="151" spans="1:18">
       <c r="A151" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B151" s="6">
         <v>0</v>
@@ -19326,7 +19326,7 @@
     </row>
     <row r="152" spans="1:18">
       <c r="A152" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B152" s="6">
         <v>0</v>
@@ -19361,7 +19361,7 @@
     </row>
     <row r="153" spans="1:18">
       <c r="A153" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B153" s="6">
         <v>0</v>
@@ -19393,7 +19393,7 @@
     </row>
     <row r="154" spans="1:18">
       <c r="A154" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B154" s="6">
         <v>0</v>
@@ -19422,7 +19422,7 @@
     </row>
     <row r="155" spans="1:18">
       <c r="A155" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B155" s="6">
         <v>0</v>
@@ -19448,7 +19448,7 @@
     </row>
     <row r="156" spans="1:18">
       <c r="A156" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B156" s="6">
         <v>0</v>
@@ -19471,7 +19471,7 @@
     </row>
     <row r="157" spans="1:18">
       <c r="A157" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B157" s="6">
         <v>0</v>
@@ -19491,7 +19491,7 @@
     </row>
     <row r="158" spans="1:18">
       <c r="A158" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B158" s="6">
         <v>0</v>
@@ -19508,7 +19508,7 @@
     </row>
     <row r="159" spans="1:18">
       <c r="A159" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B159" s="6">
         <v>0</v>
@@ -19522,7 +19522,7 @@
     </row>
     <row r="160" spans="1:18">
       <c r="A160" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B160" s="6">
         <v>0</v>
@@ -19533,7 +19533,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B161" s="6">
         <v>0</v>
@@ -19566,13 +19566,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>167</v>
+        <v>47</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>168</v>
+        <v>13</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>169</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -19942,7 +19942,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B29" s="8">
         <v>11</v>
@@ -21068,7 +21068,7 @@
     </row>
     <row r="56" spans="1:25">
       <c r="A56" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B56" s="8">
         <v>11</v>
@@ -22194,7 +22194,7 @@
     </row>
     <row r="83" spans="1:25">
       <c r="A83" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B83" s="8">
         <v>11</v>
@@ -23320,7 +23320,7 @@
     </row>
     <row r="110" spans="1:25">
       <c r="A110" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B110" s="8">
         <v>11</v>
@@ -23400,76 +23400,76 @@
         <v>2001</v>
       </c>
       <c r="B111" s="5">
-        <v>2629028.9008</v>
+        <v>41504.51667740182</v>
       </c>
       <c r="C111" s="5">
-        <v>1641956.2244</v>
+        <v>88865.83306633169</v>
       </c>
       <c r="D111" s="5">
-        <v>1294072.7156</v>
+        <v>75424.46993681956</v>
       </c>
       <c r="E111" s="5">
-        <v>1102919.4184</v>
+        <v>64283.18247732733</v>
       </c>
       <c r="F111" s="5">
-        <v>945691.7175999996</v>
+        <v>55119.23376774767</v>
       </c>
       <c r="G111" s="5">
-        <v>793372.4141559997</v>
+        <v>46241.36888047001</v>
       </c>
       <c r="H111" s="5">
-        <v>799027.0057239993</v>
+        <v>332927919.056385</v>
       </c>
       <c r="I111" s="5">
-        <v>776669.6431359993</v>
+        <v>323612351.311253</v>
       </c>
       <c r="J111" s="5">
-        <v>759052.9831359996</v>
+        <v>316272076.311149</v>
       </c>
       <c r="K111" s="5">
-        <v>738526.0904919999</v>
+        <v>307719204.3760279</v>
       </c>
       <c r="L111" s="5">
-        <v>685824.1960039996</v>
+        <v>285760081.6723832</v>
       </c>
       <c r="M111" s="5">
-        <v>633599.0597999995</v>
+        <v>263999608.2537414</v>
       </c>
       <c r="N111" s="5">
-        <v>636369.5599999996</v>
+        <v>265153983.3370912</v>
       </c>
       <c r="O111" s="5">
-        <v>577817.9446919998</v>
+        <v>240757476.9584122</v>
       </c>
       <c r="P111" s="5">
-        <v>533192.6751999995</v>
+        <v>222163614.6698152</v>
       </c>
       <c r="Q111" s="5">
-        <v>391583.7599999998</v>
+        <v>163159900.0023124</v>
       </c>
       <c r="R111" s="5">
-        <v>325322.6851999997</v>
+        <v>135551118.8352544</v>
       </c>
       <c r="S111" s="5">
-        <v>236561.4011119991</v>
+        <v>98567250.46472993</v>
       </c>
       <c r="T111" s="5">
-        <v>183364.1815679995</v>
+        <v>76401742.32108265</v>
       </c>
       <c r="U111" s="5">
-        <v>183364.1815679995</v>
+        <v>76401742.32108265</v>
       </c>
       <c r="V111" s="5">
-        <v>112765.5815679999</v>
+        <v>46985658.98733255</v>
       </c>
       <c r="W111" s="5">
-        <v>69878.58156799991</v>
+        <v>29116075.65374596</v>
       </c>
       <c r="X111" s="5">
-        <v>69878.58156799991</v>
+        <v>29116075.65374596</v>
       </c>
       <c r="Y111" s="5">
-        <v>32586.87031199969</v>
+        <v>13577862.63019231</v>
       </c>
     </row>
     <row r="112" spans="1:25">
@@ -23477,73 +23477,73 @@
         <v>2002</v>
       </c>
       <c r="B112" s="5">
-        <v>1451856.2884</v>
+        <v>37941.15633721845</v>
       </c>
       <c r="C112" s="5">
-        <v>1052487.266</v>
+        <v>61360.93293066877</v>
       </c>
       <c r="D112" s="5">
-        <v>1036872.4392</v>
+        <v>60450.57480002817</v>
       </c>
       <c r="E112" s="5">
-        <v>775450.4419999996</v>
+        <v>45209.44252699343</v>
       </c>
       <c r="F112" s="5">
-        <v>754298.7715399996</v>
+        <v>43976.2815431078</v>
       </c>
       <c r="G112" s="5">
-        <v>652401.3577039996</v>
+        <v>-271833899.0343092</v>
       </c>
       <c r="H112" s="5">
-        <v>619593.4888959997</v>
+        <v>-258163953.6980964</v>
       </c>
       <c r="I112" s="5">
-        <v>619228.0256759997</v>
+        <v>-258011677.3564348</v>
       </c>
       <c r="J112" s="5">
-        <v>580655.2203479996</v>
+        <v>-241939675.1369683</v>
       </c>
       <c r="K112" s="5">
-        <v>563318.6454479995</v>
+        <v>-234716102.262208</v>
       </c>
       <c r="L112" s="5">
-        <v>544692.5574279996</v>
+        <v>-226955232.2541324</v>
       </c>
       <c r="M112" s="5">
-        <v>482453.0559999996</v>
+        <v>-201022106.6599933</v>
       </c>
       <c r="N112" s="5">
-        <v>479937.1594239995</v>
+        <v>-199973816.420028</v>
       </c>
       <c r="O112" s="5">
-        <v>403746.8335999995</v>
+        <v>-168227847.3277486</v>
       </c>
       <c r="P112" s="5">
-        <v>351655.6235999996</v>
+        <v>-146523176.4951358</v>
       </c>
       <c r="Q112" s="5">
-        <v>321810.2303999995</v>
+        <v>-134087595.9955486</v>
       </c>
       <c r="R112" s="5">
-        <v>212949.9999479996</v>
+        <v>-88729166.64205433</v>
       </c>
       <c r="S112" s="5">
-        <v>210489.0119279996</v>
+        <v>-87703754.96708836</v>
       </c>
       <c r="T112" s="5">
-        <v>210489.0119279996</v>
+        <v>-87703754.96708836</v>
       </c>
       <c r="U112" s="5">
-        <v>118601.9913199996</v>
+        <v>-49417496.38169266</v>
       </c>
       <c r="V112" s="5">
-        <v>132638.1146599995</v>
+        <v>-55265881.10649849</v>
       </c>
       <c r="W112" s="5">
-        <v>51961.00368000055</v>
+        <v>-21650418.19928151</v>
       </c>
       <c r="X112" s="5">
-        <v>51961.00368000055</v>
+        <v>-21650418.19928151</v>
       </c>
     </row>
     <row r="113" spans="1:23">
@@ -23551,70 +23551,70 @@
         <v>2003</v>
       </c>
       <c r="B113" s="5">
-        <v>830051.4103999999</v>
+        <v>48393.85555037301</v>
       </c>
       <c r="C113" s="5">
-        <v>380721.0123999999</v>
+        <v>-287901.5520266147</v>
       </c>
       <c r="D113" s="5">
-        <v>260484.3387999998</v>
+        <v>-196978.4776164524</v>
       </c>
       <c r="E113" s="5">
-        <v>-37516.40297200019</v>
+        <v>28369.93570175418</v>
       </c>
       <c r="F113" s="5">
-        <v>135781.7297239997</v>
+        <v>103114.9223298948</v>
       </c>
       <c r="G113" s="5">
-        <v>20190.4176119999</v>
+        <v>15332.94168590581</v>
       </c>
       <c r="H113" s="5">
-        <v>25219.26805600012</v>
+        <v>-9006881.448638175</v>
       </c>
       <c r="I113" s="5">
-        <v>38914.35397200007</v>
+        <v>-13897983.56153152</v>
       </c>
       <c r="J113" s="5">
-        <v>42274.8473319998</v>
+        <v>-15098159.76154032</v>
       </c>
       <c r="K113" s="5">
-        <v>38329.90313199977</v>
+        <v>-13689251.11867273</v>
       </c>
       <c r="L113" s="5">
-        <v>42091.85839999979</v>
+        <v>-15032806.57153983</v>
       </c>
       <c r="M113" s="5">
-        <v>55995.54668399994</v>
+        <v>-19998409.53014809</v>
       </c>
       <c r="N113" s="5">
-        <v>65084.56879999978</v>
+        <v>-23244488.85731492</v>
       </c>
       <c r="O113" s="5">
-        <v>65084.66117199999</v>
+        <v>-23244521.847315</v>
       </c>
       <c r="P113" s="5">
-        <v>65084.66117199999</v>
+        <v>-23244521.847315</v>
       </c>
       <c r="Q113" s="5">
-        <v>65084.66117199999</v>
+        <v>-23244521.847315</v>
       </c>
       <c r="R113" s="5">
-        <v>61323.19415600086</v>
+        <v>-21901140.7701625</v>
       </c>
       <c r="S113" s="5">
-        <v>61323.19415600062</v>
+        <v>-21901140.77016242</v>
       </c>
       <c r="T113" s="5">
-        <v>61323.19415600062</v>
+        <v>-21901140.77016242</v>
       </c>
       <c r="U113" s="5">
-        <v>61323.19415600062</v>
+        <v>-21901140.77016242</v>
       </c>
       <c r="V113" s="5">
-        <v>61323.19415600062</v>
+        <v>-21901140.77016242</v>
       </c>
       <c r="W113" s="5">
-        <v>61323.19415600062</v>
+        <v>-21901140.77016242</v>
       </c>
     </row>
     <row r="114" spans="1:23">
@@ -23622,67 +23622,67 @@
         <v>2004</v>
       </c>
       <c r="B114" s="5">
-        <v>454341.4843999998</v>
+        <v>11475.35623648747</v>
       </c>
       <c r="C114" s="5">
-        <v>354249.8243999999</v>
+        <v>89375.77565849388</v>
       </c>
       <c r="D114" s="5">
-        <v>270184.9703200014</v>
+        <v>68166.5582601691</v>
       </c>
       <c r="E114" s="5">
-        <v>227961.5971599999</v>
+        <v>172124.4315614658</v>
       </c>
       <c r="F114" s="5">
-        <v>106187.7215199999</v>
+        <v>22122441.98364685</v>
       </c>
       <c r="G114" s="5">
-        <v>100331.2311519999</v>
+        <v>20902339.82362956</v>
       </c>
       <c r="H114" s="5">
-        <v>80749.68675199989</v>
+        <v>16822851.40690507</v>
       </c>
       <c r="I114" s="5">
-        <v>72446.6315919999</v>
+        <v>15093048.24854723</v>
       </c>
       <c r="J114" s="5">
-        <v>46582.76190399984</v>
+        <v>9704742.063470844</v>
       </c>
       <c r="K114" s="5">
-        <v>56530.9095999999</v>
+        <v>11777272.83350023</v>
       </c>
       <c r="L114" s="5">
-        <v>31033.67757599987</v>
+        <v>6465349.495091606</v>
       </c>
       <c r="M114" s="5">
-        <v>43806.00679999986</v>
+        <v>9126251.416795982</v>
       </c>
       <c r="N114" s="5">
-        <v>43356.02319999994</v>
+        <v>9032504.833461337</v>
       </c>
       <c r="O114" s="5">
-        <v>43031.40159999975</v>
+        <v>8964875.33346034</v>
       </c>
       <c r="P114" s="5">
-        <v>43032.02181199985</v>
+        <v>8965004.544293696</v>
       </c>
       <c r="Q114" s="5">
-        <v>38750.61919999961</v>
+        <v>8073045.666781004</v>
       </c>
       <c r="R114" s="5">
-        <v>38750.61919999961</v>
+        <v>8073045.666781004</v>
       </c>
       <c r="S114" s="5">
-        <v>38750.61919999961</v>
+        <v>8073045.666781004</v>
       </c>
       <c r="T114" s="5">
-        <v>38750.61919999961</v>
+        <v>8073045.666781004</v>
       </c>
       <c r="U114" s="5">
-        <v>38716.96939999959</v>
+        <v>8066035.291780902</v>
       </c>
       <c r="V114" s="5">
-        <v>38716.96939999959</v>
+        <v>8066035.291780902</v>
       </c>
     </row>
     <row r="115" spans="1:23">
@@ -23690,64 +23690,64 @@
         <v>2005</v>
       </c>
       <c r="B115" s="5">
-        <v>1102026.0192</v>
+        <v>75897.10876033065</v>
       </c>
       <c r="C115" s="5">
-        <v>723495.6185519998</v>
+        <v>164430822.3969718</v>
       </c>
       <c r="D115" s="5">
-        <v>572309.5084119996</v>
+        <v>-435150.1736709228</v>
       </c>
       <c r="E115" s="5">
-        <v>615935.9726639998</v>
+        <v>139985448.3316971</v>
       </c>
       <c r="F115" s="5">
-        <v>551433.4232159997</v>
+        <v>125325778.0027141</v>
       </c>
       <c r="G115" s="5">
-        <v>522039.1352759998</v>
+        <v>118645258.0163996</v>
       </c>
       <c r="H115" s="5">
-        <v>484803.7709399995</v>
+        <v>110182675.2128254</v>
       </c>
       <c r="I115" s="5">
-        <v>474259.0452799997</v>
+        <v>107786146.6537522</v>
       </c>
       <c r="J115" s="5">
-        <v>450011.6591999996</v>
+        <v>102275377.0901564</v>
       </c>
       <c r="K115" s="5">
-        <v>398090.5852279996</v>
+        <v>90475133.00569777</v>
       </c>
       <c r="L115" s="5">
-        <v>375192.9783999997</v>
+        <v>85271131.45391791</v>
       </c>
       <c r="M115" s="5">
-        <v>139179.8791999999</v>
+        <v>31631790.72703993</v>
       </c>
       <c r="N115" s="5">
-        <v>139168.0027999994</v>
+        <v>31629091.54522167</v>
       </c>
       <c r="O115" s="5">
-        <v>179968.6228279998</v>
+        <v>40901959.73333532</v>
       </c>
       <c r="P115" s="5">
-        <v>158350.8300600001</v>
+        <v>35988825.01337155</v>
       </c>
       <c r="Q115" s="5">
-        <v>143012.1163639999</v>
+        <v>32502753.71885171</v>
       </c>
       <c r="R115" s="5">
-        <v>109568.4378839997</v>
+        <v>24901917.70072577</v>
       </c>
       <c r="S115" s="5">
-        <v>109568.4378839997</v>
+        <v>24901917.70072577</v>
       </c>
       <c r="T115" s="5">
-        <v>109568.4378839997</v>
+        <v>24901917.70072577</v>
       </c>
       <c r="U115" s="5">
-        <v>109568.4378839997</v>
+        <v>24901917.70072577</v>
       </c>
     </row>
     <row r="116" spans="1:23">
@@ -23755,61 +23755,61 @@
         <v>2006</v>
       </c>
       <c r="B116" s="5">
-        <v>825814.7147280001</v>
+        <v>44698.55345154593</v>
       </c>
       <c r="C116" s="5">
-        <v>433700.1009559999</v>
+        <v>542125126.2155235</v>
       </c>
       <c r="D116" s="5">
-        <v>585162.9576079999</v>
+        <v>731453697.037691</v>
       </c>
       <c r="E116" s="5">
-        <v>515263.7983919999</v>
+        <v>644079748.0143833</v>
       </c>
       <c r="F116" s="5">
-        <v>505559.539168</v>
+        <v>631949423.9839242</v>
       </c>
       <c r="G116" s="5">
-        <v>450766.80446</v>
+        <v>563458505.5963312</v>
       </c>
       <c r="H116" s="5">
-        <v>400483.9479079999</v>
+        <v>500604934.9039516</v>
       </c>
       <c r="I116" s="5">
-        <v>422421.9944</v>
+        <v>528027493.0199898</v>
       </c>
       <c r="J116" s="5">
-        <v>391960.836252</v>
+        <v>489951045.3335484</v>
       </c>
       <c r="K116" s="5">
-        <v>347434.4047999999</v>
+        <v>434293006.0164412</v>
       </c>
       <c r="L116" s="5">
-        <v>243948.7335999999</v>
+        <v>304935917.011544</v>
       </c>
       <c r="M116" s="5">
-        <v>162922.6543999999</v>
+        <v>203653318.0077097</v>
       </c>
       <c r="N116" s="5">
-        <v>123605.7134359998</v>
+        <v>154507141.8008491</v>
       </c>
       <c r="O116" s="5">
-        <v>107795.8761479994</v>
+        <v>134744845.1901004</v>
       </c>
       <c r="P116" s="5">
-        <v>106938.1361479994</v>
+        <v>133672670.1900598</v>
       </c>
       <c r="Q116" s="5">
-        <v>89783.33614799939</v>
+        <v>112229170.189248</v>
       </c>
       <c r="R116" s="5">
-        <v>85164.73614799953</v>
+        <v>106455920.1890296</v>
       </c>
       <c r="S116" s="5">
-        <v>74163.25733999955</v>
+        <v>92704071.678509</v>
       </c>
       <c r="T116" s="5">
-        <v>74163.25733999955</v>
+        <v>92704071.678509</v>
       </c>
     </row>
     <row r="117" spans="1:23">
@@ -23817,58 +23817,58 @@
         <v>2007</v>
       </c>
       <c r="B117" s="5">
-        <v>3321208.718915999</v>
+        <v>167751.3697529096</v>
       </c>
       <c r="C117" s="5">
-        <v>3168103.039439999</v>
+        <v>720023418.0585489</v>
       </c>
       <c r="D117" s="5">
-        <v>3000758.823179999</v>
+        <v>681990641.6356101</v>
       </c>
       <c r="E117" s="5">
-        <v>2754436.758055999</v>
+        <v>626008354.1071171</v>
       </c>
       <c r="F117" s="5">
-        <v>2491674.139627999</v>
+        <v>566289577.1913304</v>
       </c>
       <c r="G117" s="5">
-        <v>1996791.822623999</v>
+        <v>453816323.3261596</v>
       </c>
       <c r="H117" s="5">
-        <v>1802831.155599999</v>
+        <v>409734353.5477327</v>
       </c>
       <c r="I117" s="5">
-        <v>1447643.515643999</v>
+        <v>329009889.9209202</v>
       </c>
       <c r="J117" s="5">
-        <v>1189872.996799999</v>
+        <v>270425681.0924126</v>
       </c>
       <c r="K117" s="5">
-        <v>797964.9927999992</v>
+        <v>181355680.1828264</v>
       </c>
       <c r="L117" s="5">
-        <v>667625.4615999991</v>
+        <v>151733059.4553889</v>
       </c>
       <c r="M117" s="5">
-        <v>541127.9853879986</v>
+        <v>122983633.0434108</v>
       </c>
       <c r="N117" s="5">
-        <v>468535.4433960002</v>
+        <v>106485328.0451376</v>
       </c>
       <c r="O117" s="5">
-        <v>464265.547696</v>
+        <v>105514897.2042231</v>
       </c>
       <c r="P117" s="5">
-        <v>264396.8995119995</v>
+        <v>60090204.43487945</v>
       </c>
       <c r="Q117" s="5">
-        <v>264396.8995119995</v>
+        <v>60090204.43487945</v>
       </c>
       <c r="R117" s="5">
-        <v>247222.2527280003</v>
+        <v>56186875.62031248</v>
       </c>
       <c r="S117" s="5">
-        <v>235090.9851839999</v>
+        <v>53429769.36029706</v>
       </c>
     </row>
     <row r="118" spans="1:23">
@@ -23876,55 +23876,55 @@
         <v>2008</v>
       </c>
       <c r="B118" s="5">
-        <v>892616.2424879998</v>
+        <v>42277.63875149205</v>
       </c>
       <c r="C118" s="5">
-        <v>678054.0858319999</v>
+        <v>513988.84614313</v>
       </c>
       <c r="D118" s="5">
-        <v>515803.2616519998</v>
+        <v>-1289508153.903942</v>
       </c>
       <c r="E118" s="5">
-        <v>150962.3518159997</v>
+        <v>-377405879.4738381</v>
       </c>
       <c r="F118" s="5">
-        <v>190850.0197799997</v>
+        <v>-477125049.3663569</v>
       </c>
       <c r="G118" s="5">
-        <v>169653.8787999998</v>
+        <v>-424134696.9256466</v>
       </c>
       <c r="H118" s="5">
-        <v>162725.2134319998</v>
+        <v>-406813033.5086831</v>
       </c>
       <c r="I118" s="5">
-        <v>145795.5107999998</v>
+        <v>-364488776.9361028</v>
       </c>
       <c r="J118" s="5">
-        <v>138347.6883999999</v>
+        <v>-345869220.9393671</v>
       </c>
       <c r="K118" s="5">
-        <v>92909.90159999975</v>
+        <v>-232274753.9592804</v>
       </c>
       <c r="L118" s="5">
-        <v>86237.10667199967</v>
+        <v>-215592766.6422047</v>
       </c>
       <c r="M118" s="5">
-        <v>86012.11487200158</v>
+        <v>-215030287.142308</v>
       </c>
       <c r="N118" s="5">
-        <v>105859.8885720016</v>
+        <v>-264649721.3836095</v>
       </c>
       <c r="O118" s="5">
-        <v>105529.9885720015</v>
+        <v>-263824971.3837538</v>
       </c>
       <c r="P118" s="5">
-        <v>105529.9885720015</v>
+        <v>-263824971.3837538</v>
       </c>
       <c r="Q118" s="5">
-        <v>98931.98857200146</v>
+        <v>-247329971.3866454</v>
       </c>
       <c r="R118" s="5">
-        <v>70541.19045200152</v>
+        <v>-176352976.0990882</v>
       </c>
     </row>
     <row r="119" spans="1:23">
@@ -23932,52 +23932,52 @@
         <v>2009</v>
       </c>
       <c r="B119" s="5">
-        <v>885969.6878280001</v>
+        <v>55957.86518038496</v>
       </c>
       <c r="C119" s="5">
-        <v>370912.626636</v>
+        <v>281591.7299088947</v>
       </c>
       <c r="D119" s="5">
-        <v>421210.0383760001</v>
+        <v>-175504182.6549973</v>
       </c>
       <c r="E119" s="5">
-        <v>400696.156988</v>
+        <v>-166956732.0767453</v>
       </c>
       <c r="F119" s="5">
-        <v>344688.9944</v>
+        <v>-143620414.3319672</v>
       </c>
       <c r="G119" s="5">
-        <v>298560.4497840001</v>
+        <v>-124400187.4088168</v>
       </c>
       <c r="H119" s="5">
-        <v>264177.5592</v>
+        <v>-110073982.998953</v>
       </c>
       <c r="I119" s="5">
-        <v>123096.4839999999</v>
+        <v>-51290201.66617878</v>
       </c>
       <c r="J119" s="5">
-        <v>123089.8859999999</v>
+        <v>-51287452.49951214</v>
       </c>
       <c r="K119" s="5">
-        <v>123088.1837159998</v>
+        <v>-51286743.21451209</v>
       </c>
       <c r="L119" s="5">
-        <v>123088.1837159996</v>
+        <v>-51286743.214512</v>
       </c>
       <c r="M119" s="5">
-        <v>107912.7837159997</v>
+        <v>-44963659.88123885</v>
       </c>
       <c r="N119" s="5">
-        <v>73868.9907439996</v>
+        <v>-30778746.14304041</v>
       </c>
       <c r="O119" s="5">
-        <v>73868.9907439996</v>
+        <v>-30778746.14304041</v>
       </c>
       <c r="P119" s="5">
-        <v>73868.9907439996</v>
+        <v>-30778746.14304041</v>
       </c>
       <c r="Q119" s="5">
-        <v>73868.9907439996</v>
+        <v>-30778746.14304041</v>
       </c>
     </row>
     <row r="120" spans="1:23">
@@ -23985,49 +23985,49 @@
         <v>2010</v>
       </c>
       <c r="B120" s="5">
-        <v>1006487.690004</v>
+        <v>84729.74458733236</v>
       </c>
       <c r="C120" s="5">
-        <v>635927.7657279999</v>
+        <v>264969902.390422</v>
       </c>
       <c r="D120" s="5">
-        <v>415196.0304079998</v>
+        <v>172998346.0057851</v>
       </c>
       <c r="E120" s="5">
-        <v>261180.2623999999</v>
+        <v>108825109.3348757</v>
       </c>
       <c r="F120" s="5">
-        <v>130332.3948879999</v>
+        <v>54305164.53743628</v>
       </c>
       <c r="G120" s="5">
-        <v>143618.4179999998</v>
+        <v>59841007.50084805</v>
       </c>
       <c r="H120" s="5">
-        <v>95150.82959999982</v>
+        <v>39646179.00056183</v>
       </c>
       <c r="I120" s="5">
-        <v>93654.40319999983</v>
+        <v>39022668.000553</v>
       </c>
       <c r="J120" s="5">
-        <v>99696.0730359999</v>
+        <v>41540030.43225537</v>
       </c>
       <c r="K120" s="5">
-        <v>98896.59337599948</v>
+        <v>41206913.90725047</v>
       </c>
       <c r="L120" s="5">
-        <v>97901.61497599934</v>
+        <v>40792339.5739112</v>
       </c>
       <c r="M120" s="5">
-        <v>97827.71737599932</v>
+        <v>40761548.90724409</v>
       </c>
       <c r="N120" s="5">
-        <v>96178.21737599932</v>
+        <v>40074257.24056768</v>
       </c>
       <c r="O120" s="5">
-        <v>96448.86733599938</v>
+        <v>40187028.05723598</v>
       </c>
       <c r="P120" s="5">
-        <v>88846.05791599932</v>
+        <v>37019190.79885772</v>
       </c>
     </row>
     <row r="121" spans="1:23">
@@ -24035,46 +24035,46 @@
         <v>2011</v>
       </c>
       <c r="B121" s="5">
-        <v>1610643.585408</v>
+        <v>335550746.960782</v>
       </c>
       <c r="C121" s="5">
-        <v>1177771.159432</v>
+        <v>245368991.5489052</v>
       </c>
       <c r="D121" s="5">
-        <v>756673.0491999998</v>
+        <v>157640218.5837007</v>
       </c>
       <c r="E121" s="5">
-        <v>554336.9469559998</v>
+        <v>115486863.9494358</v>
       </c>
       <c r="F121" s="5">
-        <v>453151.8531999998</v>
+        <v>94406636.08355331</v>
       </c>
       <c r="G121" s="5">
-        <v>324186.0255999998</v>
+        <v>67538755.3334907</v>
       </c>
       <c r="H121" s="5">
-        <v>227988.5051999998</v>
+        <v>47497605.25011065</v>
       </c>
       <c r="I121" s="5">
-        <v>227873.2249439997</v>
+        <v>47473588.53011058</v>
       </c>
       <c r="J121" s="5">
-        <v>202547.4617440002</v>
+        <v>42197387.86343172</v>
       </c>
       <c r="K121" s="5">
-        <v>195400.5081440003</v>
+        <v>40708439.19676161</v>
       </c>
       <c r="L121" s="5">
-        <v>142704.9873240001</v>
+        <v>29730205.69256931</v>
       </c>
       <c r="M121" s="5">
-        <v>148609.3395840002</v>
+        <v>30960279.08007219</v>
       </c>
       <c r="N121" s="5">
-        <v>148609.3395840002</v>
+        <v>30960279.08007219</v>
       </c>
       <c r="O121" s="5">
-        <v>148609.3395840002</v>
+        <v>30960279.08007219</v>
       </c>
     </row>
     <row r="122" spans="1:23">
@@ -24082,43 +24082,43 @@
         <v>2012</v>
       </c>
       <c r="B122" s="5">
-        <v>1139368.745624</v>
+        <v>71955.28378871338</v>
       </c>
       <c r="C122" s="5">
-        <v>792765.3280000001</v>
+        <v>-990956659.9671037</v>
       </c>
       <c r="D122" s="5">
-        <v>583244.9010840001</v>
+        <v>-729056126.330798</v>
       </c>
       <c r="E122" s="5">
-        <v>505856.5764</v>
+        <v>-632320720.4790092</v>
       </c>
       <c r="F122" s="5">
-        <v>508886.378</v>
+        <v>-636107972.4788834</v>
       </c>
       <c r="G122" s="5">
-        <v>500422.4636</v>
+        <v>-625528079.4792347</v>
       </c>
       <c r="H122" s="5">
-        <v>496517.1865760001</v>
+        <v>-620646483.1993967</v>
       </c>
       <c r="I122" s="5">
-        <v>446059.6413760013</v>
+        <v>-557574551.7014921</v>
       </c>
       <c r="J122" s="5">
-        <v>388557.2532240013</v>
+        <v>-485696566.5138781</v>
       </c>
       <c r="K122" s="5">
-        <v>327106.4767160013</v>
+        <v>-408883095.8814281</v>
       </c>
       <c r="L122" s="5">
-        <v>318529.0767160011</v>
+        <v>-398161345.8817838</v>
       </c>
       <c r="M122" s="5">
-        <v>111502.469468001</v>
+        <v>-139378086.8303744</v>
       </c>
       <c r="N122" s="5">
-        <v>111502.469468001</v>
+        <v>-139378086.8303744</v>
       </c>
     </row>
     <row r="123" spans="1:23">
@@ -24126,40 +24126,40 @@
         <v>2013</v>
       </c>
       <c r="B123" s="5">
-        <v>490429.5604</v>
+        <v>53102.07895534683</v>
       </c>
       <c r="C123" s="5">
-        <v>259870.130472</v>
+        <v>197170.0534688947</v>
       </c>
       <c r="D123" s="5">
-        <v>215405.1264</v>
+        <v>163433.3280728396</v>
       </c>
       <c r="E123" s="5">
-        <v>101477.4604</v>
+        <v>-63423412.74789455</v>
       </c>
       <c r="F123" s="5">
-        <v>60879.96639999992</v>
+        <v>-38049978.99873682</v>
       </c>
       <c r="G123" s="5">
-        <v>62721.63974799996</v>
+        <v>-39201024.84119864</v>
       </c>
       <c r="H123" s="5">
-        <v>62373.15978000022</v>
+        <v>-38983224.86120603</v>
       </c>
       <c r="I123" s="5">
-        <v>62373.15977999999</v>
+        <v>-38983224.86120588</v>
       </c>
       <c r="J123" s="5">
-        <v>61007.50574000017</v>
+        <v>-38129691.08623433</v>
       </c>
       <c r="K123" s="5">
-        <v>61007.50574000017</v>
+        <v>-38129691.08623433</v>
       </c>
       <c r="L123" s="5">
-        <v>60996.28914000012</v>
+        <v>-38122680.71123454</v>
       </c>
       <c r="M123" s="5">
-        <v>60996.28914000012</v>
+        <v>-38122680.71123454</v>
       </c>
     </row>
     <row r="124" spans="1:23">
@@ -24167,37 +24167,37 @@
         <v>2014</v>
       </c>
       <c r="B124" s="5">
-        <v>966302.1225159999</v>
+        <v>45771.14584001223</v>
       </c>
       <c r="C124" s="5">
-        <v>754081.794</v>
+        <v>572314.6584699582</v>
       </c>
       <c r="D124" s="5">
-        <v>428267.2755999998</v>
+        <v>-214133637.7928914</v>
       </c>
       <c r="E124" s="5">
-        <v>253639.3291999998</v>
+        <v>-126819664.5957899</v>
       </c>
       <c r="F124" s="5">
-        <v>235166.0772519999</v>
+        <v>-117583038.6220966</v>
       </c>
       <c r="G124" s="5">
-        <v>190004.0868519999</v>
+        <v>-95002043.42284618</v>
       </c>
       <c r="H124" s="5">
-        <v>228820.9258079999</v>
+        <v>-114410462.9002019</v>
       </c>
       <c r="I124" s="5">
-        <v>228820.9258079999</v>
+        <v>-114410462.9002019</v>
       </c>
       <c r="J124" s="5">
-        <v>174717.3258079998</v>
+        <v>-87358662.90109991</v>
       </c>
       <c r="K124" s="5">
-        <v>146433.9959120001</v>
+        <v>-73216997.95356949</v>
       </c>
       <c r="L124" s="5">
-        <v>156152.3352679999</v>
+        <v>-78076167.6314081</v>
       </c>
     </row>
     <row r="125" spans="1:23">
@@ -24205,34 +24205,34 @@
         <v>2015</v>
       </c>
       <c r="B125" s="5">
-        <v>3267945.68</v>
+        <v>275135.1855593729</v>
       </c>
       <c r="C125" s="5">
-        <v>2737569.4088</v>
+        <v>2072660.061175104</v>
       </c>
       <c r="D125" s="5">
-        <v>2200410.3936</v>
+        <v>-555996.1576713141</v>
       </c>
       <c r="E125" s="5">
-        <v>1672989.340208</v>
+        <v>-422728.254550231</v>
       </c>
       <c r="F125" s="5">
-        <v>1447048.022027999</v>
+        <v>-365637.7658247407</v>
       </c>
       <c r="G125" s="5">
-        <v>1125742.444867999</v>
+        <v>-284450.7895866169</v>
       </c>
       <c r="H125" s="5">
-        <v>750679.1744559985</v>
+        <v>-189680.4059167162</v>
       </c>
       <c r="I125" s="5">
-        <v>729961.4544559983</v>
+        <v>-184445.4857630877</v>
       </c>
       <c r="J125" s="5">
-        <v>719807.4095719983</v>
+        <v>-181879.7780402254</v>
       </c>
       <c r="K125" s="5">
-        <v>423049.3219239987</v>
+        <v>352541101.6083288</v>
       </c>
     </row>
     <row r="126" spans="1:23">
@@ -24240,31 +24240,31 @@
         <v>2016</v>
       </c>
       <c r="B126" s="5">
-        <v>2196234.968</v>
+        <v>48952.29596476525</v>
       </c>
       <c r="C126" s="5">
-        <v>1598076.1232</v>
+        <v>93164.89769838878</v>
       </c>
       <c r="D126" s="5">
-        <v>1150566.891964</v>
+        <v>-719104307.4791759</v>
       </c>
       <c r="E126" s="5">
-        <v>999769.2588680002</v>
+        <v>-624855786.7939564</v>
       </c>
       <c r="F126" s="5">
-        <v>731620.9173720009</v>
+        <v>-457263073.3585662</v>
       </c>
       <c r="G126" s="5">
-        <v>663619.395740001</v>
+        <v>-414762122.3384672</v>
       </c>
       <c r="H126" s="5">
-        <v>380416.410840001</v>
+        <v>-237760256.7755547</v>
       </c>
       <c r="I126" s="5">
-        <v>381012.2366320011</v>
+        <v>-238132647.8955557</v>
       </c>
       <c r="J126" s="5">
-        <v>377713.2366320011</v>
+        <v>-236070772.8955509</v>
       </c>
     </row>
     <row r="127" spans="1:23">
@@ -24272,28 +24272,28 @@
         <v>2017</v>
       </c>
       <c r="B127" s="5">
-        <v>947296.2184000001</v>
+        <v>27607.01932761354</v>
       </c>
       <c r="C127" s="5">
-        <v>793750.412736</v>
+        <v>198437603.1858725</v>
       </c>
       <c r="D127" s="5">
-        <v>772623.8938519997</v>
+        <v>-587278.7274642667</v>
       </c>
       <c r="E127" s="5">
-        <v>575852.8879039995</v>
+        <v>-218523.4091924712</v>
       </c>
       <c r="F127" s="5">
-        <v>513333.6180799996</v>
+        <v>-390189.7370629315</v>
       </c>
       <c r="G127" s="5">
-        <v>394514.8018959997</v>
+        <v>-299874.4313590715</v>
       </c>
       <c r="H127" s="5">
-        <v>239670.2063239997</v>
+        <v>-182175.5900912104</v>
       </c>
       <c r="I127" s="5">
-        <v>202811.2710839997</v>
+        <v>50702817.77147835</v>
       </c>
     </row>
     <row r="128" spans="1:23">
@@ -24301,25 +24301,25 @@
         <v>2018</v>
       </c>
       <c r="B128" s="5">
-        <v>2333181.319552</v>
+        <v>63148.3863512651</v>
       </c>
       <c r="C128" s="5">
-        <v>1673097.222868</v>
+        <v>1269036.121714202</v>
       </c>
       <c r="D128" s="5">
-        <v>1172306.937900001</v>
+        <v>889189.1215867745</v>
       </c>
       <c r="E128" s="5">
-        <v>524345.5049679992</v>
+        <v>397713.5201516993</v>
       </c>
       <c r="F128" s="5">
-        <v>537647.0333799995</v>
+        <v>-448039194.4684595</v>
       </c>
       <c r="G128" s="5">
-        <v>507489.7923079995</v>
+        <v>-422908160.2426271</v>
       </c>
       <c r="H128" s="5">
-        <v>445716.7166959993</v>
+        <v>-371430597.2343358</v>
       </c>
     </row>
     <row r="129" spans="1:25">
@@ -24327,22 +24327,22 @@
         <v>2019</v>
       </c>
       <c r="B129" s="5">
-        <v>2790434.858824</v>
+        <v>63978.49508483287</v>
       </c>
       <c r="C129" s="5">
-        <v>2073742.62732</v>
+        <v>-1657402.994980766</v>
       </c>
       <c r="D129" s="5">
-        <v>1458295.148687999</v>
+        <v>-1165517.222416842</v>
       </c>
       <c r="E129" s="5">
-        <v>1197786.644588</v>
+        <v>-957310.2977844963</v>
       </c>
       <c r="F129" s="5">
-        <v>1070970.99962</v>
+        <v>-855955.0828164688</v>
       </c>
       <c r="G129" s="5">
-        <v>598466.8157080007</v>
+        <v>8749514.849532569</v>
       </c>
     </row>
     <row r="130" spans="1:25">
@@ -24350,19 +24350,19 @@
         <v>2020</v>
       </c>
       <c r="B130" s="5">
-        <v>750650.5164680001</v>
+        <v>35431.44135126975</v>
       </c>
       <c r="C130" s="5">
-        <v>340837.5990440004</v>
+        <v>4707701.644256804</v>
       </c>
       <c r="D130" s="5">
-        <v>356461.3199480003</v>
+        <v>4923498.894312173</v>
       </c>
       <c r="E130" s="5">
-        <v>303284.8181240002</v>
+        <v>4189016.824919493</v>
       </c>
       <c r="F130" s="5">
-        <v>293853.6105320002</v>
+        <v>4058751.526687375</v>
       </c>
     </row>
     <row r="131" spans="1:25">
@@ -24370,16 +24370,16 @@
         <v>2021</v>
       </c>
       <c r="B131" s="5">
-        <v>832762.7730120003</v>
+        <v>20322.39011098748</v>
       </c>
       <c r="C131" s="5">
-        <v>581284.687592</v>
+        <v>8304066.965600809</v>
       </c>
       <c r="D131" s="5">
-        <v>401903.0537400004</v>
+        <v>5741472.196286279</v>
       </c>
       <c r="E131" s="5">
-        <v>370906.5602640001</v>
+        <v>5298665.146629089</v>
       </c>
     </row>
     <row r="132" spans="1:25">
@@ -24387,13 +24387,13 @@
         <v>2022</v>
       </c>
       <c r="B132" s="5">
-        <v>606677.1964239998</v>
+        <v>16326.43319619367</v>
       </c>
       <c r="C132" s="5">
-        <v>449644.321367999</v>
+        <v>2137092.782167369</v>
       </c>
       <c r="D132" s="5">
-        <v>473884.0933559992</v>
+        <v>2252300.823935434</v>
       </c>
     </row>
     <row r="133" spans="1:25">
@@ -24401,10 +24401,10 @@
         <v>2023</v>
       </c>
       <c r="B133" s="5">
-        <v>2120494.577396</v>
+        <v>66509.04492064692</v>
       </c>
       <c r="C133" s="5">
-        <v>1443738.205648</v>
+        <v>6797260.855216498</v>
       </c>
     </row>
     <row r="134" spans="1:25">
@@ -24412,7 +24412,7 @@
         <v>2024</v>
       </c>
       <c r="B134" s="5">
-        <v>1635509.148172</v>
+        <v>47755.43828390897</v>
       </c>
     </row>
     <row r="136" spans="1:25">
@@ -24446,7 +24446,7 @@
     </row>
     <row r="137" spans="1:25">
       <c r="A137" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B137" s="8">
         <v>11</v>
@@ -24526,76 +24526,76 @@
         <v>2001</v>
       </c>
       <c r="B138" s="5">
-        <v>2870316.4412</v>
+        <v>45313.7265120802</v>
       </c>
       <c r="C138" s="5">
-        <v>2148988.7716</v>
+        <v>116307.4110019049</v>
       </c>
       <c r="D138" s="5">
-        <v>1650633.914</v>
+        <v>96206.48555708394</v>
       </c>
       <c r="E138" s="5">
-        <v>1285395.026</v>
+        <v>74918.69454223302</v>
       </c>
       <c r="F138" s="5">
-        <v>972140.4603999997</v>
+        <v>56660.7873312662</v>
       </c>
       <c r="G138" s="5">
-        <v>912584.5767079997</v>
+        <v>53189.59834401885</v>
       </c>
       <c r="H138" s="5">
-        <v>934587.5739119998</v>
+        <v>389411489.135519</v>
       </c>
       <c r="I138" s="5">
-        <v>904046.3952199994</v>
+        <v>376685998.0136718</v>
       </c>
       <c r="J138" s="5">
-        <v>881815.1995879998</v>
+        <v>367422999.8335407</v>
       </c>
       <c r="K138" s="5">
-        <v>853975.9810719998</v>
+        <v>355823325.4517096</v>
       </c>
       <c r="L138" s="5">
-        <v>798160.5563639998</v>
+        <v>332566898.4897134</v>
       </c>
       <c r="M138" s="5">
-        <v>740655.0935439994</v>
+        <v>308606288.9810402</v>
       </c>
       <c r="N138" s="5">
-        <v>700636.7191999997</v>
+        <v>291931966.3374708</v>
       </c>
       <c r="O138" s="5">
-        <v>637243.8609799999</v>
+        <v>265518275.4120965</v>
       </c>
       <c r="P138" s="5">
-        <v>582196.0211999998</v>
+        <v>242581675.503438</v>
       </c>
       <c r="Q138" s="5">
-        <v>502010.5271999994</v>
+        <v>209171053.0029643</v>
       </c>
       <c r="R138" s="5">
-        <v>413948.3407999994</v>
+        <v>172478475.3357776</v>
       </c>
       <c r="S138" s="5">
-        <v>338714.4346639998</v>
+        <v>141131014.4453335</v>
       </c>
       <c r="T138" s="5">
-        <v>229288.7160240002</v>
+        <v>95536965.01135412</v>
       </c>
       <c r="U138" s="5">
-        <v>229288.7160240002</v>
+        <v>95536965.01135412</v>
       </c>
       <c r="V138" s="5">
-        <v>207198.5328480001</v>
+        <v>86332722.02122362</v>
       </c>
       <c r="W138" s="5">
-        <v>184974.7665639999</v>
+        <v>77072819.40275899</v>
       </c>
       <c r="X138" s="5">
-        <v>165979.3488960001</v>
+        <v>69158062.0409802</v>
       </c>
       <c r="Y138" s="5">
-        <v>154065.9077239996</v>
+        <v>64194128.21924298</v>
       </c>
     </row>
     <row r="139" spans="1:25">
@@ -24603,73 +24603,73 @@
         <v>2002</v>
       </c>
       <c r="B139" s="5">
-        <v>2022333.884</v>
+        <v>52849.36716667542</v>
       </c>
       <c r="C139" s="5">
-        <v>1468621.8064</v>
+        <v>85621.94249201304</v>
       </c>
       <c r="D139" s="5">
-        <v>1159324.7212</v>
+        <v>67589.6504978897</v>
       </c>
       <c r="E139" s="5">
-        <v>1061349.6996</v>
+        <v>61877.62060119885</v>
       </c>
       <c r="F139" s="5">
-        <v>896252.6961599998</v>
+        <v>52252.32015111604</v>
       </c>
       <c r="G139" s="5">
-        <v>757959.6718399995</v>
+        <v>-315816529.9228491</v>
       </c>
       <c r="H139" s="5">
-        <v>721365.9498079997</v>
+        <v>-300569145.7433553</v>
       </c>
       <c r="I139" s="5">
-        <v>691990.4265799997</v>
+        <v>-288329344.3987617</v>
       </c>
       <c r="J139" s="5">
-        <v>650115.0319399994</v>
+        <v>-270881263.2993408</v>
       </c>
       <c r="K139" s="5">
-        <v>629495.8728639998</v>
+        <v>-262289947.0179594</v>
       </c>
       <c r="L139" s="5">
-        <v>598697.5569159996</v>
+        <v>-249457315.3733854</v>
       </c>
       <c r="M139" s="5">
-        <v>565271.1519999995</v>
+        <v>-235529646.6588477</v>
       </c>
       <c r="N139" s="5">
-        <v>523647.5238439995</v>
+        <v>-218186468.2610901</v>
       </c>
       <c r="O139" s="5">
-        <v>476303.7199999997</v>
+        <v>-198459883.326745</v>
       </c>
       <c r="P139" s="5">
-        <v>436075.7139999997</v>
+        <v>-181698214.1606348</v>
       </c>
       <c r="Q139" s="5">
-        <v>398125.3375999995</v>
+        <v>-165885557.3278263</v>
       </c>
       <c r="R139" s="5">
-        <v>341664.8396279996</v>
+        <v>-142360349.8402739</v>
       </c>
       <c r="S139" s="5">
-        <v>300481.7863239995</v>
+        <v>-125200744.2975102</v>
       </c>
       <c r="T139" s="5">
-        <v>267455.0882479991</v>
+        <v>-111439620.0996335</v>
       </c>
       <c r="U139" s="5">
-        <v>241864.4813279994</v>
+        <v>-100776867.2166543</v>
       </c>
       <c r="V139" s="5">
-        <v>220306.3476759996</v>
+        <v>-91794311.52861926</v>
       </c>
       <c r="W139" s="5">
-        <v>199643.6154079996</v>
+        <v>-83184839.75057171</v>
       </c>
       <c r="X139" s="5">
-        <v>180048.5319119995</v>
+        <v>-75020221.62750936</v>
       </c>
     </row>
     <row r="140" spans="1:25">
@@ -24677,70 +24677,70 @@
         <v>2003</v>
       </c>
       <c r="B140" s="5">
-        <v>1375679.6184</v>
+        <v>80205.20163246249</v>
       </c>
       <c r="C140" s="5">
-        <v>687633.5803999999</v>
+        <v>-519989.095886261</v>
       </c>
       <c r="D140" s="5">
-        <v>509748.8611999999</v>
+        <v>-385472.5205686583</v>
       </c>
       <c r="E140" s="5">
-        <v>390069.4942679999</v>
+        <v>-294970.8819328457</v>
       </c>
       <c r="F140" s="5">
-        <v>162505.42438</v>
+        <v>123409.3441524961</v>
       </c>
       <c r="G140" s="5">
-        <v>79029.15148799983</v>
+        <v>60016.06279465614</v>
       </c>
       <c r="H140" s="5">
-        <v>76376.05609999993</v>
+        <v>-27277162.89305913</v>
       </c>
       <c r="I140" s="5">
-        <v>64014.65031599975</v>
+        <v>-22862375.11302637</v>
       </c>
       <c r="J140" s="5">
-        <v>66566.67753999983</v>
+        <v>-23773813.40731886</v>
       </c>
       <c r="K140" s="5">
-        <v>62231.58040399989</v>
+        <v>-22225564.43016456</v>
       </c>
       <c r="L140" s="5">
-        <v>65603.17159999977</v>
+        <v>-23429704.14303058</v>
       </c>
       <c r="M140" s="5">
-        <v>65214.44383199979</v>
+        <v>-23290872.79731527</v>
       </c>
       <c r="N140" s="5">
-        <v>65084.56879999978</v>
+        <v>-23244488.85731492</v>
       </c>
       <c r="O140" s="5">
-        <v>65084.05415600003</v>
+        <v>-23244305.05588644</v>
       </c>
       <c r="P140" s="5">
-        <v>65084.05415600003</v>
+        <v>-23244305.05588644</v>
       </c>
       <c r="Q140" s="5">
-        <v>65084.66117199999</v>
+        <v>-23244521.847315</v>
       </c>
       <c r="R140" s="5">
-        <v>61323.19415600086</v>
+        <v>-21901140.7701625</v>
       </c>
       <c r="S140" s="5">
-        <v>61323.19415600062</v>
+        <v>-21901140.77016242</v>
       </c>
       <c r="T140" s="5">
-        <v>61323.19415600062</v>
+        <v>-21901140.77016242</v>
       </c>
       <c r="U140" s="5">
-        <v>61323.19415600062</v>
+        <v>-21901140.77016242</v>
       </c>
       <c r="V140" s="5">
-        <v>61323.19415600062</v>
+        <v>-21901140.77016242</v>
       </c>
       <c r="W140" s="5">
-        <v>61323.19415600062</v>
+        <v>-21901140.77016242</v>
       </c>
     </row>
     <row r="141" spans="1:25">
@@ -24748,67 +24748,67 @@
         <v>2004</v>
       </c>
       <c r="B141" s="5">
-        <v>904443.8483999999</v>
+        <v>22843.64451112329</v>
       </c>
       <c r="C141" s="5">
-        <v>535349.0891999999</v>
+        <v>135066.3763245559</v>
       </c>
       <c r="D141" s="5">
-        <v>354367.9681880012</v>
+        <v>89405.5828509455</v>
       </c>
       <c r="E141" s="5">
-        <v>257704.7081639998</v>
+        <v>194582.2320779265</v>
       </c>
       <c r="F141" s="5">
-        <v>106187.7215199999</v>
+        <v>22122441.98364685</v>
       </c>
       <c r="G141" s="5">
-        <v>102310.6047599998</v>
+        <v>21314709.32530205</v>
       </c>
       <c r="H141" s="5">
-        <v>85086.80287599983</v>
+        <v>17726417.26608453</v>
       </c>
       <c r="I141" s="5">
-        <v>76689.47549199988</v>
+        <v>15976974.06105975</v>
       </c>
       <c r="J141" s="5">
-        <v>56643.29993199999</v>
+        <v>11800687.48600058</v>
       </c>
       <c r="K141" s="5">
-        <v>63416.58239999996</v>
+        <v>13211788.00018724</v>
       </c>
       <c r="L141" s="5">
-        <v>59475.45184399979</v>
+        <v>12390719.13434224</v>
       </c>
       <c r="M141" s="5">
-        <v>52429.59279999975</v>
+        <v>10922831.83348809</v>
       </c>
       <c r="N141" s="5">
-        <v>51969.05239999993</v>
+        <v>10826885.9168201</v>
       </c>
       <c r="O141" s="5">
-        <v>49954.02319999994</v>
+        <v>10407088.16681415</v>
       </c>
       <c r="P141" s="5">
-        <v>49307.98662799993</v>
+        <v>10272497.21431224</v>
       </c>
       <c r="Q141" s="5">
-        <v>38750.61919999961</v>
+        <v>8073045.666781004</v>
       </c>
       <c r="R141" s="5">
-        <v>38750.61919999961</v>
+        <v>8073045.666781004</v>
       </c>
       <c r="S141" s="5">
-        <v>38750.61919999961</v>
+        <v>8073045.666781004</v>
       </c>
       <c r="T141" s="5">
-        <v>38750.61919999961</v>
+        <v>8073045.666781004</v>
       </c>
       <c r="U141" s="5">
-        <v>38716.96939999959</v>
+        <v>8066035.291780902</v>
       </c>
       <c r="V141" s="5">
-        <v>38716.96939999959</v>
+        <v>8066035.291780902</v>
       </c>
     </row>
     <row r="142" spans="1:25">
@@ -24816,64 +24816,64 @@
         <v>2005</v>
       </c>
       <c r="B142" s="5">
-        <v>1742724.8092</v>
+        <v>120022.3697796145</v>
       </c>
       <c r="C142" s="5">
-        <v>1114822.074832</v>
+        <v>253368653.3690446</v>
       </c>
       <c r="D142" s="5">
-        <v>784086.1478199996</v>
+        <v>-596172.5576490245</v>
       </c>
       <c r="E142" s="5">
-        <v>715292.1536039996</v>
+        <v>162566398.5451673</v>
       </c>
       <c r="F142" s="5">
-        <v>593079.6693159996</v>
+        <v>134790833.9344626</v>
       </c>
       <c r="G142" s="5">
-        <v>556584.2046999997</v>
+        <v>126496410.15816</v>
       </c>
       <c r="H142" s="5">
-        <v>518716.8707279996</v>
+        <v>117890197.8918597</v>
       </c>
       <c r="I142" s="5">
-        <v>499630.0179759997</v>
+        <v>113552276.8118916</v>
       </c>
       <c r="J142" s="5">
-        <v>491907.6395999996</v>
+        <v>111797190.8173591</v>
       </c>
       <c r="K142" s="5">
-        <v>436097.9419559997</v>
+        <v>99113168.62563424</v>
       </c>
       <c r="L142" s="5">
-        <v>381682.7711999996</v>
+        <v>86746084.36299795</v>
       </c>
       <c r="M142" s="5">
-        <v>341770.1495999997</v>
+        <v>77675033.99942833</v>
       </c>
       <c r="N142" s="5">
-        <v>276001.2855999996</v>
+        <v>62727564.90862923</v>
       </c>
       <c r="O142" s="5">
-        <v>236838.7642279998</v>
+        <v>53826991.86960387</v>
       </c>
       <c r="P142" s="5">
-        <v>173130.9438799997</v>
+        <v>39347941.79061947</v>
       </c>
       <c r="Q142" s="5">
-        <v>155783.983728</v>
+        <v>35405450.84701218</v>
       </c>
       <c r="R142" s="5">
-        <v>113319.8627439998</v>
+        <v>25754514.25981044</v>
       </c>
       <c r="S142" s="5">
-        <v>109568.4378839997</v>
+        <v>24901917.70072577</v>
       </c>
       <c r="T142" s="5">
-        <v>109568.4378839997</v>
+        <v>24901917.70072577</v>
       </c>
       <c r="U142" s="5">
-        <v>109568.4378839997</v>
+        <v>24901917.70072577</v>
       </c>
     </row>
     <row r="143" spans="1:25">
@@ -24881,61 +24881,61 @@
         <v>2006</v>
       </c>
       <c r="B143" s="5">
-        <v>1307013.624276</v>
+        <v>70744.22059171225</v>
       </c>
       <c r="C143" s="5">
-        <v>892217.8444679999</v>
+        <v>1115272305.627222</v>
       </c>
       <c r="D143" s="5">
-        <v>698539.7038039999</v>
+        <v>873174629.7880563</v>
       </c>
       <c r="E143" s="5">
-        <v>618956.0793639999</v>
+        <v>773695099.2342902</v>
       </c>
       <c r="F143" s="5">
-        <v>559431.1930760001</v>
+        <v>699288991.3714736</v>
       </c>
       <c r="G143" s="5">
-        <v>511364.3671959999</v>
+        <v>639205459.0191988</v>
       </c>
       <c r="H143" s="5">
-        <v>466688.0555760001</v>
+        <v>583360069.4920849</v>
       </c>
       <c r="I143" s="5">
-        <v>459048.8119999999</v>
+        <v>573811015.021723</v>
       </c>
       <c r="J143" s="5">
-        <v>423260.956492</v>
+        <v>529076195.6350297</v>
       </c>
       <c r="K143" s="5">
-        <v>375366.378</v>
+        <v>469207972.5177632</v>
       </c>
       <c r="L143" s="5">
-        <v>263175.3055999998</v>
+        <v>328969132.0124539</v>
       </c>
       <c r="M143" s="5">
-        <v>226457.4356</v>
+        <v>283071794.5107164</v>
       </c>
       <c r="N143" s="5">
-        <v>212223.9001</v>
+        <v>265279875.1350428</v>
       </c>
       <c r="O143" s="5">
-        <v>186440.6315800003</v>
+        <v>233050789.4838231</v>
       </c>
       <c r="P143" s="5">
-        <v>176868.5170999996</v>
+        <v>221085646.3833693</v>
       </c>
       <c r="Q143" s="5">
-        <v>165049.9155799998</v>
+        <v>206312394.4828103</v>
       </c>
       <c r="R143" s="5">
-        <v>148685.3052559998</v>
+        <v>185856631.5770358</v>
       </c>
       <c r="S143" s="5">
-        <v>137666.9751559997</v>
+        <v>172083718.9515143</v>
       </c>
       <c r="T143" s="5">
-        <v>129659.0221439998</v>
+        <v>162073777.6861355</v>
       </c>
     </row>
     <row r="144" spans="1:25">
@@ -24943,58 +24943,58 @@
         <v>2007</v>
       </c>
       <c r="B144" s="5">
-        <v>4542287.726012</v>
+        <v>229427.010567117</v>
       </c>
       <c r="C144" s="5">
-        <v>3942627.849408</v>
+        <v>896051783.9613459</v>
       </c>
       <c r="D144" s="5">
-        <v>3617339.561096</v>
+        <v>822122627.5263894</v>
       </c>
       <c r="E144" s="5">
-        <v>3226728.789876</v>
+        <v>733347452.248623</v>
       </c>
       <c r="F144" s="5">
-        <v>2888204.544075999</v>
+        <v>656410123.657286</v>
       </c>
       <c r="G144" s="5">
-        <v>2425063.687531999</v>
+        <v>551150838.078519</v>
       </c>
       <c r="H144" s="5">
-        <v>2121719.093599999</v>
+        <v>482208884.911772</v>
       </c>
       <c r="I144" s="5">
-        <v>1894681.003076</v>
+        <v>430609318.8833033</v>
       </c>
       <c r="J144" s="5">
-        <v>1640464.932399999</v>
+        <v>372832939.1838911</v>
       </c>
       <c r="K144" s="5">
-        <v>1351426.346399999</v>
+        <v>307142351.4562531</v>
       </c>
       <c r="L144" s="5">
-        <v>1047667.622399999</v>
+        <v>238106277.8195056</v>
       </c>
       <c r="M144" s="5">
-        <v>847758.3701240001</v>
+        <v>192672356.847435</v>
       </c>
       <c r="N144" s="5">
-        <v>675473.5186799988</v>
+        <v>153516708.7917624</v>
       </c>
       <c r="O144" s="5">
-        <v>549134.5528199999</v>
+        <v>124803307.4597848</v>
       </c>
       <c r="P144" s="5">
-        <v>428554.5456919996</v>
+        <v>97398760.38508694</v>
       </c>
       <c r="Q144" s="5">
-        <v>294399.5098559987</v>
+        <v>66908979.51309901</v>
       </c>
       <c r="R144" s="5">
-        <v>264536.0777239995</v>
+        <v>60121835.84669782</v>
       </c>
       <c r="S144" s="5">
-        <v>255172.4468479995</v>
+        <v>57993737.92032234</v>
       </c>
     </row>
     <row r="145" spans="1:18">
@@ -25002,55 +25002,55 @@
         <v>2008</v>
       </c>
       <c r="B145" s="5">
-        <v>1095452.367564</v>
+        <v>51884.71513385003</v>
       </c>
       <c r="C145" s="5">
-        <v>802394.0820239999</v>
+        <v>608242.9366464677</v>
       </c>
       <c r="D145" s="5">
-        <v>579331.6955759999</v>
+        <v>-1448329238.6861</v>
       </c>
       <c r="E145" s="5">
-        <v>260613.3921559998</v>
+        <v>-651533480.2757823</v>
       </c>
       <c r="F145" s="5">
-        <v>219116.5907559998</v>
+        <v>-547791476.7939688</v>
       </c>
       <c r="G145" s="5">
-        <v>181217.5335999997</v>
+        <v>-453043833.9205784</v>
       </c>
       <c r="H145" s="5">
-        <v>172353.6088519997</v>
+        <v>-430884022.0544632</v>
       </c>
       <c r="I145" s="5">
-        <v>164192.0543999998</v>
+        <v>-410480135.9280402</v>
       </c>
       <c r="J145" s="5">
-        <v>149099.7891999998</v>
+        <v>-372749472.9346545</v>
       </c>
       <c r="K145" s="5">
-        <v>131675.7907999998</v>
+        <v>-329189476.942291</v>
       </c>
       <c r="L145" s="5">
-        <v>117587.1737719998</v>
+        <v>-293967934.3784654</v>
       </c>
       <c r="M145" s="5">
-        <v>115002.6052120014</v>
+        <v>-287506512.979602</v>
       </c>
       <c r="N145" s="5">
-        <v>111908.9217760016</v>
+        <v>-279772304.3909584</v>
       </c>
       <c r="O145" s="5">
-        <v>110389.7454720016</v>
+        <v>-275974363.6316243</v>
       </c>
       <c r="P145" s="5">
-        <v>109512.2642560017</v>
+        <v>-273780660.5920091</v>
       </c>
       <c r="Q145" s="5">
-        <v>105967.9242240016</v>
+        <v>-264919810.5135622</v>
       </c>
       <c r="R145" s="5">
-        <v>70541.19045200152</v>
+        <v>-176352976.0990882</v>
       </c>
     </row>
     <row r="146" spans="1:18">
@@ -25058,52 +25058,52 @@
         <v>2009</v>
       </c>
       <c r="B146" s="5">
-        <v>1014782.441828</v>
+        <v>64093.68158683232</v>
       </c>
       <c r="C146" s="5">
-        <v>501202.778404</v>
+        <v>380506.2089310618</v>
       </c>
       <c r="D146" s="5">
-        <v>431499.2630840001</v>
+        <v>-179791359.6166232</v>
       </c>
       <c r="E146" s="5">
-        <v>409388.151052</v>
+        <v>-170578396.2700441</v>
       </c>
       <c r="F146" s="5">
-        <v>348465.6896</v>
+        <v>-145194037.3319523</v>
       </c>
       <c r="G146" s="5">
-        <v>302365.146896</v>
+        <v>-125985477.872135</v>
       </c>
       <c r="H146" s="5">
-        <v>274058.724</v>
+        <v>-114191134.9989139</v>
       </c>
       <c r="I146" s="5">
-        <v>225193.936</v>
+        <v>-93830806.66577417</v>
       </c>
       <c r="J146" s="5">
-        <v>187840.0188</v>
+        <v>-78266674.49925552</v>
       </c>
       <c r="K146" s="5">
-        <v>172344.074764</v>
+        <v>-71810031.15098363</v>
       </c>
       <c r="L146" s="5">
-        <v>162267.7015359998</v>
+        <v>-67611542.30602346</v>
       </c>
       <c r="M146" s="5">
-        <v>129244.4344199998</v>
+        <v>-53851847.6744877</v>
       </c>
       <c r="N146" s="5">
-        <v>73868.9907439996</v>
+        <v>-30778746.14304041</v>
       </c>
       <c r="O146" s="5">
-        <v>73868.9907439996</v>
+        <v>-30778746.14304041</v>
       </c>
       <c r="P146" s="5">
-        <v>73868.9907439996</v>
+        <v>-30778746.14304041</v>
       </c>
       <c r="Q146" s="5">
-        <v>73868.9907439996</v>
+        <v>-30778746.14304041</v>
       </c>
     </row>
     <row r="147" spans="1:18">
@@ -25111,49 +25111,49 @@
         <v>2010</v>
       </c>
       <c r="B147" s="5">
-        <v>1122894.976776</v>
+        <v>94529.32760682932</v>
       </c>
       <c r="C147" s="5">
-        <v>693367.5652519999</v>
+        <v>288903152.1924279</v>
       </c>
       <c r="D147" s="5">
-        <v>451265.3565959998</v>
+        <v>188027231.9176648</v>
       </c>
       <c r="E147" s="5">
-        <v>289597.8483999998</v>
+        <v>120665770.1683768</v>
       </c>
       <c r="F147" s="5">
-        <v>189533.7944319998</v>
+        <v>78972414.34778585</v>
       </c>
       <c r="G147" s="5">
-        <v>164982.7419999999</v>
+        <v>68742809.16764089</v>
       </c>
       <c r="H147" s="5">
-        <v>106209.0775999997</v>
+        <v>44253782.33396043</v>
       </c>
       <c r="I147" s="5">
-        <v>104015.9023999998</v>
+        <v>43339959.3339475</v>
       </c>
       <c r="J147" s="5">
-        <v>99696.0730359999</v>
+        <v>41540030.43225537</v>
       </c>
       <c r="K147" s="5">
-        <v>98896.59337599948</v>
+        <v>41206913.90725047</v>
       </c>
       <c r="L147" s="5">
-        <v>98254.08013599948</v>
+        <v>40939200.05724668</v>
       </c>
       <c r="M147" s="5">
-        <v>98180.18253599945</v>
+        <v>40908409.39057957</v>
       </c>
       <c r="N147" s="5">
-        <v>97373.35270399926</v>
+        <v>40572230.29390805</v>
       </c>
       <c r="O147" s="5">
-        <v>96448.86733599938</v>
+        <v>40187028.05723598</v>
       </c>
       <c r="P147" s="5">
-        <v>88846.05791599932</v>
+        <v>37019190.79885772</v>
       </c>
     </row>
     <row r="148" spans="1:18">
@@ -25161,46 +25161,46 @@
         <v>2011</v>
       </c>
       <c r="B148" s="5">
-        <v>1700612.88412</v>
+        <v>354294350.859159</v>
       </c>
       <c r="C148" s="5">
-        <v>1225644.888244</v>
+        <v>255342685.0514284</v>
       </c>
       <c r="D148" s="5">
-        <v>756673.0491999998</v>
+        <v>157640218.5837007</v>
       </c>
       <c r="E148" s="5">
-        <v>657864.528652</v>
+        <v>137055110.1361527</v>
       </c>
       <c r="F148" s="5">
-        <v>541276.0607999999</v>
+        <v>112765846.0002628</v>
       </c>
       <c r="G148" s="5">
-        <v>405875.8635999998</v>
+        <v>84557471.58353037</v>
       </c>
       <c r="H148" s="5">
-        <v>242523.8991999999</v>
+        <v>50525812.33345106</v>
       </c>
       <c r="I148" s="5">
-        <v>238934.8643159997</v>
+        <v>49778096.73261594</v>
       </c>
       <c r="J148" s="5">
-        <v>230626.7155000002</v>
+        <v>48047232.39594535</v>
       </c>
       <c r="K148" s="5">
-        <v>216565.3878000001</v>
+        <v>45117789.12510518</v>
       </c>
       <c r="L148" s="5">
-        <v>206945.5169960002</v>
+        <v>43113649.37426719</v>
       </c>
       <c r="M148" s="5">
-        <v>187749.2826</v>
+        <v>39114433.87509117</v>
       </c>
       <c r="N148" s="5">
-        <v>178078.3432760001</v>
+        <v>37099654.84925316</v>
       </c>
       <c r="O148" s="5">
-        <v>172032.6222680002</v>
+        <v>35840129.63925023</v>
       </c>
     </row>
     <row r="149" spans="1:18">
@@ -25208,43 +25208,43 @@
         <v>2012</v>
       </c>
       <c r="B149" s="5">
-        <v>1247445.859456</v>
+        <v>78780.74694690063</v>
       </c>
       <c r="C149" s="5">
-        <v>840678.6844</v>
+        <v>-1050848355.465115</v>
       </c>
       <c r="D149" s="5">
-        <v>675912.1351920001</v>
+        <v>-844890168.9619527</v>
       </c>
       <c r="E149" s="5">
-        <v>523685.692</v>
+        <v>-654607114.9782693</v>
       </c>
       <c r="F149" s="5">
-        <v>514077.6844</v>
+        <v>-642597105.478668</v>
       </c>
       <c r="G149" s="5">
-        <v>507820.1412000001</v>
+        <v>-634775176.4789277</v>
       </c>
       <c r="H149" s="5">
-        <v>497593.848216</v>
+        <v>-621992310.249352</v>
       </c>
       <c r="I149" s="5">
-        <v>459074.1831800013</v>
+        <v>-573842728.955952</v>
       </c>
       <c r="J149" s="5">
-        <v>427015.2665480012</v>
+        <v>-533769083.1672822</v>
       </c>
       <c r="K149" s="5">
-        <v>422215.221548001</v>
+        <v>-527769026.9174812</v>
       </c>
       <c r="L149" s="5">
-        <v>390936.0565560013</v>
+        <v>-488670070.6787795</v>
       </c>
       <c r="M149" s="5">
-        <v>329680.3301240013</v>
+        <v>-412100412.6413212</v>
       </c>
       <c r="N149" s="5">
-        <v>281018.9716600012</v>
+        <v>-351273714.5633404</v>
       </c>
     </row>
     <row r="150" spans="1:18">
@@ -25252,40 +25252,40 @@
         <v>2013</v>
       </c>
       <c r="B150" s="5">
-        <v>566967.6800000001</v>
+        <v>61389.37156221594</v>
       </c>
       <c r="C150" s="5">
-        <v>303416.019948</v>
+        <v>230209.4233292896</v>
       </c>
       <c r="D150" s="5">
-        <v>224784.8432</v>
+        <v>170549.9569044027</v>
       </c>
       <c r="E150" s="5">
-        <v>171928.2652</v>
+        <v>-107455165.7464329</v>
       </c>
       <c r="F150" s="5">
-        <v>60879.96639999992</v>
+        <v>-38049978.99873682</v>
       </c>
       <c r="G150" s="5">
-        <v>62721.63974799996</v>
+        <v>-39201024.84119864</v>
       </c>
       <c r="H150" s="5">
-        <v>62373.15978000022</v>
+        <v>-38983224.86120603</v>
       </c>
       <c r="I150" s="5">
-        <v>62373.15977999999</v>
+        <v>-38983224.86120588</v>
       </c>
       <c r="J150" s="5">
-        <v>61007.50574000017</v>
+        <v>-38129691.08623433</v>
       </c>
       <c r="K150" s="5">
-        <v>61007.50574000017</v>
+        <v>-38129691.08623433</v>
       </c>
       <c r="L150" s="5">
-        <v>60996.28914000012</v>
+        <v>-38122680.71123454</v>
       </c>
       <c r="M150" s="5">
-        <v>60996.28914000012</v>
+        <v>-38122680.71123454</v>
       </c>
     </row>
     <row r="151" spans="1:18">
@@ -25293,37 +25293,37 @@
         <v>2014</v>
       </c>
       <c r="B151" s="5">
-        <v>1134034.868604</v>
+        <v>53716.19719035992</v>
       </c>
       <c r="C151" s="5">
-        <v>807518.9959999999</v>
+        <v>612871.1262902383</v>
       </c>
       <c r="D151" s="5">
-        <v>619437.7276</v>
+        <v>-309718863.7897184</v>
       </c>
       <c r="E151" s="5">
-        <v>366223.6424</v>
+        <v>-183111821.1939213</v>
       </c>
       <c r="F151" s="5">
-        <v>287208.1453479999</v>
+        <v>-143604072.6692328</v>
       </c>
       <c r="G151" s="5">
-        <v>266319.0093079996</v>
+        <v>-133159504.6495794</v>
       </c>
       <c r="H151" s="5">
-        <v>258500.4452879997</v>
+        <v>-129250222.6397092</v>
       </c>
       <c r="I151" s="5">
-        <v>254678.7781199999</v>
+        <v>-127339389.0557727</v>
       </c>
       <c r="J151" s="5">
-        <v>246510.3353559996</v>
+        <v>-123255167.6739082</v>
       </c>
       <c r="K151" s="5">
-        <v>166437.9970559999</v>
+        <v>-83218998.52523738</v>
       </c>
       <c r="L151" s="5">
-        <v>156152.3352679999</v>
+        <v>-78076167.6314081</v>
       </c>
     </row>
     <row r="152" spans="1:18">
@@ -25331,34 +25331,34 @@
         <v>2015</v>
       </c>
       <c r="B152" s="5">
-        <v>3425587.7352</v>
+        <v>288407.4000808251</v>
       </c>
       <c r="C152" s="5">
-        <v>2961316.826</v>
+        <v>2242063.011811086</v>
       </c>
       <c r="D152" s="5">
-        <v>2385869.6168</v>
+        <v>-602857.6957752153</v>
       </c>
       <c r="E152" s="5">
-        <v>1725138.216728</v>
+        <v>-435905.1487588422</v>
       </c>
       <c r="F152" s="5">
-        <v>1571390.578243999</v>
+        <v>-397056.4428552642</v>
       </c>
       <c r="G152" s="5">
-        <v>1317944.744891999</v>
+        <v>-333016.1574924183</v>
       </c>
       <c r="H152" s="5">
-        <v>1042330.924747999</v>
+        <v>-263374.5008965017</v>
       </c>
       <c r="I152" s="5">
-        <v>891072.1178439981</v>
+        <v>-225154.6689518888</v>
       </c>
       <c r="J152" s="5">
-        <v>849279.2641839986</v>
+        <v>-214594.5179361218</v>
       </c>
       <c r="K152" s="5">
-        <v>441781.2814519987</v>
+        <v>368151067.8818834</v>
       </c>
     </row>
     <row r="153" spans="1:18">
@@ -25366,31 +25366,31 @@
         <v>2016</v>
       </c>
       <c r="B153" s="5">
-        <v>2544414.0672</v>
+        <v>56712.92566109734</v>
       </c>
       <c r="C153" s="5">
-        <v>1758134.366</v>
+        <v>102495.9987640792</v>
       </c>
       <c r="D153" s="5">
-        <v>1292543.751232</v>
+        <v>-807839844.5218825</v>
       </c>
       <c r="E153" s="5">
-        <v>1092913.356828</v>
+        <v>-683070848.0190921</v>
       </c>
       <c r="F153" s="5">
-        <v>958146.976704001</v>
+        <v>-598841860.4413962</v>
       </c>
       <c r="G153" s="5">
-        <v>761208.3683600016</v>
+        <v>-475755230.2261098</v>
       </c>
       <c r="H153" s="5">
-        <v>464870.5337240011</v>
+        <v>-290544083.5781779</v>
       </c>
       <c r="I153" s="5">
-        <v>448847.0663920012</v>
+        <v>-280529416.4956546</v>
       </c>
       <c r="J153" s="5">
-        <v>421828.2036080011</v>
+        <v>-263642627.2556151</v>
       </c>
     </row>
     <row r="154" spans="1:18">
@@ -25398,28 +25398,28 @@
         <v>2017</v>
       </c>
       <c r="B154" s="5">
-        <v>1071970.7068</v>
+        <v>31240.40342021822</v>
       </c>
       <c r="C154" s="5">
-        <v>823832.806096</v>
+        <v>205958201.5259434</v>
       </c>
       <c r="D154" s="5">
-        <v>778495.9554999997</v>
+        <v>-591742.1370477267</v>
       </c>
       <c r="E154" s="5">
-        <v>698055.9106599998</v>
+        <v>-264896.7481253797</v>
       </c>
       <c r="F154" s="5">
-        <v>635947.5246879997</v>
+        <v>-483389.7268835445</v>
       </c>
       <c r="G154" s="5">
-        <v>552892.9563679997</v>
+        <v>-420259.1641593131</v>
       </c>
       <c r="H154" s="5">
-        <v>303535.3229919996</v>
+        <v>-230720.0691638762</v>
       </c>
       <c r="I154" s="5">
-        <v>202811.2710839997</v>
+        <v>50702817.77147835</v>
       </c>
     </row>
     <row r="155" spans="1:18">
@@ -25427,25 +25427,25 @@
         <v>2018</v>
       </c>
       <c r="B155" s="5">
-        <v>2495745.971004</v>
+        <v>67548.25674750193</v>
       </c>
       <c r="C155" s="5">
-        <v>1848045.027112</v>
+        <v>1401733.181972091</v>
       </c>
       <c r="D155" s="5">
-        <v>1367442.7879</v>
+        <v>1037198.716550367</v>
       </c>
       <c r="E155" s="5">
-        <v>817061.9613239996</v>
+        <v>619737.5313440545</v>
       </c>
       <c r="F155" s="5">
-        <v>700760.0578080001</v>
+        <v>-583966714.8206145</v>
       </c>
       <c r="G155" s="5">
-        <v>580315.8243239992</v>
+        <v>-483596520.2539456</v>
       </c>
       <c r="H155" s="5">
-        <v>445716.7166959993</v>
+        <v>-371430597.2343358</v>
       </c>
     </row>
     <row r="156" spans="1:18">
@@ -25453,22 +25453,22 @@
         <v>2019</v>
       </c>
       <c r="B156" s="5">
-        <v>2909069.828336</v>
+        <v>66698.53235422519</v>
       </c>
       <c r="C156" s="5">
-        <v>2424681.920644</v>
+        <v>-1937885.166755053</v>
       </c>
       <c r="D156" s="5">
-        <v>1844666.216656</v>
+        <v>-1474317.628401488</v>
       </c>
       <c r="E156" s="5">
-        <v>1597653.908359999</v>
+        <v>-1276897.305274895</v>
       </c>
       <c r="F156" s="5">
-        <v>1227509.20942</v>
+        <v>-981065.5446131399</v>
       </c>
       <c r="G156" s="5">
-        <v>803159.8555119992</v>
+        <v>11742103.15076075</v>
       </c>
     </row>
     <row r="157" spans="1:18">
@@ -25476,19 +25476,19 @@
         <v>2020</v>
       </c>
       <c r="B157" s="5">
-        <v>986836.9847160003</v>
+        <v>46579.6745358256</v>
       </c>
       <c r="C157" s="5">
-        <v>542665.1538400003</v>
+        <v>7495375.053042905</v>
       </c>
       <c r="D157" s="5">
-        <v>411049.2659320002</v>
+        <v>5677476.048787736</v>
       </c>
       <c r="E157" s="5">
-        <v>306817.0706200002</v>
+        <v>4237804.842820073</v>
       </c>
       <c r="F157" s="5">
-        <v>296702.2574440002</v>
+        <v>4098097.478510602</v>
       </c>
     </row>
     <row r="158" spans="1:18">
@@ -25496,16 +25496,16 @@
         <v>2021</v>
       </c>
       <c r="B158" s="5">
-        <v>1108507.735004</v>
+        <v>27051.55340976534</v>
       </c>
       <c r="C158" s="5">
-        <v>835307.9647080001</v>
+        <v>11932970.92440116</v>
       </c>
       <c r="D158" s="5">
-        <v>470840.6072400002</v>
+        <v>6726294.389143514</v>
       </c>
       <c r="E158" s="5">
-        <v>407240.4266639999</v>
+        <v>5817720.380914851</v>
       </c>
     </row>
     <row r="159" spans="1:18">
@@ -25513,13 +25513,13 @@
         <v>2022</v>
       </c>
       <c r="B159" s="5">
-        <v>993959.3162320002</v>
+        <v>26748.67371288941</v>
       </c>
       <c r="C159" s="5">
-        <v>554655.634912</v>
+        <v>2636195.983422143</v>
       </c>
       <c r="D159" s="5">
-        <v>510196.4898639999</v>
+        <v>2424888.259809968</v>
       </c>
     </row>
     <row r="160" spans="1:18">
@@ -25527,10 +25527,10 @@
         <v>2023</v>
       </c>
       <c r="B160" s="5">
-        <v>2728227.648035999</v>
+        <v>85570.51601603377</v>
       </c>
       <c r="C160" s="5">
-        <v>1896252.811643999</v>
+        <v>8927743.93429368</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -25538,7 +25538,7 @@
         <v>2024</v>
       </c>
       <c r="B161" s="5">
-        <v>2170416.609068</v>
+        <v>63374.26882666235</v>
       </c>
     </row>
   </sheetData>
@@ -25555,14 +25555,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="12" width="18.7109375" customWidth="1"/>
     <col min="13" max="13" width="40.7109375" customWidth="1"/>
+    <col min="14" max="14" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -25602,8 +25603,11 @@
       <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="4">
         <v>2001</v>
       </c>
@@ -25641,10 +25645,13 @@
         <v>154065.9077239996</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>14</v>
+      </c>
+      <c r="N2" s="6">
+        <v>0.01010300000380942</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="4">
         <v>2002</v>
       </c>
@@ -25682,10 +25689,13 @@
         <v>180048.5319119995</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>15</v>
+      </c>
+      <c r="N3" s="6">
+        <v>0.007374212885173717</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="4">
         <v>2003</v>
       </c>
@@ -25723,10 +25733,13 @@
         <v>61323.19415600062</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>16</v>
+      </c>
+      <c r="N4" s="6">
+        <v>0.005588225393396084</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="4">
         <v>2004</v>
       </c>
@@ -25764,10 +25777,13 @@
         <v>38716.96939999959</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>17</v>
+      </c>
+      <c r="N5" s="6">
+        <v>0.00345899834407469</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="4">
         <v>2005</v>
       </c>
@@ -25805,10 +25821,13 @@
         <v>109568.4378839997</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>18</v>
+      </c>
+      <c r="N6" s="6">
+        <v>0.006867190027689312</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="4">
         <v>2006</v>
       </c>
@@ -25846,10 +25865,13 @@
         <v>129659.0221439998</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>19</v>
+      </c>
+      <c r="N7" s="6">
+        <v>0.004557033737021419</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="4">
         <v>2007</v>
       </c>
@@ -25887,10 +25909,13 @@
         <v>255172.4468479995</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>20</v>
+      </c>
+      <c r="N8" s="6">
+        <v>0.01416215151909411</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="4">
         <v>2008</v>
       </c>
@@ -25928,10 +25953,13 @@
         <v>70541.19045200152</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>21</v>
+      </c>
+      <c r="N9" s="6">
+        <v>0.003987057685496641</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="4">
         <v>2009</v>
       </c>
@@ -25969,10 +25997,13 @@
         <v>73868.9907439996</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>22</v>
+      </c>
+      <c r="N10" s="6">
+        <v>0.003354451901309865</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="4">
         <v>2010</v>
       </c>
@@ -26010,10 +26041,13 @@
         <v>88846.05791599932</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>23</v>
+      </c>
+      <c r="N11" s="6">
+        <v>0.003614168868624826</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="4">
         <v>2011</v>
       </c>
@@ -26051,10 +26085,13 @@
         <v>172032.6222680002</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>24</v>
+      </c>
+      <c r="N12" s="6">
+        <v>0.005353624648238385</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="4">
         <v>2012</v>
       </c>
@@ -26092,10 +26129,13 @@
         <v>281018.9716600012</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>25</v>
+      </c>
+      <c r="N13" s="6">
+        <v>0.003750248487772091</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="4">
         <v>2013</v>
       </c>
@@ -26133,10 +26173,13 @@
         <v>60996.28914000012</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>26</v>
+      </c>
+      <c r="N14" s="6">
+        <v>0.001917855946344958</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="4">
         <v>2014</v>
       </c>
@@ -26174,10 +26217,13 @@
         <v>156152.3352679999</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+        <v>27</v>
+      </c>
+      <c r="N15" s="6">
+        <v>0.003776881005952719</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="4">
         <v>2015</v>
       </c>
@@ -26215,10 +26261,13 @@
         <v>441781.2814519987</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>28</v>
+      </c>
+      <c r="N16" s="6">
+        <v>0.009117219344256643</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="4">
         <v>2016</v>
       </c>
@@ -26256,10 +26305,13 @@
         <v>421828.2036080011</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>29</v>
+      </c>
+      <c r="N17" s="6">
+        <v>0.006773183189107037</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="4">
         <v>2017</v>
       </c>
@@ -26297,10 +26349,13 @@
         <v>202811.2710839997</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>30</v>
+      </c>
+      <c r="N18" s="6">
+        <v>0.003243296448208928</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="4">
         <v>2018</v>
       </c>
@@ -26338,10 +26393,13 @@
         <v>445716.7166959993</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>31</v>
+      </c>
+      <c r="N19" s="6">
+        <v>0.006413397320690939</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="4">
         <v>2019</v>
       </c>
@@ -26379,10 +26437,13 @@
         <v>803159.8555119992</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>32</v>
+      </c>
+      <c r="N20" s="6">
+        <v>0.007078112192328222</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="4">
         <v>2020</v>
       </c>
@@ -26420,10 +26481,13 @@
         <v>296702.2574440002</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>33</v>
+      </c>
+      <c r="N21" s="6">
+        <v>0.002761439262416636</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="4">
         <v>2021</v>
       </c>
@@ -26461,10 +26525,13 @@
         <v>407240.4266639999</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>34</v>
+      </c>
+      <c r="N22" s="6">
+        <v>0.002940141794494372</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="4">
         <v>2022</v>
       </c>
@@ -26502,10 +26569,13 @@
         <v>510196.4898639999</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>35</v>
+      </c>
+      <c r="N23" s="6">
+        <v>0.002713741512120429</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="4">
         <v>2023</v>
       </c>
@@ -26543,10 +26613,13 @@
         <v>1896252.811643999</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>36</v>
+      </c>
+      <c r="N24" s="6">
+        <v>0.006328793125555113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="4">
         <v>2024</v>
       </c>
@@ -26584,12 +26657,15 @@
         <v>2170416.609068</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+        <v>37</v>
+      </c>
+      <c r="N25" s="6">
+        <v>0.005062514447684894</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C27" s="5">
         <v>43616394.859456</v>
@@ -26646,10 +26722,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>10</v>
@@ -27212,7 +27288,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C27" s="5">
         <v>43616394.859456</v>
@@ -27251,10 +27327,10 @@
         <v>3</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>10</v>
@@ -27817,7 +27893,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C27" s="5">
         <v>41767854.339448</v>
@@ -27856,19 +27932,19 @@
         <v>6</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>10</v>
@@ -28647,7 +28723,7 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C27" s="5">
         <v>46003886.822088</v>
@@ -28695,10 +28771,10 @@
         <v>6</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>11</v>
@@ -28707,7 +28783,7 @@
         <v>3</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>10</v>
@@ -29486,7 +29562,7 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C27" s="5">
         <v>46003886.822088</v>
@@ -29517,14 +29593,15 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="8" width="18.7109375" customWidth="1"/>
-    <col min="9" max="9" width="40.7109375" customWidth="1"/>
+    <col min="1" max="9" width="18.7109375" customWidth="1"/>
+    <col min="10" max="10" width="40.7109375" customWidth="1"/>
+    <col min="11" max="11" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -29532,16 +29609,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>9</v>
@@ -29552,8 +29629,14 @@
       <c r="I1" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="4">
         <v>2001</v>
       </c>
@@ -29579,10 +29662,16 @@
         <v>0.002399999999965985</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>49</v>
+      </c>
+      <c r="J2" s="6">
+        <v>4561.602617345264</v>
+      </c>
+      <c r="K2" s="6">
+        <v>2.214791785104925E-06</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="4">
         <v>2002</v>
       </c>
@@ -29608,10 +29697,16 @@
         <v>-0.002400000000079672</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>50</v>
+      </c>
+      <c r="J3" s="6">
+        <v>3650.510462048229</v>
+      </c>
+      <c r="K3" s="6">
+        <v>2.020049788060651E-06</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="4">
         <v>2003</v>
       </c>
@@ -29637,10 +29732,16 @@
         <v>-0.002799999999979264</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>51</v>
+      </c>
+      <c r="J4" s="6">
+        <v>3334.750031726463</v>
+      </c>
+      <c r="K4" s="6">
+        <v>1.675755406021528E-06</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="4">
         <v>2004</v>
       </c>
@@ -29666,10 +29767,16 @@
         <v>0.00479999999993197</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>52</v>
+      </c>
+      <c r="J5" s="6">
+        <v>1807.098264996499</v>
+      </c>
+      <c r="K5" s="6">
+        <v>1.91411746172054E-06</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="4">
         <v>2005</v>
       </c>
@@ -29695,10 +29802,16 @@
         <v>0.004400000000032378</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>53</v>
+      </c>
+      <c r="J6" s="6">
+        <v>3666.938346872904</v>
+      </c>
+      <c r="K6" s="6">
+        <v>1.872731248275696E-06</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="4">
         <v>2006</v>
       </c>
@@ -29724,10 +29837,16 @@
         <v>0.0007999999999697138</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>54</v>
+      </c>
+      <c r="J7" s="6">
+        <v>3199.662405274478</v>
+      </c>
+      <c r="K7" s="6">
+        <v>1.424223296029414E-06</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="4">
         <v>2007</v>
       </c>
@@ -29753,10 +29872,16 @@
         <v>0.004399999999975535</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>55</v>
+      </c>
+      <c r="J8" s="6">
+        <v>10592.10210336286</v>
+      </c>
+      <c r="K8" s="6">
+        <v>1.337048244143889E-06</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="4">
         <v>2008</v>
       </c>
@@ -29782,10 +29907,16 @@
         <v>-0.000400000000070122</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>56</v>
+      </c>
+      <c r="J9" s="6">
+        <v>4409.791009799745</v>
+      </c>
+      <c r="K9" s="6">
+        <v>9.041375604050904E-07</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="4">
         <v>2009</v>
       </c>
@@ -29811,10 +29942,16 @@
         <v>-0.002400000000022828</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>57</v>
+      </c>
+      <c r="J10" s="6">
+        <v>3861.886079880738</v>
+      </c>
+      <c r="K10" s="6">
+        <v>8.68604570907865E-07</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="4">
         <v>2010</v>
       </c>
@@ -29840,10 +29977,16 @@
         <v>0.002399999999965985</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>58</v>
+      </c>
+      <c r="J11" s="6">
+        <v>5026.920725426721</v>
+      </c>
+      <c r="K11" s="6">
+        <v>7.189627738396509E-07</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="4">
         <v>2011</v>
       </c>
@@ -29869,10 +30012,16 @@
         <v>0.004799999999988813</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>59</v>
+      </c>
+      <c r="J12" s="6">
+        <v>5971.802279169317</v>
+      </c>
+      <c r="K12" s="6">
+        <v>8.964839085367507E-07</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="4">
         <v>2012</v>
       </c>
@@ -29898,10 +30047,16 @@
         <v>-0.0008000000000265572</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>60</v>
+      </c>
+      <c r="J13" s="6">
+        <v>5646.263969687692</v>
+      </c>
+      <c r="K13" s="6">
+        <v>6.641999927572508E-07</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="4">
         <v>2013</v>
       </c>
@@ -29927,10 +30082,16 @@
         <v>-0.001600000000053114</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>61</v>
+      </c>
+      <c r="J14" s="6">
+        <v>2638.707540376505</v>
+      </c>
+      <c r="K14" s="6">
+        <v>7.268164118223227E-07</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="4">
         <v>2014</v>
       </c>
@@ -29956,10 +30117,16 @@
         <v>-0.002000000000066393</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>62</v>
+      </c>
+      <c r="J15" s="6">
+        <v>3395.325791855204</v>
+      </c>
+      <c r="K15" s="6">
+        <v>1.112376613464546E-06</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="4">
         <v>2015</v>
       </c>
@@ -29985,10 +30152,16 @@
         <v>0.001199999999982992</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <v>63</v>
+      </c>
+      <c r="J16" s="6">
+        <v>11400.02569939496</v>
+      </c>
+      <c r="K16" s="6">
+        <v>7.997542799171524E-07</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="4">
         <v>2016</v>
       </c>
@@ -30014,10 +30187,16 @@
         <v>-0.001599999999996271</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <v>64</v>
+      </c>
+      <c r="J17" s="6">
+        <v>7383.606963645672</v>
+      </c>
+      <c r="K17" s="6">
+        <v>9.17327157642037E-07</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="4">
         <v>2017</v>
       </c>
@@ -30043,10 +30222,16 @@
         <v>0.003999999999962256</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+        <v>65</v>
+      </c>
+      <c r="J18" s="6">
+        <v>4542.333688046177</v>
+      </c>
+      <c r="K18" s="6">
+        <v>7.140154534978667E-07</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="4">
         <v>2018</v>
       </c>
@@ -30072,10 +30257,16 @@
         <v>-0.001200000000039836</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>66</v>
+      </c>
+      <c r="J19" s="6">
+        <v>8716.834816223845</v>
+      </c>
+      <c r="K19" s="6">
+        <v>7.357484059184271E-07</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="4">
         <v>2019</v>
       </c>
@@ -30101,10 +30292,16 @@
         <v>0.06839999999999691</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>67</v>
+      </c>
+      <c r="J20" s="6">
+        <v>8941.930468575263</v>
+      </c>
+      <c r="K20" s="6">
+        <v>7.915642172798054E-07</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="4">
         <v>2020</v>
       </c>
@@ -30130,10 +30327,16 @@
         <v>0.07239999999995916</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>68</v>
+      </c>
+      <c r="J21" s="6">
+        <v>3431.711389128559</v>
+      </c>
+      <c r="K21" s="6">
+        <v>8.046828387622275E-07</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="4">
         <v>2021</v>
       </c>
@@ -30159,10 +30362,16 @@
         <v>0.06999999999999318</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>69</v>
+      </c>
+      <c r="J22" s="6">
+        <v>4188.925781131618</v>
+      </c>
+      <c r="K22" s="6">
+        <v>7.018844324570743E-07</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="4">
         <v>2022</v>
       </c>
@@ -30188,10 +30397,16 @@
         <v>0.2103999999999928</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <v>70</v>
+      </c>
+      <c r="J23" s="6">
+        <v>4360.341107090202</v>
+      </c>
+      <c r="K23" s="6">
+        <v>6.223690866083173E-07</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="4">
         <v>2023</v>
       </c>
@@ -30217,10 +30432,16 @@
         <v>0.2124000000000024</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>71</v>
+      </c>
+      <c r="J24" s="6">
+        <v>10147.83267768161</v>
+      </c>
+      <c r="K24" s="6">
+        <v>6.236595859009567E-07</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="4">
         <v>2024</v>
       </c>
@@ -30246,12 +30467,18 @@
         <v>34.24759999999998</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>72</v>
+      </c>
+      <c r="J25" s="6">
+        <v>8701.6860292851</v>
+      </c>
+      <c r="K25" s="6">
+        <v>5.817854644085352E-07</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C27" s="5">
         <v>9716.214800000002</v>
@@ -30293,13 +30520,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>10</v>
@@ -30862,7 +31089,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C27" s="5">
         <v>9716.214800000002</v>
@@ -30901,19 +31128,19 @@
         <v>6</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>10</v>
@@ -31692,7 +31919,7 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C27" s="5">
         <v>10324.88784447919</v>

--- a/sample-data/sample-run/Analysis.xlsx
+++ b/sample-data/sample-run/Analysis.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="262">
   <si>
     <t>Accident Period</t>
   </si>
@@ -405,7 +405,76 @@
     <t>Averages</t>
   </si>
   <si>
-    <t>Tail</t>
+    <t>11</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>227</t>
+  </si>
+  <si>
+    <t>239</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>263</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>287</t>
   </si>
   <si>
     <t>Average - All Years</t>
@@ -673,78 +742,6 @@
   </si>
   <si>
     <t>INCURRED SEVERITY</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>155</t>
-  </si>
-  <si>
-    <t>167</t>
-  </si>
-  <si>
-    <t>179</t>
-  </si>
-  <si>
-    <t>191</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>215</t>
-  </si>
-  <si>
-    <t>227</t>
-  </si>
-  <si>
-    <t>239</t>
-  </si>
-  <si>
-    <t>251</t>
-  </si>
-  <si>
-    <t>263</t>
-  </si>
-  <si>
-    <t>275</t>
-  </si>
-  <si>
-    <t>287</t>
   </si>
   <si>
     <t>PAID TO INCURRED</t>
@@ -1221,18 +1218,18 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1240,7 +1237,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1248,7 +1245,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1256,7 +1253,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1264,15 +1261,15 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1280,7 +1277,7 @@
         <v>45</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1288,7 +1285,7 @@
         <v>46</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1296,7 +1293,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1304,7 +1301,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1312,31 +1309,31 @@
         <v>44</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -1357,76 +1354,76 @@
       <c r="A1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="3">
+      <c r="B1" s="6">
         <v>11</v>
       </c>
-      <c r="C1" s="3">
+      <c r="C1" s="6">
         <v>23</v>
       </c>
-      <c r="D1" s="3">
+      <c r="D1" s="6">
         <v>35</v>
       </c>
-      <c r="E1" s="3">
+      <c r="E1" s="6">
         <v>47</v>
       </c>
-      <c r="F1" s="3">
+      <c r="F1" s="6">
         <v>59</v>
       </c>
-      <c r="G1" s="3">
+      <c r="G1" s="6">
         <v>71</v>
       </c>
-      <c r="H1" s="3">
+      <c r="H1" s="6">
         <v>83</v>
       </c>
-      <c r="I1" s="3">
+      <c r="I1" s="6">
         <v>95</v>
       </c>
-      <c r="J1" s="3">
+      <c r="J1" s="6">
         <v>107</v>
       </c>
-      <c r="K1" s="3">
+      <c r="K1" s="6">
         <v>119</v>
       </c>
-      <c r="L1" s="3">
+      <c r="L1" s="6">
         <v>131</v>
       </c>
-      <c r="M1" s="3">
+      <c r="M1" s="6">
         <v>143</v>
       </c>
-      <c r="N1" s="3">
+      <c r="N1" s="6">
         <v>155</v>
       </c>
-      <c r="O1" s="3">
+      <c r="O1" s="6">
         <v>167</v>
       </c>
-      <c r="P1" s="3">
+      <c r="P1" s="6">
         <v>179</v>
       </c>
-      <c r="Q1" s="3">
+      <c r="Q1" s="6">
         <v>191</v>
       </c>
-      <c r="R1" s="3">
+      <c r="R1" s="6">
         <v>203</v>
       </c>
-      <c r="S1" s="3">
+      <c r="S1" s="6">
         <v>215</v>
       </c>
-      <c r="T1" s="3">
+      <c r="T1" s="6">
         <v>227</v>
       </c>
-      <c r="U1" s="3">
+      <c r="U1" s="6">
         <v>239</v>
       </c>
-      <c r="V1" s="3">
+      <c r="V1" s="6">
         <v>251</v>
       </c>
-      <c r="W1" s="3">
+      <c r="W1" s="6">
         <v>263</v>
       </c>
-      <c r="X1" s="3">
+      <c r="X1" s="6">
         <v>275</v>
       </c>
-      <c r="Y1" s="3">
+      <c r="Y1" s="6">
         <v>287</v>
       </c>
     </row>
@@ -4054,81 +4051,81 @@
         <v>124</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="W52" s="3" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="X52" s="3" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="Y52" s="3" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
     </row>
     <row r="53" spans="1:25">
       <c r="A53" s="2" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="B53" s="6">
         <v>1.7435</v>
@@ -4203,7 +4200,7 @@
     </row>
     <row r="54" spans="1:25">
       <c r="A54" s="2" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="B54" s="6">
         <v>1.6135</v>
@@ -4278,7 +4275,7 @@
     </row>
     <row r="55" spans="1:25">
       <c r="A55" s="2" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="B55" s="6">
         <v>1.7265</v>
@@ -4353,7 +4350,7 @@
     </row>
     <row r="56" spans="1:25">
       <c r="A56" s="2" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="B56" s="6">
         <v>1.4593</v>
@@ -4428,7 +4425,7 @@
     </row>
     <row r="57" spans="1:25">
       <c r="A57" s="2" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="B57" s="6">
         <v>1.4891</v>
@@ -4503,7 +4500,7 @@
     </row>
     <row r="58" spans="1:25">
       <c r="A58" s="2" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="B58" s="6">
         <v>1.784</v>
@@ -4578,7 +4575,7 @@
     </row>
     <row r="59" spans="1:25">
       <c r="A59" s="2" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="B59" s="6">
         <v>1.7024</v>
@@ -4653,7 +4650,7 @@
     </row>
     <row r="60" spans="1:25">
       <c r="A60" s="2" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="B60" s="6">
         <v>1.6456</v>
@@ -4728,7 +4725,7 @@
     </row>
     <row r="61" spans="1:25">
       <c r="A61" s="2" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="B61" s="6">
         <v>1.7774</v>
@@ -4803,7 +4800,7 @@
     </row>
     <row r="62" spans="1:25">
       <c r="A62" s="2" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="B62" s="6">
         <v>1.7371</v>
@@ -4878,7 +4875,7 @@
     </row>
     <row r="63" spans="1:25">
       <c r="A63" s="2" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="B63" s="6">
         <v>1.7238</v>
@@ -4953,7 +4950,7 @@
     </row>
     <row r="64" spans="1:25">
       <c r="A64" s="2" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="B64" s="6">
         <v>1.0888</v>
@@ -5028,7 +5025,7 @@
     </row>
     <row r="65" spans="1:25">
       <c r="A65" s="2" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="B65" s="6">
         <v>2.757</v>
@@ -5103,81 +5100,84 @@
     </row>
     <row r="67" spans="1:25">
       <c r="A67" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="M67" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="N67" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="P67" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="L67" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="M67" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="N67" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="O67" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="P67" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="Q67" s="3" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="T67" s="3" t="s">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="U67" s="3" t="s">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="V67" s="3" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="W67" s="3" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="X67" s="3" t="s">
-        <v>99</v>
+        <v>147</v>
+      </c>
+      <c r="Y67" s="3" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="68" spans="1:25">
       <c r="A68" s="2" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="B68" s="6">
         <v>1.6456</v>
@@ -5251,77 +5251,77 @@
         <v>12</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="Q69" s="2" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="R69" s="2" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="T69" s="2" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="U69" s="2" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="V69" s="2" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="W69" s="2" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="X69" s="2"/>
       <c r="Y69" s="2"/>
     </row>
     <row r="71" spans="1:25">
       <c r="A71" s="2" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="B71" s="6">
         <v>1.6456</v>
@@ -5473,18 +5473,18 @@
     </row>
     <row r="74" spans="1:25">
       <c r="A74" s="2" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
     </row>
     <row r="75" spans="1:25" ht="240" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
@@ -5512,76 +5512,76 @@
       <c r="A1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="3">
+      <c r="B1" s="6">
         <v>11</v>
       </c>
-      <c r="C1" s="3">
+      <c r="C1" s="6">
         <v>23</v>
       </c>
-      <c r="D1" s="3">
+      <c r="D1" s="6">
         <v>35</v>
       </c>
-      <c r="E1" s="3">
+      <c r="E1" s="6">
         <v>47</v>
       </c>
-      <c r="F1" s="3">
+      <c r="F1" s="6">
         <v>59</v>
       </c>
-      <c r="G1" s="3">
+      <c r="G1" s="6">
         <v>71</v>
       </c>
-      <c r="H1" s="3">
+      <c r="H1" s="6">
         <v>83</v>
       </c>
-      <c r="I1" s="3">
+      <c r="I1" s="6">
         <v>95</v>
       </c>
-      <c r="J1" s="3">
+      <c r="J1" s="6">
         <v>107</v>
       </c>
-      <c r="K1" s="3">
+      <c r="K1" s="6">
         <v>119</v>
       </c>
-      <c r="L1" s="3">
+      <c r="L1" s="6">
         <v>131</v>
       </c>
-      <c r="M1" s="3">
+      <c r="M1" s="6">
         <v>143</v>
       </c>
-      <c r="N1" s="3">
+      <c r="N1" s="6">
         <v>155</v>
       </c>
-      <c r="O1" s="3">
+      <c r="O1" s="6">
         <v>167</v>
       </c>
-      <c r="P1" s="3">
+      <c r="P1" s="6">
         <v>179</v>
       </c>
-      <c r="Q1" s="3">
+      <c r="Q1" s="6">
         <v>191</v>
       </c>
-      <c r="R1" s="3">
+      <c r="R1" s="6">
         <v>203</v>
       </c>
-      <c r="S1" s="3">
+      <c r="S1" s="6">
         <v>215</v>
       </c>
-      <c r="T1" s="3">
+      <c r="T1" s="6">
         <v>227</v>
       </c>
-      <c r="U1" s="3">
+      <c r="U1" s="6">
         <v>239</v>
       </c>
-      <c r="V1" s="3">
+      <c r="V1" s="6">
         <v>251</v>
       </c>
-      <c r="W1" s="3">
+      <c r="W1" s="6">
         <v>263</v>
       </c>
-      <c r="X1" s="3">
+      <c r="X1" s="6">
         <v>275</v>
       </c>
-      <c r="Y1" s="3">
+      <c r="Y1" s="6">
         <v>287</v>
       </c>
     </row>
@@ -8209,81 +8209,81 @@
         <v>124</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="W52" s="3" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="X52" s="3" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="Y52" s="3" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
     </row>
     <row r="53" spans="1:25">
       <c r="A53" s="2" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="B53" s="6">
         <v>2.4979</v>
@@ -8358,7 +8358,7 @@
     </row>
     <row r="54" spans="1:25">
       <c r="A54" s="2" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="B54" s="6">
         <v>2.4566</v>
@@ -8433,7 +8433,7 @@
     </row>
     <row r="55" spans="1:25">
       <c r="A55" s="2" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="B55" s="6">
         <v>2.4952</v>
@@ -8508,7 +8508,7 @@
     </row>
     <row r="56" spans="1:25">
       <c r="A56" s="2" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="B56" s="6">
         <v>2.5643</v>
@@ -8583,7 +8583,7 @@
     </row>
     <row r="57" spans="1:25">
       <c r="A57" s="2" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="B57" s="6">
         <v>2.6286</v>
@@ -8658,7 +8658,7 @@
     </row>
     <row r="58" spans="1:25">
       <c r="A58" s="2" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="B58" s="6">
         <v>2.5842</v>
@@ -8733,7 +8733,7 @@
     </row>
     <row r="59" spans="1:25">
       <c r="A59" s="2" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="B59" s="6">
         <v>2.6232</v>
@@ -8808,7 +8808,7 @@
     </row>
     <row r="60" spans="1:25">
       <c r="A60" s="2" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="B60" s="6">
         <v>2.5525</v>
@@ -8883,7 +8883,7 @@
     </row>
     <row r="61" spans="1:25">
       <c r="A61" s="2" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="B61" s="6">
         <v>2.4862</v>
@@ -8958,7 +8958,7 @@
     </row>
     <row r="62" spans="1:25">
       <c r="A62" s="2" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="B62" s="6">
         <v>2.482</v>
@@ -9033,7 +9033,7 @@
     </row>
     <row r="63" spans="1:25">
       <c r="A63" s="2" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="B63" s="6">
         <v>2.4762</v>
@@ -9108,7 +9108,7 @@
     </row>
     <row r="64" spans="1:25">
       <c r="A64" s="2" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="B64" s="6">
         <v>1.7371</v>
@@ -9183,7 +9183,7 @@
     </row>
     <row r="65" spans="1:25">
       <c r="A65" s="2" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="B65" s="6">
         <v>3.3152</v>
@@ -9258,81 +9258,84 @@
     </row>
     <row r="67" spans="1:25">
       <c r="A67" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="M67" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="N67" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="P67" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="L67" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="M67" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="N67" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="O67" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="P67" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="Q67" s="3" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="T67" s="3" t="s">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="U67" s="3" t="s">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="V67" s="3" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="W67" s="3" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="X67" s="3" t="s">
-        <v>99</v>
+        <v>147</v>
+      </c>
+      <c r="Y67" s="3" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="68" spans="1:25">
       <c r="A68" s="2" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="B68" s="6">
         <v>2.5525</v>
@@ -9406,77 +9409,77 @@
         <v>12</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="Q69" s="2" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="R69" s="2" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="T69" s="2" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="U69" s="2" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="V69" s="2" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="W69" s="2" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="X69" s="2"/>
       <c r="Y69" s="2"/>
     </row>
     <row r="71" spans="1:25">
       <c r="A71" s="2" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="B71" s="6">
         <v>2.5525</v>
@@ -9628,18 +9631,18 @@
     </row>
     <row r="74" spans="1:25">
       <c r="A74" s="2" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
     </row>
     <row r="75" spans="1:25" ht="270" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
@@ -9667,76 +9670,76 @@
       <c r="A1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="3">
+      <c r="B1" s="6">
         <v>11</v>
       </c>
-      <c r="C1" s="3">
+      <c r="C1" s="6">
         <v>23</v>
       </c>
-      <c r="D1" s="3">
+      <c r="D1" s="6">
         <v>35</v>
       </c>
-      <c r="E1" s="3">
+      <c r="E1" s="6">
         <v>47</v>
       </c>
-      <c r="F1" s="3">
+      <c r="F1" s="6">
         <v>59</v>
       </c>
-      <c r="G1" s="3">
+      <c r="G1" s="6">
         <v>71</v>
       </c>
-      <c r="H1" s="3">
+      <c r="H1" s="6">
         <v>83</v>
       </c>
-      <c r="I1" s="3">
+      <c r="I1" s="6">
         <v>95</v>
       </c>
-      <c r="J1" s="3">
+      <c r="J1" s="6">
         <v>107</v>
       </c>
-      <c r="K1" s="3">
+      <c r="K1" s="6">
         <v>119</v>
       </c>
-      <c r="L1" s="3">
+      <c r="L1" s="6">
         <v>131</v>
       </c>
-      <c r="M1" s="3">
+      <c r="M1" s="6">
         <v>143</v>
       </c>
-      <c r="N1" s="3">
+      <c r="N1" s="6">
         <v>155</v>
       </c>
-      <c r="O1" s="3">
+      <c r="O1" s="6">
         <v>167</v>
       </c>
-      <c r="P1" s="3">
+      <c r="P1" s="6">
         <v>179</v>
       </c>
-      <c r="Q1" s="3">
+      <c r="Q1" s="6">
         <v>191</v>
       </c>
-      <c r="R1" s="3">
+      <c r="R1" s="6">
         <v>203</v>
       </c>
-      <c r="S1" s="3">
+      <c r="S1" s="6">
         <v>215</v>
       </c>
-      <c r="T1" s="3">
+      <c r="T1" s="6">
         <v>227</v>
       </c>
-      <c r="U1" s="3">
+      <c r="U1" s="6">
         <v>239</v>
       </c>
-      <c r="V1" s="3">
+      <c r="V1" s="6">
         <v>251</v>
       </c>
-      <c r="W1" s="3">
+      <c r="W1" s="6">
         <v>263</v>
       </c>
-      <c r="X1" s="3">
+      <c r="X1" s="6">
         <v>275</v>
       </c>
-      <c r="Y1" s="3">
+      <c r="Y1" s="6">
         <v>287</v>
       </c>
     </row>
@@ -12364,81 +12367,81 @@
         <v>124</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="W52" s="3" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="X52" s="3" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="Y52" s="3" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
     </row>
     <row r="53" spans="1:25">
       <c r="A53" s="2" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="B53" s="6">
         <v>1.0679</v>
@@ -12513,7 +12516,7 @@
     </row>
     <row r="54" spans="1:25">
       <c r="A54" s="2" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="B54" s="6">
         <v>1.0617</v>
@@ -12588,7 +12591,7 @@
     </row>
     <row r="55" spans="1:25">
       <c r="A55" s="2" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="B55" s="6">
         <v>1.0676</v>
@@ -12663,7 +12666,7 @@
     </row>
     <row r="56" spans="1:25">
       <c r="A56" s="2" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="B56" s="6">
         <v>1.133</v>
@@ -12738,7 +12741,7 @@
     </row>
     <row r="57" spans="1:25">
       <c r="A57" s="2" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="B57" s="6">
         <v>1.133</v>
@@ -12813,7 +12816,7 @@
     </row>
     <row r="58" spans="1:25">
       <c r="A58" s="2" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="B58" s="6">
         <v>1.1204</v>
@@ -12888,7 +12891,7 @@
     </row>
     <row r="59" spans="1:25">
       <c r="A59" s="2" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="B59" s="6">
         <v>1.118</v>
@@ -12963,7 +12966,7 @@
     </row>
     <row r="60" spans="1:25">
       <c r="A60" s="2" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="B60" s="6">
         <v>1.133</v>
@@ -13038,7 +13041,7 @@
     </row>
     <row r="61" spans="1:25">
       <c r="A61" s="2" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="B61" s="6">
         <v>1.1009</v>
@@ -13113,7 +13116,7 @@
     </row>
     <row r="62" spans="1:25">
       <c r="A62" s="2" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="B62" s="6">
         <v>1.0962</v>
@@ -13188,7 +13191,7 @@
     </row>
     <row r="63" spans="1:25">
       <c r="A63" s="2" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="B63" s="6">
         <v>1.1041</v>
@@ -13263,7 +13266,7 @@
     </row>
     <row r="64" spans="1:25">
       <c r="A64" s="2" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="B64" s="6">
         <v>1</v>
@@ -13338,7 +13341,7 @@
     </row>
     <row r="65" spans="1:25">
       <c r="A65" s="2" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="B65" s="6">
         <v>1.1429</v>
@@ -13413,81 +13416,84 @@
     </row>
     <row r="67" spans="1:25">
       <c r="A67" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="M67" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="N67" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="P67" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="L67" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="M67" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="N67" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="O67" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="P67" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="Q67" s="3" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="T67" s="3" t="s">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="U67" s="3" t="s">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="V67" s="3" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="W67" s="3" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="X67" s="3" t="s">
-        <v>99</v>
+        <v>147</v>
+      </c>
+      <c r="Y67" s="3" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="68" spans="1:25">
       <c r="A68" s="2" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="B68" s="6">
         <v>1.133</v>
@@ -13563,79 +13569,79 @@
         <v>12</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="Q69" s="2" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="R69" s="2" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="T69" s="2" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="U69" s="2" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="V69" s="2" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="W69" s="2" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="X69" s="2" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="Y69" s="2"/>
     </row>
     <row r="71" spans="1:25">
       <c r="A71" s="2" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="B71" s="6">
         <v>1.133</v>
@@ -13787,18 +13793,18 @@
     </row>
     <row r="74" spans="1:25">
       <c r="A74" s="2" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
     </row>
     <row r="75" spans="1:25" ht="285" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
@@ -13826,7 +13832,7 @@
         <v>75</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -14037,7 +14043,7 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -14069,76 +14075,76 @@
         <v>75</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>215</v>
+        <v>125</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>216</v>
+        <v>126</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>217</v>
+        <v>127</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>218</v>
+        <v>128</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>219</v>
+        <v>129</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>221</v>
+        <v>131</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>222</v>
+        <v>132</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>223</v>
+        <v>133</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>224</v>
+        <v>134</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>225</v>
+        <v>135</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>227</v>
+        <v>137</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>228</v>
+        <v>138</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>229</v>
+        <v>139</v>
       </c>
       <c r="Q2" s="10" t="s">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="R2" s="10" t="s">
-        <v>231</v>
+        <v>141</v>
       </c>
       <c r="S2" s="10" t="s">
-        <v>232</v>
+        <v>142</v>
       </c>
       <c r="T2" s="10" t="s">
-        <v>233</v>
+        <v>143</v>
       </c>
       <c r="U2" s="10" t="s">
-        <v>234</v>
+        <v>144</v>
       </c>
       <c r="V2" s="10" t="s">
-        <v>235</v>
+        <v>145</v>
       </c>
       <c r="W2" s="10" t="s">
-        <v>236</v>
+        <v>146</v>
       </c>
       <c r="X2" s="10" t="s">
-        <v>237</v>
+        <v>147</v>
       </c>
       <c r="Y2" s="10" t="s">
-        <v>238</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -15163,7 +15169,7 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -15195,76 +15201,76 @@
         <v>75</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>215</v>
+        <v>125</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>216</v>
+        <v>126</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>217</v>
+        <v>127</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>218</v>
+        <v>128</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>219</v>
+        <v>129</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>221</v>
+        <v>131</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>222</v>
+        <v>132</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>223</v>
+        <v>133</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>224</v>
+        <v>134</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>225</v>
+        <v>135</v>
       </c>
       <c r="M29" s="10" t="s">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>227</v>
+        <v>137</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>228</v>
+        <v>138</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>229</v>
+        <v>139</v>
       </c>
       <c r="Q29" s="10" t="s">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="R29" s="10" t="s">
-        <v>231</v>
+        <v>141</v>
       </c>
       <c r="S29" s="10" t="s">
-        <v>232</v>
+        <v>142</v>
       </c>
       <c r="T29" s="10" t="s">
-        <v>233</v>
+        <v>143</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>234</v>
+        <v>144</v>
       </c>
       <c r="V29" s="10" t="s">
-        <v>235</v>
+        <v>145</v>
       </c>
       <c r="W29" s="10" t="s">
-        <v>236</v>
+        <v>146</v>
       </c>
       <c r="X29" s="10" t="s">
-        <v>237</v>
+        <v>147</v>
       </c>
       <c r="Y29" s="10" t="s">
-        <v>238</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -16289,7 +16295,7 @@
     </row>
     <row r="55" spans="1:25">
       <c r="A55" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -16321,76 +16327,76 @@
         <v>75</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>215</v>
+        <v>125</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>216</v>
+        <v>126</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>217</v>
+        <v>127</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>218</v>
+        <v>128</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>219</v>
+        <v>129</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>221</v>
+        <v>131</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>222</v>
+        <v>132</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>223</v>
+        <v>133</v>
       </c>
       <c r="K56" s="10" t="s">
-        <v>224</v>
+        <v>134</v>
       </c>
       <c r="L56" s="10" t="s">
-        <v>225</v>
+        <v>135</v>
       </c>
       <c r="M56" s="10" t="s">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="N56" s="10" t="s">
-        <v>227</v>
+        <v>137</v>
       </c>
       <c r="O56" s="10" t="s">
-        <v>228</v>
+        <v>138</v>
       </c>
       <c r="P56" s="10" t="s">
-        <v>229</v>
+        <v>139</v>
       </c>
       <c r="Q56" s="10" t="s">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="R56" s="10" t="s">
-        <v>231</v>
+        <v>141</v>
       </c>
       <c r="S56" s="10" t="s">
-        <v>232</v>
+        <v>142</v>
       </c>
       <c r="T56" s="10" t="s">
-        <v>233</v>
+        <v>143</v>
       </c>
       <c r="U56" s="10" t="s">
-        <v>234</v>
+        <v>144</v>
       </c>
       <c r="V56" s="10" t="s">
-        <v>235</v>
+        <v>145</v>
       </c>
       <c r="W56" s="10" t="s">
-        <v>236</v>
+        <v>146</v>
       </c>
       <c r="X56" s="10" t="s">
-        <v>237</v>
+        <v>147</v>
       </c>
       <c r="Y56" s="10" t="s">
-        <v>238</v>
+        <v>148</v>
       </c>
     </row>
     <row r="57" spans="1:25">
@@ -17415,7 +17421,7 @@
     </row>
     <row r="82" spans="1:25">
       <c r="A82" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -17447,76 +17453,76 @@
         <v>75</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>215</v>
+        <v>125</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>216</v>
+        <v>126</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>217</v>
+        <v>127</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>218</v>
+        <v>128</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>219</v>
+        <v>129</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>221</v>
+        <v>131</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>222</v>
+        <v>132</v>
       </c>
       <c r="J83" s="10" t="s">
-        <v>223</v>
+        <v>133</v>
       </c>
       <c r="K83" s="10" t="s">
-        <v>224</v>
+        <v>134</v>
       </c>
       <c r="L83" s="10" t="s">
-        <v>225</v>
+        <v>135</v>
       </c>
       <c r="M83" s="10" t="s">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>227</v>
+        <v>137</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>228</v>
+        <v>138</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>229</v>
+        <v>139</v>
       </c>
       <c r="Q83" s="10" t="s">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="R83" s="10" t="s">
-        <v>231</v>
+        <v>141</v>
       </c>
       <c r="S83" s="10" t="s">
-        <v>232</v>
+        <v>142</v>
       </c>
       <c r="T83" s="10" t="s">
-        <v>233</v>
+        <v>143</v>
       </c>
       <c r="U83" s="10" t="s">
-        <v>234</v>
+        <v>144</v>
       </c>
       <c r="V83" s="10" t="s">
-        <v>235</v>
+        <v>145</v>
       </c>
       <c r="W83" s="10" t="s">
-        <v>236</v>
+        <v>146</v>
       </c>
       <c r="X83" s="10" t="s">
-        <v>237</v>
+        <v>147</v>
       </c>
       <c r="Y83" s="10" t="s">
-        <v>238</v>
+        <v>148</v>
       </c>
     </row>
     <row r="84" spans="1:25">
@@ -18541,7 +18547,7 @@
     </row>
     <row r="109" spans="1:25">
       <c r="A109" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -18573,76 +18579,76 @@
         <v>75</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>215</v>
+        <v>125</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>216</v>
+        <v>126</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>217</v>
+        <v>127</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>218</v>
+        <v>128</v>
       </c>
       <c r="F110" s="10" t="s">
-        <v>219</v>
+        <v>129</v>
       </c>
       <c r="G110" s="10" t="s">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="H110" s="10" t="s">
-        <v>221</v>
+        <v>131</v>
       </c>
       <c r="I110" s="10" t="s">
-        <v>222</v>
+        <v>132</v>
       </c>
       <c r="J110" s="10" t="s">
-        <v>223</v>
+        <v>133</v>
       </c>
       <c r="K110" s="10" t="s">
-        <v>224</v>
+        <v>134</v>
       </c>
       <c r="L110" s="10" t="s">
-        <v>225</v>
+        <v>135</v>
       </c>
       <c r="M110" s="10" t="s">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="N110" s="10" t="s">
-        <v>227</v>
+        <v>137</v>
       </c>
       <c r="O110" s="10" t="s">
-        <v>228</v>
+        <v>138</v>
       </c>
       <c r="P110" s="10" t="s">
-        <v>229</v>
+        <v>139</v>
       </c>
       <c r="Q110" s="10" t="s">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="R110" s="10" t="s">
-        <v>231</v>
+        <v>141</v>
       </c>
       <c r="S110" s="10" t="s">
-        <v>232</v>
+        <v>142</v>
       </c>
       <c r="T110" s="10" t="s">
-        <v>233</v>
+        <v>143</v>
       </c>
       <c r="U110" s="10" t="s">
-        <v>234</v>
+        <v>144</v>
       </c>
       <c r="V110" s="10" t="s">
-        <v>235</v>
+        <v>145</v>
       </c>
       <c r="W110" s="10" t="s">
-        <v>236</v>
+        <v>146</v>
       </c>
       <c r="X110" s="10" t="s">
-        <v>237</v>
+        <v>147</v>
       </c>
       <c r="Y110" s="10" t="s">
-        <v>238</v>
+        <v>148</v>
       </c>
     </row>
     <row r="111" spans="1:25">
@@ -19667,7 +19673,7 @@
     </row>
     <row r="136" spans="1:25">
       <c r="A136" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -19699,76 +19705,76 @@
         <v>75</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>215</v>
+        <v>125</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>216</v>
+        <v>126</v>
       </c>
       <c r="D137" s="10" t="s">
-        <v>217</v>
+        <v>127</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>218</v>
+        <v>128</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>219</v>
+        <v>129</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>221</v>
+        <v>131</v>
       </c>
       <c r="I137" s="10" t="s">
-        <v>222</v>
+        <v>132</v>
       </c>
       <c r="J137" s="10" t="s">
-        <v>223</v>
+        <v>133</v>
       </c>
       <c r="K137" s="10" t="s">
-        <v>224</v>
+        <v>134</v>
       </c>
       <c r="L137" s="10" t="s">
-        <v>225</v>
+        <v>135</v>
       </c>
       <c r="M137" s="10" t="s">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>227</v>
+        <v>137</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>228</v>
+        <v>138</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>229</v>
+        <v>139</v>
       </c>
       <c r="Q137" s="10" t="s">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="R137" s="10" t="s">
-        <v>231</v>
+        <v>141</v>
       </c>
       <c r="S137" s="10" t="s">
-        <v>232</v>
+        <v>142</v>
       </c>
       <c r="T137" s="10" t="s">
-        <v>233</v>
+        <v>143</v>
       </c>
       <c r="U137" s="10" t="s">
-        <v>234</v>
+        <v>144</v>
       </c>
       <c r="V137" s="10" t="s">
-        <v>235</v>
+        <v>145</v>
       </c>
       <c r="W137" s="10" t="s">
-        <v>236</v>
+        <v>146</v>
       </c>
       <c r="X137" s="10" t="s">
-        <v>237</v>
+        <v>147</v>
       </c>
       <c r="Y137" s="10" t="s">
-        <v>238</v>
+        <v>148</v>
       </c>
     </row>
     <row r="138" spans="1:25">
@@ -21165,7 +21171,7 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -22291,7 +22297,7 @@
     </row>
     <row r="55" spans="1:25">
       <c r="A55" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -23417,7 +23423,7 @@
     </row>
     <row r="82" spans="1:25">
       <c r="A82" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -24543,7 +24549,7 @@
     </row>
     <row r="109" spans="1:25">
       <c r="A109" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -25669,7 +25675,7 @@
     </row>
     <row r="136" spans="1:25">
       <c r="A136" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
